--- a/instrumentos/exemplos/DAIR_Avaliacao_Riscos_Titulares_ANPD_v0.3_EXEMPLO-INC-2026-001.xlsx
+++ b/instrumentos/exemplos/DAIR_Avaliacao_Riscos_Titulares_ANPD_v0.3_EXEMPLO-INC-2026-001.xlsx
@@ -38,7 +38,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">ID manual e estável — A02/A03. Padrão AVR-NN. É esta ID (não a linha) que liga o mesmo registro de versão entre as quatro abas deste arquivo.</t>
+          <t xml:space="preserve">ID manual e estável — A02/A03. Padrão AVR-NN. É esta ID (não a linha) que liga o mesmo registro de versão entre as quatro abas deste arquivo. Formatação condicional (A03): sinaliza em vermelho se a MESMA combinação ID+Versão não existir também em Avaliacao_Regulatoria e em Decisao_Comunicacao — reconciliação por existência cruzada, não por posição de linha nem por coincidência entre a ID e o número da versão.</t>
         </r>
       </text>
     </comment>
@@ -50,7 +50,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Deve ser numericamente igual aos dois dígitos finais da ID (ex.: AVR-02 ⇒ 2). Divergência é sinalizada em vermelho.</t>
+          <t xml:space="preserve">Número da versão (1, 2, 3...). Não precisa coincidir com os dígitos da ID — a reconciliação entre abas é feita pela combinação ID+Versão (coluna A, nota ao lado), verificada por fórmula.</t>
         </r>
       </text>
     </comment>
@@ -72,7 +72,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">ID manual e estável — A02/A03. A mesma ID (AVR-NN) deve aparecer em Caracterizacao, nesta aba e em Decisao_Comunicacao para a mesma versão.</t>
+          <t xml:space="preserve">ID manual e estável — A02/A03. A mesma combinação ID+Versão deve existir também em Caracterizacao e em Decisao_Comunicacao para a mesma versão — verificado por fórmula (A03), não por posição de linha.</t>
         </r>
       </text>
     </comment>
@@ -130,7 +130,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">ID manual e estável — A02/A03.</t>
+          <t xml:space="preserve">ID manual e estável — A02/A03. A mesma combinação ID+Versão deve existir também em Caracterizacao e em Avaliacao_Regulatoria — verificado por fórmula (A03).</t>
         </r>
       </text>
     </comment>
@@ -188,7 +188,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">ID manual e estável — A02/A03. Registre aqui a ID DA VERSÃO DE CHEGADA (ex.: ao documentar a mudança de v1 para v2, a ID desta linha é AVR-02, igual à da mesma versão nas demais abas — não AVR-01).</t>
+          <t xml:space="preserve">ID manual e estável — A02/A03. Registre aqui a ID DA VERSÃO DE CHEGADA (ex.: ao documentar a mudança de v1 para v2, a ID desta linha é AVR-02, igual à da mesma versão nas demais abas — não AVR-01). Formatação condicional (A03): sinaliza em vermelho se a combinação ID+Versão desta linha não existir nas três abas anteriores — é esse teste cruzado, e não a posição da linha nem os dígitos da ID, que comprova a reconciliação.</t>
         </r>
       </text>
     </comment>
@@ -262,7 +262,7 @@
     <t xml:space="preserve">Identificadores são manuais e estáveis — chave de reconciliação entre abas (correção A02/A03)</t>
   </si>
   <si>
-    <t xml:space="preserve">Digite a mesma ID 'AVR-NN' na coluna A das quatro abas (Caracterizacao, Avaliacao_Regulatoria, Decisao_Comunicacao e, na linha que registra a chegada a essa versão, Historico) — é essa ID, e não a posição da linha, que relaciona os registros entre as abas. Mantenha o mesmo INC-AAAA-NNN do Instrumento 1. Referencie evidências (EVD-) e decisões (DEC-) registradas no Instrumento 1 sempre que aplicável. A coluna 'Versão' deve conter o mesmo número da ID (ex.: ID AVR-02 ⇒ Versão 2) — uma formatação condicional sinaliza em vermelho qualquer divergência entre as duas.</t>
+    <t xml:space="preserve">Digite a mesma ID 'AVR-NN' E o mesmo número de Versão na coluna A/B das quatro abas (Caracterizacao, Avaliacao_Regulatoria, Decisao_Comunicacao e, na linha que registra a chegada a essa versão, Historico) — é essa combinação ID+Versão, e não a posição da linha nem os dígitos da ID, que relaciona os registros entre as abas. Mantenha o mesmo INC-AAAA-NNN do Instrumento 1. Referencie evidências (EVD-) e decisões (DEC-) registradas no Instrumento 1 sempre que aplicável. Uma formatação condicional em cada aba verifica, por fórmula (COUNTIFS cruzado), se a mesma combinação ID+Versão também existe nas demais abas relacionadas, e sinaliza em vermelho quando não existe — essa é a prova de reconciliação, não uma coincidência entre o número da ID e o número da versão.</t>
   </si>
   <si>
     <t xml:space="preserve">Retenção</t>
@@ -882,96 +882,100 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1239,115 +1243,115 @@
   <dimension ref="A1:B14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="100"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="100"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="7" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="7" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="7" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="7" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="7" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="7" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="7" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="7" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1374,895 +1378,895 @@
   <dimension ref="A1:M53"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="L3" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="M3" s="9" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="11" t="n">
+      <c r="D4" s="12" t="n">
         <v>46314.3923611111</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="J4" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="10" t="s">
+      <c r="K4" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="L4" s="10" t="s">
+      <c r="L4" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="M4" s="10" t="s">
+      <c r="M4" s="11" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D5" s="11" t="n">
+      <c r="D5" s="12" t="n">
         <v>46314.5069444445</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="I5" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="J5" s="10" t="s">
+      <c r="J5" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="K5" s="10" t="s">
+      <c r="K5" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="L5" s="10" t="s">
+      <c r="L5" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M5" s="10" t="s">
+      <c r="M5" s="11" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="10"/>
-      <c r="M8" s="10"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10"/>
-      <c r="M12" s="10"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="9"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="9"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
-      <c r="M14" s="10"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="9"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="9"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10"/>
-      <c r="M17" s="10"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="9"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10"/>
-      <c r="M18" s="10"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="9"/>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10"/>
-      <c r="M19" s="10"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="9"/>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10"/>
-      <c r="M20" s="10"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="9"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="10"/>
-      <c r="M21" s="10"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="9"/>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="10"/>
-      <c r="K22" s="10"/>
-      <c r="L22" s="10"/>
-      <c r="M22" s="10"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="9"/>
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="10"/>
-      <c r="K23" s="10"/>
-      <c r="L23" s="10"/>
-      <c r="M23" s="10"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="9"/>
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="10"/>
-      <c r="K24" s="10"/>
-      <c r="L24" s="10"/>
-      <c r="M24" s="10"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="9"/>
-      <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="10"/>
-      <c r="K25" s="10"/>
-      <c r="L25" s="10"/>
-      <c r="M25" s="10"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="9"/>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="10"/>
-      <c r="K26" s="10"/>
-      <c r="L26" s="10"/>
-      <c r="M26" s="10"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="9"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
-      <c r="I27" s="10"/>
-      <c r="J27" s="10"/>
-      <c r="K27" s="10"/>
-      <c r="L27" s="10"/>
-      <c r="M27" s="10"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="9"/>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
-      <c r="I28" s="10"/>
-      <c r="J28" s="10"/>
-      <c r="K28" s="10"/>
-      <c r="L28" s="10"/>
-      <c r="M28" s="10"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="9"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="10"/>
-      <c r="G29" s="10"/>
-      <c r="H29" s="10"/>
-      <c r="I29" s="10"/>
-      <c r="J29" s="10"/>
-      <c r="K29" s="10"/>
-      <c r="L29" s="10"/>
-      <c r="M29" s="10"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="9"/>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="11"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
-      <c r="I30" s="10"/>
-      <c r="J30" s="10"/>
-      <c r="K30" s="10"/>
-      <c r="L30" s="10"/>
-      <c r="M30" s="10"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="9"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="10"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="10"/>
-      <c r="I31" s="10"/>
-      <c r="J31" s="10"/>
-      <c r="K31" s="10"/>
-      <c r="L31" s="10"/>
-      <c r="M31" s="10"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="9"/>
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="10"/>
-      <c r="I32" s="10"/>
-      <c r="J32" s="10"/>
-      <c r="K32" s="10"/>
-      <c r="L32" s="10"/>
-      <c r="M32" s="10"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="9"/>
-      <c r="B33" s="10"/>
-      <c r="C33" s="10"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10"/>
-      <c r="G33" s="10"/>
-      <c r="H33" s="10"/>
-      <c r="I33" s="10"/>
-      <c r="J33" s="10"/>
-      <c r="K33" s="10"/>
-      <c r="L33" s="10"/>
-      <c r="M33" s="10"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="9"/>
-      <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="10"/>
-      <c r="I34" s="10"/>
-      <c r="J34" s="10"/>
-      <c r="K34" s="10"/>
-      <c r="L34" s="10"/>
-      <c r="M34" s="10"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="9"/>
-      <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="10"/>
-      <c r="F35" s="10"/>
-      <c r="G35" s="10"/>
-      <c r="H35" s="10"/>
-      <c r="I35" s="10"/>
-      <c r="J35" s="10"/>
-      <c r="K35" s="10"/>
-      <c r="L35" s="10"/>
-      <c r="M35" s="10"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="9"/>
-      <c r="B36" s="10"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="10"/>
-      <c r="F36" s="10"/>
-      <c r="G36" s="10"/>
-      <c r="H36" s="10"/>
-      <c r="I36" s="10"/>
-      <c r="J36" s="10"/>
-      <c r="K36" s="10"/>
-      <c r="L36" s="10"/>
-      <c r="M36" s="10"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="9"/>
-      <c r="B37" s="10"/>
-      <c r="C37" s="10"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="10"/>
-      <c r="H37" s="10"/>
-      <c r="I37" s="10"/>
-      <c r="J37" s="10"/>
-      <c r="K37" s="10"/>
-      <c r="L37" s="10"/>
-      <c r="M37" s="10"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="9"/>
-      <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="11"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="10"/>
-      <c r="G38" s="10"/>
-      <c r="H38" s="10"/>
-      <c r="I38" s="10"/>
-      <c r="J38" s="10"/>
-      <c r="K38" s="10"/>
-      <c r="L38" s="10"/>
-      <c r="M38" s="10"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="9"/>
-      <c r="B39" s="10"/>
-      <c r="C39" s="10"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="10"/>
-      <c r="F39" s="10"/>
-      <c r="G39" s="10"/>
-      <c r="H39" s="10"/>
-      <c r="I39" s="10"/>
-      <c r="J39" s="10"/>
-      <c r="K39" s="10"/>
-      <c r="L39" s="10"/>
-      <c r="M39" s="10"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="9"/>
-      <c r="B40" s="10"/>
-      <c r="C40" s="10"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="10"/>
-      <c r="F40" s="10"/>
-      <c r="G40" s="10"/>
-      <c r="H40" s="10"/>
-      <c r="I40" s="10"/>
-      <c r="J40" s="10"/>
-      <c r="K40" s="10"/>
-      <c r="L40" s="10"/>
-      <c r="M40" s="10"/>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="9"/>
-      <c r="B41" s="10"/>
-      <c r="C41" s="10"/>
-      <c r="D41" s="11"/>
-      <c r="E41" s="10"/>
-      <c r="F41" s="10"/>
-      <c r="G41" s="10"/>
-      <c r="H41" s="10"/>
-      <c r="I41" s="10"/>
-      <c r="J41" s="10"/>
-      <c r="K41" s="10"/>
-      <c r="L41" s="10"/>
-      <c r="M41" s="10"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="9"/>
-      <c r="B42" s="10"/>
-      <c r="C42" s="10"/>
-      <c r="D42" s="11"/>
-      <c r="E42" s="10"/>
-      <c r="F42" s="10"/>
-      <c r="G42" s="10"/>
-      <c r="H42" s="10"/>
-      <c r="I42" s="10"/>
-      <c r="J42" s="10"/>
-      <c r="K42" s="10"/>
-      <c r="L42" s="10"/>
-      <c r="M42" s="10"/>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="9"/>
-      <c r="B43" s="10"/>
-      <c r="C43" s="10"/>
-      <c r="D43" s="11"/>
-      <c r="E43" s="10"/>
-      <c r="F43" s="10"/>
-      <c r="G43" s="10"/>
-      <c r="H43" s="10"/>
-      <c r="I43" s="10"/>
-      <c r="J43" s="10"/>
-      <c r="K43" s="10"/>
-      <c r="L43" s="10"/>
-      <c r="M43" s="10"/>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="9"/>
-      <c r="B44" s="10"/>
-      <c r="C44" s="10"/>
-      <c r="D44" s="11"/>
-      <c r="E44" s="10"/>
-      <c r="F44" s="10"/>
-      <c r="G44" s="10"/>
-      <c r="H44" s="10"/>
-      <c r="I44" s="10"/>
-      <c r="J44" s="10"/>
-      <c r="K44" s="10"/>
-      <c r="L44" s="10"/>
-      <c r="M44" s="10"/>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="9"/>
-      <c r="B45" s="10"/>
-      <c r="C45" s="10"/>
-      <c r="D45" s="11"/>
-      <c r="E45" s="10"/>
-      <c r="F45" s="10"/>
-      <c r="G45" s="10"/>
-      <c r="H45" s="10"/>
-      <c r="I45" s="10"/>
-      <c r="J45" s="10"/>
-      <c r="K45" s="10"/>
-      <c r="L45" s="10"/>
-      <c r="M45" s="10"/>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="9"/>
-      <c r="B46" s="10"/>
-      <c r="C46" s="10"/>
-      <c r="D46" s="11"/>
-      <c r="E46" s="10"/>
-      <c r="F46" s="10"/>
-      <c r="G46" s="10"/>
-      <c r="H46" s="10"/>
-      <c r="I46" s="10"/>
-      <c r="J46" s="10"/>
-      <c r="K46" s="10"/>
-      <c r="L46" s="10"/>
-      <c r="M46" s="10"/>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="9"/>
-      <c r="B47" s="10"/>
-      <c r="C47" s="10"/>
-      <c r="D47" s="11"/>
-      <c r="E47" s="10"/>
-      <c r="F47" s="10"/>
-      <c r="G47" s="10"/>
-      <c r="H47" s="10"/>
-      <c r="I47" s="10"/>
-      <c r="J47" s="10"/>
-      <c r="K47" s="10"/>
-      <c r="L47" s="10"/>
-      <c r="M47" s="10"/>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="9"/>
-      <c r="B48" s="10"/>
-      <c r="C48" s="10"/>
-      <c r="D48" s="11"/>
-      <c r="E48" s="10"/>
-      <c r="F48" s="10"/>
-      <c r="G48" s="10"/>
-      <c r="H48" s="10"/>
-      <c r="I48" s="10"/>
-      <c r="J48" s="10"/>
-      <c r="K48" s="10"/>
-      <c r="L48" s="10"/>
-      <c r="M48" s="10"/>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="9"/>
-      <c r="B49" s="10"/>
-      <c r="C49" s="10"/>
-      <c r="D49" s="11"/>
-      <c r="E49" s="10"/>
-      <c r="F49" s="10"/>
-      <c r="G49" s="10"/>
-      <c r="H49" s="10"/>
-      <c r="I49" s="10"/>
-      <c r="J49" s="10"/>
-      <c r="K49" s="10"/>
-      <c r="L49" s="10"/>
-      <c r="M49" s="10"/>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="9"/>
-      <c r="B50" s="10"/>
-      <c r="C50" s="10"/>
-      <c r="D50" s="11"/>
-      <c r="E50" s="10"/>
-      <c r="F50" s="10"/>
-      <c r="G50" s="10"/>
-      <c r="H50" s="10"/>
-      <c r="I50" s="10"/>
-      <c r="J50" s="10"/>
-      <c r="K50" s="10"/>
-      <c r="L50" s="10"/>
-      <c r="M50" s="10"/>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="9"/>
-      <c r="B51" s="10"/>
-      <c r="C51" s="10"/>
-      <c r="D51" s="11"/>
-      <c r="E51" s="10"/>
-      <c r="F51" s="10"/>
-      <c r="G51" s="10"/>
-      <c r="H51" s="10"/>
-      <c r="I51" s="10"/>
-      <c r="J51" s="10"/>
-      <c r="K51" s="10"/>
-      <c r="L51" s="10"/>
-      <c r="M51" s="10"/>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="9"/>
-      <c r="B52" s="10"/>
-      <c r="C52" s="10"/>
-      <c r="D52" s="11"/>
-      <c r="E52" s="10"/>
-      <c r="F52" s="10"/>
-      <c r="G52" s="10"/>
-      <c r="H52" s="10"/>
-      <c r="I52" s="10"/>
-      <c r="J52" s="10"/>
-      <c r="K52" s="10"/>
-      <c r="L52" s="10"/>
-      <c r="M52" s="10"/>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="9"/>
-      <c r="B53" s="10"/>
-      <c r="C53" s="10"/>
-      <c r="D53" s="11"/>
-      <c r="E53" s="10"/>
-      <c r="F53" s="10"/>
-      <c r="G53" s="10"/>
-      <c r="H53" s="10"/>
-      <c r="I53" s="10"/>
-      <c r="J53" s="10"/>
-      <c r="K53" s="10"/>
-      <c r="L53" s="10"/>
-      <c r="M53" s="10"/>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="10"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="10"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="10"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="10"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="10"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="10"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="10"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="10"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="10"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="10"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="10"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="11"/>
+      <c r="M16" s="11"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="10"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="10"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+      <c r="M18" s="11"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="10"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="10"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="11"/>
+      <c r="M20" s="11"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="10"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="10"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="11"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="10"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="11"/>
+      <c r="M23" s="11"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="10"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="11"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="11"/>
+      <c r="M24" s="11"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="10"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="11"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="10"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="11"/>
+      <c r="K26" s="11"/>
+      <c r="L26" s="11"/>
+      <c r="M26" s="11"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="10"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
+      <c r="M27" s="11"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="10"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
+      <c r="J28" s="11"/>
+      <c r="K28" s="11"/>
+      <c r="L28" s="11"/>
+      <c r="M28" s="11"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="10"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11"/>
+      <c r="L29" s="11"/>
+      <c r="M29" s="11"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="10"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
+      <c r="J30" s="11"/>
+      <c r="K30" s="11"/>
+      <c r="L30" s="11"/>
+      <c r="M30" s="11"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="10"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="11"/>
+      <c r="L31" s="11"/>
+      <c r="M31" s="11"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="10"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
+      <c r="M32" s="11"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="10"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="11"/>
+      <c r="K33" s="11"/>
+      <c r="L33" s="11"/>
+      <c r="M33" s="11"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="10"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
+      <c r="J34" s="11"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
+      <c r="M34" s="11"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="10"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="11"/>
+      <c r="J35" s="11"/>
+      <c r="K35" s="11"/>
+      <c r="L35" s="11"/>
+      <c r="M35" s="11"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="10"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="11"/>
+      <c r="J36" s="11"/>
+      <c r="K36" s="11"/>
+      <c r="L36" s="11"/>
+      <c r="M36" s="11"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="10"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="11"/>
+      <c r="J37" s="11"/>
+      <c r="K37" s="11"/>
+      <c r="L37" s="11"/>
+      <c r="M37" s="11"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="10"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="11"/>
+      <c r="J38" s="11"/>
+      <c r="K38" s="11"/>
+      <c r="L38" s="11"/>
+      <c r="M38" s="11"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="10"/>
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="11"/>
+      <c r="I39" s="11"/>
+      <c r="J39" s="11"/>
+      <c r="K39" s="11"/>
+      <c r="L39" s="11"/>
+      <c r="M39" s="11"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="10"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="11"/>
+      <c r="I40" s="11"/>
+      <c r="J40" s="11"/>
+      <c r="K40" s="11"/>
+      <c r="L40" s="11"/>
+      <c r="M40" s="11"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="10"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="11"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="11"/>
+      <c r="I41" s="11"/>
+      <c r="J41" s="11"/>
+      <c r="K41" s="11"/>
+      <c r="L41" s="11"/>
+      <c r="M41" s="11"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="10"/>
+      <c r="B42" s="11"/>
+      <c r="C42" s="11"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="11"/>
+      <c r="F42" s="11"/>
+      <c r="G42" s="11"/>
+      <c r="H42" s="11"/>
+      <c r="I42" s="11"/>
+      <c r="J42" s="11"/>
+      <c r="K42" s="11"/>
+      <c r="L42" s="11"/>
+      <c r="M42" s="11"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="10"/>
+      <c r="B43" s="11"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="11"/>
+      <c r="I43" s="11"/>
+      <c r="J43" s="11"/>
+      <c r="K43" s="11"/>
+      <c r="L43" s="11"/>
+      <c r="M43" s="11"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="10"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="12"/>
+      <c r="E44" s="11"/>
+      <c r="F44" s="11"/>
+      <c r="G44" s="11"/>
+      <c r="H44" s="11"/>
+      <c r="I44" s="11"/>
+      <c r="J44" s="11"/>
+      <c r="K44" s="11"/>
+      <c r="L44" s="11"/>
+      <c r="M44" s="11"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="10"/>
+      <c r="B45" s="11"/>
+      <c r="C45" s="11"/>
+      <c r="D45" s="12"/>
+      <c r="E45" s="11"/>
+      <c r="F45" s="11"/>
+      <c r="G45" s="11"/>
+      <c r="H45" s="11"/>
+      <c r="I45" s="11"/>
+      <c r="J45" s="11"/>
+      <c r="K45" s="11"/>
+      <c r="L45" s="11"/>
+      <c r="M45" s="11"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="10"/>
+      <c r="B46" s="11"/>
+      <c r="C46" s="11"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="11"/>
+      <c r="F46" s="11"/>
+      <c r="G46" s="11"/>
+      <c r="H46" s="11"/>
+      <c r="I46" s="11"/>
+      <c r="J46" s="11"/>
+      <c r="K46" s="11"/>
+      <c r="L46" s="11"/>
+      <c r="M46" s="11"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="10"/>
+      <c r="B47" s="11"/>
+      <c r="C47" s="11"/>
+      <c r="D47" s="12"/>
+      <c r="E47" s="11"/>
+      <c r="F47" s="11"/>
+      <c r="G47" s="11"/>
+      <c r="H47" s="11"/>
+      <c r="I47" s="11"/>
+      <c r="J47" s="11"/>
+      <c r="K47" s="11"/>
+      <c r="L47" s="11"/>
+      <c r="M47" s="11"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="10"/>
+      <c r="B48" s="11"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="12"/>
+      <c r="E48" s="11"/>
+      <c r="F48" s="11"/>
+      <c r="G48" s="11"/>
+      <c r="H48" s="11"/>
+      <c r="I48" s="11"/>
+      <c r="J48" s="11"/>
+      <c r="K48" s="11"/>
+      <c r="L48" s="11"/>
+      <c r="M48" s="11"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="10"/>
+      <c r="B49" s="11"/>
+      <c r="C49" s="11"/>
+      <c r="D49" s="12"/>
+      <c r="E49" s="11"/>
+      <c r="F49" s="11"/>
+      <c r="G49" s="11"/>
+      <c r="H49" s="11"/>
+      <c r="I49" s="11"/>
+      <c r="J49" s="11"/>
+      <c r="K49" s="11"/>
+      <c r="L49" s="11"/>
+      <c r="M49" s="11"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="10"/>
+      <c r="B50" s="11"/>
+      <c r="C50" s="11"/>
+      <c r="D50" s="12"/>
+      <c r="E50" s="11"/>
+      <c r="F50" s="11"/>
+      <c r="G50" s="11"/>
+      <c r="H50" s="11"/>
+      <c r="I50" s="11"/>
+      <c r="J50" s="11"/>
+      <c r="K50" s="11"/>
+      <c r="L50" s="11"/>
+      <c r="M50" s="11"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="10"/>
+      <c r="B51" s="11"/>
+      <c r="C51" s="11"/>
+      <c r="D51" s="12"/>
+      <c r="E51" s="11"/>
+      <c r="F51" s="11"/>
+      <c r="G51" s="11"/>
+      <c r="H51" s="11"/>
+      <c r="I51" s="11"/>
+      <c r="J51" s="11"/>
+      <c r="K51" s="11"/>
+      <c r="L51" s="11"/>
+      <c r="M51" s="11"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="10"/>
+      <c r="B52" s="11"/>
+      <c r="C52" s="11"/>
+      <c r="D52" s="12"/>
+      <c r="E52" s="11"/>
+      <c r="F52" s="11"/>
+      <c r="G52" s="11"/>
+      <c r="H52" s="11"/>
+      <c r="I52" s="11"/>
+      <c r="J52" s="11"/>
+      <c r="K52" s="11"/>
+      <c r="L52" s="11"/>
+      <c r="M52" s="11"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="10"/>
+      <c r="B53" s="11"/>
+      <c r="C53" s="11"/>
+      <c r="D53" s="12"/>
+      <c r="E53" s="11"/>
+      <c r="F53" s="11"/>
+      <c r="G53" s="11"/>
+      <c r="H53" s="11"/>
+      <c r="I53" s="11"/>
+      <c r="J53" s="11"/>
+      <c r="K53" s="11"/>
+      <c r="L53" s="11"/>
+      <c r="M53" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2273,10 +2277,8 @@
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND(A4&lt;&gt;"",COUNTIF($A$4:$A$53,A4)&gt;1)</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B4:B53">
     <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>AND($A4&lt;&gt;"",ISNUMBER(VALUE(RIGHT($A4,2))),B4&lt;&gt;VALUE(RIGHT($A4,2)))</formula>
+      <formula>AND($A4&lt;&gt;"",OR(COUNTIFS(Avaliacao_Regulatoria!$A$4:$A$53,$A4,Avaliacao_Regulatoria!$B$4:$B$53,$B4)=0,COUNTIFS(Decisao_Comunicacao!$A$4:$A$53,$A4,Decisao_Comunicacao!$B$4:$B$53,$B4)=0))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="51">
@@ -2504,1401 +2506,1401 @@
   <dimension ref="A1:S53"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="18" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="18" style="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="8"/>
+      <c r="O2" s="8"/>
+      <c r="P2" s="8"/>
+      <c r="Q2" s="8"/>
+      <c r="R2" s="8"/>
+      <c r="S2" s="8"/>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="L3" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="M3" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="N3" s="8" t="s">
+      <c r="N3" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="O3" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="P3" s="8" t="s">
+      <c r="P3" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="Q3" s="8" t="s">
+      <c r="Q3" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="R3" s="8" t="s">
+      <c r="R3" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="S3" s="8" t="s">
+      <c r="S3" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="J4" s="10" t="str">
+      <c r="J4" s="11" t="str">
         <f aca="false">IF(COUNTIF(D4:I4,"Sim")&gt;0,"Sim",IF(COUNTIF(D4:I4,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Em apuração</v>
       </c>
-      <c r="K4" s="10" t="s">
+      <c r="K4" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="L4" s="10" t="s">
+      <c r="L4" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="M4" s="10" t="s">
+      <c r="M4" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="N4" s="10" t="s">
+      <c r="N4" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="O4" s="10" t="s">
+      <c r="O4" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="P4" s="10" t="s">
+      <c r="P4" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="Q4" s="10" t="s">
+      <c r="Q4" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="R4" s="10" t="s">
+      <c r="R4" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="S4" s="10" t="s">
+      <c r="S4" s="11" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="I5" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="J5" s="10" t="str">
+      <c r="J5" s="11" t="str">
         <f aca="false">IF(COUNTIF(D5:I5,"Sim")&gt;0,"Sim",IF(COUNTIF(D5:I5,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Sim</v>
       </c>
-      <c r="K5" s="10" t="s">
+      <c r="K5" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="L5" s="10" t="s">
+      <c r="L5" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="M5" s="10" t="s">
+      <c r="M5" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="N5" s="10" t="s">
+      <c r="N5" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="O5" s="10" t="s">
+      <c r="O5" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="P5" s="10" t="s">
+      <c r="P5" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="Q5" s="10" t="s">
+      <c r="Q5" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="R5" s="10" t="s">
+      <c r="R5" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="S5" s="10" t="s">
+      <c r="S5" s="11" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10" t="str">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="10"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11" t="str">
         <f aca="false">IF(COUNTIF(D6:I6,"Sim")&gt;0,"Sim",IF(COUNTIF(D6:I6,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
-      <c r="N6" s="10"/>
-      <c r="O6" s="10"/>
-      <c r="P6" s="10"/>
-      <c r="Q6" s="10"/>
-      <c r="R6" s="10"/>
-      <c r="S6" s="10"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10" t="str">
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="11"/>
+      <c r="O6" s="11"/>
+      <c r="P6" s="11"/>
+      <c r="Q6" s="11"/>
+      <c r="R6" s="11"/>
+      <c r="S6" s="11"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="10"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11" t="str">
         <f aca="false">IF(COUNTIF(D7:I7,"Sim")&gt;0,"Sim",IF(COUNTIF(D7:I7,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
-      <c r="O7" s="10"/>
-      <c r="P7" s="10"/>
-      <c r="Q7" s="10"/>
-      <c r="R7" s="10"/>
-      <c r="S7" s="10"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10" t="str">
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="11"/>
+      <c r="P7" s="11"/>
+      <c r="Q7" s="11"/>
+      <c r="R7" s="11"/>
+      <c r="S7" s="11"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="10"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11" t="str">
         <f aca="false">IF(COUNTIF(D8:I8,"Sim")&gt;0,"Sim",IF(COUNTIF(D8:I8,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K8" s="10"/>
-      <c r="L8" s="10"/>
-      <c r="M8" s="10"/>
-      <c r="N8" s="10"/>
-      <c r="O8" s="10"/>
-      <c r="P8" s="10"/>
-      <c r="Q8" s="10"/>
-      <c r="R8" s="10"/>
-      <c r="S8" s="10"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10" t="str">
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="11"/>
+      <c r="O8" s="11"/>
+      <c r="P8" s="11"/>
+      <c r="Q8" s="11"/>
+      <c r="R8" s="11"/>
+      <c r="S8" s="11"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="10"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11" t="str">
         <f aca="false">IF(COUNTIF(D9:I9,"Sim")&gt;0,"Sim",IF(COUNTIF(D9:I9,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
-      <c r="O9" s="10"/>
-      <c r="P9" s="10"/>
-      <c r="Q9" s="10"/>
-      <c r="R9" s="10"/>
-      <c r="S9" s="10"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10" t="str">
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="11"/>
+      <c r="O9" s="11"/>
+      <c r="P9" s="11"/>
+      <c r="Q9" s="11"/>
+      <c r="R9" s="11"/>
+      <c r="S9" s="11"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="10"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11" t="str">
         <f aca="false">IF(COUNTIF(D10:I10,"Sim")&gt;0,"Sim",IF(COUNTIF(D10:I10,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
-      <c r="N10" s="10"/>
-      <c r="O10" s="10"/>
-      <c r="P10" s="10"/>
-      <c r="Q10" s="10"/>
-      <c r="R10" s="10"/>
-      <c r="S10" s="10"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10" t="str">
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="11"/>
+      <c r="O10" s="11"/>
+      <c r="P10" s="11"/>
+      <c r="Q10" s="11"/>
+      <c r="R10" s="11"/>
+      <c r="S10" s="11"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="10"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11" t="str">
         <f aca="false">IF(COUNTIF(D11:I11,"Sim")&gt;0,"Sim",IF(COUNTIF(D11:I11,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
-      <c r="N11" s="10"/>
-      <c r="O11" s="10"/>
-      <c r="P11" s="10"/>
-      <c r="Q11" s="10"/>
-      <c r="R11" s="10"/>
-      <c r="S11" s="10"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10" t="str">
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="11"/>
+      <c r="P11" s="11"/>
+      <c r="Q11" s="11"/>
+      <c r="R11" s="11"/>
+      <c r="S11" s="11"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="10"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11" t="str">
         <f aca="false">IF(COUNTIF(D12:I12,"Sim")&gt;0,"Sim",IF(COUNTIF(D12:I12,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10"/>
-      <c r="M12" s="10"/>
-      <c r="N12" s="10"/>
-      <c r="O12" s="10"/>
-      <c r="P12" s="10"/>
-      <c r="Q12" s="10"/>
-      <c r="R12" s="10"/>
-      <c r="S12" s="10"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="9"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10" t="str">
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="11"/>
+      <c r="O12" s="11"/>
+      <c r="P12" s="11"/>
+      <c r="Q12" s="11"/>
+      <c r="R12" s="11"/>
+      <c r="S12" s="11"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="10"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11" t="str">
         <f aca="false">IF(COUNTIF(D13:I13,"Sim")&gt;0,"Sim",IF(COUNTIF(D13:I13,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
-      <c r="N13" s="10"/>
-      <c r="O13" s="10"/>
-      <c r="P13" s="10"/>
-      <c r="Q13" s="10"/>
-      <c r="R13" s="10"/>
-      <c r="S13" s="10"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="9"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10" t="str">
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="11"/>
+      <c r="O13" s="11"/>
+      <c r="P13" s="11"/>
+      <c r="Q13" s="11"/>
+      <c r="R13" s="11"/>
+      <c r="S13" s="11"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="10"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11" t="str">
         <f aca="false">IF(COUNTIF(D14:I14,"Sim")&gt;0,"Sim",IF(COUNTIF(D14:I14,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
-      <c r="M14" s="10"/>
-      <c r="N14" s="10"/>
-      <c r="O14" s="10"/>
-      <c r="P14" s="10"/>
-      <c r="Q14" s="10"/>
-      <c r="R14" s="10"/>
-      <c r="S14" s="10"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="9"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10" t="str">
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="11"/>
+      <c r="O14" s="11"/>
+      <c r="P14" s="11"/>
+      <c r="Q14" s="11"/>
+      <c r="R14" s="11"/>
+      <c r="S14" s="11"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="10"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11" t="str">
         <f aca="false">IF(COUNTIF(D15:I15,"Sim")&gt;0,"Sim",IF(COUNTIF(D15:I15,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
-      <c r="N15" s="10"/>
-      <c r="O15" s="10"/>
-      <c r="P15" s="10"/>
-      <c r="Q15" s="10"/>
-      <c r="R15" s="10"/>
-      <c r="S15" s="10"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="10" t="str">
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="11"/>
+      <c r="P15" s="11"/>
+      <c r="Q15" s="11"/>
+      <c r="R15" s="11"/>
+      <c r="S15" s="11"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="10"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11" t="str">
         <f aca="false">IF(COUNTIF(D16:I16,"Sim")&gt;0,"Sim",IF(COUNTIF(D16:I16,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
-      <c r="N16" s="10"/>
-      <c r="O16" s="10"/>
-      <c r="P16" s="10"/>
-      <c r="Q16" s="10"/>
-      <c r="R16" s="10"/>
-      <c r="S16" s="10"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="9"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10" t="str">
+      <c r="K16" s="11"/>
+      <c r="L16" s="11"/>
+      <c r="M16" s="11"/>
+      <c r="N16" s="11"/>
+      <c r="O16" s="11"/>
+      <c r="P16" s="11"/>
+      <c r="Q16" s="11"/>
+      <c r="R16" s="11"/>
+      <c r="S16" s="11"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="10"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11" t="str">
         <f aca="false">IF(COUNTIF(D17:I17,"Sim")&gt;0,"Sim",IF(COUNTIF(D17:I17,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10"/>
-      <c r="M17" s="10"/>
-      <c r="N17" s="10"/>
-      <c r="O17" s="10"/>
-      <c r="P17" s="10"/>
-      <c r="Q17" s="10"/>
-      <c r="R17" s="10"/>
-      <c r="S17" s="10"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="9"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10" t="str">
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="11"/>
+      <c r="O17" s="11"/>
+      <c r="P17" s="11"/>
+      <c r="Q17" s="11"/>
+      <c r="R17" s="11"/>
+      <c r="S17" s="11"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="10"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11" t="str">
         <f aca="false">IF(COUNTIF(D18:I18,"Sim")&gt;0,"Sim",IF(COUNTIF(D18:I18,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10"/>
-      <c r="M18" s="10"/>
-      <c r="N18" s="10"/>
-      <c r="O18" s="10"/>
-      <c r="P18" s="10"/>
-      <c r="Q18" s="10"/>
-      <c r="R18" s="10"/>
-      <c r="S18" s="10"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="9"/>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10" t="str">
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+      <c r="M18" s="11"/>
+      <c r="N18" s="11"/>
+      <c r="O18" s="11"/>
+      <c r="P18" s="11"/>
+      <c r="Q18" s="11"/>
+      <c r="R18" s="11"/>
+      <c r="S18" s="11"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="10"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11" t="str">
         <f aca="false">IF(COUNTIF(D19:I19,"Sim")&gt;0,"Sim",IF(COUNTIF(D19:I19,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10"/>
-      <c r="M19" s="10"/>
-      <c r="N19" s="10"/>
-      <c r="O19" s="10"/>
-      <c r="P19" s="10"/>
-      <c r="Q19" s="10"/>
-      <c r="R19" s="10"/>
-      <c r="S19" s="10"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="9"/>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10" t="str">
+      <c r="K19" s="11"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11"/>
+      <c r="O19" s="11"/>
+      <c r="P19" s="11"/>
+      <c r="Q19" s="11"/>
+      <c r="R19" s="11"/>
+      <c r="S19" s="11"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="10"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11" t="str">
         <f aca="false">IF(COUNTIF(D20:I20,"Sim")&gt;0,"Sim",IF(COUNTIF(D20:I20,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10"/>
-      <c r="M20" s="10"/>
-      <c r="N20" s="10"/>
-      <c r="O20" s="10"/>
-      <c r="P20" s="10"/>
-      <c r="Q20" s="10"/>
-      <c r="R20" s="10"/>
-      <c r="S20" s="10"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="9"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10" t="str">
+      <c r="K20" s="11"/>
+      <c r="L20" s="11"/>
+      <c r="M20" s="11"/>
+      <c r="N20" s="11"/>
+      <c r="O20" s="11"/>
+      <c r="P20" s="11"/>
+      <c r="Q20" s="11"/>
+      <c r="R20" s="11"/>
+      <c r="S20" s="11"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="10"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11" t="str">
         <f aca="false">IF(COUNTIF(D21:I21,"Sim")&gt;0,"Sim",IF(COUNTIF(D21:I21,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K21" s="10"/>
-      <c r="L21" s="10"/>
-      <c r="M21" s="10"/>
-      <c r="N21" s="10"/>
-      <c r="O21" s="10"/>
-      <c r="P21" s="10"/>
-      <c r="Q21" s="10"/>
-      <c r="R21" s="10"/>
-      <c r="S21" s="10"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="9"/>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="10" t="str">
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="11"/>
+      <c r="O21" s="11"/>
+      <c r="P21" s="11"/>
+      <c r="Q21" s="11"/>
+      <c r="R21" s="11"/>
+      <c r="S21" s="11"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="10"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11" t="str">
         <f aca="false">IF(COUNTIF(D22:I22,"Sim")&gt;0,"Sim",IF(COUNTIF(D22:I22,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K22" s="10"/>
-      <c r="L22" s="10"/>
-      <c r="M22" s="10"/>
-      <c r="N22" s="10"/>
-      <c r="O22" s="10"/>
-      <c r="P22" s="10"/>
-      <c r="Q22" s="10"/>
-      <c r="R22" s="10"/>
-      <c r="S22" s="10"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="9"/>
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="10" t="str">
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="11"/>
+      <c r="N22" s="11"/>
+      <c r="O22" s="11"/>
+      <c r="P22" s="11"/>
+      <c r="Q22" s="11"/>
+      <c r="R22" s="11"/>
+      <c r="S22" s="11"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="10"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11" t="str">
         <f aca="false">IF(COUNTIF(D23:I23,"Sim")&gt;0,"Sim",IF(COUNTIF(D23:I23,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K23" s="10"/>
-      <c r="L23" s="10"/>
-      <c r="M23" s="10"/>
-      <c r="N23" s="10"/>
-      <c r="O23" s="10"/>
-      <c r="P23" s="10"/>
-      <c r="Q23" s="10"/>
-      <c r="R23" s="10"/>
-      <c r="S23" s="10"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="9"/>
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="10" t="str">
+      <c r="K23" s="11"/>
+      <c r="L23" s="11"/>
+      <c r="M23" s="11"/>
+      <c r="N23" s="11"/>
+      <c r="O23" s="11"/>
+      <c r="P23" s="11"/>
+      <c r="Q23" s="11"/>
+      <c r="R23" s="11"/>
+      <c r="S23" s="11"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="10"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="11" t="str">
         <f aca="false">IF(COUNTIF(D24:I24,"Sim")&gt;0,"Sim",IF(COUNTIF(D24:I24,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K24" s="10"/>
-      <c r="L24" s="10"/>
-      <c r="M24" s="10"/>
-      <c r="N24" s="10"/>
-      <c r="O24" s="10"/>
-      <c r="P24" s="10"/>
-      <c r="Q24" s="10"/>
-      <c r="R24" s="10"/>
-      <c r="S24" s="10"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="9"/>
-      <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="10" t="str">
+      <c r="K24" s="11"/>
+      <c r="L24" s="11"/>
+      <c r="M24" s="11"/>
+      <c r="N24" s="11"/>
+      <c r="O24" s="11"/>
+      <c r="P24" s="11"/>
+      <c r="Q24" s="11"/>
+      <c r="R24" s="11"/>
+      <c r="S24" s="11"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="10"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11" t="str">
         <f aca="false">IF(COUNTIF(D25:I25,"Sim")&gt;0,"Sim",IF(COUNTIF(D25:I25,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K25" s="10"/>
-      <c r="L25" s="10"/>
-      <c r="M25" s="10"/>
-      <c r="N25" s="10"/>
-      <c r="O25" s="10"/>
-      <c r="P25" s="10"/>
-      <c r="Q25" s="10"/>
-      <c r="R25" s="10"/>
-      <c r="S25" s="10"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="9"/>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="10" t="str">
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="11"/>
+      <c r="N25" s="11"/>
+      <c r="O25" s="11"/>
+      <c r="P25" s="11"/>
+      <c r="Q25" s="11"/>
+      <c r="R25" s="11"/>
+      <c r="S25" s="11"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="10"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="11" t="str">
         <f aca="false">IF(COUNTIF(D26:I26,"Sim")&gt;0,"Sim",IF(COUNTIF(D26:I26,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K26" s="10"/>
-      <c r="L26" s="10"/>
-      <c r="M26" s="10"/>
-      <c r="N26" s="10"/>
-      <c r="O26" s="10"/>
-      <c r="P26" s="10"/>
-      <c r="Q26" s="10"/>
-      <c r="R26" s="10"/>
-      <c r="S26" s="10"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="9"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
-      <c r="I27" s="10"/>
-      <c r="J27" s="10" t="str">
+      <c r="K26" s="11"/>
+      <c r="L26" s="11"/>
+      <c r="M26" s="11"/>
+      <c r="N26" s="11"/>
+      <c r="O26" s="11"/>
+      <c r="P26" s="11"/>
+      <c r="Q26" s="11"/>
+      <c r="R26" s="11"/>
+      <c r="S26" s="11"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="10"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="11" t="str">
         <f aca="false">IF(COUNTIF(D27:I27,"Sim")&gt;0,"Sim",IF(COUNTIF(D27:I27,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K27" s="10"/>
-      <c r="L27" s="10"/>
-      <c r="M27" s="10"/>
-      <c r="N27" s="10"/>
-      <c r="O27" s="10"/>
-      <c r="P27" s="10"/>
-      <c r="Q27" s="10"/>
-      <c r="R27" s="10"/>
-      <c r="S27" s="10"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="9"/>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
-      <c r="I28" s="10"/>
-      <c r="J28" s="10" t="str">
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
+      <c r="M27" s="11"/>
+      <c r="N27" s="11"/>
+      <c r="O27" s="11"/>
+      <c r="P27" s="11"/>
+      <c r="Q27" s="11"/>
+      <c r="R27" s="11"/>
+      <c r="S27" s="11"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="10"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
+      <c r="J28" s="11" t="str">
         <f aca="false">IF(COUNTIF(D28:I28,"Sim")&gt;0,"Sim",IF(COUNTIF(D28:I28,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K28" s="10"/>
-      <c r="L28" s="10"/>
-      <c r="M28" s="10"/>
-      <c r="N28" s="10"/>
-      <c r="O28" s="10"/>
-      <c r="P28" s="10"/>
-      <c r="Q28" s="10"/>
-      <c r="R28" s="10"/>
-      <c r="S28" s="10"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="9"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="10"/>
-      <c r="G29" s="10"/>
-      <c r="H29" s="10"/>
-      <c r="I29" s="10"/>
-      <c r="J29" s="10" t="str">
+      <c r="K28" s="11"/>
+      <c r="L28" s="11"/>
+      <c r="M28" s="11"/>
+      <c r="N28" s="11"/>
+      <c r="O28" s="11"/>
+      <c r="P28" s="11"/>
+      <c r="Q28" s="11"/>
+      <c r="R28" s="11"/>
+      <c r="S28" s="11"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="10"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11" t="str">
         <f aca="false">IF(COUNTIF(D29:I29,"Sim")&gt;0,"Sim",IF(COUNTIF(D29:I29,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K29" s="10"/>
-      <c r="L29" s="10"/>
-      <c r="M29" s="10"/>
-      <c r="N29" s="10"/>
-      <c r="O29" s="10"/>
-      <c r="P29" s="10"/>
-      <c r="Q29" s="10"/>
-      <c r="R29" s="10"/>
-      <c r="S29" s="10"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="9"/>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
-      <c r="I30" s="10"/>
-      <c r="J30" s="10" t="str">
+      <c r="K29" s="11"/>
+      <c r="L29" s="11"/>
+      <c r="M29" s="11"/>
+      <c r="N29" s="11"/>
+      <c r="O29" s="11"/>
+      <c r="P29" s="11"/>
+      <c r="Q29" s="11"/>
+      <c r="R29" s="11"/>
+      <c r="S29" s="11"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="10"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
+      <c r="J30" s="11" t="str">
         <f aca="false">IF(COUNTIF(D30:I30,"Sim")&gt;0,"Sim",IF(COUNTIF(D30:I30,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K30" s="10"/>
-      <c r="L30" s="10"/>
-      <c r="M30" s="10"/>
-      <c r="N30" s="10"/>
-      <c r="O30" s="10"/>
-      <c r="P30" s="10"/>
-      <c r="Q30" s="10"/>
-      <c r="R30" s="10"/>
-      <c r="S30" s="10"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="9"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="10"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="10"/>
-      <c r="I31" s="10"/>
-      <c r="J31" s="10" t="str">
+      <c r="K30" s="11"/>
+      <c r="L30" s="11"/>
+      <c r="M30" s="11"/>
+      <c r="N30" s="11"/>
+      <c r="O30" s="11"/>
+      <c r="P30" s="11"/>
+      <c r="Q30" s="11"/>
+      <c r="R30" s="11"/>
+      <c r="S30" s="11"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="10"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="11" t="str">
         <f aca="false">IF(COUNTIF(D31:I31,"Sim")&gt;0,"Sim",IF(COUNTIF(D31:I31,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K31" s="10"/>
-      <c r="L31" s="10"/>
-      <c r="M31" s="10"/>
-      <c r="N31" s="10"/>
-      <c r="O31" s="10"/>
-      <c r="P31" s="10"/>
-      <c r="Q31" s="10"/>
-      <c r="R31" s="10"/>
-      <c r="S31" s="10"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="9"/>
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="10"/>
-      <c r="I32" s="10"/>
-      <c r="J32" s="10" t="str">
+      <c r="K31" s="11"/>
+      <c r="L31" s="11"/>
+      <c r="M31" s="11"/>
+      <c r="N31" s="11"/>
+      <c r="O31" s="11"/>
+      <c r="P31" s="11"/>
+      <c r="Q31" s="11"/>
+      <c r="R31" s="11"/>
+      <c r="S31" s="11"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="10"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="11" t="str">
         <f aca="false">IF(COUNTIF(D32:I32,"Sim")&gt;0,"Sim",IF(COUNTIF(D32:I32,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K32" s="10"/>
-      <c r="L32" s="10"/>
-      <c r="M32" s="10"/>
-      <c r="N32" s="10"/>
-      <c r="O32" s="10"/>
-      <c r="P32" s="10"/>
-      <c r="Q32" s="10"/>
-      <c r="R32" s="10"/>
-      <c r="S32" s="10"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="9"/>
-      <c r="B33" s="10"/>
-      <c r="C33" s="10"/>
-      <c r="D33" s="10"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10"/>
-      <c r="G33" s="10"/>
-      <c r="H33" s="10"/>
-      <c r="I33" s="10"/>
-      <c r="J33" s="10" t="str">
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
+      <c r="M32" s="11"/>
+      <c r="N32" s="11"/>
+      <c r="O32" s="11"/>
+      <c r="P32" s="11"/>
+      <c r="Q32" s="11"/>
+      <c r="R32" s="11"/>
+      <c r="S32" s="11"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="10"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="11" t="str">
         <f aca="false">IF(COUNTIF(D33:I33,"Sim")&gt;0,"Sim",IF(COUNTIF(D33:I33,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K33" s="10"/>
-      <c r="L33" s="10"/>
-      <c r="M33" s="10"/>
-      <c r="N33" s="10"/>
-      <c r="O33" s="10"/>
-      <c r="P33" s="10"/>
-      <c r="Q33" s="10"/>
-      <c r="R33" s="10"/>
-      <c r="S33" s="10"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="9"/>
-      <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="10"/>
-      <c r="I34" s="10"/>
-      <c r="J34" s="10" t="str">
+      <c r="K33" s="11"/>
+      <c r="L33" s="11"/>
+      <c r="M33" s="11"/>
+      <c r="N33" s="11"/>
+      <c r="O33" s="11"/>
+      <c r="P33" s="11"/>
+      <c r="Q33" s="11"/>
+      <c r="R33" s="11"/>
+      <c r="S33" s="11"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="10"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
+      <c r="J34" s="11" t="str">
         <f aca="false">IF(COUNTIF(D34:I34,"Sim")&gt;0,"Sim",IF(COUNTIF(D34:I34,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K34" s="10"/>
-      <c r="L34" s="10"/>
-      <c r="M34" s="10"/>
-      <c r="N34" s="10"/>
-      <c r="O34" s="10"/>
-      <c r="P34" s="10"/>
-      <c r="Q34" s="10"/>
-      <c r="R34" s="10"/>
-      <c r="S34" s="10"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="9"/>
-      <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
-      <c r="D35" s="10"/>
-      <c r="E35" s="10"/>
-      <c r="F35" s="10"/>
-      <c r="G35" s="10"/>
-      <c r="H35" s="10"/>
-      <c r="I35" s="10"/>
-      <c r="J35" s="10" t="str">
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
+      <c r="M34" s="11"/>
+      <c r="N34" s="11"/>
+      <c r="O34" s="11"/>
+      <c r="P34" s="11"/>
+      <c r="Q34" s="11"/>
+      <c r="R34" s="11"/>
+      <c r="S34" s="11"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="10"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="11"/>
+      <c r="J35" s="11" t="str">
         <f aca="false">IF(COUNTIF(D35:I35,"Sim")&gt;0,"Sim",IF(COUNTIF(D35:I35,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K35" s="10"/>
-      <c r="L35" s="10"/>
-      <c r="M35" s="10"/>
-      <c r="N35" s="10"/>
-      <c r="O35" s="10"/>
-      <c r="P35" s="10"/>
-      <c r="Q35" s="10"/>
-      <c r="R35" s="10"/>
-      <c r="S35" s="10"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="9"/>
-      <c r="B36" s="10"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="10"/>
-      <c r="E36" s="10"/>
-      <c r="F36" s="10"/>
-      <c r="G36" s="10"/>
-      <c r="H36" s="10"/>
-      <c r="I36" s="10"/>
-      <c r="J36" s="10" t="str">
+      <c r="K35" s="11"/>
+      <c r="L35" s="11"/>
+      <c r="M35" s="11"/>
+      <c r="N35" s="11"/>
+      <c r="O35" s="11"/>
+      <c r="P35" s="11"/>
+      <c r="Q35" s="11"/>
+      <c r="R35" s="11"/>
+      <c r="S35" s="11"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="10"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="11"/>
+      <c r="J36" s="11" t="str">
         <f aca="false">IF(COUNTIF(D36:I36,"Sim")&gt;0,"Sim",IF(COUNTIF(D36:I36,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K36" s="10"/>
-      <c r="L36" s="10"/>
-      <c r="M36" s="10"/>
-      <c r="N36" s="10"/>
-      <c r="O36" s="10"/>
-      <c r="P36" s="10"/>
-      <c r="Q36" s="10"/>
-      <c r="R36" s="10"/>
-      <c r="S36" s="10"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="9"/>
-      <c r="B37" s="10"/>
-      <c r="C37" s="10"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="10"/>
-      <c r="H37" s="10"/>
-      <c r="I37" s="10"/>
-      <c r="J37" s="10" t="str">
+      <c r="K36" s="11"/>
+      <c r="L36" s="11"/>
+      <c r="M36" s="11"/>
+      <c r="N36" s="11"/>
+      <c r="O36" s="11"/>
+      <c r="P36" s="11"/>
+      <c r="Q36" s="11"/>
+      <c r="R36" s="11"/>
+      <c r="S36" s="11"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="10"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="11"/>
+      <c r="J37" s="11" t="str">
         <f aca="false">IF(COUNTIF(D37:I37,"Sim")&gt;0,"Sim",IF(COUNTIF(D37:I37,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K37" s="10"/>
-      <c r="L37" s="10"/>
-      <c r="M37" s="10"/>
-      <c r="N37" s="10"/>
-      <c r="O37" s="10"/>
-      <c r="P37" s="10"/>
-      <c r="Q37" s="10"/>
-      <c r="R37" s="10"/>
-      <c r="S37" s="10"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="9"/>
-      <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="10"/>
-      <c r="G38" s="10"/>
-      <c r="H38" s="10"/>
-      <c r="I38" s="10"/>
-      <c r="J38" s="10" t="str">
+      <c r="K37" s="11"/>
+      <c r="L37" s="11"/>
+      <c r="M37" s="11"/>
+      <c r="N37" s="11"/>
+      <c r="O37" s="11"/>
+      <c r="P37" s="11"/>
+      <c r="Q37" s="11"/>
+      <c r="R37" s="11"/>
+      <c r="S37" s="11"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="10"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="11"/>
+      <c r="J38" s="11" t="str">
         <f aca="false">IF(COUNTIF(D38:I38,"Sim")&gt;0,"Sim",IF(COUNTIF(D38:I38,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K38" s="10"/>
-      <c r="L38" s="10"/>
-      <c r="M38" s="10"/>
-      <c r="N38" s="10"/>
-      <c r="O38" s="10"/>
-      <c r="P38" s="10"/>
-      <c r="Q38" s="10"/>
-      <c r="R38" s="10"/>
-      <c r="S38" s="10"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="9"/>
-      <c r="B39" s="10"/>
-      <c r="C39" s="10"/>
-      <c r="D39" s="10"/>
-      <c r="E39" s="10"/>
-      <c r="F39" s="10"/>
-      <c r="G39" s="10"/>
-      <c r="H39" s="10"/>
-      <c r="I39" s="10"/>
-      <c r="J39" s="10" t="str">
+      <c r="K38" s="11"/>
+      <c r="L38" s="11"/>
+      <c r="M38" s="11"/>
+      <c r="N38" s="11"/>
+      <c r="O38" s="11"/>
+      <c r="P38" s="11"/>
+      <c r="Q38" s="11"/>
+      <c r="R38" s="11"/>
+      <c r="S38" s="11"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="10"/>
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="11"/>
+      <c r="I39" s="11"/>
+      <c r="J39" s="11" t="str">
         <f aca="false">IF(COUNTIF(D39:I39,"Sim")&gt;0,"Sim",IF(COUNTIF(D39:I39,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K39" s="10"/>
-      <c r="L39" s="10"/>
-      <c r="M39" s="10"/>
-      <c r="N39" s="10"/>
-      <c r="O39" s="10"/>
-      <c r="P39" s="10"/>
-      <c r="Q39" s="10"/>
-      <c r="R39" s="10"/>
-      <c r="S39" s="10"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="9"/>
-      <c r="B40" s="10"/>
-      <c r="C40" s="10"/>
-      <c r="D40" s="10"/>
-      <c r="E40" s="10"/>
-      <c r="F40" s="10"/>
-      <c r="G40" s="10"/>
-      <c r="H40" s="10"/>
-      <c r="I40" s="10"/>
-      <c r="J40" s="10" t="str">
+      <c r="K39" s="11"/>
+      <c r="L39" s="11"/>
+      <c r="M39" s="11"/>
+      <c r="N39" s="11"/>
+      <c r="O39" s="11"/>
+      <c r="P39" s="11"/>
+      <c r="Q39" s="11"/>
+      <c r="R39" s="11"/>
+      <c r="S39" s="11"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="10"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="11"/>
+      <c r="I40" s="11"/>
+      <c r="J40" s="11" t="str">
         <f aca="false">IF(COUNTIF(D40:I40,"Sim")&gt;0,"Sim",IF(COUNTIF(D40:I40,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K40" s="10"/>
-      <c r="L40" s="10"/>
-      <c r="M40" s="10"/>
-      <c r="N40" s="10"/>
-      <c r="O40" s="10"/>
-      <c r="P40" s="10"/>
-      <c r="Q40" s="10"/>
-      <c r="R40" s="10"/>
-      <c r="S40" s="10"/>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="9"/>
-      <c r="B41" s="10"/>
-      <c r="C41" s="10"/>
-      <c r="D41" s="10"/>
-      <c r="E41" s="10"/>
-      <c r="F41" s="10"/>
-      <c r="G41" s="10"/>
-      <c r="H41" s="10"/>
-      <c r="I41" s="10"/>
-      <c r="J41" s="10" t="str">
+      <c r="K40" s="11"/>
+      <c r="L40" s="11"/>
+      <c r="M40" s="11"/>
+      <c r="N40" s="11"/>
+      <c r="O40" s="11"/>
+      <c r="P40" s="11"/>
+      <c r="Q40" s="11"/>
+      <c r="R40" s="11"/>
+      <c r="S40" s="11"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="10"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="11"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="11"/>
+      <c r="I41" s="11"/>
+      <c r="J41" s="11" t="str">
         <f aca="false">IF(COUNTIF(D41:I41,"Sim")&gt;0,"Sim",IF(COUNTIF(D41:I41,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K41" s="10"/>
-      <c r="L41" s="10"/>
-      <c r="M41" s="10"/>
-      <c r="N41" s="10"/>
-      <c r="O41" s="10"/>
-      <c r="P41" s="10"/>
-      <c r="Q41" s="10"/>
-      <c r="R41" s="10"/>
-      <c r="S41" s="10"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="9"/>
-      <c r="B42" s="10"/>
-      <c r="C42" s="10"/>
-      <c r="D42" s="10"/>
-      <c r="E42" s="10"/>
-      <c r="F42" s="10"/>
-      <c r="G42" s="10"/>
-      <c r="H42" s="10"/>
-      <c r="I42" s="10"/>
-      <c r="J42" s="10" t="str">
+      <c r="K41" s="11"/>
+      <c r="L41" s="11"/>
+      <c r="M41" s="11"/>
+      <c r="N41" s="11"/>
+      <c r="O41" s="11"/>
+      <c r="P41" s="11"/>
+      <c r="Q41" s="11"/>
+      <c r="R41" s="11"/>
+      <c r="S41" s="11"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="10"/>
+      <c r="B42" s="11"/>
+      <c r="C42" s="11"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="11"/>
+      <c r="F42" s="11"/>
+      <c r="G42" s="11"/>
+      <c r="H42" s="11"/>
+      <c r="I42" s="11"/>
+      <c r="J42" s="11" t="str">
         <f aca="false">IF(COUNTIF(D42:I42,"Sim")&gt;0,"Sim",IF(COUNTIF(D42:I42,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K42" s="10"/>
-      <c r="L42" s="10"/>
-      <c r="M42" s="10"/>
-      <c r="N42" s="10"/>
-      <c r="O42" s="10"/>
-      <c r="P42" s="10"/>
-      <c r="Q42" s="10"/>
-      <c r="R42" s="10"/>
-      <c r="S42" s="10"/>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="9"/>
-      <c r="B43" s="10"/>
-      <c r="C43" s="10"/>
-      <c r="D43" s="10"/>
-      <c r="E43" s="10"/>
-      <c r="F43" s="10"/>
-      <c r="G43" s="10"/>
-      <c r="H43" s="10"/>
-      <c r="I43" s="10"/>
-      <c r="J43" s="10" t="str">
+      <c r="K42" s="11"/>
+      <c r="L42" s="11"/>
+      <c r="M42" s="11"/>
+      <c r="N42" s="11"/>
+      <c r="O42" s="11"/>
+      <c r="P42" s="11"/>
+      <c r="Q42" s="11"/>
+      <c r="R42" s="11"/>
+      <c r="S42" s="11"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="10"/>
+      <c r="B43" s="11"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="11"/>
+      <c r="I43" s="11"/>
+      <c r="J43" s="11" t="str">
         <f aca="false">IF(COUNTIF(D43:I43,"Sim")&gt;0,"Sim",IF(COUNTIF(D43:I43,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K43" s="10"/>
-      <c r="L43" s="10"/>
-      <c r="M43" s="10"/>
-      <c r="N43" s="10"/>
-      <c r="O43" s="10"/>
-      <c r="P43" s="10"/>
-      <c r="Q43" s="10"/>
-      <c r="R43" s="10"/>
-      <c r="S43" s="10"/>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="9"/>
-      <c r="B44" s="10"/>
-      <c r="C44" s="10"/>
-      <c r="D44" s="10"/>
-      <c r="E44" s="10"/>
-      <c r="F44" s="10"/>
-      <c r="G44" s="10"/>
-      <c r="H44" s="10"/>
-      <c r="I44" s="10"/>
-      <c r="J44" s="10" t="str">
+      <c r="K43" s="11"/>
+      <c r="L43" s="11"/>
+      <c r="M43" s="11"/>
+      <c r="N43" s="11"/>
+      <c r="O43" s="11"/>
+      <c r="P43" s="11"/>
+      <c r="Q43" s="11"/>
+      <c r="R43" s="11"/>
+      <c r="S43" s="11"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="10"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="11"/>
+      <c r="F44" s="11"/>
+      <c r="G44" s="11"/>
+      <c r="H44" s="11"/>
+      <c r="I44" s="11"/>
+      <c r="J44" s="11" t="str">
         <f aca="false">IF(COUNTIF(D44:I44,"Sim")&gt;0,"Sim",IF(COUNTIF(D44:I44,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K44" s="10"/>
-      <c r="L44" s="10"/>
-      <c r="M44" s="10"/>
-      <c r="N44" s="10"/>
-      <c r="O44" s="10"/>
-      <c r="P44" s="10"/>
-      <c r="Q44" s="10"/>
-      <c r="R44" s="10"/>
-      <c r="S44" s="10"/>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="9"/>
-      <c r="B45" s="10"/>
-      <c r="C45" s="10"/>
-      <c r="D45" s="10"/>
-      <c r="E45" s="10"/>
-      <c r="F45" s="10"/>
-      <c r="G45" s="10"/>
-      <c r="H45" s="10"/>
-      <c r="I45" s="10"/>
-      <c r="J45" s="10" t="str">
+      <c r="K44" s="11"/>
+      <c r="L44" s="11"/>
+      <c r="M44" s="11"/>
+      <c r="N44" s="11"/>
+      <c r="O44" s="11"/>
+      <c r="P44" s="11"/>
+      <c r="Q44" s="11"/>
+      <c r="R44" s="11"/>
+      <c r="S44" s="11"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="10"/>
+      <c r="B45" s="11"/>
+      <c r="C45" s="11"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="11"/>
+      <c r="F45" s="11"/>
+      <c r="G45" s="11"/>
+      <c r="H45" s="11"/>
+      <c r="I45" s="11"/>
+      <c r="J45" s="11" t="str">
         <f aca="false">IF(COUNTIF(D45:I45,"Sim")&gt;0,"Sim",IF(COUNTIF(D45:I45,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K45" s="10"/>
-      <c r="L45" s="10"/>
-      <c r="M45" s="10"/>
-      <c r="N45" s="10"/>
-      <c r="O45" s="10"/>
-      <c r="P45" s="10"/>
-      <c r="Q45" s="10"/>
-      <c r="R45" s="10"/>
-      <c r="S45" s="10"/>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="9"/>
-      <c r="B46" s="10"/>
-      <c r="C46" s="10"/>
-      <c r="D46" s="10"/>
-      <c r="E46" s="10"/>
-      <c r="F46" s="10"/>
-      <c r="G46" s="10"/>
-      <c r="H46" s="10"/>
-      <c r="I46" s="10"/>
-      <c r="J46" s="10" t="str">
+      <c r="K45" s="11"/>
+      <c r="L45" s="11"/>
+      <c r="M45" s="11"/>
+      <c r="N45" s="11"/>
+      <c r="O45" s="11"/>
+      <c r="P45" s="11"/>
+      <c r="Q45" s="11"/>
+      <c r="R45" s="11"/>
+      <c r="S45" s="11"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="10"/>
+      <c r="B46" s="11"/>
+      <c r="C46" s="11"/>
+      <c r="D46" s="11"/>
+      <c r="E46" s="11"/>
+      <c r="F46" s="11"/>
+      <c r="G46" s="11"/>
+      <c r="H46" s="11"/>
+      <c r="I46" s="11"/>
+      <c r="J46" s="11" t="str">
         <f aca="false">IF(COUNTIF(D46:I46,"Sim")&gt;0,"Sim",IF(COUNTIF(D46:I46,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K46" s="10"/>
-      <c r="L46" s="10"/>
-      <c r="M46" s="10"/>
-      <c r="N46" s="10"/>
-      <c r="O46" s="10"/>
-      <c r="P46" s="10"/>
-      <c r="Q46" s="10"/>
-      <c r="R46" s="10"/>
-      <c r="S46" s="10"/>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="9"/>
-      <c r="B47" s="10"/>
-      <c r="C47" s="10"/>
-      <c r="D47" s="10"/>
-      <c r="E47" s="10"/>
-      <c r="F47" s="10"/>
-      <c r="G47" s="10"/>
-      <c r="H47" s="10"/>
-      <c r="I47" s="10"/>
-      <c r="J47" s="10" t="str">
+      <c r="K46" s="11"/>
+      <c r="L46" s="11"/>
+      <c r="M46" s="11"/>
+      <c r="N46" s="11"/>
+      <c r="O46" s="11"/>
+      <c r="P46" s="11"/>
+      <c r="Q46" s="11"/>
+      <c r="R46" s="11"/>
+      <c r="S46" s="11"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="10"/>
+      <c r="B47" s="11"/>
+      <c r="C47" s="11"/>
+      <c r="D47" s="11"/>
+      <c r="E47" s="11"/>
+      <c r="F47" s="11"/>
+      <c r="G47" s="11"/>
+      <c r="H47" s="11"/>
+      <c r="I47" s="11"/>
+      <c r="J47" s="11" t="str">
         <f aca="false">IF(COUNTIF(D47:I47,"Sim")&gt;0,"Sim",IF(COUNTIF(D47:I47,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K47" s="10"/>
-      <c r="L47" s="10"/>
-      <c r="M47" s="10"/>
-      <c r="N47" s="10"/>
-      <c r="O47" s="10"/>
-      <c r="P47" s="10"/>
-      <c r="Q47" s="10"/>
-      <c r="R47" s="10"/>
-      <c r="S47" s="10"/>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="9"/>
-      <c r="B48" s="10"/>
-      <c r="C48" s="10"/>
-      <c r="D48" s="10"/>
-      <c r="E48" s="10"/>
-      <c r="F48" s="10"/>
-      <c r="G48" s="10"/>
-      <c r="H48" s="10"/>
-      <c r="I48" s="10"/>
-      <c r="J48" s="10" t="str">
+      <c r="K47" s="11"/>
+      <c r="L47" s="11"/>
+      <c r="M47" s="11"/>
+      <c r="N47" s="11"/>
+      <c r="O47" s="11"/>
+      <c r="P47" s="11"/>
+      <c r="Q47" s="11"/>
+      <c r="R47" s="11"/>
+      <c r="S47" s="11"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="10"/>
+      <c r="B48" s="11"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="11"/>
+      <c r="F48" s="11"/>
+      <c r="G48" s="11"/>
+      <c r="H48" s="11"/>
+      <c r="I48" s="11"/>
+      <c r="J48" s="11" t="str">
         <f aca="false">IF(COUNTIF(D48:I48,"Sim")&gt;0,"Sim",IF(COUNTIF(D48:I48,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K48" s="10"/>
-      <c r="L48" s="10"/>
-      <c r="M48" s="10"/>
-      <c r="N48" s="10"/>
-      <c r="O48" s="10"/>
-      <c r="P48" s="10"/>
-      <c r="Q48" s="10"/>
-      <c r="R48" s="10"/>
-      <c r="S48" s="10"/>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="9"/>
-      <c r="B49" s="10"/>
-      <c r="C49" s="10"/>
-      <c r="D49" s="10"/>
-      <c r="E49" s="10"/>
-      <c r="F49" s="10"/>
-      <c r="G49" s="10"/>
-      <c r="H49" s="10"/>
-      <c r="I49" s="10"/>
-      <c r="J49" s="10" t="str">
+      <c r="K48" s="11"/>
+      <c r="L48" s="11"/>
+      <c r="M48" s="11"/>
+      <c r="N48" s="11"/>
+      <c r="O48" s="11"/>
+      <c r="P48" s="11"/>
+      <c r="Q48" s="11"/>
+      <c r="R48" s="11"/>
+      <c r="S48" s="11"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="10"/>
+      <c r="B49" s="11"/>
+      <c r="C49" s="11"/>
+      <c r="D49" s="11"/>
+      <c r="E49" s="11"/>
+      <c r="F49" s="11"/>
+      <c r="G49" s="11"/>
+      <c r="H49" s="11"/>
+      <c r="I49" s="11"/>
+      <c r="J49" s="11" t="str">
         <f aca="false">IF(COUNTIF(D49:I49,"Sim")&gt;0,"Sim",IF(COUNTIF(D49:I49,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K49" s="10"/>
-      <c r="L49" s="10"/>
-      <c r="M49" s="10"/>
-      <c r="N49" s="10"/>
-      <c r="O49" s="10"/>
-      <c r="P49" s="10"/>
-      <c r="Q49" s="10"/>
-      <c r="R49" s="10"/>
-      <c r="S49" s="10"/>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="9"/>
-      <c r="B50" s="10"/>
-      <c r="C50" s="10"/>
-      <c r="D50" s="10"/>
-      <c r="E50" s="10"/>
-      <c r="F50" s="10"/>
-      <c r="G50" s="10"/>
-      <c r="H50" s="10"/>
-      <c r="I50" s="10"/>
-      <c r="J50" s="10" t="str">
+      <c r="K49" s="11"/>
+      <c r="L49" s="11"/>
+      <c r="M49" s="11"/>
+      <c r="N49" s="11"/>
+      <c r="O49" s="11"/>
+      <c r="P49" s="11"/>
+      <c r="Q49" s="11"/>
+      <c r="R49" s="11"/>
+      <c r="S49" s="11"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="10"/>
+      <c r="B50" s="11"/>
+      <c r="C50" s="11"/>
+      <c r="D50" s="11"/>
+      <c r="E50" s="11"/>
+      <c r="F50" s="11"/>
+      <c r="G50" s="11"/>
+      <c r="H50" s="11"/>
+      <c r="I50" s="11"/>
+      <c r="J50" s="11" t="str">
         <f aca="false">IF(COUNTIF(D50:I50,"Sim")&gt;0,"Sim",IF(COUNTIF(D50:I50,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K50" s="10"/>
-      <c r="L50" s="10"/>
-      <c r="M50" s="10"/>
-      <c r="N50" s="10"/>
-      <c r="O50" s="10"/>
-      <c r="P50" s="10"/>
-      <c r="Q50" s="10"/>
-      <c r="R50" s="10"/>
-      <c r="S50" s="10"/>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="9"/>
-      <c r="B51" s="10"/>
-      <c r="C51" s="10"/>
-      <c r="D51" s="10"/>
-      <c r="E51" s="10"/>
-      <c r="F51" s="10"/>
-      <c r="G51" s="10"/>
-      <c r="H51" s="10"/>
-      <c r="I51" s="10"/>
-      <c r="J51" s="10" t="str">
+      <c r="K50" s="11"/>
+      <c r="L50" s="11"/>
+      <c r="M50" s="11"/>
+      <c r="N50" s="11"/>
+      <c r="O50" s="11"/>
+      <c r="P50" s="11"/>
+      <c r="Q50" s="11"/>
+      <c r="R50" s="11"/>
+      <c r="S50" s="11"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="10"/>
+      <c r="B51" s="11"/>
+      <c r="C51" s="11"/>
+      <c r="D51" s="11"/>
+      <c r="E51" s="11"/>
+      <c r="F51" s="11"/>
+      <c r="G51" s="11"/>
+      <c r="H51" s="11"/>
+      <c r="I51" s="11"/>
+      <c r="J51" s="11" t="str">
         <f aca="false">IF(COUNTIF(D51:I51,"Sim")&gt;0,"Sim",IF(COUNTIF(D51:I51,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K51" s="10"/>
-      <c r="L51" s="10"/>
-      <c r="M51" s="10"/>
-      <c r="N51" s="10"/>
-      <c r="O51" s="10"/>
-      <c r="P51" s="10"/>
-      <c r="Q51" s="10"/>
-      <c r="R51" s="10"/>
-      <c r="S51" s="10"/>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="9"/>
-      <c r="B52" s="10"/>
-      <c r="C52" s="10"/>
-      <c r="D52" s="10"/>
-      <c r="E52" s="10"/>
-      <c r="F52" s="10"/>
-      <c r="G52" s="10"/>
-      <c r="H52" s="10"/>
-      <c r="I52" s="10"/>
-      <c r="J52" s="10" t="str">
+      <c r="K51" s="11"/>
+      <c r="L51" s="11"/>
+      <c r="M51" s="11"/>
+      <c r="N51" s="11"/>
+      <c r="O51" s="11"/>
+      <c r="P51" s="11"/>
+      <c r="Q51" s="11"/>
+      <c r="R51" s="11"/>
+      <c r="S51" s="11"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="10"/>
+      <c r="B52" s="11"/>
+      <c r="C52" s="11"/>
+      <c r="D52" s="11"/>
+      <c r="E52" s="11"/>
+      <c r="F52" s="11"/>
+      <c r="G52" s="11"/>
+      <c r="H52" s="11"/>
+      <c r="I52" s="11"/>
+      <c r="J52" s="11" t="str">
         <f aca="false">IF(COUNTIF(D52:I52,"Sim")&gt;0,"Sim",IF(COUNTIF(D52:I52,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K52" s="10"/>
-      <c r="L52" s="10"/>
-      <c r="M52" s="10"/>
-      <c r="N52" s="10"/>
-      <c r="O52" s="10"/>
-      <c r="P52" s="10"/>
-      <c r="Q52" s="10"/>
-      <c r="R52" s="10"/>
-      <c r="S52" s="10"/>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="9"/>
-      <c r="B53" s="10"/>
-      <c r="C53" s="10"/>
-      <c r="D53" s="10"/>
-      <c r="E53" s="10"/>
-      <c r="F53" s="10"/>
-      <c r="G53" s="10"/>
-      <c r="H53" s="10"/>
-      <c r="I53" s="10"/>
-      <c r="J53" s="10" t="str">
+      <c r="K52" s="11"/>
+      <c r="L52" s="11"/>
+      <c r="M52" s="11"/>
+      <c r="N52" s="11"/>
+      <c r="O52" s="11"/>
+      <c r="P52" s="11"/>
+      <c r="Q52" s="11"/>
+      <c r="R52" s="11"/>
+      <c r="S52" s="11"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="10"/>
+      <c r="B53" s="11"/>
+      <c r="C53" s="11"/>
+      <c r="D53" s="11"/>
+      <c r="E53" s="11"/>
+      <c r="F53" s="11"/>
+      <c r="G53" s="11"/>
+      <c r="H53" s="11"/>
+      <c r="I53" s="11"/>
+      <c r="J53" s="11" t="str">
         <f aca="false">IF(COUNTIF(D53:I53,"Sim")&gt;0,"Sim",IF(COUNTIF(D53:I53,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K53" s="10"/>
-      <c r="L53" s="10"/>
-      <c r="M53" s="10"/>
-      <c r="N53" s="10"/>
-      <c r="O53" s="10"/>
-      <c r="P53" s="10"/>
-      <c r="Q53" s="10"/>
-      <c r="R53" s="10"/>
-      <c r="S53" s="10"/>
+      <c r="K53" s="11"/>
+      <c r="L53" s="11"/>
+      <c r="M53" s="11"/>
+      <c r="N53" s="11"/>
+      <c r="O53" s="11"/>
+      <c r="P53" s="11"/>
+      <c r="Q53" s="11"/>
+      <c r="R53" s="11"/>
+      <c r="S53" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3909,10 +3911,8 @@
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND(A4&lt;&gt;"",COUNTIF($A$4:$A$53,A4)&gt;1)</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B4:B53">
     <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>AND($A4&lt;&gt;"",ISNUMBER(VALUE(RIGHT($A4,2))),B4&lt;&gt;VALUE(RIGHT($A4,2)))</formula>
+      <formula>AND($A4&lt;&gt;"",OR(COUNTIFS(Caracterizacao!$A$4:$A$53,$A4,Caracterizacao!$B$4:$B$53,$B4)=0,COUNTIFS(Decisao_Comunicacao!$A$4:$A$53,$A4,Decisao_Comunicacao!$B$4:$B$53,$B4)=0))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="451">
@@ -5740,1479 +5740,1479 @@
   <dimension ref="A1:R53"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="22"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="8"/>
+      <c r="O2" s="8"/>
+      <c r="P2" s="8"/>
+      <c r="Q2" s="8"/>
+      <c r="R2" s="8"/>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="L3" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="M3" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="N3" s="8" t="s">
+      <c r="N3" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="O3" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="P3" s="8" t="s">
+      <c r="P3" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="Q3" s="8" t="s">
+      <c r="Q3" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="R3" s="8" t="s">
+      <c r="R3" s="9" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
+    <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="C4" s="11" t="n">
+      <c r="C4" s="12" t="n">
         <v>46314.3923611111</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="E4" s="12" t="n">
+      <c r="E4" s="13" t="n">
         <f aca="false">IFERROR(IF(C4="","",WORKDAY(C4,IF(D4="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v>46317</v>
       </c>
-      <c r="F4" s="13"/>
-      <c r="G4" s="10" t="s">
+      <c r="F4" s="14"/>
+      <c r="G4" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="J4" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="K4" s="10" t="s">
+      <c r="K4" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="L4" s="10" t="s">
+      <c r="L4" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="M4" s="10" t="s">
+      <c r="M4" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="N4" s="11"/>
-      <c r="O4" s="10" t="s">
+      <c r="N4" s="12"/>
+      <c r="O4" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="P4" s="11"/>
-      <c r="Q4" s="14" t="str">
+      <c r="P4" s="12"/>
+      <c r="Q4" s="15" t="str">
         <f aca="false">IFERROR(IF(P4="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P4,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R4" s="10" t="s">
+      <c r="R4" s="11" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="s">
+    <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="C5" s="11" t="n">
+      <c r="C5" s="12" t="n">
         <v>46314.3923611111</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="E5" s="12" t="n">
+      <c r="E5" s="13" t="n">
         <f aca="false">IFERROR(IF(C5="","",WORKDAY(C5,IF(D5="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v>46317</v>
       </c>
-      <c r="F5" s="13" t="n">
+      <c r="F5" s="14" t="n">
         <v>46317</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="I5" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="J5" s="10" t="s">
+      <c r="J5" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="K5" s="10" t="s">
+      <c r="K5" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="L5" s="10" t="s">
+      <c r="L5" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="M5" s="10" t="s">
+      <c r="M5" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="N5" s="11" t="n">
+      <c r="N5" s="12" t="n">
         <v>46314.5069444445</v>
       </c>
-      <c r="O5" s="10" t="s">
+      <c r="O5" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="P5" s="11"/>
-      <c r="Q5" s="14" t="str">
+      <c r="P5" s="12"/>
+      <c r="Q5" s="15" t="str">
         <f aca="false">IFERROR(IF(P5="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P5,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R5" s="10" t="s">
+      <c r="R5" s="11" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="12" t="str">
+    <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="10"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="13" t="str">
         <f aca="false">IFERROR(IF(C6="","",WORKDAY(C6,IF(D6="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F6" s="13"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
-      <c r="N6" s="11"/>
-      <c r="O6" s="10"/>
-      <c r="P6" s="11"/>
-      <c r="Q6" s="14" t="str">
+      <c r="F6" s="14"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="12"/>
+      <c r="O6" s="11"/>
+      <c r="P6" s="12"/>
+      <c r="Q6" s="15" t="str">
         <f aca="false">IFERROR(IF(P6="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P6,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R6" s="10"/>
-    </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="12" t="str">
+      <c r="R6" s="11"/>
+    </row>
+    <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="10"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="13" t="str">
         <f aca="false">IFERROR(IF(C7="","",WORKDAY(C7,IF(D7="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F7" s="13"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
-      <c r="N7" s="11"/>
-      <c r="O7" s="10"/>
-      <c r="P7" s="11"/>
-      <c r="Q7" s="14" t="str">
+      <c r="F7" s="14"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="12"/>
+      <c r="O7" s="11"/>
+      <c r="P7" s="12"/>
+      <c r="Q7" s="15" t="str">
         <f aca="false">IFERROR(IF(P7="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P7,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R7" s="10"/>
-    </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="12" t="str">
+      <c r="R7" s="11"/>
+    </row>
+    <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="10"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="13" t="str">
         <f aca="false">IFERROR(IF(C8="","",WORKDAY(C8,IF(D8="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F8" s="13"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="10"/>
-      <c r="M8" s="10"/>
-      <c r="N8" s="11"/>
-      <c r="O8" s="10"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="14" t="str">
+      <c r="F8" s="14"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="12"/>
+      <c r="O8" s="11"/>
+      <c r="P8" s="12"/>
+      <c r="Q8" s="15" t="str">
         <f aca="false">IFERROR(IF(P8="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P8,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R8" s="10"/>
-    </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="12" t="str">
+      <c r="R8" s="11"/>
+    </row>
+    <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="10"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="13" t="str">
         <f aca="false">IFERROR(IF(C9="","",WORKDAY(C9,IF(D9="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F9" s="13"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
-      <c r="N9" s="11"/>
-      <c r="O9" s="10"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="14" t="str">
+      <c r="F9" s="14"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="12"/>
+      <c r="O9" s="11"/>
+      <c r="P9" s="12"/>
+      <c r="Q9" s="15" t="str">
         <f aca="false">IFERROR(IF(P9="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P9,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R9" s="10"/>
-    </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="12" t="str">
+      <c r="R9" s="11"/>
+    </row>
+    <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="10"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="13" t="str">
         <f aca="false">IFERROR(IF(C10="","",WORKDAY(C10,IF(D10="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F10" s="13"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
-      <c r="N10" s="11"/>
-      <c r="O10" s="10"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="14" t="str">
+      <c r="F10" s="14"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="12"/>
+      <c r="O10" s="11"/>
+      <c r="P10" s="12"/>
+      <c r="Q10" s="15" t="str">
         <f aca="false">IFERROR(IF(P10="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P10,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R10" s="10"/>
-    </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="12" t="str">
+      <c r="R10" s="11"/>
+    </row>
+    <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="10"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="13" t="str">
         <f aca="false">IFERROR(IF(C11="","",WORKDAY(C11,IF(D11="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F11" s="13"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
-      <c r="N11" s="11"/>
-      <c r="O11" s="10"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="14" t="str">
+      <c r="F11" s="14"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="12"/>
+      <c r="O11" s="11"/>
+      <c r="P11" s="12"/>
+      <c r="Q11" s="15" t="str">
         <f aca="false">IFERROR(IF(P11="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P11,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R11" s="10"/>
-    </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="12" t="str">
+      <c r="R11" s="11"/>
+    </row>
+    <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="10"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="13" t="str">
         <f aca="false">IFERROR(IF(C12="","",WORKDAY(C12,IF(D12="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F12" s="13"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10"/>
-      <c r="M12" s="10"/>
-      <c r="N12" s="11"/>
-      <c r="O12" s="10"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="14" t="str">
+      <c r="F12" s="14"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="12"/>
+      <c r="O12" s="11"/>
+      <c r="P12" s="12"/>
+      <c r="Q12" s="15" t="str">
         <f aca="false">IFERROR(IF(P12="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P12,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R12" s="10"/>
-    </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="9"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="12" t="str">
+      <c r="R12" s="11"/>
+    </row>
+    <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="10"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="13" t="str">
         <f aca="false">IFERROR(IF(C13="","",WORKDAY(C13,IF(D13="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F13" s="13"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
-      <c r="N13" s="11"/>
-      <c r="O13" s="10"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="14" t="str">
+      <c r="F13" s="14"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="12"/>
+      <c r="O13" s="11"/>
+      <c r="P13" s="12"/>
+      <c r="Q13" s="15" t="str">
         <f aca="false">IFERROR(IF(P13="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P13,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R13" s="10"/>
-    </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="9"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="12" t="str">
+      <c r="R13" s="11"/>
+    </row>
+    <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="10"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="13" t="str">
         <f aca="false">IFERROR(IF(C14="","",WORKDAY(C14,IF(D14="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F14" s="13"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
-      <c r="M14" s="10"/>
-      <c r="N14" s="11"/>
-      <c r="O14" s="10"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="14" t="str">
+      <c r="F14" s="14"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="12"/>
+      <c r="O14" s="11"/>
+      <c r="P14" s="12"/>
+      <c r="Q14" s="15" t="str">
         <f aca="false">IFERROR(IF(P14="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P14,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R14" s="10"/>
-    </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="9"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="12" t="str">
+      <c r="R14" s="11"/>
+    </row>
+    <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="10"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="13" t="str">
         <f aca="false">IFERROR(IF(C15="","",WORKDAY(C15,IF(D15="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F15" s="13"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
-      <c r="N15" s="11"/>
-      <c r="O15" s="10"/>
-      <c r="P15" s="11"/>
-      <c r="Q15" s="14" t="str">
+      <c r="F15" s="14"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="12"/>
+      <c r="O15" s="11"/>
+      <c r="P15" s="12"/>
+      <c r="Q15" s="15" t="str">
         <f aca="false">IFERROR(IF(P15="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P15,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R15" s="10"/>
-    </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="12" t="str">
+      <c r="R15" s="11"/>
+    </row>
+    <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="10"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="13" t="str">
         <f aca="false">IFERROR(IF(C16="","",WORKDAY(C16,IF(D16="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F16" s="13"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
-      <c r="N16" s="11"/>
-      <c r="O16" s="10"/>
-      <c r="P16" s="11"/>
-      <c r="Q16" s="14" t="str">
+      <c r="F16" s="14"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="11"/>
+      <c r="M16" s="11"/>
+      <c r="N16" s="12"/>
+      <c r="O16" s="11"/>
+      <c r="P16" s="12"/>
+      <c r="Q16" s="15" t="str">
         <f aca="false">IFERROR(IF(P16="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P16,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R16" s="10"/>
-    </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="9"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="12" t="str">
+      <c r="R16" s="11"/>
+    </row>
+    <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="10"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="13" t="str">
         <f aca="false">IFERROR(IF(C17="","",WORKDAY(C17,IF(D17="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F17" s="13"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10"/>
-      <c r="M17" s="10"/>
-      <c r="N17" s="11"/>
-      <c r="O17" s="10"/>
-      <c r="P17" s="11"/>
-      <c r="Q17" s="14" t="str">
+      <c r="F17" s="14"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="12"/>
+      <c r="O17" s="11"/>
+      <c r="P17" s="12"/>
+      <c r="Q17" s="15" t="str">
         <f aca="false">IFERROR(IF(P17="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P17,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R17" s="10"/>
-    </row>
-    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="9"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="12" t="str">
+      <c r="R17" s="11"/>
+    </row>
+    <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="10"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="13" t="str">
         <f aca="false">IFERROR(IF(C18="","",WORKDAY(C18,IF(D18="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F18" s="13"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10"/>
-      <c r="M18" s="10"/>
-      <c r="N18" s="11"/>
-      <c r="O18" s="10"/>
-      <c r="P18" s="11"/>
-      <c r="Q18" s="14" t="str">
+      <c r="F18" s="14"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+      <c r="M18" s="11"/>
+      <c r="N18" s="12"/>
+      <c r="O18" s="11"/>
+      <c r="P18" s="12"/>
+      <c r="Q18" s="15" t="str">
         <f aca="false">IFERROR(IF(P18="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P18,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R18" s="10"/>
-    </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="9"/>
-      <c r="B19" s="10"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="12" t="str">
+      <c r="R18" s="11"/>
+    </row>
+    <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="10"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="13" t="str">
         <f aca="false">IFERROR(IF(C19="","",WORKDAY(C19,IF(D19="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F19" s="13"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10"/>
-      <c r="M19" s="10"/>
-      <c r="N19" s="11"/>
-      <c r="O19" s="10"/>
-      <c r="P19" s="11"/>
-      <c r="Q19" s="14" t="str">
+      <c r="F19" s="14"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="12"/>
+      <c r="O19" s="11"/>
+      <c r="P19" s="12"/>
+      <c r="Q19" s="15" t="str">
         <f aca="false">IFERROR(IF(P19="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P19,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R19" s="10"/>
-    </row>
-    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="9"/>
-      <c r="B20" s="10"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="12" t="str">
+      <c r="R19" s="11"/>
+    </row>
+    <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="10"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="13" t="str">
         <f aca="false">IFERROR(IF(C20="","",WORKDAY(C20,IF(D20="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F20" s="13"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10"/>
-      <c r="M20" s="10"/>
-      <c r="N20" s="11"/>
-      <c r="O20" s="10"/>
-      <c r="P20" s="11"/>
-      <c r="Q20" s="14" t="str">
+      <c r="F20" s="14"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="11"/>
+      <c r="M20" s="11"/>
+      <c r="N20" s="12"/>
+      <c r="O20" s="11"/>
+      <c r="P20" s="12"/>
+      <c r="Q20" s="15" t="str">
         <f aca="false">IFERROR(IF(P20="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P20,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R20" s="10"/>
-    </row>
-    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="9"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="12" t="str">
+      <c r="R20" s="11"/>
+    </row>
+    <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="10"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="13" t="str">
         <f aca="false">IFERROR(IF(C21="","",WORKDAY(C21,IF(D21="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F21" s="13"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="10"/>
-      <c r="M21" s="10"/>
-      <c r="N21" s="11"/>
-      <c r="O21" s="10"/>
-      <c r="P21" s="11"/>
-      <c r="Q21" s="14" t="str">
+      <c r="F21" s="14"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="12"/>
+      <c r="O21" s="11"/>
+      <c r="P21" s="12"/>
+      <c r="Q21" s="15" t="str">
         <f aca="false">IFERROR(IF(P21="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P21,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R21" s="10"/>
-    </row>
-    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="9"/>
-      <c r="B22" s="10"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="12" t="str">
+      <c r="R21" s="11"/>
+    </row>
+    <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="10"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="13" t="str">
         <f aca="false">IFERROR(IF(C22="","",WORKDAY(C22,IF(D22="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F22" s="13"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="10"/>
-      <c r="K22" s="10"/>
-      <c r="L22" s="10"/>
-      <c r="M22" s="10"/>
-      <c r="N22" s="11"/>
-      <c r="O22" s="10"/>
-      <c r="P22" s="11"/>
-      <c r="Q22" s="14" t="str">
+      <c r="F22" s="14"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="11"/>
+      <c r="N22" s="12"/>
+      <c r="O22" s="11"/>
+      <c r="P22" s="12"/>
+      <c r="Q22" s="15" t="str">
         <f aca="false">IFERROR(IF(P22="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P22,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R22" s="10"/>
-    </row>
-    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="9"/>
-      <c r="B23" s="10"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="12" t="str">
+      <c r="R22" s="11"/>
+    </row>
+    <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="10"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="13" t="str">
         <f aca="false">IFERROR(IF(C23="","",WORKDAY(C23,IF(D23="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F23" s="13"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="10"/>
-      <c r="K23" s="10"/>
-      <c r="L23" s="10"/>
-      <c r="M23" s="10"/>
-      <c r="N23" s="11"/>
-      <c r="O23" s="10"/>
-      <c r="P23" s="11"/>
-      <c r="Q23" s="14" t="str">
+      <c r="F23" s="14"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="11"/>
+      <c r="M23" s="11"/>
+      <c r="N23" s="12"/>
+      <c r="O23" s="11"/>
+      <c r="P23" s="12"/>
+      <c r="Q23" s="15" t="str">
         <f aca="false">IFERROR(IF(P23="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P23,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R23" s="10"/>
-    </row>
-    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="9"/>
-      <c r="B24" s="10"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="12" t="str">
+      <c r="R23" s="11"/>
+    </row>
+    <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="10"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="13" t="str">
         <f aca="false">IFERROR(IF(C24="","",WORKDAY(C24,IF(D24="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F24" s="13"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="10"/>
-      <c r="K24" s="10"/>
-      <c r="L24" s="10"/>
-      <c r="M24" s="10"/>
-      <c r="N24" s="11"/>
-      <c r="O24" s="10"/>
-      <c r="P24" s="11"/>
-      <c r="Q24" s="14" t="str">
+      <c r="F24" s="14"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="11"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="11"/>
+      <c r="M24" s="11"/>
+      <c r="N24" s="12"/>
+      <c r="O24" s="11"/>
+      <c r="P24" s="12"/>
+      <c r="Q24" s="15" t="str">
         <f aca="false">IFERROR(IF(P24="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P24,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R24" s="10"/>
-    </row>
-    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="9"/>
-      <c r="B25" s="10"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="12" t="str">
+      <c r="R24" s="11"/>
+    </row>
+    <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="10"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="13" t="str">
         <f aca="false">IFERROR(IF(C25="","",WORKDAY(C25,IF(D25="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F25" s="13"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="10"/>
-      <c r="K25" s="10"/>
-      <c r="L25" s="10"/>
-      <c r="M25" s="10"/>
-      <c r="N25" s="11"/>
-      <c r="O25" s="10"/>
-      <c r="P25" s="11"/>
-      <c r="Q25" s="14" t="str">
+      <c r="F25" s="14"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="11"/>
+      <c r="N25" s="12"/>
+      <c r="O25" s="11"/>
+      <c r="P25" s="12"/>
+      <c r="Q25" s="15" t="str">
         <f aca="false">IFERROR(IF(P25="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P25,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R25" s="10"/>
-    </row>
-    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="9"/>
-      <c r="B26" s="10"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="12" t="str">
+      <c r="R25" s="11"/>
+    </row>
+    <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="10"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="13" t="str">
         <f aca="false">IFERROR(IF(C26="","",WORKDAY(C26,IF(D26="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F26" s="13"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="10"/>
-      <c r="K26" s="10"/>
-      <c r="L26" s="10"/>
-      <c r="M26" s="10"/>
-      <c r="N26" s="11"/>
-      <c r="O26" s="10"/>
-      <c r="P26" s="11"/>
-      <c r="Q26" s="14" t="str">
+      <c r="F26" s="14"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="11"/>
+      <c r="K26" s="11"/>
+      <c r="L26" s="11"/>
+      <c r="M26" s="11"/>
+      <c r="N26" s="12"/>
+      <c r="O26" s="11"/>
+      <c r="P26" s="12"/>
+      <c r="Q26" s="15" t="str">
         <f aca="false">IFERROR(IF(P26="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P26,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R26" s="10"/>
-    </row>
-    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="9"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="12" t="str">
+      <c r="R26" s="11"/>
+    </row>
+    <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="10"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="13" t="str">
         <f aca="false">IFERROR(IF(C27="","",WORKDAY(C27,IF(D27="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F27" s="13"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
-      <c r="I27" s="10"/>
-      <c r="J27" s="10"/>
-      <c r="K27" s="10"/>
-      <c r="L27" s="10"/>
-      <c r="M27" s="10"/>
-      <c r="N27" s="11"/>
-      <c r="O27" s="10"/>
-      <c r="P27" s="11"/>
-      <c r="Q27" s="14" t="str">
+      <c r="F27" s="14"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
+      <c r="M27" s="11"/>
+      <c r="N27" s="12"/>
+      <c r="O27" s="11"/>
+      <c r="P27" s="12"/>
+      <c r="Q27" s="15" t="str">
         <f aca="false">IFERROR(IF(P27="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P27,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R27" s="10"/>
-    </row>
-    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="9"/>
-      <c r="B28" s="10"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="12" t="str">
+      <c r="R27" s="11"/>
+    </row>
+    <row r="28" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="10"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="13" t="str">
         <f aca="false">IFERROR(IF(C28="","",WORKDAY(C28,IF(D28="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F28" s="13"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
-      <c r="I28" s="10"/>
-      <c r="J28" s="10"/>
-      <c r="K28" s="10"/>
-      <c r="L28" s="10"/>
-      <c r="M28" s="10"/>
-      <c r="N28" s="11"/>
-      <c r="O28" s="10"/>
-      <c r="P28" s="11"/>
-      <c r="Q28" s="14" t="str">
+      <c r="F28" s="14"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
+      <c r="J28" s="11"/>
+      <c r="K28" s="11"/>
+      <c r="L28" s="11"/>
+      <c r="M28" s="11"/>
+      <c r="N28" s="12"/>
+      <c r="O28" s="11"/>
+      <c r="P28" s="12"/>
+      <c r="Q28" s="15" t="str">
         <f aca="false">IFERROR(IF(P28="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P28,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R28" s="10"/>
-    </row>
-    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="9"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="12" t="str">
+      <c r="R28" s="11"/>
+    </row>
+    <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="10"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="13" t="str">
         <f aca="false">IFERROR(IF(C29="","",WORKDAY(C29,IF(D29="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F29" s="13"/>
-      <c r="G29" s="10"/>
-      <c r="H29" s="10"/>
-      <c r="I29" s="10"/>
-      <c r="J29" s="10"/>
-      <c r="K29" s="10"/>
-      <c r="L29" s="10"/>
-      <c r="M29" s="10"/>
-      <c r="N29" s="11"/>
-      <c r="O29" s="10"/>
-      <c r="P29" s="11"/>
-      <c r="Q29" s="14" t="str">
+      <c r="F29" s="14"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11"/>
+      <c r="L29" s="11"/>
+      <c r="M29" s="11"/>
+      <c r="N29" s="12"/>
+      <c r="O29" s="11"/>
+      <c r="P29" s="12"/>
+      <c r="Q29" s="15" t="str">
         <f aca="false">IFERROR(IF(P29="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P29,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R29" s="10"/>
-    </row>
-    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="9"/>
-      <c r="B30" s="10"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="12" t="str">
+      <c r="R29" s="11"/>
+    </row>
+    <row r="30" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="10"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="13" t="str">
         <f aca="false">IFERROR(IF(C30="","",WORKDAY(C30,IF(D30="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F30" s="13"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
-      <c r="I30" s="10"/>
-      <c r="J30" s="10"/>
-      <c r="K30" s="10"/>
-      <c r="L30" s="10"/>
-      <c r="M30" s="10"/>
-      <c r="N30" s="11"/>
-      <c r="O30" s="10"/>
-      <c r="P30" s="11"/>
-      <c r="Q30" s="14" t="str">
+      <c r="F30" s="14"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
+      <c r="J30" s="11"/>
+      <c r="K30" s="11"/>
+      <c r="L30" s="11"/>
+      <c r="M30" s="11"/>
+      <c r="N30" s="12"/>
+      <c r="O30" s="11"/>
+      <c r="P30" s="12"/>
+      <c r="Q30" s="15" t="str">
         <f aca="false">IFERROR(IF(P30="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P30,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R30" s="10"/>
-    </row>
-    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="9"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="12" t="str">
+      <c r="R30" s="11"/>
+    </row>
+    <row r="31" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="10"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="13" t="str">
         <f aca="false">IFERROR(IF(C31="","",WORKDAY(C31,IF(D31="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F31" s="13"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="10"/>
-      <c r="I31" s="10"/>
-      <c r="J31" s="10"/>
-      <c r="K31" s="10"/>
-      <c r="L31" s="10"/>
-      <c r="M31" s="10"/>
-      <c r="N31" s="11"/>
-      <c r="O31" s="10"/>
-      <c r="P31" s="11"/>
-      <c r="Q31" s="14" t="str">
+      <c r="F31" s="14"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="11"/>
+      <c r="L31" s="11"/>
+      <c r="M31" s="11"/>
+      <c r="N31" s="12"/>
+      <c r="O31" s="11"/>
+      <c r="P31" s="12"/>
+      <c r="Q31" s="15" t="str">
         <f aca="false">IFERROR(IF(P31="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P31,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R31" s="10"/>
-    </row>
-    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="9"/>
-      <c r="B32" s="10"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="12" t="str">
+      <c r="R31" s="11"/>
+    </row>
+    <row r="32" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="10"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="13" t="str">
         <f aca="false">IFERROR(IF(C32="","",WORKDAY(C32,IF(D32="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F32" s="13"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="10"/>
-      <c r="I32" s="10"/>
-      <c r="J32" s="10"/>
-      <c r="K32" s="10"/>
-      <c r="L32" s="10"/>
-      <c r="M32" s="10"/>
-      <c r="N32" s="11"/>
-      <c r="O32" s="10"/>
-      <c r="P32" s="11"/>
-      <c r="Q32" s="14" t="str">
+      <c r="F32" s="14"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
+      <c r="M32" s="11"/>
+      <c r="N32" s="12"/>
+      <c r="O32" s="11"/>
+      <c r="P32" s="12"/>
+      <c r="Q32" s="15" t="str">
         <f aca="false">IFERROR(IF(P32="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P32,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R32" s="10"/>
-    </row>
-    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="9"/>
-      <c r="B33" s="10"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="10"/>
-      <c r="E33" s="12" t="str">
+      <c r="R32" s="11"/>
+    </row>
+    <row r="33" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="10"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="13" t="str">
         <f aca="false">IFERROR(IF(C33="","",WORKDAY(C33,IF(D33="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F33" s="13"/>
-      <c r="G33" s="10"/>
-      <c r="H33" s="10"/>
-      <c r="I33" s="10"/>
-      <c r="J33" s="10"/>
-      <c r="K33" s="10"/>
-      <c r="L33" s="10"/>
-      <c r="M33" s="10"/>
-      <c r="N33" s="11"/>
-      <c r="O33" s="10"/>
-      <c r="P33" s="11"/>
-      <c r="Q33" s="14" t="str">
+      <c r="F33" s="14"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="11"/>
+      <c r="K33" s="11"/>
+      <c r="L33" s="11"/>
+      <c r="M33" s="11"/>
+      <c r="N33" s="12"/>
+      <c r="O33" s="11"/>
+      <c r="P33" s="12"/>
+      <c r="Q33" s="15" t="str">
         <f aca="false">IFERROR(IF(P33="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P33,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R33" s="10"/>
-    </row>
-    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="9"/>
-      <c r="B34" s="10"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="12" t="str">
+      <c r="R33" s="11"/>
+    </row>
+    <row r="34" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="10"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="13" t="str">
         <f aca="false">IFERROR(IF(C34="","",WORKDAY(C34,IF(D34="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F34" s="13"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="10"/>
-      <c r="I34" s="10"/>
-      <c r="J34" s="10"/>
-      <c r="K34" s="10"/>
-      <c r="L34" s="10"/>
-      <c r="M34" s="10"/>
-      <c r="N34" s="11"/>
-      <c r="O34" s="10"/>
-      <c r="P34" s="11"/>
-      <c r="Q34" s="14" t="str">
+      <c r="F34" s="14"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
+      <c r="J34" s="11"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
+      <c r="M34" s="11"/>
+      <c r="N34" s="12"/>
+      <c r="O34" s="11"/>
+      <c r="P34" s="12"/>
+      <c r="Q34" s="15" t="str">
         <f aca="false">IFERROR(IF(P34="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P34,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R34" s="10"/>
-    </row>
-    <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="9"/>
-      <c r="B35" s="10"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="10"/>
-      <c r="E35" s="12" t="str">
+      <c r="R34" s="11"/>
+    </row>
+    <row r="35" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="10"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="13" t="str">
         <f aca="false">IFERROR(IF(C35="","",WORKDAY(C35,IF(D35="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F35" s="13"/>
-      <c r="G35" s="10"/>
-      <c r="H35" s="10"/>
-      <c r="I35" s="10"/>
-      <c r="J35" s="10"/>
-      <c r="K35" s="10"/>
-      <c r="L35" s="10"/>
-      <c r="M35" s="10"/>
-      <c r="N35" s="11"/>
-      <c r="O35" s="10"/>
-      <c r="P35" s="11"/>
-      <c r="Q35" s="14" t="str">
+      <c r="F35" s="14"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="11"/>
+      <c r="J35" s="11"/>
+      <c r="K35" s="11"/>
+      <c r="L35" s="11"/>
+      <c r="M35" s="11"/>
+      <c r="N35" s="12"/>
+      <c r="O35" s="11"/>
+      <c r="P35" s="12"/>
+      <c r="Q35" s="15" t="str">
         <f aca="false">IFERROR(IF(P35="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P35,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R35" s="10"/>
-    </row>
-    <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="9"/>
-      <c r="B36" s="10"/>
-      <c r="C36" s="11"/>
-      <c r="D36" s="10"/>
-      <c r="E36" s="12" t="str">
+      <c r="R35" s="11"/>
+    </row>
+    <row r="36" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="10"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="13" t="str">
         <f aca="false">IFERROR(IF(C36="","",WORKDAY(C36,IF(D36="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F36" s="13"/>
-      <c r="G36" s="10"/>
-      <c r="H36" s="10"/>
-      <c r="I36" s="10"/>
-      <c r="J36" s="10"/>
-      <c r="K36" s="10"/>
-      <c r="L36" s="10"/>
-      <c r="M36" s="10"/>
-      <c r="N36" s="11"/>
-      <c r="O36" s="10"/>
-      <c r="P36" s="11"/>
-      <c r="Q36" s="14" t="str">
+      <c r="F36" s="14"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="11"/>
+      <c r="J36" s="11"/>
+      <c r="K36" s="11"/>
+      <c r="L36" s="11"/>
+      <c r="M36" s="11"/>
+      <c r="N36" s="12"/>
+      <c r="O36" s="11"/>
+      <c r="P36" s="12"/>
+      <c r="Q36" s="15" t="str">
         <f aca="false">IFERROR(IF(P36="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P36,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R36" s="10"/>
-    </row>
-    <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="9"/>
-      <c r="B37" s="10"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="12" t="str">
+      <c r="R36" s="11"/>
+    </row>
+    <row r="37" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="10"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="13" t="str">
         <f aca="false">IFERROR(IF(C37="","",WORKDAY(C37,IF(D37="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F37" s="13"/>
-      <c r="G37" s="10"/>
-      <c r="H37" s="10"/>
-      <c r="I37" s="10"/>
-      <c r="J37" s="10"/>
-      <c r="K37" s="10"/>
-      <c r="L37" s="10"/>
-      <c r="M37" s="10"/>
-      <c r="N37" s="11"/>
-      <c r="O37" s="10"/>
-      <c r="P37" s="11"/>
-      <c r="Q37" s="14" t="str">
+      <c r="F37" s="14"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="11"/>
+      <c r="J37" s="11"/>
+      <c r="K37" s="11"/>
+      <c r="L37" s="11"/>
+      <c r="M37" s="11"/>
+      <c r="N37" s="12"/>
+      <c r="O37" s="11"/>
+      <c r="P37" s="12"/>
+      <c r="Q37" s="15" t="str">
         <f aca="false">IFERROR(IF(P37="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P37,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R37" s="10"/>
-    </row>
-    <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="9"/>
-      <c r="B38" s="10"/>
-      <c r="C38" s="11"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="12" t="str">
+      <c r="R37" s="11"/>
+    </row>
+    <row r="38" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="10"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="12"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="13" t="str">
         <f aca="false">IFERROR(IF(C38="","",WORKDAY(C38,IF(D38="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F38" s="13"/>
-      <c r="G38" s="10"/>
-      <c r="H38" s="10"/>
-      <c r="I38" s="10"/>
-      <c r="J38" s="10"/>
-      <c r="K38" s="10"/>
-      <c r="L38" s="10"/>
-      <c r="M38" s="10"/>
-      <c r="N38" s="11"/>
-      <c r="O38" s="10"/>
-      <c r="P38" s="11"/>
-      <c r="Q38" s="14" t="str">
+      <c r="F38" s="14"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="11"/>
+      <c r="J38" s="11"/>
+      <c r="K38" s="11"/>
+      <c r="L38" s="11"/>
+      <c r="M38" s="11"/>
+      <c r="N38" s="12"/>
+      <c r="O38" s="11"/>
+      <c r="P38" s="12"/>
+      <c r="Q38" s="15" t="str">
         <f aca="false">IFERROR(IF(P38="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P38,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R38" s="10"/>
-    </row>
-    <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="9"/>
-      <c r="B39" s="10"/>
-      <c r="C39" s="11"/>
-      <c r="D39" s="10"/>
-      <c r="E39" s="12" t="str">
+      <c r="R38" s="11"/>
+    </row>
+    <row r="39" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="10"/>
+      <c r="B39" s="11"/>
+      <c r="C39" s="12"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="13" t="str">
         <f aca="false">IFERROR(IF(C39="","",WORKDAY(C39,IF(D39="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F39" s="13"/>
-      <c r="G39" s="10"/>
-      <c r="H39" s="10"/>
-      <c r="I39" s="10"/>
-      <c r="J39" s="10"/>
-      <c r="K39" s="10"/>
-      <c r="L39" s="10"/>
-      <c r="M39" s="10"/>
-      <c r="N39" s="11"/>
-      <c r="O39" s="10"/>
-      <c r="P39" s="11"/>
-      <c r="Q39" s="14" t="str">
+      <c r="F39" s="14"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="11"/>
+      <c r="I39" s="11"/>
+      <c r="J39" s="11"/>
+      <c r="K39" s="11"/>
+      <c r="L39" s="11"/>
+      <c r="M39" s="11"/>
+      <c r="N39" s="12"/>
+      <c r="O39" s="11"/>
+      <c r="P39" s="12"/>
+      <c r="Q39" s="15" t="str">
         <f aca="false">IFERROR(IF(P39="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P39,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R39" s="10"/>
-    </row>
-    <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="9"/>
-      <c r="B40" s="10"/>
-      <c r="C40" s="11"/>
-      <c r="D40" s="10"/>
-      <c r="E40" s="12" t="str">
+      <c r="R39" s="11"/>
+    </row>
+    <row r="40" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="10"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="12"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="13" t="str">
         <f aca="false">IFERROR(IF(C40="","",WORKDAY(C40,IF(D40="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F40" s="13"/>
-      <c r="G40" s="10"/>
-      <c r="H40" s="10"/>
-      <c r="I40" s="10"/>
-      <c r="J40" s="10"/>
-      <c r="K40" s="10"/>
-      <c r="L40" s="10"/>
-      <c r="M40" s="10"/>
-      <c r="N40" s="11"/>
-      <c r="O40" s="10"/>
-      <c r="P40" s="11"/>
-      <c r="Q40" s="14" t="str">
+      <c r="F40" s="14"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="11"/>
+      <c r="I40" s="11"/>
+      <c r="J40" s="11"/>
+      <c r="K40" s="11"/>
+      <c r="L40" s="11"/>
+      <c r="M40" s="11"/>
+      <c r="N40" s="12"/>
+      <c r="O40" s="11"/>
+      <c r="P40" s="12"/>
+      <c r="Q40" s="15" t="str">
         <f aca="false">IFERROR(IF(P40="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P40,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R40" s="10"/>
-    </row>
-    <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="9"/>
-      <c r="B41" s="10"/>
-      <c r="C41" s="11"/>
-      <c r="D41" s="10"/>
-      <c r="E41" s="12" t="str">
+      <c r="R40" s="11"/>
+    </row>
+    <row r="41" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="10"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="13" t="str">
         <f aca="false">IFERROR(IF(C41="","",WORKDAY(C41,IF(D41="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F41" s="13"/>
-      <c r="G41" s="10"/>
-      <c r="H41" s="10"/>
-      <c r="I41" s="10"/>
-      <c r="J41" s="10"/>
-      <c r="K41" s="10"/>
-      <c r="L41" s="10"/>
-      <c r="M41" s="10"/>
-      <c r="N41" s="11"/>
-      <c r="O41" s="10"/>
-      <c r="P41" s="11"/>
-      <c r="Q41" s="14" t="str">
+      <c r="F41" s="14"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="11"/>
+      <c r="I41" s="11"/>
+      <c r="J41" s="11"/>
+      <c r="K41" s="11"/>
+      <c r="L41" s="11"/>
+      <c r="M41" s="11"/>
+      <c r="N41" s="12"/>
+      <c r="O41" s="11"/>
+      <c r="P41" s="12"/>
+      <c r="Q41" s="15" t="str">
         <f aca="false">IFERROR(IF(P41="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P41,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R41" s="10"/>
-    </row>
-    <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="9"/>
-      <c r="B42" s="10"/>
-      <c r="C42" s="11"/>
-      <c r="D42" s="10"/>
-      <c r="E42" s="12" t="str">
+      <c r="R41" s="11"/>
+    </row>
+    <row r="42" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="10"/>
+      <c r="B42" s="11"/>
+      <c r="C42" s="12"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="13" t="str">
         <f aca="false">IFERROR(IF(C42="","",WORKDAY(C42,IF(D42="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F42" s="13"/>
-      <c r="G42" s="10"/>
-      <c r="H42" s="10"/>
-      <c r="I42" s="10"/>
-      <c r="J42" s="10"/>
-      <c r="K42" s="10"/>
-      <c r="L42" s="10"/>
-      <c r="M42" s="10"/>
-      <c r="N42" s="11"/>
-      <c r="O42" s="10"/>
-      <c r="P42" s="11"/>
-      <c r="Q42" s="14" t="str">
+      <c r="F42" s="14"/>
+      <c r="G42" s="11"/>
+      <c r="H42" s="11"/>
+      <c r="I42" s="11"/>
+      <c r="J42" s="11"/>
+      <c r="K42" s="11"/>
+      <c r="L42" s="11"/>
+      <c r="M42" s="11"/>
+      <c r="N42" s="12"/>
+      <c r="O42" s="11"/>
+      <c r="P42" s="12"/>
+      <c r="Q42" s="15" t="str">
         <f aca="false">IFERROR(IF(P42="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P42,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R42" s="10"/>
-    </row>
-    <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="9"/>
-      <c r="B43" s="10"/>
-      <c r="C43" s="11"/>
-      <c r="D43" s="10"/>
-      <c r="E43" s="12" t="str">
+      <c r="R42" s="11"/>
+    </row>
+    <row r="43" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="10"/>
+      <c r="B43" s="11"/>
+      <c r="C43" s="12"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="13" t="str">
         <f aca="false">IFERROR(IF(C43="","",WORKDAY(C43,IF(D43="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F43" s="13"/>
-      <c r="G43" s="10"/>
-      <c r="H43" s="10"/>
-      <c r="I43" s="10"/>
-      <c r="J43" s="10"/>
-      <c r="K43" s="10"/>
-      <c r="L43" s="10"/>
-      <c r="M43" s="10"/>
-      <c r="N43" s="11"/>
-      <c r="O43" s="10"/>
-      <c r="P43" s="11"/>
-      <c r="Q43" s="14" t="str">
+      <c r="F43" s="14"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="11"/>
+      <c r="I43" s="11"/>
+      <c r="J43" s="11"/>
+      <c r="K43" s="11"/>
+      <c r="L43" s="11"/>
+      <c r="M43" s="11"/>
+      <c r="N43" s="12"/>
+      <c r="O43" s="11"/>
+      <c r="P43" s="12"/>
+      <c r="Q43" s="15" t="str">
         <f aca="false">IFERROR(IF(P43="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P43,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R43" s="10"/>
-    </row>
-    <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="9"/>
-      <c r="B44" s="10"/>
-      <c r="C44" s="11"/>
-      <c r="D44" s="10"/>
-      <c r="E44" s="12" t="str">
+      <c r="R43" s="11"/>
+    </row>
+    <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="10"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="12"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="13" t="str">
         <f aca="false">IFERROR(IF(C44="","",WORKDAY(C44,IF(D44="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F44" s="13"/>
-      <c r="G44" s="10"/>
-      <c r="H44" s="10"/>
-      <c r="I44" s="10"/>
-      <c r="J44" s="10"/>
-      <c r="K44" s="10"/>
-      <c r="L44" s="10"/>
-      <c r="M44" s="10"/>
-      <c r="N44" s="11"/>
-      <c r="O44" s="10"/>
-      <c r="P44" s="11"/>
-      <c r="Q44" s="14" t="str">
+      <c r="F44" s="14"/>
+      <c r="G44" s="11"/>
+      <c r="H44" s="11"/>
+      <c r="I44" s="11"/>
+      <c r="J44" s="11"/>
+      <c r="K44" s="11"/>
+      <c r="L44" s="11"/>
+      <c r="M44" s="11"/>
+      <c r="N44" s="12"/>
+      <c r="O44" s="11"/>
+      <c r="P44" s="12"/>
+      <c r="Q44" s="15" t="str">
         <f aca="false">IFERROR(IF(P44="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P44,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R44" s="10"/>
-    </row>
-    <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="9"/>
-      <c r="B45" s="10"/>
-      <c r="C45" s="11"/>
-      <c r="D45" s="10"/>
-      <c r="E45" s="12" t="str">
+      <c r="R44" s="11"/>
+    </row>
+    <row r="45" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="10"/>
+      <c r="B45" s="11"/>
+      <c r="C45" s="12"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="13" t="str">
         <f aca="false">IFERROR(IF(C45="","",WORKDAY(C45,IF(D45="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F45" s="13"/>
-      <c r="G45" s="10"/>
-      <c r="H45" s="10"/>
-      <c r="I45" s="10"/>
-      <c r="J45" s="10"/>
-      <c r="K45" s="10"/>
-      <c r="L45" s="10"/>
-      <c r="M45" s="10"/>
-      <c r="N45" s="11"/>
-      <c r="O45" s="10"/>
-      <c r="P45" s="11"/>
-      <c r="Q45" s="14" t="str">
+      <c r="F45" s="14"/>
+      <c r="G45" s="11"/>
+      <c r="H45" s="11"/>
+      <c r="I45" s="11"/>
+      <c r="J45" s="11"/>
+      <c r="K45" s="11"/>
+      <c r="L45" s="11"/>
+      <c r="M45" s="11"/>
+      <c r="N45" s="12"/>
+      <c r="O45" s="11"/>
+      <c r="P45" s="12"/>
+      <c r="Q45" s="15" t="str">
         <f aca="false">IFERROR(IF(P45="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P45,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R45" s="10"/>
-    </row>
-    <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="9"/>
-      <c r="B46" s="10"/>
-      <c r="C46" s="11"/>
-      <c r="D46" s="10"/>
-      <c r="E46" s="12" t="str">
+      <c r="R45" s="11"/>
+    </row>
+    <row r="46" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="10"/>
+      <c r="B46" s="11"/>
+      <c r="C46" s="12"/>
+      <c r="D46" s="11"/>
+      <c r="E46" s="13" t="str">
         <f aca="false">IFERROR(IF(C46="","",WORKDAY(C46,IF(D46="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F46" s="13"/>
-      <c r="G46" s="10"/>
-      <c r="H46" s="10"/>
-      <c r="I46" s="10"/>
-      <c r="J46" s="10"/>
-      <c r="K46" s="10"/>
-      <c r="L46" s="10"/>
-      <c r="M46" s="10"/>
-      <c r="N46" s="11"/>
-      <c r="O46" s="10"/>
-      <c r="P46" s="11"/>
-      <c r="Q46" s="14" t="str">
+      <c r="F46" s="14"/>
+      <c r="G46" s="11"/>
+      <c r="H46" s="11"/>
+      <c r="I46" s="11"/>
+      <c r="J46" s="11"/>
+      <c r="K46" s="11"/>
+      <c r="L46" s="11"/>
+      <c r="M46" s="11"/>
+      <c r="N46" s="12"/>
+      <c r="O46" s="11"/>
+      <c r="P46" s="12"/>
+      <c r="Q46" s="15" t="str">
         <f aca="false">IFERROR(IF(P46="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P46,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R46" s="10"/>
-    </row>
-    <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="9"/>
-      <c r="B47" s="10"/>
-      <c r="C47" s="11"/>
-      <c r="D47" s="10"/>
-      <c r="E47" s="12" t="str">
+      <c r="R46" s="11"/>
+    </row>
+    <row r="47" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="10"/>
+      <c r="B47" s="11"/>
+      <c r="C47" s="12"/>
+      <c r="D47" s="11"/>
+      <c r="E47" s="13" t="str">
         <f aca="false">IFERROR(IF(C47="","",WORKDAY(C47,IF(D47="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F47" s="13"/>
-      <c r="G47" s="10"/>
-      <c r="H47" s="10"/>
-      <c r="I47" s="10"/>
-      <c r="J47" s="10"/>
-      <c r="K47" s="10"/>
-      <c r="L47" s="10"/>
-      <c r="M47" s="10"/>
-      <c r="N47" s="11"/>
-      <c r="O47" s="10"/>
-      <c r="P47" s="11"/>
-      <c r="Q47" s="14" t="str">
+      <c r="F47" s="14"/>
+      <c r="G47" s="11"/>
+      <c r="H47" s="11"/>
+      <c r="I47" s="11"/>
+      <c r="J47" s="11"/>
+      <c r="K47" s="11"/>
+      <c r="L47" s="11"/>
+      <c r="M47" s="11"/>
+      <c r="N47" s="12"/>
+      <c r="O47" s="11"/>
+      <c r="P47" s="12"/>
+      <c r="Q47" s="15" t="str">
         <f aca="false">IFERROR(IF(P47="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P47,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R47" s="10"/>
-    </row>
-    <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="9"/>
-      <c r="B48" s="10"/>
-      <c r="C48" s="11"/>
-      <c r="D48" s="10"/>
-      <c r="E48" s="12" t="str">
+      <c r="R47" s="11"/>
+    </row>
+    <row r="48" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="10"/>
+      <c r="B48" s="11"/>
+      <c r="C48" s="12"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="13" t="str">
         <f aca="false">IFERROR(IF(C48="","",WORKDAY(C48,IF(D48="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F48" s="13"/>
-      <c r="G48" s="10"/>
-      <c r="H48" s="10"/>
-      <c r="I48" s="10"/>
-      <c r="J48" s="10"/>
-      <c r="K48" s="10"/>
-      <c r="L48" s="10"/>
-      <c r="M48" s="10"/>
-      <c r="N48" s="11"/>
-      <c r="O48" s="10"/>
-      <c r="P48" s="11"/>
-      <c r="Q48" s="14" t="str">
+      <c r="F48" s="14"/>
+      <c r="G48" s="11"/>
+      <c r="H48" s="11"/>
+      <c r="I48" s="11"/>
+      <c r="J48" s="11"/>
+      <c r="K48" s="11"/>
+      <c r="L48" s="11"/>
+      <c r="M48" s="11"/>
+      <c r="N48" s="12"/>
+      <c r="O48" s="11"/>
+      <c r="P48" s="12"/>
+      <c r="Q48" s="15" t="str">
         <f aca="false">IFERROR(IF(P48="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P48,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R48" s="10"/>
-    </row>
-    <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="9"/>
-      <c r="B49" s="10"/>
-      <c r="C49" s="11"/>
-      <c r="D49" s="10"/>
-      <c r="E49" s="12" t="str">
+      <c r="R48" s="11"/>
+    </row>
+    <row r="49" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="10"/>
+      <c r="B49" s="11"/>
+      <c r="C49" s="12"/>
+      <c r="D49" s="11"/>
+      <c r="E49" s="13" t="str">
         <f aca="false">IFERROR(IF(C49="","",WORKDAY(C49,IF(D49="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F49" s="13"/>
-      <c r="G49" s="10"/>
-      <c r="H49" s="10"/>
-      <c r="I49" s="10"/>
-      <c r="J49" s="10"/>
-      <c r="K49" s="10"/>
-      <c r="L49" s="10"/>
-      <c r="M49" s="10"/>
-      <c r="N49" s="11"/>
-      <c r="O49" s="10"/>
-      <c r="P49" s="11"/>
-      <c r="Q49" s="14" t="str">
+      <c r="F49" s="14"/>
+      <c r="G49" s="11"/>
+      <c r="H49" s="11"/>
+      <c r="I49" s="11"/>
+      <c r="J49" s="11"/>
+      <c r="K49" s="11"/>
+      <c r="L49" s="11"/>
+      <c r="M49" s="11"/>
+      <c r="N49" s="12"/>
+      <c r="O49" s="11"/>
+      <c r="P49" s="12"/>
+      <c r="Q49" s="15" t="str">
         <f aca="false">IFERROR(IF(P49="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P49,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R49" s="10"/>
-    </row>
-    <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="9"/>
-      <c r="B50" s="10"/>
-      <c r="C50" s="11"/>
-      <c r="D50" s="10"/>
-      <c r="E50" s="12" t="str">
+      <c r="R49" s="11"/>
+    </row>
+    <row r="50" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="10"/>
+      <c r="B50" s="11"/>
+      <c r="C50" s="12"/>
+      <c r="D50" s="11"/>
+      <c r="E50" s="13" t="str">
         <f aca="false">IFERROR(IF(C50="","",WORKDAY(C50,IF(D50="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F50" s="13"/>
-      <c r="G50" s="10"/>
-      <c r="H50" s="10"/>
-      <c r="I50" s="10"/>
-      <c r="J50" s="10"/>
-      <c r="K50" s="10"/>
-      <c r="L50" s="10"/>
-      <c r="M50" s="10"/>
-      <c r="N50" s="11"/>
-      <c r="O50" s="10"/>
-      <c r="P50" s="11"/>
-      <c r="Q50" s="14" t="str">
+      <c r="F50" s="14"/>
+      <c r="G50" s="11"/>
+      <c r="H50" s="11"/>
+      <c r="I50" s="11"/>
+      <c r="J50" s="11"/>
+      <c r="K50" s="11"/>
+      <c r="L50" s="11"/>
+      <c r="M50" s="11"/>
+      <c r="N50" s="12"/>
+      <c r="O50" s="11"/>
+      <c r="P50" s="12"/>
+      <c r="Q50" s="15" t="str">
         <f aca="false">IFERROR(IF(P50="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P50,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R50" s="10"/>
-    </row>
-    <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="9"/>
-      <c r="B51" s="10"/>
-      <c r="C51" s="11"/>
-      <c r="D51" s="10"/>
-      <c r="E51" s="12" t="str">
+      <c r="R50" s="11"/>
+    </row>
+    <row r="51" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="10"/>
+      <c r="B51" s="11"/>
+      <c r="C51" s="12"/>
+      <c r="D51" s="11"/>
+      <c r="E51" s="13" t="str">
         <f aca="false">IFERROR(IF(C51="","",WORKDAY(C51,IF(D51="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F51" s="13"/>
-      <c r="G51" s="10"/>
-      <c r="H51" s="10"/>
-      <c r="I51" s="10"/>
-      <c r="J51" s="10"/>
-      <c r="K51" s="10"/>
-      <c r="L51" s="10"/>
-      <c r="M51" s="10"/>
-      <c r="N51" s="11"/>
-      <c r="O51" s="10"/>
-      <c r="P51" s="11"/>
-      <c r="Q51" s="14" t="str">
+      <c r="F51" s="14"/>
+      <c r="G51" s="11"/>
+      <c r="H51" s="11"/>
+      <c r="I51" s="11"/>
+      <c r="J51" s="11"/>
+      <c r="K51" s="11"/>
+      <c r="L51" s="11"/>
+      <c r="M51" s="11"/>
+      <c r="N51" s="12"/>
+      <c r="O51" s="11"/>
+      <c r="P51" s="12"/>
+      <c r="Q51" s="15" t="str">
         <f aca="false">IFERROR(IF(P51="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P51,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R51" s="10"/>
-    </row>
-    <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="9"/>
-      <c r="B52" s="10"/>
-      <c r="C52" s="11"/>
-      <c r="D52" s="10"/>
-      <c r="E52" s="12" t="str">
+      <c r="R51" s="11"/>
+    </row>
+    <row r="52" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="10"/>
+      <c r="B52" s="11"/>
+      <c r="C52" s="12"/>
+      <c r="D52" s="11"/>
+      <c r="E52" s="13" t="str">
         <f aca="false">IFERROR(IF(C52="","",WORKDAY(C52,IF(D52="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F52" s="13"/>
-      <c r="G52" s="10"/>
-      <c r="H52" s="10"/>
-      <c r="I52" s="10"/>
-      <c r="J52" s="10"/>
-      <c r="K52" s="10"/>
-      <c r="L52" s="10"/>
-      <c r="M52" s="10"/>
-      <c r="N52" s="11"/>
-      <c r="O52" s="10"/>
-      <c r="P52" s="11"/>
-      <c r="Q52" s="14" t="str">
+      <c r="F52" s="14"/>
+      <c r="G52" s="11"/>
+      <c r="H52" s="11"/>
+      <c r="I52" s="11"/>
+      <c r="J52" s="11"/>
+      <c r="K52" s="11"/>
+      <c r="L52" s="11"/>
+      <c r="M52" s="11"/>
+      <c r="N52" s="12"/>
+      <c r="O52" s="11"/>
+      <c r="P52" s="12"/>
+      <c r="Q52" s="15" t="str">
         <f aca="false">IFERROR(IF(P52="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P52,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R52" s="10"/>
-    </row>
-    <row r="53" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="9"/>
-      <c r="B53" s="10"/>
-      <c r="C53" s="11"/>
-      <c r="D53" s="10"/>
-      <c r="E53" s="12" t="str">
+      <c r="R52" s="11"/>
+    </row>
+    <row r="53" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="10"/>
+      <c r="B53" s="11"/>
+      <c r="C53" s="12"/>
+      <c r="D53" s="11"/>
+      <c r="E53" s="13" t="str">
         <f aca="false">IFERROR(IF(C53="","",WORKDAY(C53,IF(D53="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F53" s="13"/>
-      <c r="G53" s="10"/>
-      <c r="H53" s="10"/>
-      <c r="I53" s="10"/>
-      <c r="J53" s="10"/>
-      <c r="K53" s="10"/>
-      <c r="L53" s="10"/>
-      <c r="M53" s="10"/>
-      <c r="N53" s="11"/>
-      <c r="O53" s="10"/>
-      <c r="P53" s="11"/>
-      <c r="Q53" s="14" t="str">
+      <c r="F53" s="14"/>
+      <c r="G53" s="11"/>
+      <c r="H53" s="11"/>
+      <c r="I53" s="11"/>
+      <c r="J53" s="11"/>
+      <c r="K53" s="11"/>
+      <c r="L53" s="11"/>
+      <c r="M53" s="11"/>
+      <c r="N53" s="12"/>
+      <c r="O53" s="11"/>
+      <c r="P53" s="12"/>
+      <c r="Q53" s="15" t="str">
         <f aca="false">IFERROR(IF(P53="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P53,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R53" s="10"/>
+      <c r="R53" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -7223,10 +7223,8 @@
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND(A4&lt;&gt;"",COUNTIF($A$4:$A$53,A4)&gt;1)</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B4:B53">
     <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>AND($A4&lt;&gt;"",ISNUMBER(VALUE(RIGHT($A4,2))),B4&lt;&gt;VALUE(RIGHT($A4,2)))</formula>
+      <formula>AND($A4&lt;&gt;"",OR(COUNTIFS(Caracterizacao!$A$4:$A$53,$A4,Caracterizacao!$B$4:$B$53,$B4)=0,COUNTIFS(Avaliacao_Regulatoria!$A$4:$A$53,$A4,Avaliacao_Regulatoria!$B$4:$B$53,$B4)=0))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="151">
@@ -7854,638 +7852,638 @@
   <dimension ref="A1:I53"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="30"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="9" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="C4" s="11" t="n">
+      <c r="C4" s="12" t="n">
         <v>46314.5069444445</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="11" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="9"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="9"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="9"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="9"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="9"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="9"/>
-      <c r="B19" s="10"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
-      <c r="I19" s="10"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="9"/>
-      <c r="B20" s="10"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="9"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="9"/>
-      <c r="B22" s="10"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="10"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="9"/>
-      <c r="B23" s="10"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
-      <c r="I23" s="10"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="9"/>
-      <c r="B24" s="10"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="10"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="9"/>
-      <c r="B25" s="10"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
-      <c r="I25" s="10"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="9"/>
-      <c r="B26" s="10"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
-      <c r="I26" s="10"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="9"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
-      <c r="I27" s="10"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="9"/>
-      <c r="B28" s="10"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
-      <c r="I28" s="10"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="9"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="10"/>
-      <c r="G29" s="10"/>
-      <c r="H29" s="10"/>
-      <c r="I29" s="10"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="9"/>
-      <c r="B30" s="10"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
-      <c r="I30" s="10"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="9"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="10"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="10"/>
-      <c r="I31" s="10"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="9"/>
-      <c r="B32" s="10"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="10"/>
-      <c r="I32" s="10"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="9"/>
-      <c r="B33" s="10"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="10"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10"/>
-      <c r="G33" s="10"/>
-      <c r="H33" s="10"/>
-      <c r="I33" s="10"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="9"/>
-      <c r="B34" s="10"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="10"/>
-      <c r="I34" s="10"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="9"/>
-      <c r="B35" s="10"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="10"/>
-      <c r="E35" s="10"/>
-      <c r="F35" s="10"/>
-      <c r="G35" s="10"/>
-      <c r="H35" s="10"/>
-      <c r="I35" s="10"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="9"/>
-      <c r="B36" s="10"/>
-      <c r="C36" s="11"/>
-      <c r="D36" s="10"/>
-      <c r="E36" s="10"/>
-      <c r="F36" s="10"/>
-      <c r="G36" s="10"/>
-      <c r="H36" s="10"/>
-      <c r="I36" s="10"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="9"/>
-      <c r="B37" s="10"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="10"/>
-      <c r="H37" s="10"/>
-      <c r="I37" s="10"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="9"/>
-      <c r="B38" s="10"/>
-      <c r="C38" s="11"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="10"/>
-      <c r="G38" s="10"/>
-      <c r="H38" s="10"/>
-      <c r="I38" s="10"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="9"/>
-      <c r="B39" s="10"/>
-      <c r="C39" s="11"/>
-      <c r="D39" s="10"/>
-      <c r="E39" s="10"/>
-      <c r="F39" s="10"/>
-      <c r="G39" s="10"/>
-      <c r="H39" s="10"/>
-      <c r="I39" s="10"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="9"/>
-      <c r="B40" s="10"/>
-      <c r="C40" s="11"/>
-      <c r="D40" s="10"/>
-      <c r="E40" s="10"/>
-      <c r="F40" s="10"/>
-      <c r="G40" s="10"/>
-      <c r="H40" s="10"/>
-      <c r="I40" s="10"/>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="9"/>
-      <c r="B41" s="10"/>
-      <c r="C41" s="11"/>
-      <c r="D41" s="10"/>
-      <c r="E41" s="10"/>
-      <c r="F41" s="10"/>
-      <c r="G41" s="10"/>
-      <c r="H41" s="10"/>
-      <c r="I41" s="10"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="9"/>
-      <c r="B42" s="10"/>
-      <c r="C42" s="11"/>
-      <c r="D42" s="10"/>
-      <c r="E42" s="10"/>
-      <c r="F42" s="10"/>
-      <c r="G42" s="10"/>
-      <c r="H42" s="10"/>
-      <c r="I42" s="10"/>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="9"/>
-      <c r="B43" s="10"/>
-      <c r="C43" s="11"/>
-      <c r="D43" s="10"/>
-      <c r="E43" s="10"/>
-      <c r="F43" s="10"/>
-      <c r="G43" s="10"/>
-      <c r="H43" s="10"/>
-      <c r="I43" s="10"/>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="9"/>
-      <c r="B44" s="10"/>
-      <c r="C44" s="11"/>
-      <c r="D44" s="10"/>
-      <c r="E44" s="10"/>
-      <c r="F44" s="10"/>
-      <c r="G44" s="10"/>
-      <c r="H44" s="10"/>
-      <c r="I44" s="10"/>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="9"/>
-      <c r="B45" s="10"/>
-      <c r="C45" s="11"/>
-      <c r="D45" s="10"/>
-      <c r="E45" s="10"/>
-      <c r="F45" s="10"/>
-      <c r="G45" s="10"/>
-      <c r="H45" s="10"/>
-      <c r="I45" s="10"/>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="9"/>
-      <c r="B46" s="10"/>
-      <c r="C46" s="11"/>
-      <c r="D46" s="10"/>
-      <c r="E46" s="10"/>
-      <c r="F46" s="10"/>
-      <c r="G46" s="10"/>
-      <c r="H46" s="10"/>
-      <c r="I46" s="10"/>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="9"/>
-      <c r="B47" s="10"/>
-      <c r="C47" s="11"/>
-      <c r="D47" s="10"/>
-      <c r="E47" s="10"/>
-      <c r="F47" s="10"/>
-      <c r="G47" s="10"/>
-      <c r="H47" s="10"/>
-      <c r="I47" s="10"/>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="9"/>
-      <c r="B48" s="10"/>
-      <c r="C48" s="11"/>
-      <c r="D48" s="10"/>
-      <c r="E48" s="10"/>
-      <c r="F48" s="10"/>
-      <c r="G48" s="10"/>
-      <c r="H48" s="10"/>
-      <c r="I48" s="10"/>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="9"/>
-      <c r="B49" s="10"/>
-      <c r="C49" s="11"/>
-      <c r="D49" s="10"/>
-      <c r="E49" s="10"/>
-      <c r="F49" s="10"/>
-      <c r="G49" s="10"/>
-      <c r="H49" s="10"/>
-      <c r="I49" s="10"/>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="9"/>
-      <c r="B50" s="10"/>
-      <c r="C50" s="11"/>
-      <c r="D50" s="10"/>
-      <c r="E50" s="10"/>
-      <c r="F50" s="10"/>
-      <c r="G50" s="10"/>
-      <c r="H50" s="10"/>
-      <c r="I50" s="10"/>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="9"/>
-      <c r="B51" s="10"/>
-      <c r="C51" s="11"/>
-      <c r="D51" s="10"/>
-      <c r="E51" s="10"/>
-      <c r="F51" s="10"/>
-      <c r="G51" s="10"/>
-      <c r="H51" s="10"/>
-      <c r="I51" s="10"/>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="9"/>
-      <c r="B52" s="10"/>
-      <c r="C52" s="11"/>
-      <c r="D52" s="10"/>
-      <c r="E52" s="10"/>
-      <c r="F52" s="10"/>
-      <c r="G52" s="10"/>
-      <c r="H52" s="10"/>
-      <c r="I52" s="10"/>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="9"/>
-      <c r="B53" s="10"/>
-      <c r="C53" s="11"/>
-      <c r="D53" s="10"/>
-      <c r="E53" s="10"/>
-      <c r="F53" s="10"/>
-      <c r="G53" s="10"/>
-      <c r="H53" s="10"/>
-      <c r="I53" s="10"/>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="10"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="10"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="10"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="10"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="10"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="10"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="10"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="10"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="10"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="10"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="10"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="10"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="10"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="10"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="10"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="10"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="10"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="10"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="10"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="10"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="10"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="10"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="10"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="10"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="10"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="10"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="10"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="10"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="10"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="10"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="10"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="11"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="10"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="11"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="10"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="11"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="10"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="12"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="11"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="10"/>
+      <c r="B39" s="11"/>
+      <c r="C39" s="12"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="11"/>
+      <c r="I39" s="11"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="10"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="12"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="11"/>
+      <c r="I40" s="11"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="10"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="11"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="11"/>
+      <c r="I41" s="11"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="10"/>
+      <c r="B42" s="11"/>
+      <c r="C42" s="12"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="11"/>
+      <c r="F42" s="11"/>
+      <c r="G42" s="11"/>
+      <c r="H42" s="11"/>
+      <c r="I42" s="11"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="10"/>
+      <c r="B43" s="11"/>
+      <c r="C43" s="12"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="11"/>
+      <c r="I43" s="11"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="10"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="12"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="11"/>
+      <c r="F44" s="11"/>
+      <c r="G44" s="11"/>
+      <c r="H44" s="11"/>
+      <c r="I44" s="11"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="10"/>
+      <c r="B45" s="11"/>
+      <c r="C45" s="12"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="11"/>
+      <c r="F45" s="11"/>
+      <c r="G45" s="11"/>
+      <c r="H45" s="11"/>
+      <c r="I45" s="11"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="10"/>
+      <c r="B46" s="11"/>
+      <c r="C46" s="12"/>
+      <c r="D46" s="11"/>
+      <c r="E46" s="11"/>
+      <c r="F46" s="11"/>
+      <c r="G46" s="11"/>
+      <c r="H46" s="11"/>
+      <c r="I46" s="11"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="10"/>
+      <c r="B47" s="11"/>
+      <c r="C47" s="12"/>
+      <c r="D47" s="11"/>
+      <c r="E47" s="11"/>
+      <c r="F47" s="11"/>
+      <c r="G47" s="11"/>
+      <c r="H47" s="11"/>
+      <c r="I47" s="11"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="10"/>
+      <c r="B48" s="11"/>
+      <c r="C48" s="12"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="11"/>
+      <c r="F48" s="11"/>
+      <c r="G48" s="11"/>
+      <c r="H48" s="11"/>
+      <c r="I48" s="11"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="10"/>
+      <c r="B49" s="11"/>
+      <c r="C49" s="12"/>
+      <c r="D49" s="11"/>
+      <c r="E49" s="11"/>
+      <c r="F49" s="11"/>
+      <c r="G49" s="11"/>
+      <c r="H49" s="11"/>
+      <c r="I49" s="11"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="10"/>
+      <c r="B50" s="11"/>
+      <c r="C50" s="12"/>
+      <c r="D50" s="11"/>
+      <c r="E50" s="11"/>
+      <c r="F50" s="11"/>
+      <c r="G50" s="11"/>
+      <c r="H50" s="11"/>
+      <c r="I50" s="11"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="10"/>
+      <c r="B51" s="11"/>
+      <c r="C51" s="12"/>
+      <c r="D51" s="11"/>
+      <c r="E51" s="11"/>
+      <c r="F51" s="11"/>
+      <c r="G51" s="11"/>
+      <c r="H51" s="11"/>
+      <c r="I51" s="11"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="10"/>
+      <c r="B52" s="11"/>
+      <c r="C52" s="12"/>
+      <c r="D52" s="11"/>
+      <c r="E52" s="11"/>
+      <c r="F52" s="11"/>
+      <c r="G52" s="11"/>
+      <c r="H52" s="11"/>
+      <c r="I52" s="11"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="10"/>
+      <c r="B53" s="11"/>
+      <c r="C53" s="12"/>
+      <c r="D53" s="11"/>
+      <c r="E53" s="11"/>
+      <c r="F53" s="11"/>
+      <c r="G53" s="11"/>
+      <c r="H53" s="11"/>
+      <c r="I53" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -8496,10 +8494,8 @@
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND(A4&lt;&gt;"",COUNTIF($A$4:$A$53,A4)&gt;1)</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B4:B53">
     <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>AND($A4&lt;&gt;"",ISNUMBER(VALUE(RIGHT($A4,2))),B4&lt;&gt;VALUE(RIGHT($A4,2)))</formula>
+      <formula>AND($A4&lt;&gt;"",OR(COUNTIFS(Caracterizacao!$A$4:$A$53,$A4,Caracterizacao!$B$4:$B$53,$B4)=0,COUNTIFS(Avaliacao_Regulatoria!$A$4:$A$53,$A4,Avaliacao_Regulatoria!$B$4:$B$53,$B4)=0,COUNTIFS(Decisao_Comunicacao!$A$4:$A$53,$A4,Decisao_Comunicacao!$B$4:$B$53,$B4)=0))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -8527,117 +8523,117 @@
   <dimension ref="A1:F10"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="1" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16" t="s">
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="18" t="s">
         <v>150</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="18" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="D6" s="21" t="s">
         <v>155</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="21" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="19" t="s">
         <v>157</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="21" t="s">
         <v>155</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="D7" s="21" t="s">
         <v>156</v>
       </c>
-      <c r="E7" s="21" t="s">
+      <c r="E7" s="22" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="19" t="s">
         <v>159</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="21" t="s">
         <v>155</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="21" t="s">
         <v>156</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="22" t="s">
         <v>158</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" s="22" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="22" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="23" t="s">
         <v>160</v>
       </c>
-      <c r="B10" s="22"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/instrumentos/exemplos/DAIR_Avaliacao_Riscos_Titulares_ANPD_v0.3_EXEMPLO-INC-2026-001.xlsx
+++ b/instrumentos/exemplos/DAIR_Avaliacao_Riscos_Titulares_ANPD_v0.3_EXEMPLO-INC-2026-001.xlsx
@@ -24,13 +24,13 @@
 </workbook>
 </file>
 
-<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <authors>
     <author>Unknown Author</author>
   </authors>
   <commentList>
-    <comment ref="D3" authorId="0">
+    <comment ref="A3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -38,7 +38,157 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Fórmula: data do marco de conhecimento + 3 dias úteis (função WORKDAY, sem considerar feriados). Agentes de pequeno porte têm prazo em dobro — ajustar manualmente quando aplicável.</t>
+          <t xml:space="preserve">ID manual e estável — A02/A03. Padrão AVR-NN. É esta ID (não a linha) que liga o mesmo registro de versão entre as quatro abas deste arquivo. Formatação condicional (A03): sinaliza em vermelho se a MESMA combinação ID+Versão não existir também em Avaliacao_Regulatoria e em Decisao_Comunicacao — reconciliação por existência cruzada, não por posição de linha nem por coincidência entre a ID e o número da versão.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Número da versão (1, 2, 3...). Não precisa coincidir com os dígitos da ID — a reconciliação entre abas é feita pela combinação ID+Versão (coluna A, nota ao lado), verificada por fórmula.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">ID manual e estável — A02/A03. A mesma combinação ID+Versão deve existir também em Caracterizacao e em Decisao_Comunicacao para a mesma versão — verificado por fórmula (A03), não por posição de linha.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Não trate a quantidade de titulares, isoladamente, como prova de dado financeiro ou de larga escala — fundamente separadamente cada um na coluna L (A08).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">'Larga escala' não tem limiar numérico definido no RCIS nem em orientação oficial da ANPD — fundamente qualitativamente (volume, abrangência, duração, proporção da base) na coluna L, sem usar um número de titulares como regra automática (A08).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Calculado a partir das colunas D a I (não editar). Atendida se qualquer inciso I a VI estiver marcado 'Sim' — corrige a redação anterior que citava apenas o inciso II (A05).</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">ID manual e estável — A02/A03. A mesma combinação ID+Versão deve existir também em Caracterizacao e em Avaliacao_Regulatoria — verificado por fórmula (A03).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Cálculo de apoio: WORKDAY(marco, 3 ou 6 dias úteis conforme pequeno porte) — NÃO considera feriados nacionais/municipais nem prazo setorial específico (A06). Não presume pequeno porte: use o campo de elegibilidade ao lado.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Campo que efetivamente vale. Preencha com fundamento, calendário de referência e responsável (colunas G a I) — não decorre apenas da fórmula de apoio.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Contado a partir da DATA DA COMUNICAÇÃO EFETIVAMENTE REALIZADA (coluna P), nunca de uma data apenas planejada (A06).</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">ID manual e estável — A02/A03. Registre aqui a ID DA VERSÃO DE CHEGADA (ex.: ao documentar a mudança de v1 para v2, a ID desta linha é AVR-02, igual à da mesma versão nas demais abas — não AVR-01). Formatação condicional (A03): sinaliza em vermelho se a combinação ID+Versão desta linha não existir nas três abas anteriores — é esse teste cruzado, e não a posição da linha nem os dígitos da ID, que comprova a reconciliação.</t>
         </r>
       </text>
     </comment>
@@ -47,7 +197,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="161">
   <si>
     <t xml:space="preserve">DAIR — Avaliação de Riscos aos Titulares e Decisão de Comunicação</t>
   </si>
@@ -70,7 +220,7 @@
     <t xml:space="preserve">Por que versões e não uma avaliação única</t>
   </si>
   <si>
-    <t xml:space="preserve">Novas evidências podem alterar a natureza dos dados, o universo de titulares ou as condições de risco. Cada vez que isso ocorrer, registre uma NOVA LINHA com a mesma ID da Avaliação e versão incrementada (v1, v2, v3...) em vez de sobrescrever a anterior. A aba Historico resume o que mudou entre versões.</t>
+    <t xml:space="preserve">Novas evidências podem alterar a natureza dos dados, o universo de titulares ou as condições de risco. Cada vez que isso ocorrer, registre uma NOVA LINHA com uma NOVA ID de avaliação (AVR-02, AVR-03...) em vez de sobrescrever a anterior. A aba Historico resume o que mudou entre versões.</t>
   </si>
   <si>
     <t xml:space="preserve">Regra central — leia antes de preencher</t>
@@ -79,16 +229,28 @@
     <t xml:space="preserve">Este instrumento NÃO calcula automaticamente se a comunicação é obrigatória. O campo 'Resultado da Avaliação' é preenchido manualmente pelo responsável pela análise e aprovado por quem tem autoridade para isso, com fundamentação registrada. Uma matriz de probabilidade e impacto está disponível na aba Matriz_Apoio apenas para priorização interna — ela não substitui os critérios jurídicos do art. 5º do RCIS e não deve ser citada como fundamento da decisão de comunicação.</t>
   </si>
   <si>
-    <t xml:space="preserve">As duas condições cumulativas (art. 5º do RCIS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Condição A: o incidente pode afetar significativamente interesses e direitos fundamentais dos titulares? Condição B: envolve ao menos uma categoria prevista no art. 5º, II (dados sensíveis; dados de crianças, adolescentes ou idosos; dados financeiros; dados de autenticação; dados sob sigilo legal/judicial/profissional; ou tratamento em larga escala, conforme §2º)? As duas condições são cumulativas — ambas devem estar fundamentadamente demonstradas.</t>
+    <t xml:space="preserve">As duas condições cumulativas (art. 5º, caput, do RCIS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Condição A: o incidente pode afetar significativamente interesses e direitos fundamentais dos titulares? Condição B: envolve, cumulativamente, ao menos uma das categorias dos incisos I a VI do art. 5º — I. dados pessoais sensíveis; II. dados de crianças, adolescentes ou idosos; III. dados financeiros; IV. dados de autenticação em sistemas; V. dados sob sigilo legal, judicial ou profissional; VI. tratamento em larga escala. As duas condições são cumulativas — ambas devem estar fundamentadamente demonstradas, e a presença de qualquer um dos seis incisos satisfaz a Condição B (não apenas o inciso II).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'Larga escala' e pequeno porte não têm limiar numérico automático</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O RCIS não define um número fixo de titulares como limiar de 'larga escala' (inciso VI), nem as orientações oficiais da ANPD trazem esse critério objetivo — a avaliação exige fundamentação qualitativa (volume, abrangência geográfica, duração, proporção da base), registrada na coluna correspondente. Da mesma forma, a condição de 'agente de tratamento de pequeno porte' (que dobra os prazos do art. 6º, §8º, e do art. 9º, §6º) não decorre do nome ou do tamanho aparente da organização — depende de enquadramento formal nos critérios da Resolução CD/ANPD nº 2/2022, a ser confirmado pelo Jurídico/Encarregado.</t>
   </si>
   <si>
     <t xml:space="preserve">Prazos (apoio, não substitui validação jurídica)</t>
   </si>
   <si>
-    <t xml:space="preserve">O prazo de comunicação à ANPD e aos titulares é de 3 dias úteis contados do marco de conhecimento pelo controlador (art. 6º, §1º e art. 9º, caput, do RCIS), dobrado para agentes de tratamento de pequeno porte. Complementações à ANPD têm prazo de até 20 dias úteis da comunicação (art. 6º, §3º). A fórmula de prazo nesta planilha usa dias úteis corridos simples e NÃO considera feriados nacionais, municipais ou regras específicas — sempre validar com o Jurídico.</t>
+    <t xml:space="preserve">O prazo de comunicação à ANPD e aos titulares é de 3 dias úteis contados do marco de conhecimento pelo controlador (art. 6º, §1º e art. 9º, caput, do RCIS). Complementações à ANPD têm prazo de até 20 dias úteis contados da comunicação EFETIVAMENTE REALIZADA (art. 6º, §3º) — nunca de uma data apenas planejada. A fórmula de prazo nesta planilha usa a função WORKDAY (dias úteis simples, sem feriados) e serve apenas de apoio; o prazo aplicável validado é um campo manual separado, com fundamento, calendário de referência e responsável pela validação.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marco de conhecimento e ampliação de escopo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quando uma nova versão apenas amplia o escopo de titulares/dados do MESMO incidente (sem criar um incidente novo), preserve o marco de conhecimento original na nova versão, a menos que haja fundamento específico para fixar um novo marco — documente a escolha na aba Historico. Um horário calculado como 00h00 de uma data (por exemplo, resultado de uma fórmula de apoio) nunca deve ser tratado como horário jurídico de vencimento do prazo.</t>
   </si>
   <si>
     <t xml:space="preserve">Resultados possíveis</t>
@@ -97,10 +259,10 @@
     <t xml:space="preserve">Avaliação pendente · Informações insuficientes · Condições regulatórias potencialmente atendidas · Condições regulatórias não demonstradas · Decisão fundamentada e aprovada. Nenhum desses resultados declara conformidade legal automaticamente — todos exigem fundamentação registrada nas colunas correspondentes.</t>
   </si>
   <si>
-    <t xml:space="preserve">Identificadores</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Use o padrão AVR-NN para a avaliação (uma ID por incidente, versões sucessivas) e mantenha o mesmo INC-AAAA-NNN do Instrumento 1. Referencie evidências (EVD-) e decisões (DEC-) registradas no Instrumento 1 sempre que aplicável.</t>
+    <t xml:space="preserve">Identificadores são manuais e estáveis — chave de reconciliação entre abas (correção A02/A03)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digite a mesma ID 'AVR-NN' E o mesmo número de Versão na coluna A/B das quatro abas (Caracterizacao, Avaliacao_Regulatoria, Decisao_Comunicacao e, na linha que registra a chegada a essa versão, Historico) — é essa combinação ID+Versão, e não a posição da linha nem os dígitos da ID, que relaciona os registros entre as abas. Mantenha o mesmo INC-AAAA-NNN do Instrumento 1. Referencie evidências (EVD-) e decisões (DEC-) registradas no Instrumento 1 sempre que aplicável. Uma formatação condicional em cada aba verifica, por fórmula (COUNTIFS cruzado), se a mesma combinação ID+Versão também existe nas demais abas relacionadas, e sinaliza em vermelho quando não existe — essa é a prova de reconciliação, não uma coincidência entre o número da ID e o número da versão.</t>
   </si>
   <si>
     <t xml:space="preserve">Retenção</t>
@@ -109,6 +271,12 @@
     <t xml:space="preserve">O art. 10 do RCIS exige registro de todos os incidentes com dados pessoais, inclusive os não comunicados, por no mínimo 5 anos. Preserve todas as versões desta avaliação, mesmo as substituídas.</t>
   </si>
   <si>
+    <t xml:space="preserve">O que a proteção de células NÃO garante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O destaque de células (amarelo/cinza) é um controle de usabilidade/consistência de preenchimento, não um controle de segurança da informação. A proteção de acesso, confidencialidade e integridade deste arquivo preenchido é de responsabilidade da organização (A11).</t>
+  </si>
+  <si>
     <t xml:space="preserve">Caracterização</t>
   </si>
   <si>
@@ -154,6 +322,9 @@
     <t xml:space="preserve">Grau de Certeza das Evidências</t>
   </si>
   <si>
+    <t xml:space="preserve">AVR-01</t>
+  </si>
+  <si>
     <t xml:space="preserve">1</t>
   </si>
   <si>
@@ -187,6 +358,9 @@
     <t xml:space="preserve">Confirmado</t>
   </si>
   <si>
+    <t xml:space="preserve">AVR-02</t>
+  </si>
+  <si>
     <t xml:space="preserve">2</t>
   </si>
   <si>
@@ -211,16 +385,34 @@
     <t xml:space="preserve">Avaliação Regulatória — Critérios Cumulativos do Art. 5º do RCIS</t>
   </si>
   <si>
-    <t xml:space="preserve">Condição A — Potencial de Afetação Significativa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Condição B — Categoria do Art. 5º, II, RCIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Categoria(s) Aplicável(is)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fundamentação das Duas Condições Cumulativas</t>
+    <t xml:space="preserve">Condição A — Potencial de Afetação Significativa (art. 5º, caput)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I — Dados Sensíveis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">II — Crianças/Adolescentes/Idosos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">III — Dados Financeiros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IV — Dados de Autenticação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V — Sigilo Legal/Judicial/Profissional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VI — Larga Escala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Condição B — Atendida? (algum inciso I a VI = Sim)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fundamentação da Condição A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fundamentação de Cada Inciso Assinalado (inclusive incertezas de 'larga escala')</t>
   </si>
   <si>
     <t xml:space="preserve">Evidências Utilizadas (IDs)</t>
@@ -232,7 +424,10 @@
     <t xml:space="preserve">Resultado da Avaliação</t>
   </si>
   <si>
-    <t xml:space="preserve">Necessidade de Aprofundamento</t>
+    <t xml:space="preserve">Estado da Análise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Necessidade de Aprofundamento Técnico (descrever o quê)</t>
   </si>
   <si>
     <t xml:space="preserve">Responsável pela Análise</t>
@@ -244,19 +439,28 @@
     <t xml:space="preserve">Em apuração</t>
   </si>
   <si>
-    <t xml:space="preserve">Apenas 200 registros confirmados; sem confirmação de exportação, redistribuição ou maior universo de titulares. Informação insuficiente para concluir pelas duas condições cumulativas do art. 5º do RCIS.</t>
+    <t xml:space="preserve">Não</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apenas 200 registros confirmados; sem confirmação de exportação, redistribuição ou maior universo de titulares — impacto significativo ainda não demonstrado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inciso II (crianças/adolescentes/idosos) em apuração: ainda não há confirmação de que titulares menores de idade estejam entre os 200 registros acessados. Demais incisos não identificados nesta versão.</t>
   </si>
   <si>
     <t xml:space="preserve">EVD-002</t>
   </si>
   <si>
-    <t xml:space="preserve">Extensão real do acesso; existência de exportação</t>
+    <t xml:space="preserve">Extensão real do acesso; existência de exportação; perfil etário dos titulares confirmados</t>
   </si>
   <si>
     <t xml:space="preserve">Informações insuficientes</t>
   </si>
   <si>
-    <t xml:space="preserve">Não — aprofundar Scope e monitorar prazo</t>
+    <t xml:space="preserve">Parecer em elaboração</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sim — aprofundar Scope (extensão do acesso) e confirmar perfil etário dos titulares antes de concluir o inciso II</t>
   </si>
   <si>
     <t xml:space="preserve">Encarregado/DPO</t>
@@ -268,22 +472,25 @@
     <t xml:space="preserve">Sim</t>
   </si>
   <si>
-    <t xml:space="preserve">Dados financeiros relacionados a pedidos; avaliação de tratamento em larga escala</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exportação confirmada de 30.000 registros distintos, incluindo dados de identificação e informações financeiras de pedidos, para fora do ambiente autorizado. Potencial de fraude e engenharia social direcionada com dados verdadeiros de compra. Presença de dados financeiros (art. 5º, II, RCIS) e tratamento em larga escala, sujeita a validação jurídica da extensão do conceito.</t>
+    <t xml:space="preserve">Exportação confirmada de 30.000 registros distintos, incluindo dados de identificação e informações financeiras de pedidos, para fora do ambiente autorizado. Potencial de fraude e engenharia social direcionada com dados verdadeiros de compra — afetação significativa demonstrada pela natureza financeira dos dados e pela escala da exposição.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">III (financeiro): os dados exportados incluem valores e datas de pedidos associados a identificação pessoal, aptos a viabilizar fraude — fundamento autônomo, independente da quantidade de titulares. VI (larga escala): 30.000 titulares distintos de uma base de ~180 mil clientes, exportados em uma única operação não autorizada — fundamentado pela combinação de volume absoluto, abrangência (toda a base de pedidos do período) e natureza não segmentada da exportação, não apenas pelo número isolado de titulares. II (crianças/adolescentes/idosos): permanece em apuração — a extração não permite segmentar por faixa etária sem análise adicional.</t>
   </si>
   <si>
     <t xml:space="preserve">EVD-004; EVD-006</t>
   </si>
   <si>
-    <t xml:space="preserve">Circulação e uso dos dados após a exportação permanecem desconhecidos</t>
+    <t xml:space="preserve">Circulação e uso dos dados após a exportação permanecem desconhecidos; perfil etário ainda não segmentado</t>
   </si>
   <si>
     <t xml:space="preserve">Condições regulatórias potencialmente atendidas</t>
   </si>
   <si>
-    <t xml:space="preserve">Sim — confirmar interpretação de 'larga escala' com o Jurídico</t>
+    <t xml:space="preserve">Análise aprovada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sim — confirmar classificação de 'larga escala' e o perfil etário (inciso II) com o Jurídico antes da autorização de envio</t>
   </si>
   <si>
     <t xml:space="preserve">Representante autorizado do controlador</t>
@@ -295,16 +502,31 @@
     <t xml:space="preserve">Marco de Conhecimento Aplicável</t>
   </si>
   <si>
-    <t xml:space="preserve">Prazo Regulatório (apoio — 3 dias úteis)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regras Específicas ou Exceções</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comunicação à ANPD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comunicação aos Titulares</t>
+    <t xml:space="preserve">Pequeno Porte — Elegibilidade (validar, não presumir)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Calculada de Apoio (WORKDAY, sem feriados)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prazo Aplicável Validado (manual)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fundamento da Validação do Prazo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calendário de Referência Utilizado (feriados considerados)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Responsável pela Validação do Prazo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regras Específicas ou Exceções (ressalva de prazo setorial)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comunicação à ANPD — Decisão</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comunicação aos Titulares — Decisão</t>
   </si>
   <si>
     <t xml:space="preserve">Fundamentação da Decisão</t>
@@ -316,51 +538,60 @@
     <t xml:space="preserve">Evidências de Aprovação (ID Decisão)</t>
   </si>
   <si>
-    <t xml:space="preserve">Estado das Comunicações</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Necessidade de Complementação</t>
+    <t xml:space="preserve">Data da Comunicação à ANPD Efetivamente Realizada (base da complementação)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Necessidade de Complementação (até 20 dias úteis da comunicação efetiva)</t>
   </si>
   <si>
     <t xml:space="preserve">Reavaliações Posteriores</t>
   </si>
   <si>
+    <t xml:space="preserve">Não avaliado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prazo não fixado nesta versão — avaliação ainda em apuração (ver Avaliacao_Regulatoria, AVR-01).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Não aplicável nesta versão</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nenhuma exceção identificada nesta versão</t>
   </si>
   <si>
     <t xml:space="preserve">Pendente de decisão</t>
   </si>
   <si>
-    <t xml:space="preserve">Informação insuficiente para decidir; aguardar aprofundamento do Scope</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Não aplicável</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Não</t>
+    <t xml:space="preserve">Informação insuficiente para decidir; aguardar aprofundamento do Scope e do perfil etário dos titulares</t>
   </si>
   <si>
     <t xml:space="preserve">Sim — ver versão 2</t>
   </si>
   <si>
+    <t xml:space="preserve">Não elegível</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 dias úteis a partir do marco de conhecimento de 19/10/2026 (mantido da versão 1 — a versão 2 apenas amplia o escopo do mesmo incidente, não reinicia o prazo). Agente não enquadrado como pequeno porte neste exercício.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calendário nacional de feriados 2026 (nenhum feriado no intervalo 19–22/10/2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jurídico</t>
+  </si>
+  <si>
     <t xml:space="preserve">Agente de tratamento não é de pequeno porte neste exercício; prazo simples de 3 dias úteis</t>
   </si>
   <si>
     <t xml:space="preserve">Decidido: comunicar</t>
   </si>
   <si>
-    <t xml:space="preserve">Condições cumulativas do art. 5º do RCIS consideradas atendidas: potencial de afetação significativa e presença de categoria (dados financeiros / larga escala). Decisão sujeita à validação jurídica final antes do protocolo.</t>
+    <t xml:space="preserve">Condições cumulativas do art. 5º do RCIS consideradas atendidas: potencial de afetação significativa (Condição A) e presença dos incisos III (dados financeiros) e VI (larga escala) da Condição B, fundamentados separadamente na avaliação AVR-02. Decisão sujeita à validação jurídica final antes do protocolo.</t>
   </si>
   <si>
     <t xml:space="preserve">DEC-003</t>
   </si>
   <si>
-    <t xml:space="preserve">Planejada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Não identificada nesta versão</t>
-  </si>
-  <si>
     <t xml:space="preserve">Não — versão vigente</t>
   </si>
   <si>
@@ -388,19 +619,19 @@
     <t xml:space="preserve">Exportação de 30.000 registros confirmada (E04-E06)</t>
   </si>
   <si>
-    <t xml:space="preserve">Ampliado de 200 registros para 30.000 titulares distintos</t>
+    <t xml:space="preserve">Ampliado de 200 registros para 30.000 titulares distintos, mantendo o mesmo incidente e o mesmo marco de conhecimento (19/10/2026 09h25)</t>
   </si>
   <si>
     <t xml:space="preserve">Elevado de 'informação insuficiente' para 'condições potencialmente atendidas'</t>
   </si>
   <si>
-    <t xml:space="preserve">Avaliação pendente (v1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Condições regulatórias potencialmente atendidas (v2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nova evidência alterou substancialmente a natureza e a extensão do incidente, exigindo reabertura da avaliação conforme regra de atualização do instrumento</t>
+    <t xml:space="preserve">Informações insuficientes (AVR-01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Condições regulatórias potencialmente atendidas (AVR-02)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nova evidência alterou substancialmente a natureza e a extensão do incidente, exigindo reabertura da avaliação conforme regra de atualização do instrumento. A ID desta linha (AVR-02) corresponde à versão de chegada, consistente com as demais abas para esta mesma versão.</t>
   </si>
   <si>
     <t xml:space="preserve">Matriz de Probabilidade x Impacto — Apoio à Priorização</t>
@@ -573,14 +804,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEDEDED"/>
-        <bgColor rgb="FFE2EFDA"/>
+        <fgColor rgb="FFFFFDE7"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFDE7"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFEDEDED"/>
+        <bgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -651,92 +882,100 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -749,6 +988,15 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDE9E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -992,7 +1240,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="38"/>
@@ -1081,6 +1329,30 @@
       </c>
       <c r="B11" s="7" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1103,7 +1375,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
@@ -1121,7 +1393,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1138,7 +1410,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -1155,137 +1427,132 @@
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="str">
-        <f aca="false">IF(E4="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v>AVR-01</v>
+      <c r="A4" s="10" t="s">
+        <v>41</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D4" s="12" t="n">
         <v>46314.3923611111</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="K4" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="L4" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="M4" s="11" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="11" t="s">
         <v>43</v>
-      </c>
-      <c r="L4" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="M4" s="11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="str">
-        <f aca="false">IF(E5="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v>AVR-02</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>36</v>
       </c>
       <c r="D5" s="12" t="n">
         <v>46314.5069444445</v>
       </c>
       <c r="E5" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="H5" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="F5" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="G5" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>40</v>
-      </c>
       <c r="I5" s="11" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="L5" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M5" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="M5" s="11" t="s">
-        <v>45</v>
-      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="str">
-        <f aca="false">IF(E6="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
+      <c r="A6" s="10"/>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
+      <c r="D6" s="12"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
@@ -1297,13 +1564,10 @@
       <c r="M6" s="11"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="str">
-        <f aca="false">IF(E7="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
+      <c r="A7" s="10"/>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
+      <c r="D7" s="12"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="11"/>
@@ -1315,13 +1579,10 @@
       <c r="M7" s="11"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10" t="str">
-        <f aca="false">IF(E8="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
+      <c r="A8" s="10"/>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
+      <c r="D8" s="12"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
@@ -1333,13 +1594,10 @@
       <c r="M8" s="11"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="str">
-        <f aca="false">IF(E9="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
+      <c r="A9" s="10"/>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
+      <c r="D9" s="12"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="11"/>
@@ -1351,13 +1609,10 @@
       <c r="M9" s="11"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10" t="str">
-        <f aca="false">IF(E10="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
+      <c r="A10" s="10"/>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
+      <c r="D10" s="12"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="11"/>
@@ -1369,13 +1624,10 @@
       <c r="M10" s="11"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10" t="str">
-        <f aca="false">IF(E11="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
+      <c r="A11" s="10"/>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
+      <c r="D11" s="12"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="11"/>
@@ -1387,13 +1639,10 @@
       <c r="M11" s="11"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10" t="str">
-        <f aca="false">IF(E12="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
+      <c r="A12" s="10"/>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
+      <c r="D12" s="12"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="11"/>
@@ -1405,13 +1654,10 @@
       <c r="M12" s="11"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10" t="str">
-        <f aca="false">IF(E13="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
+      <c r="A13" s="10"/>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
+      <c r="D13" s="12"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="11"/>
@@ -1423,13 +1669,10 @@
       <c r="M13" s="11"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10" t="str">
-        <f aca="false">IF(E14="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
+      <c r="A14" s="10"/>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
+      <c r="D14" s="12"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="11"/>
@@ -1441,13 +1684,10 @@
       <c r="M14" s="11"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10" t="str">
-        <f aca="false">IF(E15="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
+      <c r="A15" s="10"/>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
+      <c r="D15" s="12"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="11"/>
@@ -1459,13 +1699,10 @@
       <c r="M15" s="11"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10" t="str">
-        <f aca="false">IF(E16="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
+      <c r="A16" s="10"/>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
+      <c r="D16" s="12"/>
       <c r="E16" s="11"/>
       <c r="F16" s="11"/>
       <c r="G16" s="11"/>
@@ -1477,13 +1714,10 @@
       <c r="M16" s="11"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10" t="str">
-        <f aca="false">IF(E17="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
+      <c r="A17" s="10"/>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
+      <c r="D17" s="12"/>
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
       <c r="G17" s="11"/>
@@ -1495,13 +1729,10 @@
       <c r="M17" s="11"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10" t="str">
-        <f aca="false">IF(E18="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
+      <c r="A18" s="10"/>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
+      <c r="D18" s="12"/>
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
       <c r="G18" s="11"/>
@@ -1513,13 +1744,10 @@
       <c r="M18" s="11"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10" t="str">
-        <f aca="false">IF(E19="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
+      <c r="A19" s="10"/>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
+      <c r="D19" s="12"/>
       <c r="E19" s="11"/>
       <c r="F19" s="11"/>
       <c r="G19" s="11"/>
@@ -1530,74 +1758,732 @@
       <c r="L19" s="11"/>
       <c r="M19" s="11"/>
     </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="10"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="11"/>
+      <c r="M20" s="11"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="10"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="10"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="11"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="10"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="11"/>
+      <c r="M23" s="11"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="10"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="11"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="11"/>
+      <c r="M24" s="11"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="10"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="11"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="10"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="11"/>
+      <c r="K26" s="11"/>
+      <c r="L26" s="11"/>
+      <c r="M26" s="11"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="10"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
+      <c r="M27" s="11"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="10"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
+      <c r="J28" s="11"/>
+      <c r="K28" s="11"/>
+      <c r="L28" s="11"/>
+      <c r="M28" s="11"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="10"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11"/>
+      <c r="L29" s="11"/>
+      <c r="M29" s="11"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="10"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
+      <c r="J30" s="11"/>
+      <c r="K30" s="11"/>
+      <c r="L30" s="11"/>
+      <c r="M30" s="11"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="10"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="11"/>
+      <c r="L31" s="11"/>
+      <c r="M31" s="11"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="10"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
+      <c r="M32" s="11"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="10"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="11"/>
+      <c r="K33" s="11"/>
+      <c r="L33" s="11"/>
+      <c r="M33" s="11"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="10"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
+      <c r="J34" s="11"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
+      <c r="M34" s="11"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="10"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="11"/>
+      <c r="J35" s="11"/>
+      <c r="K35" s="11"/>
+      <c r="L35" s="11"/>
+      <c r="M35" s="11"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="10"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="11"/>
+      <c r="J36" s="11"/>
+      <c r="K36" s="11"/>
+      <c r="L36" s="11"/>
+      <c r="M36" s="11"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="10"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="11"/>
+      <c r="J37" s="11"/>
+      <c r="K37" s="11"/>
+      <c r="L37" s="11"/>
+      <c r="M37" s="11"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="10"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="11"/>
+      <c r="J38" s="11"/>
+      <c r="K38" s="11"/>
+      <c r="L38" s="11"/>
+      <c r="M38" s="11"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="10"/>
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="11"/>
+      <c r="I39" s="11"/>
+      <c r="J39" s="11"/>
+      <c r="K39" s="11"/>
+      <c r="L39" s="11"/>
+      <c r="M39" s="11"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="10"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="11"/>
+      <c r="I40" s="11"/>
+      <c r="J40" s="11"/>
+      <c r="K40" s="11"/>
+      <c r="L40" s="11"/>
+      <c r="M40" s="11"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="10"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="11"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="11"/>
+      <c r="I41" s="11"/>
+      <c r="J41" s="11"/>
+      <c r="K41" s="11"/>
+      <c r="L41" s="11"/>
+      <c r="M41" s="11"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="10"/>
+      <c r="B42" s="11"/>
+      <c r="C42" s="11"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="11"/>
+      <c r="F42" s="11"/>
+      <c r="G42" s="11"/>
+      <c r="H42" s="11"/>
+      <c r="I42" s="11"/>
+      <c r="J42" s="11"/>
+      <c r="K42" s="11"/>
+      <c r="L42" s="11"/>
+      <c r="M42" s="11"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="10"/>
+      <c r="B43" s="11"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="11"/>
+      <c r="I43" s="11"/>
+      <c r="J43" s="11"/>
+      <c r="K43" s="11"/>
+      <c r="L43" s="11"/>
+      <c r="M43" s="11"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="10"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="12"/>
+      <c r="E44" s="11"/>
+      <c r="F44" s="11"/>
+      <c r="G44" s="11"/>
+      <c r="H44" s="11"/>
+      <c r="I44" s="11"/>
+      <c r="J44" s="11"/>
+      <c r="K44" s="11"/>
+      <c r="L44" s="11"/>
+      <c r="M44" s="11"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="10"/>
+      <c r="B45" s="11"/>
+      <c r="C45" s="11"/>
+      <c r="D45" s="12"/>
+      <c r="E45" s="11"/>
+      <c r="F45" s="11"/>
+      <c r="G45" s="11"/>
+      <c r="H45" s="11"/>
+      <c r="I45" s="11"/>
+      <c r="J45" s="11"/>
+      <c r="K45" s="11"/>
+      <c r="L45" s="11"/>
+      <c r="M45" s="11"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="10"/>
+      <c r="B46" s="11"/>
+      <c r="C46" s="11"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="11"/>
+      <c r="F46" s="11"/>
+      <c r="G46" s="11"/>
+      <c r="H46" s="11"/>
+      <c r="I46" s="11"/>
+      <c r="J46" s="11"/>
+      <c r="K46" s="11"/>
+      <c r="L46" s="11"/>
+      <c r="M46" s="11"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="10"/>
+      <c r="B47" s="11"/>
+      <c r="C47" s="11"/>
+      <c r="D47" s="12"/>
+      <c r="E47" s="11"/>
+      <c r="F47" s="11"/>
+      <c r="G47" s="11"/>
+      <c r="H47" s="11"/>
+      <c r="I47" s="11"/>
+      <c r="J47" s="11"/>
+      <c r="K47" s="11"/>
+      <c r="L47" s="11"/>
+      <c r="M47" s="11"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="10"/>
+      <c r="B48" s="11"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="12"/>
+      <c r="E48" s="11"/>
+      <c r="F48" s="11"/>
+      <c r="G48" s="11"/>
+      <c r="H48" s="11"/>
+      <c r="I48" s="11"/>
+      <c r="J48" s="11"/>
+      <c r="K48" s="11"/>
+      <c r="L48" s="11"/>
+      <c r="M48" s="11"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="10"/>
+      <c r="B49" s="11"/>
+      <c r="C49" s="11"/>
+      <c r="D49" s="12"/>
+      <c r="E49" s="11"/>
+      <c r="F49" s="11"/>
+      <c r="G49" s="11"/>
+      <c r="H49" s="11"/>
+      <c r="I49" s="11"/>
+      <c r="J49" s="11"/>
+      <c r="K49" s="11"/>
+      <c r="L49" s="11"/>
+      <c r="M49" s="11"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="10"/>
+      <c r="B50" s="11"/>
+      <c r="C50" s="11"/>
+      <c r="D50" s="12"/>
+      <c r="E50" s="11"/>
+      <c r="F50" s="11"/>
+      <c r="G50" s="11"/>
+      <c r="H50" s="11"/>
+      <c r="I50" s="11"/>
+      <c r="J50" s="11"/>
+      <c r="K50" s="11"/>
+      <c r="L50" s="11"/>
+      <c r="M50" s="11"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="10"/>
+      <c r="B51" s="11"/>
+      <c r="C51" s="11"/>
+      <c r="D51" s="12"/>
+      <c r="E51" s="11"/>
+      <c r="F51" s="11"/>
+      <c r="G51" s="11"/>
+      <c r="H51" s="11"/>
+      <c r="I51" s="11"/>
+      <c r="J51" s="11"/>
+      <c r="K51" s="11"/>
+      <c r="L51" s="11"/>
+      <c r="M51" s="11"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="10"/>
+      <c r="B52" s="11"/>
+      <c r="C52" s="11"/>
+      <c r="D52" s="12"/>
+      <c r="E52" s="11"/>
+      <c r="F52" s="11"/>
+      <c r="G52" s="11"/>
+      <c r="H52" s="11"/>
+      <c r="I52" s="11"/>
+      <c r="J52" s="11"/>
+      <c r="K52" s="11"/>
+      <c r="L52" s="11"/>
+      <c r="M52" s="11"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="10"/>
+      <c r="B53" s="11"/>
+      <c r="C53" s="11"/>
+      <c r="D53" s="12"/>
+      <c r="E53" s="11"/>
+      <c r="F53" s="11"/>
+      <c r="G53" s="11"/>
+      <c r="H53" s="11"/>
+      <c r="I53" s="11"/>
+      <c r="J53" s="11"/>
+      <c r="K53" s="11"/>
+      <c r="L53" s="11"/>
+      <c r="M53" s="11"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A2:M2"/>
   </mergeCells>
-  <dataValidations count="16">
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M4" type="list">
+  <conditionalFormatting sqref="A4:A53">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>AND(A4&lt;&gt;"",COUNTIF($A$4:$A$53,A4)&gt;1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>AND($A4&lt;&gt;"",OR(COUNTIFS(Avaliacao_Regulatoria!$A$4:$A$53,$A4,Avaliacao_Regulatoria!$B$4:$B$53,$B4)=0,COUNTIFS(Decisao_Comunicacao!$A$4:$A$53,$A4,Decisao_Comunicacao!$B$4:$B$53,$B4)=0))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="51">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M4" type="list">
       <formula1>"Confirmado,Hipótese,Inferido,Desconhecido,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M5" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M5" type="list">
       <formula1>"Confirmado,Hipótese,Inferido,Desconhecido,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M6" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M6" type="list">
       <formula1>"Confirmado,Hipótese,Inferido,Desconhecido,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M7" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M7" type="list">
       <formula1>"Confirmado,Hipótese,Inferido,Desconhecido,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M8" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M8" type="list">
       <formula1>"Confirmado,Hipótese,Inferido,Desconhecido,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M9" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M9" type="list">
       <formula1>"Confirmado,Hipótese,Inferido,Desconhecido,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M10" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M10" type="list">
       <formula1>"Confirmado,Hipótese,Inferido,Desconhecido,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M11" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M11" type="list">
       <formula1>"Confirmado,Hipótese,Inferido,Desconhecido,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M12" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M12" type="list">
       <formula1>"Confirmado,Hipótese,Inferido,Desconhecido,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M13" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M13" type="list">
       <formula1>"Confirmado,Hipótese,Inferido,Desconhecido,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M14" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M14" type="list">
       <formula1>"Confirmado,Hipótese,Inferido,Desconhecido,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M15" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M15" type="list">
       <formula1>"Confirmado,Hipótese,Inferido,Desconhecido,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M16" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M16" type="list">
       <formula1>"Confirmado,Hipótese,Inferido,Desconhecido,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M17" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M17" type="list">
       <formula1>"Confirmado,Hipótese,Inferido,Desconhecido,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M18" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M18" type="list">
       <formula1>"Confirmado,Hipótese,Inferido,Desconhecido,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M19" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M19" type="list">
       <formula1>"Confirmado,Hipótese,Inferido,Desconhecido,Não aplicável"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M20" type="list">
+      <formula1>"Confirmado,Hipótese,Inferido,Desconhecido,Não aplicável"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M21" type="list">
+      <formula1>"Confirmado,Hipótese,Inferido,Desconhecido,Não aplicável"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M22" type="list">
+      <formula1>"Confirmado,Hipótese,Inferido,Desconhecido,Não aplicável"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M23" type="list">
+      <formula1>"Confirmado,Hipótese,Inferido,Desconhecido,Não aplicável"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M24" type="list">
+      <formula1>"Confirmado,Hipótese,Inferido,Desconhecido,Não aplicável"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M25" type="list">
+      <formula1>"Confirmado,Hipótese,Inferido,Desconhecido,Não aplicável"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M26" type="list">
+      <formula1>"Confirmado,Hipótese,Inferido,Desconhecido,Não aplicável"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M27" type="list">
+      <formula1>"Confirmado,Hipótese,Inferido,Desconhecido,Não aplicável"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M28" type="list">
+      <formula1>"Confirmado,Hipótese,Inferido,Desconhecido,Não aplicável"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M29" type="list">
+      <formula1>"Confirmado,Hipótese,Inferido,Desconhecido,Não aplicável"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M30" type="list">
+      <formula1>"Confirmado,Hipótese,Inferido,Desconhecido,Não aplicável"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M31" type="list">
+      <formula1>"Confirmado,Hipótese,Inferido,Desconhecido,Não aplicável"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M32" type="list">
+      <formula1>"Confirmado,Hipótese,Inferido,Desconhecido,Não aplicável"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M33" type="list">
+      <formula1>"Confirmado,Hipótese,Inferido,Desconhecido,Não aplicável"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M34" type="list">
+      <formula1>"Confirmado,Hipótese,Inferido,Desconhecido,Não aplicável"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M35" type="list">
+      <formula1>"Confirmado,Hipótese,Inferido,Desconhecido,Não aplicável"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M36" type="list">
+      <formula1>"Confirmado,Hipótese,Inferido,Desconhecido,Não aplicável"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M37" type="list">
+      <formula1>"Confirmado,Hipótese,Inferido,Desconhecido,Não aplicável"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M38" type="list">
+      <formula1>"Confirmado,Hipótese,Inferido,Desconhecido,Não aplicável"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M39" type="list">
+      <formula1>"Confirmado,Hipótese,Inferido,Desconhecido,Não aplicável"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M40" type="list">
+      <formula1>"Confirmado,Hipótese,Inferido,Desconhecido,Não aplicável"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M41" type="list">
+      <formula1>"Confirmado,Hipótese,Inferido,Desconhecido,Não aplicável"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M42" type="list">
+      <formula1>"Confirmado,Hipótese,Inferido,Desconhecido,Não aplicável"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M43" type="list">
+      <formula1>"Confirmado,Hipótese,Inferido,Desconhecido,Não aplicável"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M44" type="list">
+      <formula1>"Confirmado,Hipótese,Inferido,Desconhecido,Não aplicável"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M45" type="list">
+      <formula1>"Confirmado,Hipótese,Inferido,Desconhecido,Não aplicável"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M46" type="list">
+      <formula1>"Confirmado,Hipótese,Inferido,Desconhecido,Não aplicável"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M47" type="list">
+      <formula1>"Confirmado,Hipótese,Inferido,Desconhecido,Não aplicável"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M48" type="list">
+      <formula1>"Confirmado,Hipótese,Inferido,Desconhecido,Não aplicável"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M49" type="list">
+      <formula1>"Confirmado,Hipótese,Inferido,Desconhecido,Não aplicável"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M50" type="list">
+      <formula1>"Confirmado,Hipótese,Inferido,Desconhecido,Não aplicável"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M51" type="list">
+      <formula1>"Confirmado,Hipótese,Inferido,Desconhecido,Não aplicável"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M52" type="list">
+      <formula1>"Confirmado,Hipótese,Inferido,Desconhecido,Não aplicável"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M53" type="list">
+      <formula1>"Confirmado,Hipótese,Inferido,Desconhecido,Não aplicável"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Este identificador já existe nesta coluna. Cada ID deve ser único e estável (não reutilize nem renumere IDs já atribuídos). Padrão esperado: AVR-01." errorStyle="stop" errorTitle="ID duplicado" operator="between" prompt="Digite um identificador único e estável, padrão AVR-01. Não é gerado automaticamente — preserve o mesmo ID após inserir, excluir ou reordenar linhas." promptTitle="Identificador manual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A4:A53" type="custom">
+      <formula1>OR(A4="",COUNTIF($A$4:$A$53,A4)&lt;=1)</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -1608,6 +2494,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -1616,703 +2503,31 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:S53"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="18" style="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-    </row>
-    <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="J3" s="9" t="s">
         <v>61</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="L3" s="9" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="str">
-        <f aca="false">IF(F4="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v>AVR-01</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="J4" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="K4" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L4" s="11" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="str">
-        <f aca="false">IF(F5="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v>AVR-02</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="G5" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="K5" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L5" s="11" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="str">
-        <f aca="false">IF(F6="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="str">
-        <f aca="false">IF(F7="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10" t="str">
-        <f aca="false">IF(F8="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="str">
-        <f aca="false">IF(F9="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="11"/>
-      <c r="L9" s="11"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10" t="str">
-        <f aca="false">IF(F10="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10" t="str">
-        <f aca="false">IF(F11="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10" t="str">
-        <f aca="false">IF(F12="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10" t="str">
-        <f aca="false">IF(F13="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10" t="str">
-        <f aca="false">IF(F14="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10" t="str">
-        <f aca="false">IF(F15="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10" t="str">
-        <f aca="false">IF(F16="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10" t="str">
-        <f aca="false">IF(F17="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10" t="str">
-        <f aca="false">IF(F18="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10" t="str">
-        <f aca="false">IF(F19="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
-      <c r="J19" s="11"/>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
-  </mergeCells>
-  <dataValidations count="64">
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C4" type="list">
-      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D4" type="list">
-      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E4" type="list">
-      <formula1>"Dados sensíveis,Dados de crianças/adolescentes/idosos,Dados financeiros,Dados de autenticação,Dados sob sigilo legal/judicial/profissional,Tratamento em larga escala,Nenhuma identificada,Em apuração"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I4" type="list">
-      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C5" type="list">
-      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D5" type="list">
-      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E5" type="list">
-      <formula1>"Dados sensíveis,Dados de crianças/adolescentes/idosos,Dados financeiros,Dados de autenticação,Dados sob sigilo legal/judicial/profissional,Tratamento em larga escala,Nenhuma identificada,Em apuração"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I5" type="list">
-      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C6" type="list">
-      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D6" type="list">
-      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E6" type="list">
-      <formula1>"Dados sensíveis,Dados de crianças/adolescentes/idosos,Dados financeiros,Dados de autenticação,Dados sob sigilo legal/judicial/profissional,Tratamento em larga escala,Nenhuma identificada,Em apuração"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I6" type="list">
-      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C7" type="list">
-      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D7" type="list">
-      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E7" type="list">
-      <formula1>"Dados sensíveis,Dados de crianças/adolescentes/idosos,Dados financeiros,Dados de autenticação,Dados sob sigilo legal/judicial/profissional,Tratamento em larga escala,Nenhuma identificada,Em apuração"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I7" type="list">
-      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C8" type="list">
-      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D8" type="list">
-      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E8" type="list">
-      <formula1>"Dados sensíveis,Dados de crianças/adolescentes/idosos,Dados financeiros,Dados de autenticação,Dados sob sigilo legal/judicial/profissional,Tratamento em larga escala,Nenhuma identificada,Em apuração"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I8" type="list">
-      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C9" type="list">
-      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D9" type="list">
-      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E9" type="list">
-      <formula1>"Dados sensíveis,Dados de crianças/adolescentes/idosos,Dados financeiros,Dados de autenticação,Dados sob sigilo legal/judicial/profissional,Tratamento em larga escala,Nenhuma identificada,Em apuração"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I9" type="list">
-      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C10" type="list">
-      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D10" type="list">
-      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E10" type="list">
-      <formula1>"Dados sensíveis,Dados de crianças/adolescentes/idosos,Dados financeiros,Dados de autenticação,Dados sob sigilo legal/judicial/profissional,Tratamento em larga escala,Nenhuma identificada,Em apuração"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I10" type="list">
-      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C11" type="list">
-      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D11" type="list">
-      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E11" type="list">
-      <formula1>"Dados sensíveis,Dados de crianças/adolescentes/idosos,Dados financeiros,Dados de autenticação,Dados sob sigilo legal/judicial/profissional,Tratamento em larga escala,Nenhuma identificada,Em apuração"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I11" type="list">
-      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C12" type="list">
-      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D12" type="list">
-      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E12" type="list">
-      <formula1>"Dados sensíveis,Dados de crianças/adolescentes/idosos,Dados financeiros,Dados de autenticação,Dados sob sigilo legal/judicial/profissional,Tratamento em larga escala,Nenhuma identificada,Em apuração"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I12" type="list">
-      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C13" type="list">
-      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D13" type="list">
-      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E13" type="list">
-      <formula1>"Dados sensíveis,Dados de crianças/adolescentes/idosos,Dados financeiros,Dados de autenticação,Dados sob sigilo legal/judicial/profissional,Tratamento em larga escala,Nenhuma identificada,Em apuração"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I13" type="list">
-      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C14" type="list">
-      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D14" type="list">
-      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E14" type="list">
-      <formula1>"Dados sensíveis,Dados de crianças/adolescentes/idosos,Dados financeiros,Dados de autenticação,Dados sob sigilo legal/judicial/profissional,Tratamento em larga escala,Nenhuma identificada,Em apuração"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I14" type="list">
-      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C15" type="list">
-      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D15" type="list">
-      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E15" type="list">
-      <formula1>"Dados sensíveis,Dados de crianças/adolescentes/idosos,Dados financeiros,Dados de autenticação,Dados sob sigilo legal/judicial/profissional,Tratamento em larga escala,Nenhuma identificada,Em apuração"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I15" type="list">
-      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C16" type="list">
-      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D16" type="list">
-      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E16" type="list">
-      <formula1>"Dados sensíveis,Dados de crianças/adolescentes/idosos,Dados financeiros,Dados de autenticação,Dados sob sigilo legal/judicial/profissional,Tratamento em larga escala,Nenhuma identificada,Em apuração"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I16" type="list">
-      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C17" type="list">
-      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D17" type="list">
-      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E17" type="list">
-      <formula1>"Dados sensíveis,Dados de crianças/adolescentes/idosos,Dados financeiros,Dados de autenticação,Dados sob sigilo legal/judicial/profissional,Tratamento em larga escala,Nenhuma identificada,Em apuração"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I17" type="list">
-      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C18" type="list">
-      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D18" type="list">
-      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E18" type="list">
-      <formula1>"Dados sensíveis,Dados de crianças/adolescentes/idosos,Dados financeiros,Dados de autenticação,Dados sob sigilo legal/judicial/profissional,Tratamento em larga escala,Nenhuma identificada,Em apuração"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I18" type="list">
-      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C19" type="list">
-      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D19" type="list">
-      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E19" type="list">
-      <formula1>"Dados sensíveis,Dados de crianças/adolescentes/idosos,Dados financeiros,Dados de autenticação,Dados sob sigilo legal/judicial/profissional,Tratamento em larga escala,Nenhuma identificada,Em apuração"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I19" type="list">
-      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:M19"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="1" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="1" width="22"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>80</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2326,10 +2541,16 @@
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -2343,145 +2564,3418 @@
       <c r="K2" s="8"/>
       <c r="L2" s="8"/>
       <c r="M2" s="8"/>
+      <c r="N2" s="8"/>
+      <c r="O2" s="8"/>
+      <c r="P2" s="8"/>
+      <c r="Q2" s="8"/>
+      <c r="R2" s="8"/>
+      <c r="S2" s="8"/>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C3" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="N3" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="O3" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="P3" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q3" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="R3" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="S3" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="J4" s="11" t="str">
+        <f aca="false">IF(COUNTIF(D4:I4,"Sim")&gt;0,"Sim",IF(COUNTIF(D4:I4,"Em apuração")&gt;0,"Em apuração","Não"))</f>
+        <v>Em apuração</v>
+      </c>
+      <c r="K4" s="11" t="s">
         <v>81</v>
       </c>
+      <c r="L4" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="M4" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="N4" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="O4" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="P4" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q4" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="R4" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="S4" s="11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="J5" s="11" t="str">
+        <f aca="false">IF(COUNTIF(D5:I5,"Sim")&gt;0,"Sim",IF(COUNTIF(D5:I5,"Em apuração")&gt;0,"Em apuração","Não"))</f>
+        <v>Sim</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="L5" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="M5" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="N5" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="O5" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="P5" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q5" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="R5" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="S5" s="11" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="10"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11" t="str">
+        <f aca="false">IF(COUNTIF(D6:I6,"Sim")&gt;0,"Sim",IF(COUNTIF(D6:I6,"Em apuração")&gt;0,"Em apuração","Não"))</f>
+        <v>Não</v>
+      </c>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="11"/>
+      <c r="O6" s="11"/>
+      <c r="P6" s="11"/>
+      <c r="Q6" s="11"/>
+      <c r="R6" s="11"/>
+      <c r="S6" s="11"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="10"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11" t="str">
+        <f aca="false">IF(COUNTIF(D7:I7,"Sim")&gt;0,"Sim",IF(COUNTIF(D7:I7,"Em apuração")&gt;0,"Em apuração","Não"))</f>
+        <v>Não</v>
+      </c>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="11"/>
+      <c r="P7" s="11"/>
+      <c r="Q7" s="11"/>
+      <c r="R7" s="11"/>
+      <c r="S7" s="11"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="10"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11" t="str">
+        <f aca="false">IF(COUNTIF(D8:I8,"Sim")&gt;0,"Sim",IF(COUNTIF(D8:I8,"Em apuração")&gt;0,"Em apuração","Não"))</f>
+        <v>Não</v>
+      </c>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="11"/>
+      <c r="O8" s="11"/>
+      <c r="P8" s="11"/>
+      <c r="Q8" s="11"/>
+      <c r="R8" s="11"/>
+      <c r="S8" s="11"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="10"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11" t="str">
+        <f aca="false">IF(COUNTIF(D9:I9,"Sim")&gt;0,"Sim",IF(COUNTIF(D9:I9,"Em apuração")&gt;0,"Em apuração","Não"))</f>
+        <v>Não</v>
+      </c>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="11"/>
+      <c r="O9" s="11"/>
+      <c r="P9" s="11"/>
+      <c r="Q9" s="11"/>
+      <c r="R9" s="11"/>
+      <c r="S9" s="11"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="10"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11" t="str">
+        <f aca="false">IF(COUNTIF(D10:I10,"Sim")&gt;0,"Sim",IF(COUNTIF(D10:I10,"Em apuração")&gt;0,"Em apuração","Não"))</f>
+        <v>Não</v>
+      </c>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="11"/>
+      <c r="O10" s="11"/>
+      <c r="P10" s="11"/>
+      <c r="Q10" s="11"/>
+      <c r="R10" s="11"/>
+      <c r="S10" s="11"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="10"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11" t="str">
+        <f aca="false">IF(COUNTIF(D11:I11,"Sim")&gt;0,"Sim",IF(COUNTIF(D11:I11,"Em apuração")&gt;0,"Em apuração","Não"))</f>
+        <v>Não</v>
+      </c>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="11"/>
+      <c r="P11" s="11"/>
+      <c r="Q11" s="11"/>
+      <c r="R11" s="11"/>
+      <c r="S11" s="11"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="10"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11" t="str">
+        <f aca="false">IF(COUNTIF(D12:I12,"Sim")&gt;0,"Sim",IF(COUNTIF(D12:I12,"Em apuração")&gt;0,"Em apuração","Não"))</f>
+        <v>Não</v>
+      </c>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="11"/>
+      <c r="O12" s="11"/>
+      <c r="P12" s="11"/>
+      <c r="Q12" s="11"/>
+      <c r="R12" s="11"/>
+      <c r="S12" s="11"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="10"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11" t="str">
+        <f aca="false">IF(COUNTIF(D13:I13,"Sim")&gt;0,"Sim",IF(COUNTIF(D13:I13,"Em apuração")&gt;0,"Em apuração","Não"))</f>
+        <v>Não</v>
+      </c>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="11"/>
+      <c r="O13" s="11"/>
+      <c r="P13" s="11"/>
+      <c r="Q13" s="11"/>
+      <c r="R13" s="11"/>
+      <c r="S13" s="11"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="10"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11" t="str">
+        <f aca="false">IF(COUNTIF(D14:I14,"Sim")&gt;0,"Sim",IF(COUNTIF(D14:I14,"Em apuração")&gt;0,"Em apuração","Não"))</f>
+        <v>Não</v>
+      </c>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="11"/>
+      <c r="O14" s="11"/>
+      <c r="P14" s="11"/>
+      <c r="Q14" s="11"/>
+      <c r="R14" s="11"/>
+      <c r="S14" s="11"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="10"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11" t="str">
+        <f aca="false">IF(COUNTIF(D15:I15,"Sim")&gt;0,"Sim",IF(COUNTIF(D15:I15,"Em apuração")&gt;0,"Em apuração","Não"))</f>
+        <v>Não</v>
+      </c>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="11"/>
+      <c r="P15" s="11"/>
+      <c r="Q15" s="11"/>
+      <c r="R15" s="11"/>
+      <c r="S15" s="11"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="10"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11" t="str">
+        <f aca="false">IF(COUNTIF(D16:I16,"Sim")&gt;0,"Sim",IF(COUNTIF(D16:I16,"Em apuração")&gt;0,"Em apuração","Não"))</f>
+        <v>Não</v>
+      </c>
+      <c r="K16" s="11"/>
+      <c r="L16" s="11"/>
+      <c r="M16" s="11"/>
+      <c r="N16" s="11"/>
+      <c r="O16" s="11"/>
+      <c r="P16" s="11"/>
+      <c r="Q16" s="11"/>
+      <c r="R16" s="11"/>
+      <c r="S16" s="11"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="10"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11" t="str">
+        <f aca="false">IF(COUNTIF(D17:I17,"Sim")&gt;0,"Sim",IF(COUNTIF(D17:I17,"Em apuração")&gt;0,"Em apuração","Não"))</f>
+        <v>Não</v>
+      </c>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="11"/>
+      <c r="O17" s="11"/>
+      <c r="P17" s="11"/>
+      <c r="Q17" s="11"/>
+      <c r="R17" s="11"/>
+      <c r="S17" s="11"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="10"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11" t="str">
+        <f aca="false">IF(COUNTIF(D18:I18,"Sim")&gt;0,"Sim",IF(COUNTIF(D18:I18,"Em apuração")&gt;0,"Em apuração","Não"))</f>
+        <v>Não</v>
+      </c>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+      <c r="M18" s="11"/>
+      <c r="N18" s="11"/>
+      <c r="O18" s="11"/>
+      <c r="P18" s="11"/>
+      <c r="Q18" s="11"/>
+      <c r="R18" s="11"/>
+      <c r="S18" s="11"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="10"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11" t="str">
+        <f aca="false">IF(COUNTIF(D19:I19,"Sim")&gt;0,"Sim",IF(COUNTIF(D19:I19,"Em apuração")&gt;0,"Em apuração","Não"))</f>
+        <v>Não</v>
+      </c>
+      <c r="K19" s="11"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11"/>
+      <c r="O19" s="11"/>
+      <c r="P19" s="11"/>
+      <c r="Q19" s="11"/>
+      <c r="R19" s="11"/>
+      <c r="S19" s="11"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="10"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11" t="str">
+        <f aca="false">IF(COUNTIF(D20:I20,"Sim")&gt;0,"Sim",IF(COUNTIF(D20:I20,"Em apuração")&gt;0,"Em apuração","Não"))</f>
+        <v>Não</v>
+      </c>
+      <c r="K20" s="11"/>
+      <c r="L20" s="11"/>
+      <c r="M20" s="11"/>
+      <c r="N20" s="11"/>
+      <c r="O20" s="11"/>
+      <c r="P20" s="11"/>
+      <c r="Q20" s="11"/>
+      <c r="R20" s="11"/>
+      <c r="S20" s="11"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="10"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11" t="str">
+        <f aca="false">IF(COUNTIF(D21:I21,"Sim")&gt;0,"Sim",IF(COUNTIF(D21:I21,"Em apuração")&gt;0,"Em apuração","Não"))</f>
+        <v>Não</v>
+      </c>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="11"/>
+      <c r="O21" s="11"/>
+      <c r="P21" s="11"/>
+      <c r="Q21" s="11"/>
+      <c r="R21" s="11"/>
+      <c r="S21" s="11"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="10"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11" t="str">
+        <f aca="false">IF(COUNTIF(D22:I22,"Sim")&gt;0,"Sim",IF(COUNTIF(D22:I22,"Em apuração")&gt;0,"Em apuração","Não"))</f>
+        <v>Não</v>
+      </c>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="11"/>
+      <c r="N22" s="11"/>
+      <c r="O22" s="11"/>
+      <c r="P22" s="11"/>
+      <c r="Q22" s="11"/>
+      <c r="R22" s="11"/>
+      <c r="S22" s="11"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="10"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11" t="str">
+        <f aca="false">IF(COUNTIF(D23:I23,"Sim")&gt;0,"Sim",IF(COUNTIF(D23:I23,"Em apuração")&gt;0,"Em apuração","Não"))</f>
+        <v>Não</v>
+      </c>
+      <c r="K23" s="11"/>
+      <c r="L23" s="11"/>
+      <c r="M23" s="11"/>
+      <c r="N23" s="11"/>
+      <c r="O23" s="11"/>
+      <c r="P23" s="11"/>
+      <c r="Q23" s="11"/>
+      <c r="R23" s="11"/>
+      <c r="S23" s="11"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="10"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="11" t="str">
+        <f aca="false">IF(COUNTIF(D24:I24,"Sim")&gt;0,"Sim",IF(COUNTIF(D24:I24,"Em apuração")&gt;0,"Em apuração","Não"))</f>
+        <v>Não</v>
+      </c>
+      <c r="K24" s="11"/>
+      <c r="L24" s="11"/>
+      <c r="M24" s="11"/>
+      <c r="N24" s="11"/>
+      <c r="O24" s="11"/>
+      <c r="P24" s="11"/>
+      <c r="Q24" s="11"/>
+      <c r="R24" s="11"/>
+      <c r="S24" s="11"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="10"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11" t="str">
+        <f aca="false">IF(COUNTIF(D25:I25,"Sim")&gt;0,"Sim",IF(COUNTIF(D25:I25,"Em apuração")&gt;0,"Em apuração","Não"))</f>
+        <v>Não</v>
+      </c>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="11"/>
+      <c r="N25" s="11"/>
+      <c r="O25" s="11"/>
+      <c r="P25" s="11"/>
+      <c r="Q25" s="11"/>
+      <c r="R25" s="11"/>
+      <c r="S25" s="11"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="10"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="11" t="str">
+        <f aca="false">IF(COUNTIF(D26:I26,"Sim")&gt;0,"Sim",IF(COUNTIF(D26:I26,"Em apuração")&gt;0,"Em apuração","Não"))</f>
+        <v>Não</v>
+      </c>
+      <c r="K26" s="11"/>
+      <c r="L26" s="11"/>
+      <c r="M26" s="11"/>
+      <c r="N26" s="11"/>
+      <c r="O26" s="11"/>
+      <c r="P26" s="11"/>
+      <c r="Q26" s="11"/>
+      <c r="R26" s="11"/>
+      <c r="S26" s="11"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="10"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="11" t="str">
+        <f aca="false">IF(COUNTIF(D27:I27,"Sim")&gt;0,"Sim",IF(COUNTIF(D27:I27,"Em apuração")&gt;0,"Em apuração","Não"))</f>
+        <v>Não</v>
+      </c>
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
+      <c r="M27" s="11"/>
+      <c r="N27" s="11"/>
+      <c r="O27" s="11"/>
+      <c r="P27" s="11"/>
+      <c r="Q27" s="11"/>
+      <c r="R27" s="11"/>
+      <c r="S27" s="11"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="10"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
+      <c r="J28" s="11" t="str">
+        <f aca="false">IF(COUNTIF(D28:I28,"Sim")&gt;0,"Sim",IF(COUNTIF(D28:I28,"Em apuração")&gt;0,"Em apuração","Não"))</f>
+        <v>Não</v>
+      </c>
+      <c r="K28" s="11"/>
+      <c r="L28" s="11"/>
+      <c r="M28" s="11"/>
+      <c r="N28" s="11"/>
+      <c r="O28" s="11"/>
+      <c r="P28" s="11"/>
+      <c r="Q28" s="11"/>
+      <c r="R28" s="11"/>
+      <c r="S28" s="11"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="10"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11" t="str">
+        <f aca="false">IF(COUNTIF(D29:I29,"Sim")&gt;0,"Sim",IF(COUNTIF(D29:I29,"Em apuração")&gt;0,"Em apuração","Não"))</f>
+        <v>Não</v>
+      </c>
+      <c r="K29" s="11"/>
+      <c r="L29" s="11"/>
+      <c r="M29" s="11"/>
+      <c r="N29" s="11"/>
+      <c r="O29" s="11"/>
+      <c r="P29" s="11"/>
+      <c r="Q29" s="11"/>
+      <c r="R29" s="11"/>
+      <c r="S29" s="11"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="10"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
+      <c r="J30" s="11" t="str">
+        <f aca="false">IF(COUNTIF(D30:I30,"Sim")&gt;0,"Sim",IF(COUNTIF(D30:I30,"Em apuração")&gt;0,"Em apuração","Não"))</f>
+        <v>Não</v>
+      </c>
+      <c r="K30" s="11"/>
+      <c r="L30" s="11"/>
+      <c r="M30" s="11"/>
+      <c r="N30" s="11"/>
+      <c r="O30" s="11"/>
+      <c r="P30" s="11"/>
+      <c r="Q30" s="11"/>
+      <c r="R30" s="11"/>
+      <c r="S30" s="11"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="10"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="11" t="str">
+        <f aca="false">IF(COUNTIF(D31:I31,"Sim")&gt;0,"Sim",IF(COUNTIF(D31:I31,"Em apuração")&gt;0,"Em apuração","Não"))</f>
+        <v>Não</v>
+      </c>
+      <c r="K31" s="11"/>
+      <c r="L31" s="11"/>
+      <c r="M31" s="11"/>
+      <c r="N31" s="11"/>
+      <c r="O31" s="11"/>
+      <c r="P31" s="11"/>
+      <c r="Q31" s="11"/>
+      <c r="R31" s="11"/>
+      <c r="S31" s="11"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="10"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="11" t="str">
+        <f aca="false">IF(COUNTIF(D32:I32,"Sim")&gt;0,"Sim",IF(COUNTIF(D32:I32,"Em apuração")&gt;0,"Em apuração","Não"))</f>
+        <v>Não</v>
+      </c>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
+      <c r="M32" s="11"/>
+      <c r="N32" s="11"/>
+      <c r="O32" s="11"/>
+      <c r="P32" s="11"/>
+      <c r="Q32" s="11"/>
+      <c r="R32" s="11"/>
+      <c r="S32" s="11"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="10"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="11" t="str">
+        <f aca="false">IF(COUNTIF(D33:I33,"Sim")&gt;0,"Sim",IF(COUNTIF(D33:I33,"Em apuração")&gt;0,"Em apuração","Não"))</f>
+        <v>Não</v>
+      </c>
+      <c r="K33" s="11"/>
+      <c r="L33" s="11"/>
+      <c r="M33" s="11"/>
+      <c r="N33" s="11"/>
+      <c r="O33" s="11"/>
+      <c r="P33" s="11"/>
+      <c r="Q33" s="11"/>
+      <c r="R33" s="11"/>
+      <c r="S33" s="11"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="10"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
+      <c r="J34" s="11" t="str">
+        <f aca="false">IF(COUNTIF(D34:I34,"Sim")&gt;0,"Sim",IF(COUNTIF(D34:I34,"Em apuração")&gt;0,"Em apuração","Não"))</f>
+        <v>Não</v>
+      </c>
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
+      <c r="M34" s="11"/>
+      <c r="N34" s="11"/>
+      <c r="O34" s="11"/>
+      <c r="P34" s="11"/>
+      <c r="Q34" s="11"/>
+      <c r="R34" s="11"/>
+      <c r="S34" s="11"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="10"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="11"/>
+      <c r="J35" s="11" t="str">
+        <f aca="false">IF(COUNTIF(D35:I35,"Sim")&gt;0,"Sim",IF(COUNTIF(D35:I35,"Em apuração")&gt;0,"Em apuração","Não"))</f>
+        <v>Não</v>
+      </c>
+      <c r="K35" s="11"/>
+      <c r="L35" s="11"/>
+      <c r="M35" s="11"/>
+      <c r="N35" s="11"/>
+      <c r="O35" s="11"/>
+      <c r="P35" s="11"/>
+      <c r="Q35" s="11"/>
+      <c r="R35" s="11"/>
+      <c r="S35" s="11"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="10"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="11"/>
+      <c r="J36" s="11" t="str">
+        <f aca="false">IF(COUNTIF(D36:I36,"Sim")&gt;0,"Sim",IF(COUNTIF(D36:I36,"Em apuração")&gt;0,"Em apuração","Não"))</f>
+        <v>Não</v>
+      </c>
+      <c r="K36" s="11"/>
+      <c r="L36" s="11"/>
+      <c r="M36" s="11"/>
+      <c r="N36" s="11"/>
+      <c r="O36" s="11"/>
+      <c r="P36" s="11"/>
+      <c r="Q36" s="11"/>
+      <c r="R36" s="11"/>
+      <c r="S36" s="11"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="10"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="11"/>
+      <c r="J37" s="11" t="str">
+        <f aca="false">IF(COUNTIF(D37:I37,"Sim")&gt;0,"Sim",IF(COUNTIF(D37:I37,"Em apuração")&gt;0,"Em apuração","Não"))</f>
+        <v>Não</v>
+      </c>
+      <c r="K37" s="11"/>
+      <c r="L37" s="11"/>
+      <c r="M37" s="11"/>
+      <c r="N37" s="11"/>
+      <c r="O37" s="11"/>
+      <c r="P37" s="11"/>
+      <c r="Q37" s="11"/>
+      <c r="R37" s="11"/>
+      <c r="S37" s="11"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="10"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="11"/>
+      <c r="J38" s="11" t="str">
+        <f aca="false">IF(COUNTIF(D38:I38,"Sim")&gt;0,"Sim",IF(COUNTIF(D38:I38,"Em apuração")&gt;0,"Em apuração","Não"))</f>
+        <v>Não</v>
+      </c>
+      <c r="K38" s="11"/>
+      <c r="L38" s="11"/>
+      <c r="M38" s="11"/>
+      <c r="N38" s="11"/>
+      <c r="O38" s="11"/>
+      <c r="P38" s="11"/>
+      <c r="Q38" s="11"/>
+      <c r="R38" s="11"/>
+      <c r="S38" s="11"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="10"/>
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="11"/>
+      <c r="I39" s="11"/>
+      <c r="J39" s="11" t="str">
+        <f aca="false">IF(COUNTIF(D39:I39,"Sim")&gt;0,"Sim",IF(COUNTIF(D39:I39,"Em apuração")&gt;0,"Em apuração","Não"))</f>
+        <v>Não</v>
+      </c>
+      <c r="K39" s="11"/>
+      <c r="L39" s="11"/>
+      <c r="M39" s="11"/>
+      <c r="N39" s="11"/>
+      <c r="O39" s="11"/>
+      <c r="P39" s="11"/>
+      <c r="Q39" s="11"/>
+      <c r="R39" s="11"/>
+      <c r="S39" s="11"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="10"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="11"/>
+      <c r="I40" s="11"/>
+      <c r="J40" s="11" t="str">
+        <f aca="false">IF(COUNTIF(D40:I40,"Sim")&gt;0,"Sim",IF(COUNTIF(D40:I40,"Em apuração")&gt;0,"Em apuração","Não"))</f>
+        <v>Não</v>
+      </c>
+      <c r="K40" s="11"/>
+      <c r="L40" s="11"/>
+      <c r="M40" s="11"/>
+      <c r="N40" s="11"/>
+      <c r="O40" s="11"/>
+      <c r="P40" s="11"/>
+      <c r="Q40" s="11"/>
+      <c r="R40" s="11"/>
+      <c r="S40" s="11"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="10"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="11"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="11"/>
+      <c r="I41" s="11"/>
+      <c r="J41" s="11" t="str">
+        <f aca="false">IF(COUNTIF(D41:I41,"Sim")&gt;0,"Sim",IF(COUNTIF(D41:I41,"Em apuração")&gt;0,"Em apuração","Não"))</f>
+        <v>Não</v>
+      </c>
+      <c r="K41" s="11"/>
+      <c r="L41" s="11"/>
+      <c r="M41" s="11"/>
+      <c r="N41" s="11"/>
+      <c r="O41" s="11"/>
+      <c r="P41" s="11"/>
+      <c r="Q41" s="11"/>
+      <c r="R41" s="11"/>
+      <c r="S41" s="11"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="10"/>
+      <c r="B42" s="11"/>
+      <c r="C42" s="11"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="11"/>
+      <c r="F42" s="11"/>
+      <c r="G42" s="11"/>
+      <c r="H42" s="11"/>
+      <c r="I42" s="11"/>
+      <c r="J42" s="11" t="str">
+        <f aca="false">IF(COUNTIF(D42:I42,"Sim")&gt;0,"Sim",IF(COUNTIF(D42:I42,"Em apuração")&gt;0,"Em apuração","Não"))</f>
+        <v>Não</v>
+      </c>
+      <c r="K42" s="11"/>
+      <c r="L42" s="11"/>
+      <c r="M42" s="11"/>
+      <c r="N42" s="11"/>
+      <c r="O42" s="11"/>
+      <c r="P42" s="11"/>
+      <c r="Q42" s="11"/>
+      <c r="R42" s="11"/>
+      <c r="S42" s="11"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="10"/>
+      <c r="B43" s="11"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="11"/>
+      <c r="I43" s="11"/>
+      <c r="J43" s="11" t="str">
+        <f aca="false">IF(COUNTIF(D43:I43,"Sim")&gt;0,"Sim",IF(COUNTIF(D43:I43,"Em apuração")&gt;0,"Em apuração","Não"))</f>
+        <v>Não</v>
+      </c>
+      <c r="K43" s="11"/>
+      <c r="L43" s="11"/>
+      <c r="M43" s="11"/>
+      <c r="N43" s="11"/>
+      <c r="O43" s="11"/>
+      <c r="P43" s="11"/>
+      <c r="Q43" s="11"/>
+      <c r="R43" s="11"/>
+      <c r="S43" s="11"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="10"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="11"/>
+      <c r="F44" s="11"/>
+      <c r="G44" s="11"/>
+      <c r="H44" s="11"/>
+      <c r="I44" s="11"/>
+      <c r="J44" s="11" t="str">
+        <f aca="false">IF(COUNTIF(D44:I44,"Sim")&gt;0,"Sim",IF(COUNTIF(D44:I44,"Em apuração")&gt;0,"Em apuração","Não"))</f>
+        <v>Não</v>
+      </c>
+      <c r="K44" s="11"/>
+      <c r="L44" s="11"/>
+      <c r="M44" s="11"/>
+      <c r="N44" s="11"/>
+      <c r="O44" s="11"/>
+      <c r="P44" s="11"/>
+      <c r="Q44" s="11"/>
+      <c r="R44" s="11"/>
+      <c r="S44" s="11"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="10"/>
+      <c r="B45" s="11"/>
+      <c r="C45" s="11"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="11"/>
+      <c r="F45" s="11"/>
+      <c r="G45" s="11"/>
+      <c r="H45" s="11"/>
+      <c r="I45" s="11"/>
+      <c r="J45" s="11" t="str">
+        <f aca="false">IF(COUNTIF(D45:I45,"Sim")&gt;0,"Sim",IF(COUNTIF(D45:I45,"Em apuração")&gt;0,"Em apuração","Não"))</f>
+        <v>Não</v>
+      </c>
+      <c r="K45" s="11"/>
+      <c r="L45" s="11"/>
+      <c r="M45" s="11"/>
+      <c r="N45" s="11"/>
+      <c r="O45" s="11"/>
+      <c r="P45" s="11"/>
+      <c r="Q45" s="11"/>
+      <c r="R45" s="11"/>
+      <c r="S45" s="11"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="10"/>
+      <c r="B46" s="11"/>
+      <c r="C46" s="11"/>
+      <c r="D46" s="11"/>
+      <c r="E46" s="11"/>
+      <c r="F46" s="11"/>
+      <c r="G46" s="11"/>
+      <c r="H46" s="11"/>
+      <c r="I46" s="11"/>
+      <c r="J46" s="11" t="str">
+        <f aca="false">IF(COUNTIF(D46:I46,"Sim")&gt;0,"Sim",IF(COUNTIF(D46:I46,"Em apuração")&gt;0,"Em apuração","Não"))</f>
+        <v>Não</v>
+      </c>
+      <c r="K46" s="11"/>
+      <c r="L46" s="11"/>
+      <c r="M46" s="11"/>
+      <c r="N46" s="11"/>
+      <c r="O46" s="11"/>
+      <c r="P46" s="11"/>
+      <c r="Q46" s="11"/>
+      <c r="R46" s="11"/>
+      <c r="S46" s="11"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="10"/>
+      <c r="B47" s="11"/>
+      <c r="C47" s="11"/>
+      <c r="D47" s="11"/>
+      <c r="E47" s="11"/>
+      <c r="F47" s="11"/>
+      <c r="G47" s="11"/>
+      <c r="H47" s="11"/>
+      <c r="I47" s="11"/>
+      <c r="J47" s="11" t="str">
+        <f aca="false">IF(COUNTIF(D47:I47,"Sim")&gt;0,"Sim",IF(COUNTIF(D47:I47,"Em apuração")&gt;0,"Em apuração","Não"))</f>
+        <v>Não</v>
+      </c>
+      <c r="K47" s="11"/>
+      <c r="L47" s="11"/>
+      <c r="M47" s="11"/>
+      <c r="N47" s="11"/>
+      <c r="O47" s="11"/>
+      <c r="P47" s="11"/>
+      <c r="Q47" s="11"/>
+      <c r="R47" s="11"/>
+      <c r="S47" s="11"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="10"/>
+      <c r="B48" s="11"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="11"/>
+      <c r="F48" s="11"/>
+      <c r="G48" s="11"/>
+      <c r="H48" s="11"/>
+      <c r="I48" s="11"/>
+      <c r="J48" s="11" t="str">
+        <f aca="false">IF(COUNTIF(D48:I48,"Sim")&gt;0,"Sim",IF(COUNTIF(D48:I48,"Em apuração")&gt;0,"Em apuração","Não"))</f>
+        <v>Não</v>
+      </c>
+      <c r="K48" s="11"/>
+      <c r="L48" s="11"/>
+      <c r="M48" s="11"/>
+      <c r="N48" s="11"/>
+      <c r="O48" s="11"/>
+      <c r="P48" s="11"/>
+      <c r="Q48" s="11"/>
+      <c r="R48" s="11"/>
+      <c r="S48" s="11"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="10"/>
+      <c r="B49" s="11"/>
+      <c r="C49" s="11"/>
+      <c r="D49" s="11"/>
+      <c r="E49" s="11"/>
+      <c r="F49" s="11"/>
+      <c r="G49" s="11"/>
+      <c r="H49" s="11"/>
+      <c r="I49" s="11"/>
+      <c r="J49" s="11" t="str">
+        <f aca="false">IF(COUNTIF(D49:I49,"Sim")&gt;0,"Sim",IF(COUNTIF(D49:I49,"Em apuração")&gt;0,"Em apuração","Não"))</f>
+        <v>Não</v>
+      </c>
+      <c r="K49" s="11"/>
+      <c r="L49" s="11"/>
+      <c r="M49" s="11"/>
+      <c r="N49" s="11"/>
+      <c r="O49" s="11"/>
+      <c r="P49" s="11"/>
+      <c r="Q49" s="11"/>
+      <c r="R49" s="11"/>
+      <c r="S49" s="11"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="10"/>
+      <c r="B50" s="11"/>
+      <c r="C50" s="11"/>
+      <c r="D50" s="11"/>
+      <c r="E50" s="11"/>
+      <c r="F50" s="11"/>
+      <c r="G50" s="11"/>
+      <c r="H50" s="11"/>
+      <c r="I50" s="11"/>
+      <c r="J50" s="11" t="str">
+        <f aca="false">IF(COUNTIF(D50:I50,"Sim")&gt;0,"Sim",IF(COUNTIF(D50:I50,"Em apuração")&gt;0,"Em apuração","Não"))</f>
+        <v>Não</v>
+      </c>
+      <c r="K50" s="11"/>
+      <c r="L50" s="11"/>
+      <c r="M50" s="11"/>
+      <c r="N50" s="11"/>
+      <c r="O50" s="11"/>
+      <c r="P50" s="11"/>
+      <c r="Q50" s="11"/>
+      <c r="R50" s="11"/>
+      <c r="S50" s="11"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="10"/>
+      <c r="B51" s="11"/>
+      <c r="C51" s="11"/>
+      <c r="D51" s="11"/>
+      <c r="E51" s="11"/>
+      <c r="F51" s="11"/>
+      <c r="G51" s="11"/>
+      <c r="H51" s="11"/>
+      <c r="I51" s="11"/>
+      <c r="J51" s="11" t="str">
+        <f aca="false">IF(COUNTIF(D51:I51,"Sim")&gt;0,"Sim",IF(COUNTIF(D51:I51,"Em apuração")&gt;0,"Em apuração","Não"))</f>
+        <v>Não</v>
+      </c>
+      <c r="K51" s="11"/>
+      <c r="L51" s="11"/>
+      <c r="M51" s="11"/>
+      <c r="N51" s="11"/>
+      <c r="O51" s="11"/>
+      <c r="P51" s="11"/>
+      <c r="Q51" s="11"/>
+      <c r="R51" s="11"/>
+      <c r="S51" s="11"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="10"/>
+      <c r="B52" s="11"/>
+      <c r="C52" s="11"/>
+      <c r="D52" s="11"/>
+      <c r="E52" s="11"/>
+      <c r="F52" s="11"/>
+      <c r="G52" s="11"/>
+      <c r="H52" s="11"/>
+      <c r="I52" s="11"/>
+      <c r="J52" s="11" t="str">
+        <f aca="false">IF(COUNTIF(D52:I52,"Sim")&gt;0,"Sim",IF(COUNTIF(D52:I52,"Em apuração")&gt;0,"Em apuração","Não"))</f>
+        <v>Não</v>
+      </c>
+      <c r="K52" s="11"/>
+      <c r="L52" s="11"/>
+      <c r="M52" s="11"/>
+      <c r="N52" s="11"/>
+      <c r="O52" s="11"/>
+      <c r="P52" s="11"/>
+      <c r="Q52" s="11"/>
+      <c r="R52" s="11"/>
+      <c r="S52" s="11"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="10"/>
+      <c r="B53" s="11"/>
+      <c r="C53" s="11"/>
+      <c r="D53" s="11"/>
+      <c r="E53" s="11"/>
+      <c r="F53" s="11"/>
+      <c r="G53" s="11"/>
+      <c r="H53" s="11"/>
+      <c r="I53" s="11"/>
+      <c r="J53" s="11" t="str">
+        <f aca="false">IF(COUNTIF(D53:I53,"Sim")&gt;0,"Sim",IF(COUNTIF(D53:I53,"Em apuração")&gt;0,"Em apuração","Não"))</f>
+        <v>Não</v>
+      </c>
+      <c r="K53" s="11"/>
+      <c r="L53" s="11"/>
+      <c r="M53" s="11"/>
+      <c r="N53" s="11"/>
+      <c r="O53" s="11"/>
+      <c r="P53" s="11"/>
+      <c r="Q53" s="11"/>
+      <c r="R53" s="11"/>
+      <c r="S53" s="11"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A2:S2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A4:A53">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>AND(A4&lt;&gt;"",COUNTIF($A$4:$A$53,A4)&gt;1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>AND($A4&lt;&gt;"",OR(COUNTIFS(Caracterizacao!$A$4:$A$53,$A4,Caracterizacao!$B$4:$B$53,$B4)=0,COUNTIFS(Decisao_Comunicacao!$A$4:$A$53,$A4,Decisao_Comunicacao!$B$4:$B$53,$B4)=0))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="451">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C4" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D4" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E4" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F4" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G4" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H4" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I4" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="O4" type="list">
+      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P4" type="list">
+      <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C5" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D5" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E5" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F5" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G5" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H5" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I5" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="O5" type="list">
+      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P5" type="list">
+      <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C6" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D6" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E6" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F6" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G6" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H6" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I6" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="O6" type="list">
+      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P6" type="list">
+      <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C7" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D7" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E7" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F7" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G7" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H7" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I7" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="O7" type="list">
+      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P7" type="list">
+      <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C8" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D8" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E8" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F8" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G8" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H8" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I8" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="O8" type="list">
+      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P8" type="list">
+      <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C9" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D9" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E9" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F9" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G9" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H9" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I9" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="O9" type="list">
+      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P9" type="list">
+      <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C10" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D10" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E10" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F10" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G10" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H10" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I10" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="O10" type="list">
+      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P10" type="list">
+      <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C11" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D11" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E11" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F11" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G11" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H11" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I11" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="O11" type="list">
+      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P11" type="list">
+      <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C12" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D12" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E12" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F12" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G12" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H12" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I12" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="O12" type="list">
+      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P12" type="list">
+      <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C13" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D13" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E13" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F13" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G13" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H13" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I13" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="O13" type="list">
+      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P13" type="list">
+      <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C14" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D14" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E14" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F14" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G14" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H14" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I14" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="O14" type="list">
+      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P14" type="list">
+      <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C15" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D15" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E15" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F15" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G15" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H15" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I15" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="O15" type="list">
+      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P15" type="list">
+      <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C16" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D16" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E16" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F16" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G16" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H16" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I16" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="O16" type="list">
+      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P16" type="list">
+      <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C17" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D17" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E17" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F17" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G17" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H17" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I17" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="O17" type="list">
+      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P17" type="list">
+      <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C18" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D18" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E18" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F18" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G18" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H18" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I18" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="O18" type="list">
+      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P18" type="list">
+      <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C19" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D19" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E19" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F19" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G19" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H19" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I19" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="O19" type="list">
+      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P19" type="list">
+      <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C20" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D20" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E20" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F20" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G20" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H20" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I20" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="O20" type="list">
+      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P20" type="list">
+      <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C21" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D21" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E21" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F21" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G21" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H21" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I21" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="O21" type="list">
+      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P21" type="list">
+      <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C22" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D22" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E22" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F22" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G22" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H22" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I22" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="O22" type="list">
+      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P22" type="list">
+      <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C23" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D23" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E23" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F23" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G23" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H23" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I23" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="O23" type="list">
+      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P23" type="list">
+      <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C24" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D24" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E24" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F24" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G24" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H24" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I24" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="O24" type="list">
+      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P24" type="list">
+      <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C25" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D25" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E25" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F25" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G25" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H25" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I25" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="O25" type="list">
+      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P25" type="list">
+      <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C26" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D26" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E26" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F26" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G26" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H26" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I26" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="O26" type="list">
+      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P26" type="list">
+      <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C27" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D27" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E27" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F27" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G27" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H27" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I27" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="O27" type="list">
+      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P27" type="list">
+      <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C28" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D28" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E28" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F28" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G28" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H28" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I28" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="O28" type="list">
+      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P28" type="list">
+      <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C29" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D29" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E29" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F29" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G29" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H29" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I29" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="O29" type="list">
+      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P29" type="list">
+      <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C30" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D30" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E30" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F30" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G30" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H30" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I30" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="O30" type="list">
+      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P30" type="list">
+      <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C31" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D31" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E31" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F31" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G31" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H31" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I31" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="O31" type="list">
+      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P31" type="list">
+      <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C32" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D32" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E32" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F32" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G32" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H32" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I32" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="O32" type="list">
+      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P32" type="list">
+      <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C33" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D33" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E33" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F33" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G33" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H33" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I33" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="O33" type="list">
+      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P33" type="list">
+      <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C34" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D34" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E34" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F34" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G34" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H34" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I34" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="O34" type="list">
+      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P34" type="list">
+      <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C35" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D35" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E35" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F35" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G35" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H35" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I35" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="O35" type="list">
+      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P35" type="list">
+      <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C36" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D36" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E36" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F36" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G36" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H36" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I36" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="O36" type="list">
+      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P36" type="list">
+      <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C37" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D37" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E37" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F37" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G37" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H37" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I37" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="O37" type="list">
+      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P37" type="list">
+      <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C38" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D38" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E38" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F38" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G38" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H38" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I38" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="O38" type="list">
+      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P38" type="list">
+      <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C39" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D39" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E39" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F39" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G39" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H39" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I39" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="O39" type="list">
+      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P39" type="list">
+      <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C40" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D40" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E40" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F40" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G40" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H40" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I40" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="O40" type="list">
+      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P40" type="list">
+      <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C41" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D41" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E41" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F41" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G41" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H41" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I41" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="O41" type="list">
+      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P41" type="list">
+      <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C42" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D42" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E42" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F42" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G42" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H42" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I42" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="O42" type="list">
+      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P42" type="list">
+      <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C43" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D43" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E43" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F43" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G43" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H43" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I43" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="O43" type="list">
+      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P43" type="list">
+      <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C44" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D44" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E44" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F44" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G44" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H44" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I44" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="O44" type="list">
+      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P44" type="list">
+      <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C45" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D45" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E45" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F45" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G45" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H45" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I45" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="O45" type="list">
+      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P45" type="list">
+      <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C46" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D46" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E46" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F46" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G46" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H46" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I46" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="O46" type="list">
+      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P46" type="list">
+      <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C47" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D47" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E47" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F47" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G47" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H47" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I47" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="O47" type="list">
+      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P47" type="list">
+      <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C48" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D48" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E48" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F48" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G48" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H48" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I48" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="O48" type="list">
+      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P48" type="list">
+      <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C49" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D49" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E49" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F49" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G49" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H49" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I49" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="O49" type="list">
+      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P49" type="list">
+      <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C50" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D50" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E50" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F50" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G50" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H50" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I50" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="O50" type="list">
+      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P50" type="list">
+      <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C51" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D51" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E51" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F51" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G51" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H51" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I51" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="O51" type="list">
+      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P51" type="list">
+      <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C52" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D52" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E52" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F52" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G52" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H52" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I52" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="O52" type="list">
+      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P52" type="list">
+      <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C53" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D53" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E53" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F53" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G53" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H53" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I53" type="list">
+      <formula1>"Sim,Não,Em apuração,Não demonstrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha com base na fundamentação registrada. Não há cálculo automático." promptTitle="Resultado (manual)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="O53" type="list">
+      <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P53" type="list">
+      <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Este identificador já existe nesta coluna. Cada ID deve ser único e estável (não reutilize nem renumere IDs já atribuídos). Padrão esperado: AVR-01." errorStyle="stop" errorTitle="ID duplicado" operator="between" prompt="Digite um identificador único e estável, padrão AVR-01. Não é gerado automaticamente — preserve o mesmo ID após inserir, excluir ou reordenar linhas." promptTitle="Identificador manual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A4:A53" type="custom">
+      <formula1>OR(A4="",COUNTIF($A$4:$A$53,A4)&lt;=1)</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:R53"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="8"/>
+      <c r="O2" s="8"/>
+      <c r="P2" s="8"/>
+      <c r="Q2" s="8"/>
+      <c r="R2" s="8"/>
+    </row>
+    <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>100</v>
+      </c>
       <c r="D3" s="9" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="str">
-        <f aca="false">IF(C4="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v>AVR-01</v>
+        <v>110</v>
+      </c>
+      <c r="N3" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="O3" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="P3" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q3" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="R3" s="9" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="10" t="s">
+        <v>41</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C4" s="12" t="n">
         <v>46314.3923611111</v>
       </c>
-      <c r="D4" s="13" t="n">
-        <f aca="false">IFERROR(IF(C4="","",WORKDAY(C4,3)),"Verificar formato de data em C"&amp;ROW())</f>
+      <c r="D4" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="E4" s="13" t="n">
+        <f aca="false">IFERROR(IF(C4="","",WORKDAY(C4,IF(D4="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v>46317</v>
       </c>
-      <c r="E4" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>93</v>
-      </c>
+      <c r="F4" s="14"/>
       <c r="G4" s="11" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="I4" s="11"/>
+        <v>118</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>89</v>
+      </c>
       <c r="J4" s="11" t="s">
-        <v>71</v>
+        <v>119</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="str">
-        <f aca="false">IF(C5="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v>AVR-02</v>
+        <v>121</v>
+      </c>
+      <c r="N4" s="12"/>
+      <c r="O4" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="P4" s="12"/>
+      <c r="Q4" s="15" t="str">
+        <f aca="false">IFERROR(IF(P4="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P4,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
+        <v>Sem data de comunicação efetiva registrada</v>
+      </c>
+      <c r="R4" s="11" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="10" t="s">
+        <v>53</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="C5" s="12" t="n">
         <v>46314.3923611111</v>
       </c>
-      <c r="D5" s="13" t="n">
-        <f aca="false">IFERROR(IF(C5="","",WORKDAY(C5,3)),"Verificar formato de data em C"&amp;ROW())</f>
+      <c r="D5" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="E5" s="13" t="n">
+        <f aca="false">IFERROR(IF(C5="","",WORKDAY(C5,IF(D5="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v>46317</v>
       </c>
-      <c r="E5" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>99</v>
+      <c r="F5" s="14" t="n">
+        <v>46317</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="I5" s="12" t="n">
+        <v>125</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="L5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M5" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="N5" s="12" t="n">
         <v>46314.5069444445</v>
       </c>
-      <c r="J5" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="K5" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="L5" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="M5" s="11" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="str">
-        <f aca="false">IF(C6="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
+      <c r="O5" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="P5" s="12"/>
+      <c r="Q5" s="15" t="str">
+        <f aca="false">IFERROR(IF(P5="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P5,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
+        <v>Sem data de comunicação efetiva registrada</v>
+      </c>
+      <c r="R5" s="11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="10"/>
       <c r="B6" s="11"/>
       <c r="C6" s="12"/>
-      <c r="D6" s="13" t="str">
-        <f aca="false">IFERROR(IF(C6="","",WORKDAY(C6,3)),"Verificar formato de data em C"&amp;ROW())</f>
+      <c r="D6" s="11"/>
+      <c r="E6" s="13" t="str">
+        <f aca="false">IFERROR(IF(C6="","",WORKDAY(C6,IF(D6="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
+      <c r="F6" s="14"/>
       <c r="G6" s="11"/>
       <c r="H6" s="11"/>
       <c r="I6" s="11"/>
@@ -2489,20 +5983,25 @@
       <c r="K6" s="11"/>
       <c r="L6" s="11"/>
       <c r="M6" s="11"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="str">
-        <f aca="false">IF(C7="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
+      <c r="N6" s="12"/>
+      <c r="O6" s="11"/>
+      <c r="P6" s="12"/>
+      <c r="Q6" s="15" t="str">
+        <f aca="false">IFERROR(IF(P6="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P6,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
+        <v>Sem data de comunicação efetiva registrada</v>
+      </c>
+      <c r="R6" s="11"/>
+    </row>
+    <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="10"/>
       <c r="B7" s="11"/>
       <c r="C7" s="12"/>
-      <c r="D7" s="13" t="str">
-        <f aca="false">IFERROR(IF(C7="","",WORKDAY(C7,3)),"Verificar formato de data em C"&amp;ROW())</f>
+      <c r="D7" s="11"/>
+      <c r="E7" s="13" t="str">
+        <f aca="false">IFERROR(IF(C7="","",WORKDAY(C7,IF(D7="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
+      <c r="F7" s="14"/>
       <c r="G7" s="11"/>
       <c r="H7" s="11"/>
       <c r="I7" s="11"/>
@@ -2510,20 +6009,25 @@
       <c r="K7" s="11"/>
       <c r="L7" s="11"/>
       <c r="M7" s="11"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10" t="str">
-        <f aca="false">IF(C8="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
+      <c r="N7" s="12"/>
+      <c r="O7" s="11"/>
+      <c r="P7" s="12"/>
+      <c r="Q7" s="15" t="str">
+        <f aca="false">IFERROR(IF(P7="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P7,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
+        <v>Sem data de comunicação efetiva registrada</v>
+      </c>
+      <c r="R7" s="11"/>
+    </row>
+    <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="10"/>
       <c r="B8" s="11"/>
       <c r="C8" s="12"/>
-      <c r="D8" s="13" t="str">
-        <f aca="false">IFERROR(IF(C8="","",WORKDAY(C8,3)),"Verificar formato de data em C"&amp;ROW())</f>
+      <c r="D8" s="11"/>
+      <c r="E8" s="13" t="str">
+        <f aca="false">IFERROR(IF(C8="","",WORKDAY(C8,IF(D8="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
+      <c r="F8" s="14"/>
       <c r="G8" s="11"/>
       <c r="H8" s="11"/>
       <c r="I8" s="11"/>
@@ -2531,20 +6035,25 @@
       <c r="K8" s="11"/>
       <c r="L8" s="11"/>
       <c r="M8" s="11"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="str">
-        <f aca="false">IF(C9="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
+      <c r="N8" s="12"/>
+      <c r="O8" s="11"/>
+      <c r="P8" s="12"/>
+      <c r="Q8" s="15" t="str">
+        <f aca="false">IFERROR(IF(P8="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P8,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
+        <v>Sem data de comunicação efetiva registrada</v>
+      </c>
+      <c r="R8" s="11"/>
+    </row>
+    <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="10"/>
       <c r="B9" s="11"/>
       <c r="C9" s="12"/>
-      <c r="D9" s="13" t="str">
-        <f aca="false">IFERROR(IF(C9="","",WORKDAY(C9,3)),"Verificar formato de data em C"&amp;ROW())</f>
+      <c r="D9" s="11"/>
+      <c r="E9" s="13" t="str">
+        <f aca="false">IFERROR(IF(C9="","",WORKDAY(C9,IF(D9="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
+      <c r="F9" s="14"/>
       <c r="G9" s="11"/>
       <c r="H9" s="11"/>
       <c r="I9" s="11"/>
@@ -2552,20 +6061,25 @@
       <c r="K9" s="11"/>
       <c r="L9" s="11"/>
       <c r="M9" s="11"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10" t="str">
-        <f aca="false">IF(C10="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
+      <c r="N9" s="12"/>
+      <c r="O9" s="11"/>
+      <c r="P9" s="12"/>
+      <c r="Q9" s="15" t="str">
+        <f aca="false">IFERROR(IF(P9="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P9,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
+        <v>Sem data de comunicação efetiva registrada</v>
+      </c>
+      <c r="R9" s="11"/>
+    </row>
+    <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="10"/>
       <c r="B10" s="11"/>
       <c r="C10" s="12"/>
-      <c r="D10" s="13" t="str">
-        <f aca="false">IFERROR(IF(C10="","",WORKDAY(C10,3)),"Verificar formato de data em C"&amp;ROW())</f>
+      <c r="D10" s="11"/>
+      <c r="E10" s="13" t="str">
+        <f aca="false">IFERROR(IF(C10="","",WORKDAY(C10,IF(D10="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
+      <c r="F10" s="14"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -2573,20 +6087,25 @@
       <c r="K10" s="11"/>
       <c r="L10" s="11"/>
       <c r="M10" s="11"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10" t="str">
-        <f aca="false">IF(C11="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
+      <c r="N10" s="12"/>
+      <c r="O10" s="11"/>
+      <c r="P10" s="12"/>
+      <c r="Q10" s="15" t="str">
+        <f aca="false">IFERROR(IF(P10="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P10,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
+        <v>Sem data de comunicação efetiva registrada</v>
+      </c>
+      <c r="R10" s="11"/>
+    </row>
+    <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="10"/>
       <c r="B11" s="11"/>
       <c r="C11" s="12"/>
-      <c r="D11" s="13" t="str">
-        <f aca="false">IFERROR(IF(C11="","",WORKDAY(C11,3)),"Verificar formato de data em C"&amp;ROW())</f>
+      <c r="D11" s="11"/>
+      <c r="E11" s="13" t="str">
+        <f aca="false">IFERROR(IF(C11="","",WORKDAY(C11,IF(D11="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
+      <c r="F11" s="14"/>
       <c r="G11" s="11"/>
       <c r="H11" s="11"/>
       <c r="I11" s="11"/>
@@ -2594,20 +6113,25 @@
       <c r="K11" s="11"/>
       <c r="L11" s="11"/>
       <c r="M11" s="11"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10" t="str">
-        <f aca="false">IF(C12="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
+      <c r="N11" s="12"/>
+      <c r="O11" s="11"/>
+      <c r="P11" s="12"/>
+      <c r="Q11" s="15" t="str">
+        <f aca="false">IFERROR(IF(P11="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P11,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
+        <v>Sem data de comunicação efetiva registrada</v>
+      </c>
+      <c r="R11" s="11"/>
+    </row>
+    <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="10"/>
       <c r="B12" s="11"/>
       <c r="C12" s="12"/>
-      <c r="D12" s="13" t="str">
-        <f aca="false">IFERROR(IF(C12="","",WORKDAY(C12,3)),"Verificar formato de data em C"&amp;ROW())</f>
+      <c r="D12" s="11"/>
+      <c r="E12" s="13" t="str">
+        <f aca="false">IFERROR(IF(C12="","",WORKDAY(C12,IF(D12="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
+      <c r="F12" s="14"/>
       <c r="G12" s="11"/>
       <c r="H12" s="11"/>
       <c r="I12" s="11"/>
@@ -2615,20 +6139,25 @@
       <c r="K12" s="11"/>
       <c r="L12" s="11"/>
       <c r="M12" s="11"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10" t="str">
-        <f aca="false">IF(C13="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
+      <c r="N12" s="12"/>
+      <c r="O12" s="11"/>
+      <c r="P12" s="12"/>
+      <c r="Q12" s="15" t="str">
+        <f aca="false">IFERROR(IF(P12="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P12,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
+        <v>Sem data de comunicação efetiva registrada</v>
+      </c>
+      <c r="R12" s="11"/>
+    </row>
+    <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="10"/>
       <c r="B13" s="11"/>
       <c r="C13" s="12"/>
-      <c r="D13" s="13" t="str">
-        <f aca="false">IFERROR(IF(C13="","",WORKDAY(C13,3)),"Verificar formato de data em C"&amp;ROW())</f>
+      <c r="D13" s="11"/>
+      <c r="E13" s="13" t="str">
+        <f aca="false">IFERROR(IF(C13="","",WORKDAY(C13,IF(D13="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
+      <c r="F13" s="14"/>
       <c r="G13" s="11"/>
       <c r="H13" s="11"/>
       <c r="I13" s="11"/>
@@ -2636,20 +6165,25 @@
       <c r="K13" s="11"/>
       <c r="L13" s="11"/>
       <c r="M13" s="11"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10" t="str">
-        <f aca="false">IF(C14="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
+      <c r="N13" s="12"/>
+      <c r="O13" s="11"/>
+      <c r="P13" s="12"/>
+      <c r="Q13" s="15" t="str">
+        <f aca="false">IFERROR(IF(P13="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P13,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
+        <v>Sem data de comunicação efetiva registrada</v>
+      </c>
+      <c r="R13" s="11"/>
+    </row>
+    <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="10"/>
       <c r="B14" s="11"/>
       <c r="C14" s="12"/>
-      <c r="D14" s="13" t="str">
-        <f aca="false">IFERROR(IF(C14="","",WORKDAY(C14,3)),"Verificar formato de data em C"&amp;ROW())</f>
+      <c r="D14" s="11"/>
+      <c r="E14" s="13" t="str">
+        <f aca="false">IFERROR(IF(C14="","",WORKDAY(C14,IF(D14="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
+      <c r="F14" s="14"/>
       <c r="G14" s="11"/>
       <c r="H14" s="11"/>
       <c r="I14" s="11"/>
@@ -2657,20 +6191,25 @@
       <c r="K14" s="11"/>
       <c r="L14" s="11"/>
       <c r="M14" s="11"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10" t="str">
-        <f aca="false">IF(C15="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
+      <c r="N14" s="12"/>
+      <c r="O14" s="11"/>
+      <c r="P14" s="12"/>
+      <c r="Q14" s="15" t="str">
+        <f aca="false">IFERROR(IF(P14="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P14,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
+        <v>Sem data de comunicação efetiva registrada</v>
+      </c>
+      <c r="R14" s="11"/>
+    </row>
+    <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="10"/>
       <c r="B15" s="11"/>
       <c r="C15" s="12"/>
-      <c r="D15" s="13" t="str">
-        <f aca="false">IFERROR(IF(C15="","",WORKDAY(C15,3)),"Verificar formato de data em C"&amp;ROW())</f>
+      <c r="D15" s="11"/>
+      <c r="E15" s="13" t="str">
+        <f aca="false">IFERROR(IF(C15="","",WORKDAY(C15,IF(D15="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
+      <c r="F15" s="14"/>
       <c r="G15" s="11"/>
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
@@ -2678,20 +6217,25 @@
       <c r="K15" s="11"/>
       <c r="L15" s="11"/>
       <c r="M15" s="11"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10" t="str">
-        <f aca="false">IF(C16="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
+      <c r="N15" s="12"/>
+      <c r="O15" s="11"/>
+      <c r="P15" s="12"/>
+      <c r="Q15" s="15" t="str">
+        <f aca="false">IFERROR(IF(P15="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P15,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
+        <v>Sem data de comunicação efetiva registrada</v>
+      </c>
+      <c r="R15" s="11"/>
+    </row>
+    <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="10"/>
       <c r="B16" s="11"/>
       <c r="C16" s="12"/>
-      <c r="D16" s="13" t="str">
-        <f aca="false">IFERROR(IF(C16="","",WORKDAY(C16,3)),"Verificar formato de data em C"&amp;ROW())</f>
+      <c r="D16" s="11"/>
+      <c r="E16" s="13" t="str">
+        <f aca="false">IFERROR(IF(C16="","",WORKDAY(C16,IF(D16="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
+      <c r="F16" s="14"/>
       <c r="G16" s="11"/>
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
@@ -2699,20 +6243,25 @@
       <c r="K16" s="11"/>
       <c r="L16" s="11"/>
       <c r="M16" s="11"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10" t="str">
-        <f aca="false">IF(C17="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
+      <c r="N16" s="12"/>
+      <c r="O16" s="11"/>
+      <c r="P16" s="12"/>
+      <c r="Q16" s="15" t="str">
+        <f aca="false">IFERROR(IF(P16="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P16,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
+        <v>Sem data de comunicação efetiva registrada</v>
+      </c>
+      <c r="R16" s="11"/>
+    </row>
+    <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="10"/>
       <c r="B17" s="11"/>
       <c r="C17" s="12"/>
-      <c r="D17" s="13" t="str">
-        <f aca="false">IFERROR(IF(C17="","",WORKDAY(C17,3)),"Verificar formato de data em C"&amp;ROW())</f>
+      <c r="D17" s="11"/>
+      <c r="E17" s="13" t="str">
+        <f aca="false">IFERROR(IF(C17="","",WORKDAY(C17,IF(D17="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
+      <c r="F17" s="14"/>
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
@@ -2720,20 +6269,25 @@
       <c r="K17" s="11"/>
       <c r="L17" s="11"/>
       <c r="M17" s="11"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10" t="str">
-        <f aca="false">IF(C18="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
+      <c r="N17" s="12"/>
+      <c r="O17" s="11"/>
+      <c r="P17" s="12"/>
+      <c r="Q17" s="15" t="str">
+        <f aca="false">IFERROR(IF(P17="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P17,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
+        <v>Sem data de comunicação efetiva registrada</v>
+      </c>
+      <c r="R17" s="11"/>
+    </row>
+    <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="10"/>
       <c r="B18" s="11"/>
       <c r="C18" s="12"/>
-      <c r="D18" s="13" t="str">
-        <f aca="false">IFERROR(IF(C18="","",WORKDAY(C18,3)),"Verificar formato de data em C"&amp;ROW())</f>
+      <c r="D18" s="11"/>
+      <c r="E18" s="13" t="str">
+        <f aca="false">IFERROR(IF(C18="","",WORKDAY(C18,IF(D18="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
+      <c r="F18" s="14"/>
       <c r="G18" s="11"/>
       <c r="H18" s="11"/>
       <c r="I18" s="11"/>
@@ -2741,20 +6295,25 @@
       <c r="K18" s="11"/>
       <c r="L18" s="11"/>
       <c r="M18" s="11"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10" t="str">
-        <f aca="false">IF(C19="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
+      <c r="N18" s="12"/>
+      <c r="O18" s="11"/>
+      <c r="P18" s="12"/>
+      <c r="Q18" s="15" t="str">
+        <f aca="false">IFERROR(IF(P18="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P18,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
+        <v>Sem data de comunicação efetiva registrada</v>
+      </c>
+      <c r="R18" s="11"/>
+    </row>
+    <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="10"/>
       <c r="B19" s="11"/>
       <c r="C19" s="12"/>
-      <c r="D19" s="13" t="str">
-        <f aca="false">IFERROR(IF(C19="","",WORKDAY(C19,3)),"Verificar formato de data em C"&amp;ROW())</f>
+      <c r="D19" s="11"/>
+      <c r="E19" s="13" t="str">
+        <f aca="false">IFERROR(IF(C19="","",WORKDAY(C19,IF(D19="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
+      <c r="F19" s="14"/>
       <c r="G19" s="11"/>
       <c r="H19" s="11"/>
       <c r="I19" s="11"/>
@@ -2762,203 +6321,1515 @@
       <c r="K19" s="11"/>
       <c r="L19" s="11"/>
       <c r="M19" s="11"/>
+      <c r="N19" s="12"/>
+      <c r="O19" s="11"/>
+      <c r="P19" s="12"/>
+      <c r="Q19" s="15" t="str">
+        <f aca="false">IFERROR(IF(P19="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P19,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
+        <v>Sem data de comunicação efetiva registrada</v>
+      </c>
+      <c r="R19" s="11"/>
+    </row>
+    <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="10"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="13" t="str">
+        <f aca="false">IFERROR(IF(C20="","",WORKDAY(C20,IF(D20="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <v/>
+      </c>
+      <c r="F20" s="14"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="11"/>
+      <c r="M20" s="11"/>
+      <c r="N20" s="12"/>
+      <c r="O20" s="11"/>
+      <c r="P20" s="12"/>
+      <c r="Q20" s="15" t="str">
+        <f aca="false">IFERROR(IF(P20="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P20,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
+        <v>Sem data de comunicação efetiva registrada</v>
+      </c>
+      <c r="R20" s="11"/>
+    </row>
+    <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="10"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="13" t="str">
+        <f aca="false">IFERROR(IF(C21="","",WORKDAY(C21,IF(D21="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <v/>
+      </c>
+      <c r="F21" s="14"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="12"/>
+      <c r="O21" s="11"/>
+      <c r="P21" s="12"/>
+      <c r="Q21" s="15" t="str">
+        <f aca="false">IFERROR(IF(P21="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P21,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
+        <v>Sem data de comunicação efetiva registrada</v>
+      </c>
+      <c r="R21" s="11"/>
+    </row>
+    <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="10"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="13" t="str">
+        <f aca="false">IFERROR(IF(C22="","",WORKDAY(C22,IF(D22="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <v/>
+      </c>
+      <c r="F22" s="14"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="11"/>
+      <c r="N22" s="12"/>
+      <c r="O22" s="11"/>
+      <c r="P22" s="12"/>
+      <c r="Q22" s="15" t="str">
+        <f aca="false">IFERROR(IF(P22="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P22,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
+        <v>Sem data de comunicação efetiva registrada</v>
+      </c>
+      <c r="R22" s="11"/>
+    </row>
+    <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="10"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="13" t="str">
+        <f aca="false">IFERROR(IF(C23="","",WORKDAY(C23,IF(D23="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <v/>
+      </c>
+      <c r="F23" s="14"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="11"/>
+      <c r="M23" s="11"/>
+      <c r="N23" s="12"/>
+      <c r="O23" s="11"/>
+      <c r="P23" s="12"/>
+      <c r="Q23" s="15" t="str">
+        <f aca="false">IFERROR(IF(P23="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P23,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
+        <v>Sem data de comunicação efetiva registrada</v>
+      </c>
+      <c r="R23" s="11"/>
+    </row>
+    <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="10"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="13" t="str">
+        <f aca="false">IFERROR(IF(C24="","",WORKDAY(C24,IF(D24="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <v/>
+      </c>
+      <c r="F24" s="14"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="11"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="11"/>
+      <c r="M24" s="11"/>
+      <c r="N24" s="12"/>
+      <c r="O24" s="11"/>
+      <c r="P24" s="12"/>
+      <c r="Q24" s="15" t="str">
+        <f aca="false">IFERROR(IF(P24="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P24,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
+        <v>Sem data de comunicação efetiva registrada</v>
+      </c>
+      <c r="R24" s="11"/>
+    </row>
+    <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="10"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="13" t="str">
+        <f aca="false">IFERROR(IF(C25="","",WORKDAY(C25,IF(D25="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <v/>
+      </c>
+      <c r="F25" s="14"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="11"/>
+      <c r="N25" s="12"/>
+      <c r="O25" s="11"/>
+      <c r="P25" s="12"/>
+      <c r="Q25" s="15" t="str">
+        <f aca="false">IFERROR(IF(P25="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P25,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
+        <v>Sem data de comunicação efetiva registrada</v>
+      </c>
+      <c r="R25" s="11"/>
+    </row>
+    <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="10"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="13" t="str">
+        <f aca="false">IFERROR(IF(C26="","",WORKDAY(C26,IF(D26="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <v/>
+      </c>
+      <c r="F26" s="14"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="11"/>
+      <c r="K26" s="11"/>
+      <c r="L26" s="11"/>
+      <c r="M26" s="11"/>
+      <c r="N26" s="12"/>
+      <c r="O26" s="11"/>
+      <c r="P26" s="12"/>
+      <c r="Q26" s="15" t="str">
+        <f aca="false">IFERROR(IF(P26="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P26,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
+        <v>Sem data de comunicação efetiva registrada</v>
+      </c>
+      <c r="R26" s="11"/>
+    </row>
+    <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="10"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="13" t="str">
+        <f aca="false">IFERROR(IF(C27="","",WORKDAY(C27,IF(D27="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <v/>
+      </c>
+      <c r="F27" s="14"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
+      <c r="M27" s="11"/>
+      <c r="N27" s="12"/>
+      <c r="O27" s="11"/>
+      <c r="P27" s="12"/>
+      <c r="Q27" s="15" t="str">
+        <f aca="false">IFERROR(IF(P27="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P27,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
+        <v>Sem data de comunicação efetiva registrada</v>
+      </c>
+      <c r="R27" s="11"/>
+    </row>
+    <row r="28" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="10"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="13" t="str">
+        <f aca="false">IFERROR(IF(C28="","",WORKDAY(C28,IF(D28="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <v/>
+      </c>
+      <c r="F28" s="14"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
+      <c r="J28" s="11"/>
+      <c r="K28" s="11"/>
+      <c r="L28" s="11"/>
+      <c r="M28" s="11"/>
+      <c r="N28" s="12"/>
+      <c r="O28" s="11"/>
+      <c r="P28" s="12"/>
+      <c r="Q28" s="15" t="str">
+        <f aca="false">IFERROR(IF(P28="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P28,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
+        <v>Sem data de comunicação efetiva registrada</v>
+      </c>
+      <c r="R28" s="11"/>
+    </row>
+    <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="10"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="13" t="str">
+        <f aca="false">IFERROR(IF(C29="","",WORKDAY(C29,IF(D29="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <v/>
+      </c>
+      <c r="F29" s="14"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11"/>
+      <c r="L29" s="11"/>
+      <c r="M29" s="11"/>
+      <c r="N29" s="12"/>
+      <c r="O29" s="11"/>
+      <c r="P29" s="12"/>
+      <c r="Q29" s="15" t="str">
+        <f aca="false">IFERROR(IF(P29="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P29,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
+        <v>Sem data de comunicação efetiva registrada</v>
+      </c>
+      <c r="R29" s="11"/>
+    </row>
+    <row r="30" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="10"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="13" t="str">
+        <f aca="false">IFERROR(IF(C30="","",WORKDAY(C30,IF(D30="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <v/>
+      </c>
+      <c r="F30" s="14"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
+      <c r="J30" s="11"/>
+      <c r="K30" s="11"/>
+      <c r="L30" s="11"/>
+      <c r="M30" s="11"/>
+      <c r="N30" s="12"/>
+      <c r="O30" s="11"/>
+      <c r="P30" s="12"/>
+      <c r="Q30" s="15" t="str">
+        <f aca="false">IFERROR(IF(P30="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P30,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
+        <v>Sem data de comunicação efetiva registrada</v>
+      </c>
+      <c r="R30" s="11"/>
+    </row>
+    <row r="31" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="10"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="13" t="str">
+        <f aca="false">IFERROR(IF(C31="","",WORKDAY(C31,IF(D31="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <v/>
+      </c>
+      <c r="F31" s="14"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="11"/>
+      <c r="L31" s="11"/>
+      <c r="M31" s="11"/>
+      <c r="N31" s="12"/>
+      <c r="O31" s="11"/>
+      <c r="P31" s="12"/>
+      <c r="Q31" s="15" t="str">
+        <f aca="false">IFERROR(IF(P31="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P31,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
+        <v>Sem data de comunicação efetiva registrada</v>
+      </c>
+      <c r="R31" s="11"/>
+    </row>
+    <row r="32" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="10"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="13" t="str">
+        <f aca="false">IFERROR(IF(C32="","",WORKDAY(C32,IF(D32="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <v/>
+      </c>
+      <c r="F32" s="14"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
+      <c r="M32" s="11"/>
+      <c r="N32" s="12"/>
+      <c r="O32" s="11"/>
+      <c r="P32" s="12"/>
+      <c r="Q32" s="15" t="str">
+        <f aca="false">IFERROR(IF(P32="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P32,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
+        <v>Sem data de comunicação efetiva registrada</v>
+      </c>
+      <c r="R32" s="11"/>
+    </row>
+    <row r="33" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="10"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="13" t="str">
+        <f aca="false">IFERROR(IF(C33="","",WORKDAY(C33,IF(D33="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <v/>
+      </c>
+      <c r="F33" s="14"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="11"/>
+      <c r="K33" s="11"/>
+      <c r="L33" s="11"/>
+      <c r="M33" s="11"/>
+      <c r="N33" s="12"/>
+      <c r="O33" s="11"/>
+      <c r="P33" s="12"/>
+      <c r="Q33" s="15" t="str">
+        <f aca="false">IFERROR(IF(P33="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P33,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
+        <v>Sem data de comunicação efetiva registrada</v>
+      </c>
+      <c r="R33" s="11"/>
+    </row>
+    <row r="34" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="10"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="13" t="str">
+        <f aca="false">IFERROR(IF(C34="","",WORKDAY(C34,IF(D34="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <v/>
+      </c>
+      <c r="F34" s="14"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
+      <c r="J34" s="11"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
+      <c r="M34" s="11"/>
+      <c r="N34" s="12"/>
+      <c r="O34" s="11"/>
+      <c r="P34" s="12"/>
+      <c r="Q34" s="15" t="str">
+        <f aca="false">IFERROR(IF(P34="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P34,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
+        <v>Sem data de comunicação efetiva registrada</v>
+      </c>
+      <c r="R34" s="11"/>
+    </row>
+    <row r="35" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="10"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="13" t="str">
+        <f aca="false">IFERROR(IF(C35="","",WORKDAY(C35,IF(D35="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <v/>
+      </c>
+      <c r="F35" s="14"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="11"/>
+      <c r="J35" s="11"/>
+      <c r="K35" s="11"/>
+      <c r="L35" s="11"/>
+      <c r="M35" s="11"/>
+      <c r="N35" s="12"/>
+      <c r="O35" s="11"/>
+      <c r="P35" s="12"/>
+      <c r="Q35" s="15" t="str">
+        <f aca="false">IFERROR(IF(P35="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P35,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
+        <v>Sem data de comunicação efetiva registrada</v>
+      </c>
+      <c r="R35" s="11"/>
+    </row>
+    <row r="36" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="10"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="13" t="str">
+        <f aca="false">IFERROR(IF(C36="","",WORKDAY(C36,IF(D36="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <v/>
+      </c>
+      <c r="F36" s="14"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="11"/>
+      <c r="J36" s="11"/>
+      <c r="K36" s="11"/>
+      <c r="L36" s="11"/>
+      <c r="M36" s="11"/>
+      <c r="N36" s="12"/>
+      <c r="O36" s="11"/>
+      <c r="P36" s="12"/>
+      <c r="Q36" s="15" t="str">
+        <f aca="false">IFERROR(IF(P36="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P36,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
+        <v>Sem data de comunicação efetiva registrada</v>
+      </c>
+      <c r="R36" s="11"/>
+    </row>
+    <row r="37" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="10"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="13" t="str">
+        <f aca="false">IFERROR(IF(C37="","",WORKDAY(C37,IF(D37="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <v/>
+      </c>
+      <c r="F37" s="14"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="11"/>
+      <c r="J37" s="11"/>
+      <c r="K37" s="11"/>
+      <c r="L37" s="11"/>
+      <c r="M37" s="11"/>
+      <c r="N37" s="12"/>
+      <c r="O37" s="11"/>
+      <c r="P37" s="12"/>
+      <c r="Q37" s="15" t="str">
+        <f aca="false">IFERROR(IF(P37="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P37,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
+        <v>Sem data de comunicação efetiva registrada</v>
+      </c>
+      <c r="R37" s="11"/>
+    </row>
+    <row r="38" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="10"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="12"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="13" t="str">
+        <f aca="false">IFERROR(IF(C38="","",WORKDAY(C38,IF(D38="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <v/>
+      </c>
+      <c r="F38" s="14"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="11"/>
+      <c r="J38" s="11"/>
+      <c r="K38" s="11"/>
+      <c r="L38" s="11"/>
+      <c r="M38" s="11"/>
+      <c r="N38" s="12"/>
+      <c r="O38" s="11"/>
+      <c r="P38" s="12"/>
+      <c r="Q38" s="15" t="str">
+        <f aca="false">IFERROR(IF(P38="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P38,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
+        <v>Sem data de comunicação efetiva registrada</v>
+      </c>
+      <c r="R38" s="11"/>
+    </row>
+    <row r="39" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="10"/>
+      <c r="B39" s="11"/>
+      <c r="C39" s="12"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="13" t="str">
+        <f aca="false">IFERROR(IF(C39="","",WORKDAY(C39,IF(D39="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <v/>
+      </c>
+      <c r="F39" s="14"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="11"/>
+      <c r="I39" s="11"/>
+      <c r="J39" s="11"/>
+      <c r="K39" s="11"/>
+      <c r="L39" s="11"/>
+      <c r="M39" s="11"/>
+      <c r="N39" s="12"/>
+      <c r="O39" s="11"/>
+      <c r="P39" s="12"/>
+      <c r="Q39" s="15" t="str">
+        <f aca="false">IFERROR(IF(P39="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P39,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
+        <v>Sem data de comunicação efetiva registrada</v>
+      </c>
+      <c r="R39" s="11"/>
+    </row>
+    <row r="40" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="10"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="12"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="13" t="str">
+        <f aca="false">IFERROR(IF(C40="","",WORKDAY(C40,IF(D40="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <v/>
+      </c>
+      <c r="F40" s="14"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="11"/>
+      <c r="I40" s="11"/>
+      <c r="J40" s="11"/>
+      <c r="K40" s="11"/>
+      <c r="L40" s="11"/>
+      <c r="M40" s="11"/>
+      <c r="N40" s="12"/>
+      <c r="O40" s="11"/>
+      <c r="P40" s="12"/>
+      <c r="Q40" s="15" t="str">
+        <f aca="false">IFERROR(IF(P40="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P40,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
+        <v>Sem data de comunicação efetiva registrada</v>
+      </c>
+      <c r="R40" s="11"/>
+    </row>
+    <row r="41" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="10"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="13" t="str">
+        <f aca="false">IFERROR(IF(C41="","",WORKDAY(C41,IF(D41="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <v/>
+      </c>
+      <c r="F41" s="14"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="11"/>
+      <c r="I41" s="11"/>
+      <c r="J41" s="11"/>
+      <c r="K41" s="11"/>
+      <c r="L41" s="11"/>
+      <c r="M41" s="11"/>
+      <c r="N41" s="12"/>
+      <c r="O41" s="11"/>
+      <c r="P41" s="12"/>
+      <c r="Q41" s="15" t="str">
+        <f aca="false">IFERROR(IF(P41="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P41,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
+        <v>Sem data de comunicação efetiva registrada</v>
+      </c>
+      <c r="R41" s="11"/>
+    </row>
+    <row r="42" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="10"/>
+      <c r="B42" s="11"/>
+      <c r="C42" s="12"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="13" t="str">
+        <f aca="false">IFERROR(IF(C42="","",WORKDAY(C42,IF(D42="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <v/>
+      </c>
+      <c r="F42" s="14"/>
+      <c r="G42" s="11"/>
+      <c r="H42" s="11"/>
+      <c r="I42" s="11"/>
+      <c r="J42" s="11"/>
+      <c r="K42" s="11"/>
+      <c r="L42" s="11"/>
+      <c r="M42" s="11"/>
+      <c r="N42" s="12"/>
+      <c r="O42" s="11"/>
+      <c r="P42" s="12"/>
+      <c r="Q42" s="15" t="str">
+        <f aca="false">IFERROR(IF(P42="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P42,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
+        <v>Sem data de comunicação efetiva registrada</v>
+      </c>
+      <c r="R42" s="11"/>
+    </row>
+    <row r="43" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="10"/>
+      <c r="B43" s="11"/>
+      <c r="C43" s="12"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="13" t="str">
+        <f aca="false">IFERROR(IF(C43="","",WORKDAY(C43,IF(D43="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <v/>
+      </c>
+      <c r="F43" s="14"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="11"/>
+      <c r="I43" s="11"/>
+      <c r="J43" s="11"/>
+      <c r="K43" s="11"/>
+      <c r="L43" s="11"/>
+      <c r="M43" s="11"/>
+      <c r="N43" s="12"/>
+      <c r="O43" s="11"/>
+      <c r="P43" s="12"/>
+      <c r="Q43" s="15" t="str">
+        <f aca="false">IFERROR(IF(P43="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P43,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
+        <v>Sem data de comunicação efetiva registrada</v>
+      </c>
+      <c r="R43" s="11"/>
+    </row>
+    <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="10"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="12"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="13" t="str">
+        <f aca="false">IFERROR(IF(C44="","",WORKDAY(C44,IF(D44="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <v/>
+      </c>
+      <c r="F44" s="14"/>
+      <c r="G44" s="11"/>
+      <c r="H44" s="11"/>
+      <c r="I44" s="11"/>
+      <c r="J44" s="11"/>
+      <c r="K44" s="11"/>
+      <c r="L44" s="11"/>
+      <c r="M44" s="11"/>
+      <c r="N44" s="12"/>
+      <c r="O44" s="11"/>
+      <c r="P44" s="12"/>
+      <c r="Q44" s="15" t="str">
+        <f aca="false">IFERROR(IF(P44="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P44,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
+        <v>Sem data de comunicação efetiva registrada</v>
+      </c>
+      <c r="R44" s="11"/>
+    </row>
+    <row r="45" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="10"/>
+      <c r="B45" s="11"/>
+      <c r="C45" s="12"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="13" t="str">
+        <f aca="false">IFERROR(IF(C45="","",WORKDAY(C45,IF(D45="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <v/>
+      </c>
+      <c r="F45" s="14"/>
+      <c r="G45" s="11"/>
+      <c r="H45" s="11"/>
+      <c r="I45" s="11"/>
+      <c r="J45" s="11"/>
+      <c r="K45" s="11"/>
+      <c r="L45" s="11"/>
+      <c r="M45" s="11"/>
+      <c r="N45" s="12"/>
+      <c r="O45" s="11"/>
+      <c r="P45" s="12"/>
+      <c r="Q45" s="15" t="str">
+        <f aca="false">IFERROR(IF(P45="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P45,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
+        <v>Sem data de comunicação efetiva registrada</v>
+      </c>
+      <c r="R45" s="11"/>
+    </row>
+    <row r="46" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="10"/>
+      <c r="B46" s="11"/>
+      <c r="C46" s="12"/>
+      <c r="D46" s="11"/>
+      <c r="E46" s="13" t="str">
+        <f aca="false">IFERROR(IF(C46="","",WORKDAY(C46,IF(D46="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <v/>
+      </c>
+      <c r="F46" s="14"/>
+      <c r="G46" s="11"/>
+      <c r="H46" s="11"/>
+      <c r="I46" s="11"/>
+      <c r="J46" s="11"/>
+      <c r="K46" s="11"/>
+      <c r="L46" s="11"/>
+      <c r="M46" s="11"/>
+      <c r="N46" s="12"/>
+      <c r="O46" s="11"/>
+      <c r="P46" s="12"/>
+      <c r="Q46" s="15" t="str">
+        <f aca="false">IFERROR(IF(P46="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P46,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
+        <v>Sem data de comunicação efetiva registrada</v>
+      </c>
+      <c r="R46" s="11"/>
+    </row>
+    <row r="47" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="10"/>
+      <c r="B47" s="11"/>
+      <c r="C47" s="12"/>
+      <c r="D47" s="11"/>
+      <c r="E47" s="13" t="str">
+        <f aca="false">IFERROR(IF(C47="","",WORKDAY(C47,IF(D47="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <v/>
+      </c>
+      <c r="F47" s="14"/>
+      <c r="G47" s="11"/>
+      <c r="H47" s="11"/>
+      <c r="I47" s="11"/>
+      <c r="J47" s="11"/>
+      <c r="K47" s="11"/>
+      <c r="L47" s="11"/>
+      <c r="M47" s="11"/>
+      <c r="N47" s="12"/>
+      <c r="O47" s="11"/>
+      <c r="P47" s="12"/>
+      <c r="Q47" s="15" t="str">
+        <f aca="false">IFERROR(IF(P47="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P47,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
+        <v>Sem data de comunicação efetiva registrada</v>
+      </c>
+      <c r="R47" s="11"/>
+    </row>
+    <row r="48" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="10"/>
+      <c r="B48" s="11"/>
+      <c r="C48" s="12"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="13" t="str">
+        <f aca="false">IFERROR(IF(C48="","",WORKDAY(C48,IF(D48="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <v/>
+      </c>
+      <c r="F48" s="14"/>
+      <c r="G48" s="11"/>
+      <c r="H48" s="11"/>
+      <c r="I48" s="11"/>
+      <c r="J48" s="11"/>
+      <c r="K48" s="11"/>
+      <c r="L48" s="11"/>
+      <c r="M48" s="11"/>
+      <c r="N48" s="12"/>
+      <c r="O48" s="11"/>
+      <c r="P48" s="12"/>
+      <c r="Q48" s="15" t="str">
+        <f aca="false">IFERROR(IF(P48="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P48,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
+        <v>Sem data de comunicação efetiva registrada</v>
+      </c>
+      <c r="R48" s="11"/>
+    </row>
+    <row r="49" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="10"/>
+      <c r="B49" s="11"/>
+      <c r="C49" s="12"/>
+      <c r="D49" s="11"/>
+      <c r="E49" s="13" t="str">
+        <f aca="false">IFERROR(IF(C49="","",WORKDAY(C49,IF(D49="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <v/>
+      </c>
+      <c r="F49" s="14"/>
+      <c r="G49" s="11"/>
+      <c r="H49" s="11"/>
+      <c r="I49" s="11"/>
+      <c r="J49" s="11"/>
+      <c r="K49" s="11"/>
+      <c r="L49" s="11"/>
+      <c r="M49" s="11"/>
+      <c r="N49" s="12"/>
+      <c r="O49" s="11"/>
+      <c r="P49" s="12"/>
+      <c r="Q49" s="15" t="str">
+        <f aca="false">IFERROR(IF(P49="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P49,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
+        <v>Sem data de comunicação efetiva registrada</v>
+      </c>
+      <c r="R49" s="11"/>
+    </row>
+    <row r="50" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="10"/>
+      <c r="B50" s="11"/>
+      <c r="C50" s="12"/>
+      <c r="D50" s="11"/>
+      <c r="E50" s="13" t="str">
+        <f aca="false">IFERROR(IF(C50="","",WORKDAY(C50,IF(D50="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <v/>
+      </c>
+      <c r="F50" s="14"/>
+      <c r="G50" s="11"/>
+      <c r="H50" s="11"/>
+      <c r="I50" s="11"/>
+      <c r="J50" s="11"/>
+      <c r="K50" s="11"/>
+      <c r="L50" s="11"/>
+      <c r="M50" s="11"/>
+      <c r="N50" s="12"/>
+      <c r="O50" s="11"/>
+      <c r="P50" s="12"/>
+      <c r="Q50" s="15" t="str">
+        <f aca="false">IFERROR(IF(P50="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P50,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
+        <v>Sem data de comunicação efetiva registrada</v>
+      </c>
+      <c r="R50" s="11"/>
+    </row>
+    <row r="51" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="10"/>
+      <c r="B51" s="11"/>
+      <c r="C51" s="12"/>
+      <c r="D51" s="11"/>
+      <c r="E51" s="13" t="str">
+        <f aca="false">IFERROR(IF(C51="","",WORKDAY(C51,IF(D51="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <v/>
+      </c>
+      <c r="F51" s="14"/>
+      <c r="G51" s="11"/>
+      <c r="H51" s="11"/>
+      <c r="I51" s="11"/>
+      <c r="J51" s="11"/>
+      <c r="K51" s="11"/>
+      <c r="L51" s="11"/>
+      <c r="M51" s="11"/>
+      <c r="N51" s="12"/>
+      <c r="O51" s="11"/>
+      <c r="P51" s="12"/>
+      <c r="Q51" s="15" t="str">
+        <f aca="false">IFERROR(IF(P51="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P51,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
+        <v>Sem data de comunicação efetiva registrada</v>
+      </c>
+      <c r="R51" s="11"/>
+    </row>
+    <row r="52" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="10"/>
+      <c r="B52" s="11"/>
+      <c r="C52" s="12"/>
+      <c r="D52" s="11"/>
+      <c r="E52" s="13" t="str">
+        <f aca="false">IFERROR(IF(C52="","",WORKDAY(C52,IF(D52="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <v/>
+      </c>
+      <c r="F52" s="14"/>
+      <c r="G52" s="11"/>
+      <c r="H52" s="11"/>
+      <c r="I52" s="11"/>
+      <c r="J52" s="11"/>
+      <c r="K52" s="11"/>
+      <c r="L52" s="11"/>
+      <c r="M52" s="11"/>
+      <c r="N52" s="12"/>
+      <c r="O52" s="11"/>
+      <c r="P52" s="12"/>
+      <c r="Q52" s="15" t="str">
+        <f aca="false">IFERROR(IF(P52="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P52,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
+        <v>Sem data de comunicação efetiva registrada</v>
+      </c>
+      <c r="R52" s="11"/>
+    </row>
+    <row r="53" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="10"/>
+      <c r="B53" s="11"/>
+      <c r="C53" s="12"/>
+      <c r="D53" s="11"/>
+      <c r="E53" s="13" t="str">
+        <f aca="false">IFERROR(IF(C53="","",WORKDAY(C53,IF(D53="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <v/>
+      </c>
+      <c r="F53" s="14"/>
+      <c r="G53" s="11"/>
+      <c r="H53" s="11"/>
+      <c r="I53" s="11"/>
+      <c r="J53" s="11"/>
+      <c r="K53" s="11"/>
+      <c r="L53" s="11"/>
+      <c r="M53" s="11"/>
+      <c r="N53" s="12"/>
+      <c r="O53" s="11"/>
+      <c r="P53" s="12"/>
+      <c r="Q53" s="15" t="str">
+        <f aca="false">IFERROR(IF(P53="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P53,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
+        <v>Sem data de comunicação efetiva registrada</v>
+      </c>
+      <c r="R53" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A2:R2"/>
   </mergeCells>
-  <dataValidations count="48">
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F4" type="list">
-      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G4" type="list">
-      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K4" type="list">
-      <formula1>"Não aplicável,Planejada,Aprovada,Realizada,Complementação pendente"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F5" type="list">
-      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G5" type="list">
-      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K5" type="list">
-      <formula1>"Não aplicável,Planejada,Aprovada,Realizada,Complementação pendente"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F6" type="list">
-      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G6" type="list">
-      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K6" type="list">
-      <formula1>"Não aplicável,Planejada,Aprovada,Realizada,Complementação pendente"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F7" type="list">
-      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G7" type="list">
-      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K7" type="list">
-      <formula1>"Não aplicável,Planejada,Aprovada,Realizada,Complementação pendente"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F8" type="list">
-      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G8" type="list">
-      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K8" type="list">
-      <formula1>"Não aplicável,Planejada,Aprovada,Realizada,Complementação pendente"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F9" type="list">
-      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G9" type="list">
-      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K9" type="list">
-      <formula1>"Não aplicável,Planejada,Aprovada,Realizada,Complementação pendente"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F10" type="list">
-      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G10" type="list">
-      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K10" type="list">
-      <formula1>"Não aplicável,Planejada,Aprovada,Realizada,Complementação pendente"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F11" type="list">
-      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G11" type="list">
-      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K11" type="list">
-      <formula1>"Não aplicável,Planejada,Aprovada,Realizada,Complementação pendente"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F12" type="list">
-      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G12" type="list">
-      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K12" type="list">
-      <formula1>"Não aplicável,Planejada,Aprovada,Realizada,Complementação pendente"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F13" type="list">
-      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G13" type="list">
-      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K13" type="list">
-      <formula1>"Não aplicável,Planejada,Aprovada,Realizada,Complementação pendente"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F14" type="list">
-      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G14" type="list">
-      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K14" type="list">
-      <formula1>"Não aplicável,Planejada,Aprovada,Realizada,Complementação pendente"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F15" type="list">
-      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G15" type="list">
-      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K15" type="list">
-      <formula1>"Não aplicável,Planejada,Aprovada,Realizada,Complementação pendente"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F16" type="list">
-      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G16" type="list">
-      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K16" type="list">
-      <formula1>"Não aplicável,Planejada,Aprovada,Realizada,Complementação pendente"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F17" type="list">
-      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G17" type="list">
-      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K17" type="list">
-      <formula1>"Não aplicável,Planejada,Aprovada,Realizada,Complementação pendente"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F18" type="list">
-      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G18" type="list">
-      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K18" type="list">
-      <formula1>"Não aplicável,Planejada,Aprovada,Realizada,Complementação pendente"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F19" type="list">
-      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G19" type="list">
-      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K19" type="list">
-      <formula1>"Não aplicável,Planejada,Aprovada,Realizada,Complementação pendente"</formula1>
+  <conditionalFormatting sqref="A4:A53">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>AND(A4&lt;&gt;"",COUNTIF($A$4:$A$53,A4)&gt;1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>AND($A4&lt;&gt;"",OR(COUNTIFS(Caracterizacao!$A$4:$A$53,$A4,Caracterizacao!$B$4:$B$53,$B4)=0,COUNTIFS(Avaliacao_Regulatoria!$A$4:$A$53,$A4,Avaliacao_Regulatoria!$B$4:$B$53,$B4)=0))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="151">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D4" type="list">
+      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K4" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L4" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D5" type="list">
+      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K5" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L5" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D6" type="list">
+      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K6" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L6" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D7" type="list">
+      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K7" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L7" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D8" type="list">
+      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K8" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L8" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D9" type="list">
+      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K9" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L9" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D10" type="list">
+      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K10" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L10" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D11" type="list">
+      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K11" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L11" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D12" type="list">
+      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K12" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L12" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D13" type="list">
+      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K13" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L13" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D14" type="list">
+      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K14" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L14" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D15" type="list">
+      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K15" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L15" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D16" type="list">
+      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K16" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L16" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D17" type="list">
+      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K17" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L17" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D18" type="list">
+      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K18" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L18" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D19" type="list">
+      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K19" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L19" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D20" type="list">
+      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K20" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L20" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D21" type="list">
+      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K21" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L21" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D22" type="list">
+      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K22" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L22" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D23" type="list">
+      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K23" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L23" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D24" type="list">
+      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K24" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L24" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D25" type="list">
+      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K25" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L25" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D26" type="list">
+      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K26" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L26" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D27" type="list">
+      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K27" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L27" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D28" type="list">
+      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K28" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L28" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D29" type="list">
+      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K29" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L29" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D30" type="list">
+      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K30" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L30" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D31" type="list">
+      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K31" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L31" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D32" type="list">
+      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K32" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L32" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D33" type="list">
+      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K33" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L33" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D34" type="list">
+      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K34" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L34" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D35" type="list">
+      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K35" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L35" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D36" type="list">
+      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K36" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L36" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D37" type="list">
+      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K37" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L37" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D38" type="list">
+      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K38" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L38" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D39" type="list">
+      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K39" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L39" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D40" type="list">
+      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K40" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L40" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D41" type="list">
+      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K41" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L41" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D42" type="list">
+      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K42" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L42" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D43" type="list">
+      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K43" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L43" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D44" type="list">
+      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K44" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L44" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D45" type="list">
+      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K45" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L45" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D46" type="list">
+      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K46" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L46" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D47" type="list">
+      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K47" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L47" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D48" type="list">
+      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K48" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L48" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D49" type="list">
+      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K49" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L49" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D50" type="list">
+      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K50" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L50" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D51" type="list">
+      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K51" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L51" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D52" type="list">
+      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K52" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L52" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D53" type="list">
+      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K53" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L53" type="list">
+      <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Este identificador já existe nesta coluna. Cada ID deve ser único e estável (não reutilize nem renumere IDs já atribuídos). Padrão esperado: AVR-01." errorStyle="stop" errorTitle="ID duplicado" operator="between" prompt="Digite um identificador único e estável, padrão AVR-01. Não é gerado automaticamente — preserve o mesmo ID após inserir, excluir ou reordenar linhas." promptTitle="Identificador manual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A4:A53" type="custom">
+      <formula1>OR(A4="",COUNTIF($A$4:$A$53,A4)&lt;=1)</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -2978,7 +7849,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
@@ -2993,7 +7864,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3006,7 +7877,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -3019,70 +7890,66 @@
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>106</v>
+        <v>133</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>110</v>
+        <v>137</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>111</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="str">
-        <f aca="false">IF(C4="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v>AVR-01</v>
+      <c r="A4" s="10" t="s">
+        <v>53</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="C4" s="12" t="n">
         <v>46314.5069444445</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>116</v>
+        <v>143</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>117</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="str">
-        <f aca="false">IF(C5="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
+      <c r="A5" s="10"/>
       <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
+      <c r="C5" s="12"/>
       <c r="D5" s="11"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
@@ -3091,12 +7958,9 @@
       <c r="I5" s="11"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="str">
-        <f aca="false">IF(C6="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
+      <c r="A6" s="10"/>
       <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
+      <c r="C6" s="12"/>
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
@@ -3105,12 +7969,9 @@
       <c r="I6" s="11"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="str">
-        <f aca="false">IF(C7="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
+      <c r="A7" s="10"/>
       <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
+      <c r="C7" s="12"/>
       <c r="D7" s="11"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
@@ -3119,12 +7980,9 @@
       <c r="I7" s="11"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10" t="str">
-        <f aca="false">IF(C8="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
+      <c r="A8" s="10"/>
       <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
+      <c r="C8" s="12"/>
       <c r="D8" s="11"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
@@ -3133,12 +7991,9 @@
       <c r="I8" s="11"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="str">
-        <f aca="false">IF(C9="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
+      <c r="A9" s="10"/>
       <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
+      <c r="C9" s="12"/>
       <c r="D9" s="11"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
@@ -3147,12 +8002,9 @@
       <c r="I9" s="11"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10" t="str">
-        <f aca="false">IF(C10="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
+      <c r="A10" s="10"/>
       <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
+      <c r="C10" s="12"/>
       <c r="D10" s="11"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
@@ -3161,12 +8013,9 @@
       <c r="I10" s="11"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10" t="str">
-        <f aca="false">IF(C11="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
+      <c r="A11" s="10"/>
       <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
+      <c r="C11" s="12"/>
       <c r="D11" s="11"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
@@ -3175,12 +8024,9 @@
       <c r="I11" s="11"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10" t="str">
-        <f aca="false">IF(C12="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
+      <c r="A12" s="10"/>
       <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
+      <c r="C12" s="12"/>
       <c r="D12" s="11"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
@@ -3189,12 +8035,9 @@
       <c r="I12" s="11"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10" t="str">
-        <f aca="false">IF(C13="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
+      <c r="A13" s="10"/>
       <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
+      <c r="C13" s="12"/>
       <c r="D13" s="11"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
@@ -3203,12 +8046,9 @@
       <c r="I13" s="11"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10" t="str">
-        <f aca="false">IF(C14="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
+      <c r="A14" s="10"/>
       <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
+      <c r="C14" s="12"/>
       <c r="D14" s="11"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
@@ -3217,12 +8057,9 @@
       <c r="I14" s="11"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10" t="str">
-        <f aca="false">IF(C15="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
+      <c r="A15" s="10"/>
       <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
+      <c r="C15" s="12"/>
       <c r="D15" s="11"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
@@ -3231,12 +8068,9 @@
       <c r="I15" s="11"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10" t="str">
-        <f aca="false">IF(C16="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
+      <c r="A16" s="10"/>
       <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
+      <c r="C16" s="12"/>
       <c r="D16" s="11"/>
       <c r="E16" s="11"/>
       <c r="F16" s="11"/>
@@ -3245,12 +8079,9 @@
       <c r="I16" s="11"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10" t="str">
-        <f aca="false">IF(C17="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
+      <c r="A17" s="10"/>
       <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
+      <c r="C17" s="12"/>
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
@@ -3259,12 +8090,9 @@
       <c r="I17" s="11"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10" t="str">
-        <f aca="false">IF(C18="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
+      <c r="A18" s="10"/>
       <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
+      <c r="C18" s="12"/>
       <c r="D18" s="11"/>
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
@@ -3273,12 +8101,9 @@
       <c r="I18" s="11"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10" t="str">
-        <f aca="false">IF(C19="","","AVR-"&amp;TEXT(ROW()-3,"00"))</f>
-        <v/>
-      </c>
+      <c r="A19" s="10"/>
       <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
+      <c r="C19" s="12"/>
       <c r="D19" s="11"/>
       <c r="E19" s="11"/>
       <c r="F19" s="11"/>
@@ -3286,11 +8111,399 @@
       <c r="H19" s="11"/>
       <c r="I19" s="11"/>
     </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="10"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="10"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="10"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="10"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="10"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="10"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="10"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="10"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="10"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="10"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="10"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="10"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="10"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="10"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="10"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="10"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="11"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="10"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="11"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="10"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="11"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="10"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="12"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="11"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="10"/>
+      <c r="B39" s="11"/>
+      <c r="C39" s="12"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="11"/>
+      <c r="I39" s="11"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="10"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="12"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="11"/>
+      <c r="I40" s="11"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="10"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="11"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="11"/>
+      <c r="I41" s="11"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="10"/>
+      <c r="B42" s="11"/>
+      <c r="C42" s="12"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="11"/>
+      <c r="F42" s="11"/>
+      <c r="G42" s="11"/>
+      <c r="H42" s="11"/>
+      <c r="I42" s="11"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="10"/>
+      <c r="B43" s="11"/>
+      <c r="C43" s="12"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="11"/>
+      <c r="I43" s="11"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="10"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="12"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="11"/>
+      <c r="F44" s="11"/>
+      <c r="G44" s="11"/>
+      <c r="H44" s="11"/>
+      <c r="I44" s="11"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="10"/>
+      <c r="B45" s="11"/>
+      <c r="C45" s="12"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="11"/>
+      <c r="F45" s="11"/>
+      <c r="G45" s="11"/>
+      <c r="H45" s="11"/>
+      <c r="I45" s="11"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="10"/>
+      <c r="B46" s="11"/>
+      <c r="C46" s="12"/>
+      <c r="D46" s="11"/>
+      <c r="E46" s="11"/>
+      <c r="F46" s="11"/>
+      <c r="G46" s="11"/>
+      <c r="H46" s="11"/>
+      <c r="I46" s="11"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="10"/>
+      <c r="B47" s="11"/>
+      <c r="C47" s="12"/>
+      <c r="D47" s="11"/>
+      <c r="E47" s="11"/>
+      <c r="F47" s="11"/>
+      <c r="G47" s="11"/>
+      <c r="H47" s="11"/>
+      <c r="I47" s="11"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="10"/>
+      <c r="B48" s="11"/>
+      <c r="C48" s="12"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="11"/>
+      <c r="F48" s="11"/>
+      <c r="G48" s="11"/>
+      <c r="H48" s="11"/>
+      <c r="I48" s="11"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="10"/>
+      <c r="B49" s="11"/>
+      <c r="C49" s="12"/>
+      <c r="D49" s="11"/>
+      <c r="E49" s="11"/>
+      <c r="F49" s="11"/>
+      <c r="G49" s="11"/>
+      <c r="H49" s="11"/>
+      <c r="I49" s="11"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="10"/>
+      <c r="B50" s="11"/>
+      <c r="C50" s="12"/>
+      <c r="D50" s="11"/>
+      <c r="E50" s="11"/>
+      <c r="F50" s="11"/>
+      <c r="G50" s="11"/>
+      <c r="H50" s="11"/>
+      <c r="I50" s="11"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="10"/>
+      <c r="B51" s="11"/>
+      <c r="C51" s="12"/>
+      <c r="D51" s="11"/>
+      <c r="E51" s="11"/>
+      <c r="F51" s="11"/>
+      <c r="G51" s="11"/>
+      <c r="H51" s="11"/>
+      <c r="I51" s="11"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="10"/>
+      <c r="B52" s="11"/>
+      <c r="C52" s="12"/>
+      <c r="D52" s="11"/>
+      <c r="E52" s="11"/>
+      <c r="F52" s="11"/>
+      <c r="G52" s="11"/>
+      <c r="H52" s="11"/>
+      <c r="I52" s="11"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="10"/>
+      <c r="B53" s="11"/>
+      <c r="C53" s="12"/>
+      <c r="D53" s="11"/>
+      <c r="E53" s="11"/>
+      <c r="F53" s="11"/>
+      <c r="G53" s="11"/>
+      <c r="H53" s="11"/>
+      <c r="I53" s="11"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
+  <conditionalFormatting sqref="A4:A53">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>AND(A4&lt;&gt;"",COUNTIF($A$4:$A$53,A4)&gt;1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>AND($A4&lt;&gt;"",OR(COUNTIFS(Caracterizacao!$A$4:$A$53,$A4,Caracterizacao!$B$4:$B$53,$B4)=0,COUNTIFS(Avaliacao_Regulatoria!$A$4:$A$53,$A4,Avaliacao_Regulatoria!$B$4:$B$53,$B4)=0,COUNTIFS(Decisao_Comunicacao!$A$4:$A$53,$A4,Decisao_Comunicacao!$B$4:$B$53,$B4)=0))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" error="Este identificador já existe nesta coluna. Cada ID deve ser único e estável (não reutilize nem renumere IDs já atribuídos). Padrão esperado: AVR-02." errorStyle="stop" errorTitle="ID duplicado" operator="between" prompt="Digite um identificador único e estável, padrão AVR-02. Não é gerado automaticamente — preserve o mesmo ID após inserir, excluir ou reordenar linhas." promptTitle="Identificador manual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A4:A53" type="custom">
+      <formula1>OR(A4="",COUNTIF($A$4:$A$53,A4)&lt;=1)</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -3298,6 +8511,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -3315,7 +8529,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3325,7 +8539,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -3334,92 +8548,92 @@
       <c r="F2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
+      <c r="A3" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>123</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="E5" s="16" t="s">
-        <v>125</v>
+      <c r="A5" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="E6" s="19" t="s">
-        <v>129</v>
+      <c r="A6" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="17" t="s">
-        <v>130</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="E7" s="20" t="s">
-        <v>131</v>
+      <c r="A7" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="17" t="s">
-        <v>132</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="E8" s="20" t="s">
-        <v>131</v>
+      <c r="A8" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="21" t="s">
-        <v>133</v>
-      </c>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
+      <c r="A10" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="B10" s="23"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/instrumentos/exemplos/DAIR_Avaliacao_Riscos_Titulares_ANPD_v0.3_EXEMPLO-INC-2026-001.xlsx
+++ b/instrumentos/exemplos/DAIR_Avaliacao_Riscos_Titulares_ANPD_v0.3_EXEMPLO-INC-2026-001.xlsx
@@ -38,7 +38,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">ID manual e estável — A02/A03. Padrão AVR-NN. É esta ID (não a linha) que liga o mesmo registro de versão entre as quatro abas deste arquivo. Formatação condicional (A03): sinaliza em vermelho se a MESMA combinação ID+Versão não existir também em Avaliacao_Regulatoria e em Decisao_Comunicacao — reconciliação por existência cruzada, não por posição de linha nem por coincidência entre a ID e o número da versão.</t>
+          <t xml:space="preserve">ID manual e estável: A02/A03. Padrão AVR-NN. É esta ID (não a linha) que liga o mesmo registro de versão entre as quatro abas deste arquivo. Formatação condicional (A03): sinaliza em vermelho se a MESMA combinação ID+Versão não existir também em Avaliacao_Regulatoria e em Decisao_Comunicacao: reconciliação por existência cruzada, não por posição de linha nem por coincidência entre a ID e o número da versão.</t>
         </r>
       </text>
     </comment>
@@ -50,7 +50,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Número da versão (1, 2, 3...). Não precisa coincidir com os dígitos da ID — a reconciliação entre abas é feita pela combinação ID+Versão (coluna A, nota ao lado), verificada por fórmula.</t>
+          <t xml:space="preserve">Número da versão (1, 2, 3...). Não precisa coincidir com os dígitos da ID: a reconciliação entre abas é feita pela combinação ID+Versão (coluna A, nota ao lado), verificada por fórmula.</t>
         </r>
       </text>
     </comment>
@@ -72,7 +72,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">ID manual e estável — A02/A03. A mesma combinação ID+Versão deve existir também em Caracterizacao e em Decisao_Comunicacao para a mesma versão — verificado por fórmula (A03), não por posição de linha.</t>
+          <t xml:space="preserve">ID manual e estável: A02/A03. A mesma combinação ID+Versão deve existir também em Caracterizacao e em Decisao_Comunicacao para a mesma versão: verificado por fórmula (A03), não por posição de linha.</t>
         </r>
       </text>
     </comment>
@@ -84,7 +84,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Não trate a quantidade de titulares, isoladamente, como prova de dado financeiro ou de larga escala — fundamente separadamente cada um na coluna L (A08).</t>
+          <t xml:space="preserve">Não trate a quantidade de titulares, isoladamente, como prova de dado financeiro ou de larga escala: fundamente separadamente cada um na coluna L (A08).</t>
         </r>
       </text>
     </comment>
@@ -96,7 +96,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">'Larga escala' não tem limiar numérico definido no RCIS nem em orientação oficial da ANPD — fundamente qualitativamente (volume, abrangência, duração, proporção da base) na coluna L, sem usar um número de titulares como regra automática (A08).</t>
+          <t xml:space="preserve">'Larga escala' não tem limiar numérico definido no RCIS nem em orientação oficial da ANPD: fundamente qualitativamente (volume, abrangência, duração, proporção da base) na coluna L, sem usar um número de titulares como regra automática (A08).</t>
         </r>
       </text>
     </comment>
@@ -108,7 +108,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Calculado a partir das colunas D a I (não editar). Atendida se qualquer inciso I a VI estiver marcado 'Sim' — corrige a redação anterior que citava apenas o inciso II (A05).</t>
+          <t xml:space="preserve">Calculado a partir das colunas D a I (não editar). Atendida se qualquer inciso I a VI estiver marcado 'Sim': corrige a redação anterior que citava apenas o inciso II (A05).</t>
         </r>
       </text>
     </comment>
@@ -130,7 +130,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">ID manual e estável — A02/A03. A mesma combinação ID+Versão deve existir também em Caracterizacao e em Avaliacao_Regulatoria — verificado por fórmula (A03).</t>
+          <t xml:space="preserve">ID manual e estável: A02/A03. A mesma combinação ID+Versão deve existir também em Caracterizacao e em Avaliacao_Regulatoria: verificado por fórmula (A03).</t>
         </r>
       </text>
     </comment>
@@ -142,7 +142,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Cálculo de apoio: WORKDAY(marco, 3 ou 6 dias úteis conforme pequeno porte) — NÃO considera feriados nacionais/municipais nem prazo setorial específico (A06). Não presume pequeno porte: use o campo de elegibilidade ao lado.</t>
+          <t xml:space="preserve">Cálculo de apoio: WORKDAY(marco, 3 ou 6 dias úteis conforme pequeno porte); NÃO considera feriados nacionais/municipais nem prazo setorial específico (A06). Não presume pequeno porte: use o campo de elegibilidade ao lado.</t>
         </r>
       </text>
     </comment>
@@ -154,7 +154,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Campo que efetivamente vale. Preencha com fundamento, calendário de referência e responsável (colunas G a I) — não decorre apenas da fórmula de apoio.</t>
+          <t xml:space="preserve">Campo que efetivamente vale. Preencha com fundamento, calendário de referência e responsável (colunas G a I): não decorre apenas da fórmula de apoio.</t>
         </r>
       </text>
     </comment>
@@ -188,7 +188,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">ID manual e estável — A02/A03. Registre aqui a ID DA VERSÃO DE CHEGADA (ex.: ao documentar a mudança de v1 para v2, a ID desta linha é AVR-02, igual à da mesma versão nas demais abas — não AVR-01). Formatação condicional (A03): sinaliza em vermelho se a combinação ID+Versão desta linha não existir nas três abas anteriores — é esse teste cruzado, e não a posição da linha nem os dígitos da ID, que comprova a reconciliação.</t>
+          <t xml:space="preserve">ID manual e estável: A02/A03. Registre aqui a ID DA VERSÃO DE CHEGADA (ex.: ao documentar a mudança de v1 para v2, a ID desta linha é AVR-02, igual à da mesma versão nas demais abas: não AVR-01). Formatação condicional (A03): sinaliza em vermelho se a combinação ID+Versão desta linha não existir nas três abas anteriores; é esse teste cruzado, e não a posição da linha nem os dígitos da ID, que comprova a reconciliação.</t>
         </r>
       </text>
     </comment>
@@ -199,7 +199,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="161">
   <si>
-    <t xml:space="preserve">DAIR — Avaliação de Riscos aos Titulares e Decisão de Comunicação</t>
+    <t xml:space="preserve">DAIR: Avaliação de Riscos aos Titulares e Decisão de Comunicação</t>
   </si>
   <si>
     <t xml:space="preserve">Versão 0.3 · Instrumento 2 de 5 · Modelo reutilizável</t>
@@ -223,46 +223,46 @@
     <t xml:space="preserve">Novas evidências podem alterar a natureza dos dados, o universo de titulares ou as condições de risco. Cada vez que isso ocorrer, registre uma NOVA LINHA com uma NOVA ID de avaliação (AVR-02, AVR-03...) em vez de sobrescrever a anterior. A aba Historico resume o que mudou entre versões.</t>
   </si>
   <si>
-    <t xml:space="preserve">Regra central — leia antes de preencher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Este instrumento NÃO calcula automaticamente se a comunicação é obrigatória. O campo 'Resultado da Avaliação' é preenchido manualmente pelo responsável pela análise e aprovado por quem tem autoridade para isso, com fundamentação registrada. Uma matriz de probabilidade e impacto está disponível na aba Matriz_Apoio apenas para priorização interna — ela não substitui os critérios jurídicos do art. 5º do RCIS e não deve ser citada como fundamento da decisão de comunicação.</t>
+    <t xml:space="preserve">Regra central: leia antes de preencher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Este instrumento NÃO calcula automaticamente se a comunicação é obrigatória. O campo 'Resultado da Avaliação' é preenchido manualmente pelo responsável pela análise e aprovado por quem tem autoridade para isso, com fundamentação registrada. Uma matriz de probabilidade e impacto está disponível na aba Matriz_Apoio apenas para priorização interna: ela não substitui os critérios jurídicos do art. 5º do RCIS e não deve ser citada como fundamento da decisão de comunicação.</t>
   </si>
   <si>
     <t xml:space="preserve">As duas condições cumulativas (art. 5º, caput, do RCIS)</t>
   </si>
   <si>
-    <t xml:space="preserve">Condição A: o incidente pode afetar significativamente interesses e direitos fundamentais dos titulares? Condição B: envolve, cumulativamente, ao menos uma das categorias dos incisos I a VI do art. 5º — I. dados pessoais sensíveis; II. dados de crianças, adolescentes ou idosos; III. dados financeiros; IV. dados de autenticação em sistemas; V. dados sob sigilo legal, judicial ou profissional; VI. tratamento em larga escala. As duas condições são cumulativas — ambas devem estar fundamentadamente demonstradas, e a presença de qualquer um dos seis incisos satisfaz a Condição B (não apenas o inciso II).</t>
+    <t xml:space="preserve">Condição A: o incidente pode afetar significativamente interesses e direitos fundamentais dos titulares? Condição B: envolve, cumulativamente, ao menos uma das categorias dos incisos I a VI do art. 5º: I. dados pessoais sensíveis; II. dados de crianças, adolescentes ou idosos; III. dados financeiros; IV. dados de autenticação em sistemas; V. dados sob sigilo legal, judicial ou profissional; VI. tratamento em larga escala. As duas condições são cumulativas: ambas devem estar fundamentadamente demonstradas, e a presença de qualquer um dos seis incisos satisfaz a Condição B (não apenas o inciso II).</t>
   </si>
   <si>
     <t xml:space="preserve">'Larga escala' e pequeno porte não têm limiar numérico automático</t>
   </si>
   <si>
-    <t xml:space="preserve">O RCIS não define um número fixo de titulares como limiar de 'larga escala' (inciso VI), nem as orientações oficiais da ANPD trazem esse critério objetivo — a avaliação exige fundamentação qualitativa (volume, abrangência geográfica, duração, proporção da base), registrada na coluna correspondente. Da mesma forma, a condição de 'agente de tratamento de pequeno porte' (que dobra os prazos do art. 6º, §8º, e do art. 9º, §6º) não decorre do nome ou do tamanho aparente da organização — depende de enquadramento formal nos critérios da Resolução CD/ANPD nº 2/2022, a ser confirmado pelo Jurídico/Encarregado.</t>
+    <t xml:space="preserve">O RCIS não define um número fixo de titulares como limiar de 'larga escala' (inciso VI), nem as orientações oficiais da ANPD trazem esse critério objetivo: a avaliação exige fundamentação qualitativa (volume, abrangência geográfica, duração, proporção da base), registrada na coluna correspondente. Da mesma forma, a condição de 'agente de tratamento de pequeno porte' (que dobra os prazos do art. 6º, §8º, e do art. 9º, §6º) não decorre do nome ou do tamanho aparente da organização: depende de enquadramento formal nos critérios da Resolução CD/ANPD nº 2/2022, a ser confirmado pelo Jurídico/Encarregado.</t>
   </si>
   <si>
     <t xml:space="preserve">Prazos (apoio, não substitui validação jurídica)</t>
   </si>
   <si>
-    <t xml:space="preserve">O prazo de comunicação à ANPD e aos titulares é de 3 dias úteis contados do marco de conhecimento pelo controlador (art. 6º, §1º e art. 9º, caput, do RCIS). Complementações à ANPD têm prazo de até 20 dias úteis contados da comunicação EFETIVAMENTE REALIZADA (art. 6º, §3º) — nunca de uma data apenas planejada. A fórmula de prazo nesta planilha usa a função WORKDAY (dias úteis simples, sem feriados) e serve apenas de apoio; o prazo aplicável validado é um campo manual separado, com fundamento, calendário de referência e responsável pela validação.</t>
+    <t xml:space="preserve">O prazo de comunicação à ANPD e aos titulares é de 3 dias úteis contados do marco de conhecimento pelo controlador (art. 6º, §1º e art. 9º, caput, do RCIS). Complementações à ANPD têm prazo de até 20 dias úteis contados da comunicação EFETIVAMENTE REALIZADA (art. 6º, §3º): nunca de uma data apenas planejada. A fórmula de prazo nesta planilha usa a função WORKDAY (dias úteis simples, sem feriados) e serve apenas de apoio; o prazo aplicável validado é um campo manual separado, com fundamento, calendário de referência e responsável pela validação.</t>
   </si>
   <si>
     <t xml:space="preserve">Marco de conhecimento e ampliação de escopo</t>
   </si>
   <si>
-    <t xml:space="preserve">Quando uma nova versão apenas amplia o escopo de titulares/dados do MESMO incidente (sem criar um incidente novo), preserve o marco de conhecimento original na nova versão, a menos que haja fundamento específico para fixar um novo marco — documente a escolha na aba Historico. Um horário calculado como 00h00 de uma data (por exemplo, resultado de uma fórmula de apoio) nunca deve ser tratado como horário jurídico de vencimento do prazo.</t>
+    <t xml:space="preserve">Quando uma nova versão apenas amplia o escopo de titulares/dados do MESMO incidente (sem criar um incidente novo), preserve o marco de conhecimento original na nova versão, a menos que haja fundamento específico para fixar um novo marco: documente a escolha na aba Historico. Um horário calculado como 00h00 de uma data (por exemplo, resultado de uma fórmula de apoio) nunca deve ser tratado como horário jurídico de vencimento do prazo.</t>
   </si>
   <si>
     <t xml:space="preserve">Resultados possíveis</t>
   </si>
   <si>
-    <t xml:space="preserve">Avaliação pendente · Informações insuficientes · Condições regulatórias potencialmente atendidas · Condições regulatórias não demonstradas · Decisão fundamentada e aprovada. Nenhum desses resultados declara conformidade legal automaticamente — todos exigem fundamentação registrada nas colunas correspondentes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identificadores são manuais e estáveis — chave de reconciliação entre abas (correção A02/A03)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Digite a mesma ID 'AVR-NN' E o mesmo número de Versão na coluna A/B das quatro abas (Caracterizacao, Avaliacao_Regulatoria, Decisao_Comunicacao e, na linha que registra a chegada a essa versão, Historico) — é essa combinação ID+Versão, e não a posição da linha nem os dígitos da ID, que relaciona os registros entre as abas. Mantenha o mesmo INC-AAAA-NNN do Instrumento 1. Referencie evidências (EVD-) e decisões (DEC-) registradas no Instrumento 1 sempre que aplicável. Uma formatação condicional em cada aba verifica, por fórmula (COUNTIFS cruzado), se a mesma combinação ID+Versão também existe nas demais abas relacionadas, e sinaliza em vermelho quando não existe — essa é a prova de reconciliação, não uma coincidência entre o número da ID e o número da versão.</t>
+    <t xml:space="preserve">Avaliação pendente · Informações insuficientes · Condições regulatórias potencialmente atendidas · Condições regulatórias não demonstradas · Decisão fundamentada e aprovada. Nenhum desses resultados declara conformidade legal automaticamente: todos exigem fundamentação registrada nas colunas correspondentes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identificadores são manuais e estáveis: chave de reconciliação entre abas (correção A02/A03)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digite a mesma ID 'AVR-NN' E o mesmo número de Versão na coluna A/B das quatro abas (Caracterizacao, Avaliacao_Regulatoria, Decisao_Comunicacao e, na linha que registra a chegada a essa versão, Historico): é essa combinação ID+Versão, e não a posição da linha nem os dígitos da ID, que relaciona os registros entre as abas. Mantenha o mesmo INC-AAAA-NNN do Instrumento 1. Referencie evidências (EVD-) e decisões (DEC-) registradas no Instrumento 1 sempre que aplicável. Uma formatação condicional em cada aba verifica, por fórmula (COUNTIFS cruzado), se a mesma combinação ID+Versão também existe nas demais abas relacionadas, e sinaliza em vermelho quando não existe: essa é a prova de reconciliação, não uma coincidência entre o número da ID e o número da versão.</t>
   </si>
   <si>
     <t xml:space="preserve">Retenção</t>
@@ -280,7 +280,7 @@
     <t xml:space="preserve">Caracterização</t>
   </si>
   <si>
-    <t xml:space="preserve">EXEMPLO FICTÍCIO — INC-2026-001 — SOMENTE TREINAMENTO (Aurora Comércio Digital S.A., controladora fictícia)</t>
+    <t xml:space="preserve">EXEMPLO FICTÍCIO: INC-2026-001: SOMENTE TREINAMENTO (Aurora Comércio Digital S.A., controladora fictícia)</t>
   </si>
   <si>
     <t xml:space="preserve">ID da Avaliação</t>
@@ -331,7 +331,7 @@
     <t xml:space="preserve">INC-2026-001</t>
   </si>
   <si>
-    <t xml:space="preserve">Comprometimento de confidencialidade — acesso não autorizado a dados pessoais</t>
+    <t xml:space="preserve">Comprometimento de confidencialidade: acesso não autorizado a dados pessoais</t>
   </si>
   <si>
     <t xml:space="preserve">Atendimento a clientes; faturamento de pedidos</t>
@@ -364,7 +364,7 @@
     <t xml:space="preserve">2</t>
   </si>
   <si>
-    <t xml:space="preserve">Comprometimento de confidencialidade — acesso e exportação não autorizados de dados pessoais</t>
+    <t xml:space="preserve">Comprometimento de confidencialidade: acesso e exportação não autorizados de dados pessoais</t>
   </si>
   <si>
     <t xml:space="preserve">Nome, CPF, telefone, e-mail, endereço, valores e datas de pedidos</t>
@@ -382,31 +382,31 @@
     <t xml:space="preserve">Revogação do token (E07), revisão de integrações e permissões</t>
   </si>
   <si>
-    <t xml:space="preserve">Avaliação Regulatória — Critérios Cumulativos do Art. 5º do RCIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Condição A — Potencial de Afetação Significativa (art. 5º, caput)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I — Dados Sensíveis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">II — Crianças/Adolescentes/Idosos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">III — Dados Financeiros</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IV — Dados de Autenticação</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V — Sigilo Legal/Judicial/Profissional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VI — Larga Escala</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Condição B — Atendida? (algum inciso I a VI = Sim)</t>
+    <t xml:space="preserve">Avaliação Regulatória: Critérios Cumulativos do Art. 5º do RCIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Condição A: Potencial de Afetação Significativa (art. 5º, caput)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I: Dados Sensíveis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">II: Crianças/Adolescentes/Idosos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">III: Dados Financeiros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IV: Dados de Autenticação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V: Sigilo Legal/Judicial/Profissional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VI: Larga Escala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Condição B: Atendida? (algum inciso I a VI = Sim)</t>
   </si>
   <si>
     <t xml:space="preserve">Fundamentação da Condição A</t>
@@ -442,7 +442,7 @@
     <t xml:space="preserve">Não</t>
   </si>
   <si>
-    <t xml:space="preserve">Apenas 200 registros confirmados; sem confirmação de exportação, redistribuição ou maior universo de titulares — impacto significativo ainda não demonstrado.</t>
+    <t xml:space="preserve">Apenas 200 registros confirmados; sem confirmação de exportação, redistribuição ou maior universo de titulares: impacto significativo ainda não demonstrado.</t>
   </si>
   <si>
     <t xml:space="preserve">Inciso II (crianças/adolescentes/idosos) em apuração: ainda não há confirmação de que titulares menores de idade estejam entre os 200 registros acessados. Demais incisos não identificados nesta versão.</t>
@@ -460,22 +460,22 @@
     <t xml:space="preserve">Parecer em elaboração</t>
   </si>
   <si>
-    <t xml:space="preserve">Sim — aprofundar Scope (extensão do acesso) e confirmar perfil etário dos titulares antes de concluir o inciso II</t>
+    <t xml:space="preserve">Sim: aprofundar Scope (extensão do acesso) e confirmar perfil etário dos titulares antes de concluir o inciso II</t>
   </si>
   <si>
     <t xml:space="preserve">Encarregado/DPO</t>
   </si>
   <si>
-    <t xml:space="preserve">—</t>
+    <t xml:space="preserve">N/A</t>
   </si>
   <si>
     <t xml:space="preserve">Sim</t>
   </si>
   <si>
-    <t xml:space="preserve">Exportação confirmada de 30.000 registros distintos, incluindo dados de identificação e informações financeiras de pedidos, para fora do ambiente autorizado. Potencial de fraude e engenharia social direcionada com dados verdadeiros de compra — afetação significativa demonstrada pela natureza financeira dos dados e pela escala da exposição.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">III (financeiro): os dados exportados incluem valores e datas de pedidos associados a identificação pessoal, aptos a viabilizar fraude — fundamento autônomo, independente da quantidade de titulares. VI (larga escala): 30.000 titulares distintos de uma base de ~180 mil clientes, exportados em uma única operação não autorizada — fundamentado pela combinação de volume absoluto, abrangência (toda a base de pedidos do período) e natureza não segmentada da exportação, não apenas pelo número isolado de titulares. II (crianças/adolescentes/idosos): permanece em apuração — a extração não permite segmentar por faixa etária sem análise adicional.</t>
+    <t xml:space="preserve">Exportação confirmada de 30.000 registros distintos, incluindo dados de identificação e informações financeiras de pedidos, para fora do ambiente autorizado. Potencial de fraude e engenharia social direcionada com dados verdadeiros de compra: afetação significativa demonstrada pela natureza financeira dos dados e pela escala da exposição.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">III (financeiro): os dados exportados incluem valores e datas de pedidos associados a identificação pessoal, aptos a viabilizar fraude: fundamento autônomo, independente da quantidade de titulares. VI (larga escala): 30.000 titulares distintos de uma base de ~180 mil clientes, exportados em uma única operação não autorizada: fundamentado pela combinação de volume absoluto, abrangência (toda a base de pedidos do período) e natureza não segmentada da exportação, não apenas pelo número isolado de titulares. II (crianças/adolescentes/idosos): permanece em apuração: a extração não permite segmentar por faixa etária sem análise adicional.</t>
   </si>
   <si>
     <t xml:space="preserve">EVD-004; EVD-006</t>
@@ -490,7 +490,7 @@
     <t xml:space="preserve">Análise aprovada</t>
   </si>
   <si>
-    <t xml:space="preserve">Sim — confirmar classificação de 'larga escala' e o perfil etário (inciso II) com o Jurídico antes da autorização de envio</t>
+    <t xml:space="preserve">Sim: confirmar classificação de 'larga escala' e o perfil etário (inciso II) com o Jurídico antes da autorização de envio</t>
   </si>
   <si>
     <t xml:space="preserve">Representante autorizado do controlador</t>
@@ -502,7 +502,7 @@
     <t xml:space="preserve">Marco de Conhecimento Aplicável</t>
   </si>
   <si>
-    <t xml:space="preserve">Pequeno Porte — Elegibilidade (validar, não presumir)</t>
+    <t xml:space="preserve">Pequeno Porte: Elegibilidade (validar, não presumir)</t>
   </si>
   <si>
     <t xml:space="preserve">Data Calculada de Apoio (WORKDAY, sem feriados)</t>
@@ -523,10 +523,10 @@
     <t xml:space="preserve">Regras Específicas ou Exceções (ressalva de prazo setorial)</t>
   </si>
   <si>
-    <t xml:space="preserve">Comunicação à ANPD — Decisão</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comunicação aos Titulares — Decisão</t>
+    <t xml:space="preserve">Comunicação à ANPD: Decisão</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comunicação aos Titulares: Decisão</t>
   </si>
   <si>
     <t xml:space="preserve">Fundamentação da Decisão</t>
@@ -550,7 +550,7 @@
     <t xml:space="preserve">Não avaliado</t>
   </si>
   <si>
-    <t xml:space="preserve">Prazo não fixado nesta versão — avaliação ainda em apuração (ver Avaliacao_Regulatoria, AVR-01).</t>
+    <t xml:space="preserve">Prazo não fixado nesta versão: avaliação ainda em apuração (ver Avaliacao_Regulatoria, AVR-01).</t>
   </si>
   <si>
     <t xml:space="preserve">Não aplicável nesta versão</t>
@@ -565,16 +565,16 @@
     <t xml:space="preserve">Informação insuficiente para decidir; aguardar aprofundamento do Scope e do perfil etário dos titulares</t>
   </si>
   <si>
-    <t xml:space="preserve">Sim — ver versão 2</t>
+    <t xml:space="preserve">Sim: ver versão 2</t>
   </si>
   <si>
     <t xml:space="preserve">Não elegível</t>
   </si>
   <si>
-    <t xml:space="preserve">3 dias úteis a partir do marco de conhecimento de 19/10/2026 (mantido da versão 1 — a versão 2 apenas amplia o escopo do mesmo incidente, não reinicia o prazo). Agente não enquadrado como pequeno porte neste exercício.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calendário nacional de feriados 2026 (nenhum feriado no intervalo 19–22/10/2026)</t>
+    <t xml:space="preserve">3 dias úteis a partir do marco de conhecimento de 19/10/2026 (mantido da versão 1: a versão 2 apenas amplia o escopo do mesmo incidente, não reinicia o prazo). Agente não enquadrado como pequeno porte neste exercício.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calendário nacional de feriados 2026 (nenhum feriado no intervalo 19 a 22/10/2026)</t>
   </si>
   <si>
     <t xml:space="preserve">Jurídico</t>
@@ -592,7 +592,7 @@
     <t xml:space="preserve">DEC-003</t>
   </si>
   <si>
-    <t xml:space="preserve">Não — versão vigente</t>
+    <t xml:space="preserve">Não: versão vigente</t>
   </si>
   <si>
     <t xml:space="preserve">Histórico de Versões</t>
@@ -634,7 +634,7 @@
     <t xml:space="preserve">Nova evidência alterou substancialmente a natureza e a extensão do incidente, exigindo reabertura da avaliação conforme regra de atualização do instrumento. A ID desta linha (AVR-02) corresponde à versão de chegada, consistente com as demais abas para esta mesma versão.</t>
   </si>
   <si>
-    <t xml:space="preserve">Matriz de Probabilidade x Impacto — Apoio à Priorização</t>
+    <t xml:space="preserve">Matriz de Probabilidade x Impacto: Apoio à Priorização</t>
   </si>
   <si>
     <t xml:space="preserve">USO INTERNO. Esta matriz NÃO determina obrigação de comunicação e não substitui os critérios do art. 5º do RCIS.</t>
@@ -1253,7 +1253,7 @@
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -1466,7 +1466,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
         <v>41</v>
       </c>
@@ -1507,7 +1507,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
         <v>53</v>
       </c>
@@ -1548,7 +1548,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10"/>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -1563,7 +1563,7 @@
       <c r="L6" s="11"/>
       <c r="M6" s="11"/>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10"/>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -1578,7 +1578,7 @@
       <c r="L7" s="11"/>
       <c r="M7" s="11"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10"/>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -1593,7 +1593,7 @@
       <c r="L8" s="11"/>
       <c r="M8" s="11"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10"/>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -1608,7 +1608,7 @@
       <c r="L9" s="11"/>
       <c r="M9" s="11"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10"/>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
@@ -1623,7 +1623,7 @@
       <c r="L10" s="11"/>
       <c r="M10" s="11"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10"/>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
@@ -1638,7 +1638,7 @@
       <c r="L11" s="11"/>
       <c r="M11" s="11"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10"/>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -1653,7 +1653,7 @@
       <c r="L12" s="11"/>
       <c r="M12" s="11"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10"/>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -1668,7 +1668,7 @@
       <c r="L13" s="11"/>
       <c r="M13" s="11"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10"/>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -1683,7 +1683,7 @@
       <c r="L14" s="11"/>
       <c r="M14" s="11"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10"/>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -1698,7 +1698,7 @@
       <c r="L15" s="11"/>
       <c r="M15" s="11"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10"/>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -1713,7 +1713,7 @@
       <c r="L16" s="11"/>
       <c r="M16" s="11"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10"/>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -1728,7 +1728,7 @@
       <c r="L17" s="11"/>
       <c r="M17" s="11"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10"/>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -1743,7 +1743,7 @@
       <c r="L18" s="11"/>
       <c r="M18" s="11"/>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="10"/>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -1758,7 +1758,7 @@
       <c r="L19" s="11"/>
       <c r="M19" s="11"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10"/>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -1773,7 +1773,7 @@
       <c r="L20" s="11"/>
       <c r="M20" s="11"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="10"/>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -1788,7 +1788,7 @@
       <c r="L21" s="11"/>
       <c r="M21" s="11"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="10"/>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -1803,7 +1803,7 @@
       <c r="L22" s="11"/>
       <c r="M22" s="11"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="10"/>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -1818,7 +1818,7 @@
       <c r="L23" s="11"/>
       <c r="M23" s="11"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="10"/>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -1833,7 +1833,7 @@
       <c r="L24" s="11"/>
       <c r="M24" s="11"/>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="10"/>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -1848,7 +1848,7 @@
       <c r="L25" s="11"/>
       <c r="M25" s="11"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="10"/>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -1863,7 +1863,7 @@
       <c r="L26" s="11"/>
       <c r="M26" s="11"/>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="10"/>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -1878,7 +1878,7 @@
       <c r="L27" s="11"/>
       <c r="M27" s="11"/>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="10"/>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -1893,7 +1893,7 @@
       <c r="L28" s="11"/>
       <c r="M28" s="11"/>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="10"/>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -1908,7 +1908,7 @@
       <c r="L29" s="11"/>
       <c r="M29" s="11"/>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="10"/>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -1923,7 +1923,7 @@
       <c r="L30" s="11"/>
       <c r="M30" s="11"/>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -1938,7 +1938,7 @@
       <c r="L31" s="11"/>
       <c r="M31" s="11"/>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="10"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -1953,7 +1953,7 @@
       <c r="L32" s="11"/>
       <c r="M32" s="11"/>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10"/>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -1968,7 +1968,7 @@
       <c r="L33" s="11"/>
       <c r="M33" s="11"/>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="10"/>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -1983,7 +1983,7 @@
       <c r="L34" s="11"/>
       <c r="M34" s="11"/>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="10"/>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -1998,7 +1998,7 @@
       <c r="L35" s="11"/>
       <c r="M35" s="11"/>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="10"/>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -2013,7 +2013,7 @@
       <c r="L36" s="11"/>
       <c r="M36" s="11"/>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="10"/>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -2028,7 +2028,7 @@
       <c r="L37" s="11"/>
       <c r="M37" s="11"/>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="10"/>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -2043,7 +2043,7 @@
       <c r="L38" s="11"/>
       <c r="M38" s="11"/>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="10"/>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -2058,7 +2058,7 @@
       <c r="L39" s="11"/>
       <c r="M39" s="11"/>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="10"/>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -2073,7 +2073,7 @@
       <c r="L40" s="11"/>
       <c r="M40" s="11"/>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="10"/>
       <c r="B41" s="11"/>
       <c r="C41" s="11"/>
@@ -2088,7 +2088,7 @@
       <c r="L41" s="11"/>
       <c r="M41" s="11"/>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="10"/>
       <c r="B42" s="11"/>
       <c r="C42" s="11"/>
@@ -2103,7 +2103,7 @@
       <c r="L42" s="11"/>
       <c r="M42" s="11"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="10"/>
       <c r="B43" s="11"/>
       <c r="C43" s="11"/>
@@ -2118,7 +2118,7 @@
       <c r="L43" s="11"/>
       <c r="M43" s="11"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="10"/>
       <c r="B44" s="11"/>
       <c r="C44" s="11"/>
@@ -2133,7 +2133,7 @@
       <c r="L44" s="11"/>
       <c r="M44" s="11"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="10"/>
       <c r="B45" s="11"/>
       <c r="C45" s="11"/>
@@ -2148,7 +2148,7 @@
       <c r="L45" s="11"/>
       <c r="M45" s="11"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="10"/>
       <c r="B46" s="11"/>
       <c r="C46" s="11"/>
@@ -2163,7 +2163,7 @@
       <c r="L46" s="11"/>
       <c r="M46" s="11"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="10"/>
       <c r="B47" s="11"/>
       <c r="C47" s="11"/>
@@ -2178,7 +2178,7 @@
       <c r="L47" s="11"/>
       <c r="M47" s="11"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="10"/>
       <c r="B48" s="11"/>
       <c r="C48" s="11"/>
@@ -2193,7 +2193,7 @@
       <c r="L48" s="11"/>
       <c r="M48" s="11"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="10"/>
       <c r="B49" s="11"/>
       <c r="C49" s="11"/>
@@ -2208,7 +2208,7 @@
       <c r="L49" s="11"/>
       <c r="M49" s="11"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="10"/>
       <c r="B50" s="11"/>
       <c r="C50" s="11"/>
@@ -2223,7 +2223,7 @@
       <c r="L50" s="11"/>
       <c r="M50" s="11"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="10"/>
       <c r="B51" s="11"/>
       <c r="C51" s="11"/>
@@ -2238,7 +2238,7 @@
       <c r="L51" s="11"/>
       <c r="M51" s="11"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="10"/>
       <c r="B52" s="11"/>
       <c r="C52" s="11"/>
@@ -2253,7 +2253,7 @@
       <c r="L52" s="11"/>
       <c r="M52" s="11"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="10"/>
       <c r="B53" s="11"/>
       <c r="C53" s="11"/>
@@ -2482,7 +2482,7 @@
       <formula1>"Confirmado,Hipótese,Inferido,Desconhecido,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Este identificador já existe nesta coluna. Cada ID deve ser único e estável (não reutilize nem renumere IDs já atribuídos). Padrão esperado: AVR-01." errorStyle="stop" errorTitle="ID duplicado" operator="between" prompt="Digite um identificador único e estável, padrão AVR-01. Não é gerado automaticamente — preserve o mesmo ID após inserir, excluir ou reordenar linhas." promptTitle="Identificador manual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A4:A53" type="custom">
+    <dataValidation allowBlank="true" error="Este identificador já existe nesta coluna. Cada ID deve ser único e estável (não reutilize nem renumere IDs já atribuídos). Padrão esperado: AVR-01." errorStyle="stop" errorTitle="ID duplicado" operator="between" prompt="Digite um identificador único e estável, padrão AVR-01. Não é gerado automaticamente; preserve o mesmo ID após inserir, excluir ou reordenar linhas." promptTitle="Identificador manual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A4:A53" type="custom">
       <formula1>OR(A4="",COUNTIF($A$4:$A$53,A4)&lt;=1)</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -2630,7 +2630,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
         <v>41</v>
       </c>
@@ -2690,7 +2690,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
         <v>53</v>
       </c>
@@ -2750,7 +2750,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10"/>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -2774,7 +2774,7 @@
       <c r="R6" s="11"/>
       <c r="S6" s="11"/>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10"/>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -2798,7 +2798,7 @@
       <c r="R7" s="11"/>
       <c r="S7" s="11"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10"/>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -2822,7 +2822,7 @@
       <c r="R8" s="11"/>
       <c r="S8" s="11"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10"/>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -2846,7 +2846,7 @@
       <c r="R9" s="11"/>
       <c r="S9" s="11"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10"/>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
@@ -2870,7 +2870,7 @@
       <c r="R10" s="11"/>
       <c r="S10" s="11"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10"/>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
@@ -2894,7 +2894,7 @@
       <c r="R11" s="11"/>
       <c r="S11" s="11"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10"/>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -2918,7 +2918,7 @@
       <c r="R12" s="11"/>
       <c r="S12" s="11"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10"/>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -2942,7 +2942,7 @@
       <c r="R13" s="11"/>
       <c r="S13" s="11"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10"/>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -2966,7 +2966,7 @@
       <c r="R14" s="11"/>
       <c r="S14" s="11"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10"/>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -2990,7 +2990,7 @@
       <c r="R15" s="11"/>
       <c r="S15" s="11"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10"/>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -3014,7 +3014,7 @@
       <c r="R16" s="11"/>
       <c r="S16" s="11"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10"/>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -3038,7 +3038,7 @@
       <c r="R17" s="11"/>
       <c r="S17" s="11"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10"/>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -3062,7 +3062,7 @@
       <c r="R18" s="11"/>
       <c r="S18" s="11"/>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="10"/>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -3086,7 +3086,7 @@
       <c r="R19" s="11"/>
       <c r="S19" s="11"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10"/>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -3110,7 +3110,7 @@
       <c r="R20" s="11"/>
       <c r="S20" s="11"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="10"/>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -3134,7 +3134,7 @@
       <c r="R21" s="11"/>
       <c r="S21" s="11"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="10"/>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -3158,7 +3158,7 @@
       <c r="R22" s="11"/>
       <c r="S22" s="11"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="10"/>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -3182,7 +3182,7 @@
       <c r="R23" s="11"/>
       <c r="S23" s="11"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="10"/>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -3206,7 +3206,7 @@
       <c r="R24" s="11"/>
       <c r="S24" s="11"/>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="10"/>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -3230,7 +3230,7 @@
       <c r="R25" s="11"/>
       <c r="S25" s="11"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="10"/>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -3254,7 +3254,7 @@
       <c r="R26" s="11"/>
       <c r="S26" s="11"/>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="10"/>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -3278,7 +3278,7 @@
       <c r="R27" s="11"/>
       <c r="S27" s="11"/>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="10"/>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -3302,7 +3302,7 @@
       <c r="R28" s="11"/>
       <c r="S28" s="11"/>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="10"/>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -3326,7 +3326,7 @@
       <c r="R29" s="11"/>
       <c r="S29" s="11"/>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="10"/>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -3350,7 +3350,7 @@
       <c r="R30" s="11"/>
       <c r="S30" s="11"/>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -3374,7 +3374,7 @@
       <c r="R31" s="11"/>
       <c r="S31" s="11"/>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="10"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -3398,7 +3398,7 @@
       <c r="R32" s="11"/>
       <c r="S32" s="11"/>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10"/>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -3422,7 +3422,7 @@
       <c r="R33" s="11"/>
       <c r="S33" s="11"/>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="10"/>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -3446,7 +3446,7 @@
       <c r="R34" s="11"/>
       <c r="S34" s="11"/>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="10"/>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -3470,7 +3470,7 @@
       <c r="R35" s="11"/>
       <c r="S35" s="11"/>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="10"/>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -3494,7 +3494,7 @@
       <c r="R36" s="11"/>
       <c r="S36" s="11"/>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="10"/>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -3518,7 +3518,7 @@
       <c r="R37" s="11"/>
       <c r="S37" s="11"/>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="10"/>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -3542,7 +3542,7 @@
       <c r="R38" s="11"/>
       <c r="S38" s="11"/>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="10"/>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -3566,7 +3566,7 @@
       <c r="R39" s="11"/>
       <c r="S39" s="11"/>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="10"/>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -3590,7 +3590,7 @@
       <c r="R40" s="11"/>
       <c r="S40" s="11"/>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="10"/>
       <c r="B41" s="11"/>
       <c r="C41" s="11"/>
@@ -3614,7 +3614,7 @@
       <c r="R41" s="11"/>
       <c r="S41" s="11"/>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="10"/>
       <c r="B42" s="11"/>
       <c r="C42" s="11"/>
@@ -3638,7 +3638,7 @@
       <c r="R42" s="11"/>
       <c r="S42" s="11"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="10"/>
       <c r="B43" s="11"/>
       <c r="C43" s="11"/>
@@ -3662,7 +3662,7 @@
       <c r="R43" s="11"/>
       <c r="S43" s="11"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="10"/>
       <c r="B44" s="11"/>
       <c r="C44" s="11"/>
@@ -3686,7 +3686,7 @@
       <c r="R44" s="11"/>
       <c r="S44" s="11"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="10"/>
       <c r="B45" s="11"/>
       <c r="C45" s="11"/>
@@ -3710,7 +3710,7 @@
       <c r="R45" s="11"/>
       <c r="S45" s="11"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="10"/>
       <c r="B46" s="11"/>
       <c r="C46" s="11"/>
@@ -3734,7 +3734,7 @@
       <c r="R46" s="11"/>
       <c r="S46" s="11"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="10"/>
       <c r="B47" s="11"/>
       <c r="C47" s="11"/>
@@ -3758,7 +3758,7 @@
       <c r="R47" s="11"/>
       <c r="S47" s="11"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="10"/>
       <c r="B48" s="11"/>
       <c r="C48" s="11"/>
@@ -3782,7 +3782,7 @@
       <c r="R48" s="11"/>
       <c r="S48" s="11"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="10"/>
       <c r="B49" s="11"/>
       <c r="C49" s="11"/>
@@ -3806,7 +3806,7 @@
       <c r="R49" s="11"/>
       <c r="S49" s="11"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="10"/>
       <c r="B50" s="11"/>
       <c r="C50" s="11"/>
@@ -3830,7 +3830,7 @@
       <c r="R50" s="11"/>
       <c r="S50" s="11"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="10"/>
       <c r="B51" s="11"/>
       <c r="C51" s="11"/>
@@ -3854,7 +3854,7 @@
       <c r="R51" s="11"/>
       <c r="S51" s="11"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="10"/>
       <c r="B52" s="11"/>
       <c r="C52" s="11"/>
@@ -3878,7 +3878,7 @@
       <c r="R52" s="11"/>
       <c r="S52" s="11"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="10"/>
       <c r="B53" s="11"/>
       <c r="C53" s="11"/>
@@ -3948,7 +3948,7 @@
       <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P4" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio: são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P4" type="list">
       <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -3984,7 +3984,7 @@
       <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P5" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio: são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P5" type="list">
       <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4020,7 +4020,7 @@
       <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P6" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio: são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P6" type="list">
       <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4056,7 +4056,7 @@
       <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P7" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio: são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P7" type="list">
       <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4092,7 +4092,7 @@
       <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P8" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio: são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P8" type="list">
       <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4128,7 +4128,7 @@
       <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P9" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio: são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P9" type="list">
       <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4164,7 +4164,7 @@
       <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P10" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio: são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P10" type="list">
       <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4200,7 +4200,7 @@
       <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P11" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio: são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P11" type="list">
       <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4236,7 +4236,7 @@
       <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P12" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio: são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P12" type="list">
       <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4272,7 +4272,7 @@
       <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P13" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio: são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P13" type="list">
       <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4308,7 +4308,7 @@
       <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P14" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio: são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P14" type="list">
       <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4344,7 +4344,7 @@
       <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P15" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio: são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P15" type="list">
       <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4380,7 +4380,7 @@
       <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P16" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio: são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P16" type="list">
       <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4416,7 +4416,7 @@
       <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P17" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio: são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P17" type="list">
       <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4452,7 +4452,7 @@
       <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P18" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio: são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P18" type="list">
       <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4488,7 +4488,7 @@
       <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P19" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio: são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P19" type="list">
       <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4524,7 +4524,7 @@
       <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P20" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio: são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P20" type="list">
       <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4560,7 +4560,7 @@
       <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P21" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio: são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P21" type="list">
       <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4596,7 +4596,7 @@
       <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P22" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio: são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P22" type="list">
       <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4632,7 +4632,7 @@
       <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P23" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio: são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P23" type="list">
       <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4668,7 +4668,7 @@
       <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P24" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio: são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P24" type="list">
       <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4704,7 +4704,7 @@
       <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P25" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio: são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P25" type="list">
       <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4740,7 +4740,7 @@
       <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P26" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio: são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P26" type="list">
       <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4776,7 +4776,7 @@
       <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P27" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio: são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P27" type="list">
       <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4812,7 +4812,7 @@
       <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P28" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio: são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P28" type="list">
       <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4848,7 +4848,7 @@
       <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P29" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio: são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P29" type="list">
       <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4884,7 +4884,7 @@
       <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P30" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio: são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P30" type="list">
       <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4920,7 +4920,7 @@
       <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P31" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio: são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P31" type="list">
       <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4956,7 +4956,7 @@
       <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P32" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio: são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P32" type="list">
       <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4992,7 +4992,7 @@
       <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P33" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio: são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P33" type="list">
       <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5028,7 +5028,7 @@
       <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P34" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio: são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P34" type="list">
       <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5064,7 +5064,7 @@
       <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P35" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio: são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P35" type="list">
       <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5100,7 +5100,7 @@
       <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P36" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio: são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P36" type="list">
       <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5136,7 +5136,7 @@
       <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P37" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio: são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P37" type="list">
       <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5172,7 +5172,7 @@
       <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P38" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio: são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P38" type="list">
       <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5208,7 +5208,7 @@
       <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P39" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio: são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P39" type="list">
       <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5244,7 +5244,7 @@
       <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P40" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio: são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P40" type="list">
       <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5280,7 +5280,7 @@
       <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P41" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio: são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P41" type="list">
       <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5316,7 +5316,7 @@
       <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P42" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio: são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P42" type="list">
       <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5352,7 +5352,7 @@
       <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P43" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio: são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P43" type="list">
       <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5388,7 +5388,7 @@
       <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P44" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio: são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P44" type="list">
       <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5424,7 +5424,7 @@
       <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P45" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio: são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P45" type="list">
       <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5460,7 +5460,7 @@
       <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P46" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio: são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P46" type="list">
       <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5496,7 +5496,7 @@
       <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P47" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio: são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P47" type="list">
       <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5532,7 +5532,7 @@
       <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P48" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio: são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P48" type="list">
       <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5568,7 +5568,7 @@
       <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P49" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio: são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P49" type="list">
       <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5604,7 +5604,7 @@
       <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P50" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio: são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P50" type="list">
       <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5640,7 +5640,7 @@
       <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P51" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio: são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P51" type="list">
       <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5676,7 +5676,7 @@
       <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P52" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio: são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P52" type="list">
       <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5712,11 +5712,11 @@
       <formula1>"Avaliação pendente,Informações insuficientes,Condições regulatórias potencialmente atendidas,Condições regulatórias não demonstradas,Decisão fundamentada e aprovada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio — são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P53" type="list">
+    <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Distinga parecer em elaboração de análise aprovada, decisão de comunicar e autorização de envio: são marcos diferentes." promptTitle="Estado da análise (A08)" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P53" type="list">
       <formula1>"Parecer em elaboração,Análise concluída,aguardando aprovação,Análise aprovada,Decisão de comunicar confirmada,Autorização de envio emitida"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Este identificador já existe nesta coluna. Cada ID deve ser único e estável (não reutilize nem renumere IDs já atribuídos). Padrão esperado: AVR-01." errorStyle="stop" errorTitle="ID duplicado" operator="between" prompt="Digite um identificador único e estável, padrão AVR-01. Não é gerado automaticamente — preserve o mesmo ID após inserir, excluir ou reordenar linhas." promptTitle="Identificador manual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A4:A53" type="custom">
+    <dataValidation allowBlank="true" error="Este identificador já existe nesta coluna. Cada ID deve ser único e estável (não reutilize nem renumere IDs já atribuídos). Padrão esperado: AVR-01." errorStyle="stop" errorTitle="ID duplicado" operator="between" prompt="Digite um identificador único e estável, padrão AVR-01. Não é gerado automaticamente; preserve o mesmo ID após inserir, excluir ou reordenar linhas." promptTitle="Identificador manual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A4:A53" type="custom">
       <formula1>OR(A4="",COUNTIF($A$4:$A$53,A4)&lt;=1)</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5858,7 +5858,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
         <v>41</v>
       </c>
@@ -5872,7 +5872,7 @@
         <v>116</v>
       </c>
       <c r="E4" s="13" t="n">
-        <f aca="false">IFERROR(IF(C4="","",WORKDAY(C4,IF(D4="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <f aca="false">IFERROR(IF(C4="","",WORKDAY(C4,IF(D4="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v>46317</v>
       </c>
       <c r="F4" s="14"/>
@@ -5910,7 +5910,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
         <v>53</v>
       </c>
@@ -5924,7 +5924,7 @@
         <v>123</v>
       </c>
       <c r="E5" s="13" t="n">
-        <f aca="false">IFERROR(IF(C5="","",WORKDAY(C5,IF(D5="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <f aca="false">IFERROR(IF(C5="","",WORKDAY(C5,IF(D5="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v>46317</v>
       </c>
       <c r="F5" s="14" t="n">
@@ -5966,13 +5966,13 @@
         <v>131</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10"/>
       <c r="B6" s="11"/>
       <c r="C6" s="12"/>
       <c r="D6" s="11"/>
       <c r="E6" s="13" t="str">
-        <f aca="false">IFERROR(IF(C6="","",WORKDAY(C6,IF(D6="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <f aca="false">IFERROR(IF(C6="","",WORKDAY(C6,IF(D6="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
       <c r="F6" s="14"/>
@@ -5992,13 +5992,13 @@
       </c>
       <c r="R6" s="11"/>
     </row>
-    <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10"/>
       <c r="B7" s="11"/>
       <c r="C7" s="12"/>
       <c r="D7" s="11"/>
       <c r="E7" s="13" t="str">
-        <f aca="false">IFERROR(IF(C7="","",WORKDAY(C7,IF(D7="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <f aca="false">IFERROR(IF(C7="","",WORKDAY(C7,IF(D7="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
       <c r="F7" s="14"/>
@@ -6018,13 +6018,13 @@
       </c>
       <c r="R7" s="11"/>
     </row>
-    <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10"/>
       <c r="B8" s="11"/>
       <c r="C8" s="12"/>
       <c r="D8" s="11"/>
       <c r="E8" s="13" t="str">
-        <f aca="false">IFERROR(IF(C8="","",WORKDAY(C8,IF(D8="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <f aca="false">IFERROR(IF(C8="","",WORKDAY(C8,IF(D8="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
       <c r="F8" s="14"/>
@@ -6044,13 +6044,13 @@
       </c>
       <c r="R8" s="11"/>
     </row>
-    <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10"/>
       <c r="B9" s="11"/>
       <c r="C9" s="12"/>
       <c r="D9" s="11"/>
       <c r="E9" s="13" t="str">
-        <f aca="false">IFERROR(IF(C9="","",WORKDAY(C9,IF(D9="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <f aca="false">IFERROR(IF(C9="","",WORKDAY(C9,IF(D9="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
       <c r="F9" s="14"/>
@@ -6070,13 +6070,13 @@
       </c>
       <c r="R9" s="11"/>
     </row>
-    <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10"/>
       <c r="B10" s="11"/>
       <c r="C10" s="12"/>
       <c r="D10" s="11"/>
       <c r="E10" s="13" t="str">
-        <f aca="false">IFERROR(IF(C10="","",WORKDAY(C10,IF(D10="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <f aca="false">IFERROR(IF(C10="","",WORKDAY(C10,IF(D10="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
       <c r="F10" s="14"/>
@@ -6096,13 +6096,13 @@
       </c>
       <c r="R10" s="11"/>
     </row>
-    <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10"/>
       <c r="B11" s="11"/>
       <c r="C11" s="12"/>
       <c r="D11" s="11"/>
       <c r="E11" s="13" t="str">
-        <f aca="false">IFERROR(IF(C11="","",WORKDAY(C11,IF(D11="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <f aca="false">IFERROR(IF(C11="","",WORKDAY(C11,IF(D11="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
       <c r="F11" s="14"/>
@@ -6122,13 +6122,13 @@
       </c>
       <c r="R11" s="11"/>
     </row>
-    <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10"/>
       <c r="B12" s="11"/>
       <c r="C12" s="12"/>
       <c r="D12" s="11"/>
       <c r="E12" s="13" t="str">
-        <f aca="false">IFERROR(IF(C12="","",WORKDAY(C12,IF(D12="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <f aca="false">IFERROR(IF(C12="","",WORKDAY(C12,IF(D12="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
       <c r="F12" s="14"/>
@@ -6148,13 +6148,13 @@
       </c>
       <c r="R12" s="11"/>
     </row>
-    <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10"/>
       <c r="B13" s="11"/>
       <c r="C13" s="12"/>
       <c r="D13" s="11"/>
       <c r="E13" s="13" t="str">
-        <f aca="false">IFERROR(IF(C13="","",WORKDAY(C13,IF(D13="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <f aca="false">IFERROR(IF(C13="","",WORKDAY(C13,IF(D13="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
       <c r="F13" s="14"/>
@@ -6174,13 +6174,13 @@
       </c>
       <c r="R13" s="11"/>
     </row>
-    <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10"/>
       <c r="B14" s="11"/>
       <c r="C14" s="12"/>
       <c r="D14" s="11"/>
       <c r="E14" s="13" t="str">
-        <f aca="false">IFERROR(IF(C14="","",WORKDAY(C14,IF(D14="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <f aca="false">IFERROR(IF(C14="","",WORKDAY(C14,IF(D14="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
       <c r="F14" s="14"/>
@@ -6200,13 +6200,13 @@
       </c>
       <c r="R14" s="11"/>
     </row>
-    <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10"/>
       <c r="B15" s="11"/>
       <c r="C15" s="12"/>
       <c r="D15" s="11"/>
       <c r="E15" s="13" t="str">
-        <f aca="false">IFERROR(IF(C15="","",WORKDAY(C15,IF(D15="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <f aca="false">IFERROR(IF(C15="","",WORKDAY(C15,IF(D15="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
       <c r="F15" s="14"/>
@@ -6226,13 +6226,13 @@
       </c>
       <c r="R15" s="11"/>
     </row>
-    <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10"/>
       <c r="B16" s="11"/>
       <c r="C16" s="12"/>
       <c r="D16" s="11"/>
       <c r="E16" s="13" t="str">
-        <f aca="false">IFERROR(IF(C16="","",WORKDAY(C16,IF(D16="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <f aca="false">IFERROR(IF(C16="","",WORKDAY(C16,IF(D16="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
       <c r="F16" s="14"/>
@@ -6252,13 +6252,13 @@
       </c>
       <c r="R16" s="11"/>
     </row>
-    <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10"/>
       <c r="B17" s="11"/>
       <c r="C17" s="12"/>
       <c r="D17" s="11"/>
       <c r="E17" s="13" t="str">
-        <f aca="false">IFERROR(IF(C17="","",WORKDAY(C17,IF(D17="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <f aca="false">IFERROR(IF(C17="","",WORKDAY(C17,IF(D17="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
       <c r="F17" s="14"/>
@@ -6278,13 +6278,13 @@
       </c>
       <c r="R17" s="11"/>
     </row>
-    <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10"/>
       <c r="B18" s="11"/>
       <c r="C18" s="12"/>
       <c r="D18" s="11"/>
       <c r="E18" s="13" t="str">
-        <f aca="false">IFERROR(IF(C18="","",WORKDAY(C18,IF(D18="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <f aca="false">IFERROR(IF(C18="","",WORKDAY(C18,IF(D18="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
       <c r="F18" s="14"/>
@@ -6304,13 +6304,13 @@
       </c>
       <c r="R18" s="11"/>
     </row>
-    <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="10"/>
       <c r="B19" s="11"/>
       <c r="C19" s="12"/>
       <c r="D19" s="11"/>
       <c r="E19" s="13" t="str">
-        <f aca="false">IFERROR(IF(C19="","",WORKDAY(C19,IF(D19="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <f aca="false">IFERROR(IF(C19="","",WORKDAY(C19,IF(D19="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
       <c r="F19" s="14"/>
@@ -6330,13 +6330,13 @@
       </c>
       <c r="R19" s="11"/>
     </row>
-    <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10"/>
       <c r="B20" s="11"/>
       <c r="C20" s="12"/>
       <c r="D20" s="11"/>
       <c r="E20" s="13" t="str">
-        <f aca="false">IFERROR(IF(C20="","",WORKDAY(C20,IF(D20="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <f aca="false">IFERROR(IF(C20="","",WORKDAY(C20,IF(D20="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
       <c r="F20" s="14"/>
@@ -6356,13 +6356,13 @@
       </c>
       <c r="R20" s="11"/>
     </row>
-    <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="10"/>
       <c r="B21" s="11"/>
       <c r="C21" s="12"/>
       <c r="D21" s="11"/>
       <c r="E21" s="13" t="str">
-        <f aca="false">IFERROR(IF(C21="","",WORKDAY(C21,IF(D21="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <f aca="false">IFERROR(IF(C21="","",WORKDAY(C21,IF(D21="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
       <c r="F21" s="14"/>
@@ -6382,13 +6382,13 @@
       </c>
       <c r="R21" s="11"/>
     </row>
-    <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="10"/>
       <c r="B22" s="11"/>
       <c r="C22" s="12"/>
       <c r="D22" s="11"/>
       <c r="E22" s="13" t="str">
-        <f aca="false">IFERROR(IF(C22="","",WORKDAY(C22,IF(D22="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <f aca="false">IFERROR(IF(C22="","",WORKDAY(C22,IF(D22="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
       <c r="F22" s="14"/>
@@ -6408,13 +6408,13 @@
       </c>
       <c r="R22" s="11"/>
     </row>
-    <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="10"/>
       <c r="B23" s="11"/>
       <c r="C23" s="12"/>
       <c r="D23" s="11"/>
       <c r="E23" s="13" t="str">
-        <f aca="false">IFERROR(IF(C23="","",WORKDAY(C23,IF(D23="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <f aca="false">IFERROR(IF(C23="","",WORKDAY(C23,IF(D23="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
       <c r="F23" s="14"/>
@@ -6434,13 +6434,13 @@
       </c>
       <c r="R23" s="11"/>
     </row>
-    <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="10"/>
       <c r="B24" s="11"/>
       <c r="C24" s="12"/>
       <c r="D24" s="11"/>
       <c r="E24" s="13" t="str">
-        <f aca="false">IFERROR(IF(C24="","",WORKDAY(C24,IF(D24="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <f aca="false">IFERROR(IF(C24="","",WORKDAY(C24,IF(D24="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
       <c r="F24" s="14"/>
@@ -6460,13 +6460,13 @@
       </c>
       <c r="R24" s="11"/>
     </row>
-    <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="10"/>
       <c r="B25" s="11"/>
       <c r="C25" s="12"/>
       <c r="D25" s="11"/>
       <c r="E25" s="13" t="str">
-        <f aca="false">IFERROR(IF(C25="","",WORKDAY(C25,IF(D25="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <f aca="false">IFERROR(IF(C25="","",WORKDAY(C25,IF(D25="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
       <c r="F25" s="14"/>
@@ -6486,13 +6486,13 @@
       </c>
       <c r="R25" s="11"/>
     </row>
-    <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="10"/>
       <c r="B26" s="11"/>
       <c r="C26" s="12"/>
       <c r="D26" s="11"/>
       <c r="E26" s="13" t="str">
-        <f aca="false">IFERROR(IF(C26="","",WORKDAY(C26,IF(D26="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <f aca="false">IFERROR(IF(C26="","",WORKDAY(C26,IF(D26="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
       <c r="F26" s="14"/>
@@ -6512,13 +6512,13 @@
       </c>
       <c r="R26" s="11"/>
     </row>
-    <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="10"/>
       <c r="B27" s="11"/>
       <c r="C27" s="12"/>
       <c r="D27" s="11"/>
       <c r="E27" s="13" t="str">
-        <f aca="false">IFERROR(IF(C27="","",WORKDAY(C27,IF(D27="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <f aca="false">IFERROR(IF(C27="","",WORKDAY(C27,IF(D27="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
       <c r="F27" s="14"/>
@@ -6538,13 +6538,13 @@
       </c>
       <c r="R27" s="11"/>
     </row>
-    <row r="28" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="10"/>
       <c r="B28" s="11"/>
       <c r="C28" s="12"/>
       <c r="D28" s="11"/>
       <c r="E28" s="13" t="str">
-        <f aca="false">IFERROR(IF(C28="","",WORKDAY(C28,IF(D28="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <f aca="false">IFERROR(IF(C28="","",WORKDAY(C28,IF(D28="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
       <c r="F28" s="14"/>
@@ -6564,13 +6564,13 @@
       </c>
       <c r="R28" s="11"/>
     </row>
-    <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="10"/>
       <c r="B29" s="11"/>
       <c r="C29" s="12"/>
       <c r="D29" s="11"/>
       <c r="E29" s="13" t="str">
-        <f aca="false">IFERROR(IF(C29="","",WORKDAY(C29,IF(D29="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <f aca="false">IFERROR(IF(C29="","",WORKDAY(C29,IF(D29="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
       <c r="F29" s="14"/>
@@ -6590,13 +6590,13 @@
       </c>
       <c r="R29" s="11"/>
     </row>
-    <row r="30" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="10"/>
       <c r="B30" s="11"/>
       <c r="C30" s="12"/>
       <c r="D30" s="11"/>
       <c r="E30" s="13" t="str">
-        <f aca="false">IFERROR(IF(C30="","",WORKDAY(C30,IF(D30="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <f aca="false">IFERROR(IF(C30="","",WORKDAY(C30,IF(D30="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
       <c r="F30" s="14"/>
@@ -6616,13 +6616,13 @@
       </c>
       <c r="R30" s="11"/>
     </row>
-    <row r="31" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
       <c r="C31" s="12"/>
       <c r="D31" s="11"/>
       <c r="E31" s="13" t="str">
-        <f aca="false">IFERROR(IF(C31="","",WORKDAY(C31,IF(D31="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <f aca="false">IFERROR(IF(C31="","",WORKDAY(C31,IF(D31="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
       <c r="F31" s="14"/>
@@ -6642,13 +6642,13 @@
       </c>
       <c r="R31" s="11"/>
     </row>
-    <row r="32" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="10"/>
       <c r="B32" s="11"/>
       <c r="C32" s="12"/>
       <c r="D32" s="11"/>
       <c r="E32" s="13" t="str">
-        <f aca="false">IFERROR(IF(C32="","",WORKDAY(C32,IF(D32="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <f aca="false">IFERROR(IF(C32="","",WORKDAY(C32,IF(D32="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
       <c r="F32" s="14"/>
@@ -6668,13 +6668,13 @@
       </c>
       <c r="R32" s="11"/>
     </row>
-    <row r="33" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10"/>
       <c r="B33" s="11"/>
       <c r="C33" s="12"/>
       <c r="D33" s="11"/>
       <c r="E33" s="13" t="str">
-        <f aca="false">IFERROR(IF(C33="","",WORKDAY(C33,IF(D33="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <f aca="false">IFERROR(IF(C33="","",WORKDAY(C33,IF(D33="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
       <c r="F33" s="14"/>
@@ -6694,13 +6694,13 @@
       </c>
       <c r="R33" s="11"/>
     </row>
-    <row r="34" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="10"/>
       <c r="B34" s="11"/>
       <c r="C34" s="12"/>
       <c r="D34" s="11"/>
       <c r="E34" s="13" t="str">
-        <f aca="false">IFERROR(IF(C34="","",WORKDAY(C34,IF(D34="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <f aca="false">IFERROR(IF(C34="","",WORKDAY(C34,IF(D34="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
       <c r="F34" s="14"/>
@@ -6720,13 +6720,13 @@
       </c>
       <c r="R34" s="11"/>
     </row>
-    <row r="35" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="10"/>
       <c r="B35" s="11"/>
       <c r="C35" s="12"/>
       <c r="D35" s="11"/>
       <c r="E35" s="13" t="str">
-        <f aca="false">IFERROR(IF(C35="","",WORKDAY(C35,IF(D35="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <f aca="false">IFERROR(IF(C35="","",WORKDAY(C35,IF(D35="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
       <c r="F35" s="14"/>
@@ -6746,13 +6746,13 @@
       </c>
       <c r="R35" s="11"/>
     </row>
-    <row r="36" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="10"/>
       <c r="B36" s="11"/>
       <c r="C36" s="12"/>
       <c r="D36" s="11"/>
       <c r="E36" s="13" t="str">
-        <f aca="false">IFERROR(IF(C36="","",WORKDAY(C36,IF(D36="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <f aca="false">IFERROR(IF(C36="","",WORKDAY(C36,IF(D36="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
       <c r="F36" s="14"/>
@@ -6772,13 +6772,13 @@
       </c>
       <c r="R36" s="11"/>
     </row>
-    <row r="37" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="10"/>
       <c r="B37" s="11"/>
       <c r="C37" s="12"/>
       <c r="D37" s="11"/>
       <c r="E37" s="13" t="str">
-        <f aca="false">IFERROR(IF(C37="","",WORKDAY(C37,IF(D37="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <f aca="false">IFERROR(IF(C37="","",WORKDAY(C37,IF(D37="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
       <c r="F37" s="14"/>
@@ -6798,13 +6798,13 @@
       </c>
       <c r="R37" s="11"/>
     </row>
-    <row r="38" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="10"/>
       <c r="B38" s="11"/>
       <c r="C38" s="12"/>
       <c r="D38" s="11"/>
       <c r="E38" s="13" t="str">
-        <f aca="false">IFERROR(IF(C38="","",WORKDAY(C38,IF(D38="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <f aca="false">IFERROR(IF(C38="","",WORKDAY(C38,IF(D38="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
       <c r="F38" s="14"/>
@@ -6824,13 +6824,13 @@
       </c>
       <c r="R38" s="11"/>
     </row>
-    <row r="39" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="10"/>
       <c r="B39" s="11"/>
       <c r="C39" s="12"/>
       <c r="D39" s="11"/>
       <c r="E39" s="13" t="str">
-        <f aca="false">IFERROR(IF(C39="","",WORKDAY(C39,IF(D39="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <f aca="false">IFERROR(IF(C39="","",WORKDAY(C39,IF(D39="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
       <c r="F39" s="14"/>
@@ -6850,13 +6850,13 @@
       </c>
       <c r="R39" s="11"/>
     </row>
-    <row r="40" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="10"/>
       <c r="B40" s="11"/>
       <c r="C40" s="12"/>
       <c r="D40" s="11"/>
       <c r="E40" s="13" t="str">
-        <f aca="false">IFERROR(IF(C40="","",WORKDAY(C40,IF(D40="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <f aca="false">IFERROR(IF(C40="","",WORKDAY(C40,IF(D40="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
       <c r="F40" s="14"/>
@@ -6876,13 +6876,13 @@
       </c>
       <c r="R40" s="11"/>
     </row>
-    <row r="41" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="10"/>
       <c r="B41" s="11"/>
       <c r="C41" s="12"/>
       <c r="D41" s="11"/>
       <c r="E41" s="13" t="str">
-        <f aca="false">IFERROR(IF(C41="","",WORKDAY(C41,IF(D41="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <f aca="false">IFERROR(IF(C41="","",WORKDAY(C41,IF(D41="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
       <c r="F41" s="14"/>
@@ -6902,13 +6902,13 @@
       </c>
       <c r="R41" s="11"/>
     </row>
-    <row r="42" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="10"/>
       <c r="B42" s="11"/>
       <c r="C42" s="12"/>
       <c r="D42" s="11"/>
       <c r="E42" s="13" t="str">
-        <f aca="false">IFERROR(IF(C42="","",WORKDAY(C42,IF(D42="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <f aca="false">IFERROR(IF(C42="","",WORKDAY(C42,IF(D42="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
       <c r="F42" s="14"/>
@@ -6928,13 +6928,13 @@
       </c>
       <c r="R42" s="11"/>
     </row>
-    <row r="43" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="10"/>
       <c r="B43" s="11"/>
       <c r="C43" s="12"/>
       <c r="D43" s="11"/>
       <c r="E43" s="13" t="str">
-        <f aca="false">IFERROR(IF(C43="","",WORKDAY(C43,IF(D43="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <f aca="false">IFERROR(IF(C43="","",WORKDAY(C43,IF(D43="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
       <c r="F43" s="14"/>
@@ -6954,13 +6954,13 @@
       </c>
       <c r="R43" s="11"/>
     </row>
-    <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="10"/>
       <c r="B44" s="11"/>
       <c r="C44" s="12"/>
       <c r="D44" s="11"/>
       <c r="E44" s="13" t="str">
-        <f aca="false">IFERROR(IF(C44="","",WORKDAY(C44,IF(D44="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <f aca="false">IFERROR(IF(C44="","",WORKDAY(C44,IF(D44="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
       <c r="F44" s="14"/>
@@ -6980,13 +6980,13 @@
       </c>
       <c r="R44" s="11"/>
     </row>
-    <row r="45" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="10"/>
       <c r="B45" s="11"/>
       <c r="C45" s="12"/>
       <c r="D45" s="11"/>
       <c r="E45" s="13" t="str">
-        <f aca="false">IFERROR(IF(C45="","",WORKDAY(C45,IF(D45="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <f aca="false">IFERROR(IF(C45="","",WORKDAY(C45,IF(D45="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
       <c r="F45" s="14"/>
@@ -7006,13 +7006,13 @@
       </c>
       <c r="R45" s="11"/>
     </row>
-    <row r="46" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="10"/>
       <c r="B46" s="11"/>
       <c r="C46" s="12"/>
       <c r="D46" s="11"/>
       <c r="E46" s="13" t="str">
-        <f aca="false">IFERROR(IF(C46="","",WORKDAY(C46,IF(D46="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <f aca="false">IFERROR(IF(C46="","",WORKDAY(C46,IF(D46="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
       <c r="F46" s="14"/>
@@ -7032,13 +7032,13 @@
       </c>
       <c r="R46" s="11"/>
     </row>
-    <row r="47" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="10"/>
       <c r="B47" s="11"/>
       <c r="C47" s="12"/>
       <c r="D47" s="11"/>
       <c r="E47" s="13" t="str">
-        <f aca="false">IFERROR(IF(C47="","",WORKDAY(C47,IF(D47="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <f aca="false">IFERROR(IF(C47="","",WORKDAY(C47,IF(D47="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
       <c r="F47" s="14"/>
@@ -7058,13 +7058,13 @@
       </c>
       <c r="R47" s="11"/>
     </row>
-    <row r="48" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="10"/>
       <c r="B48" s="11"/>
       <c r="C48" s="12"/>
       <c r="D48" s="11"/>
       <c r="E48" s="13" t="str">
-        <f aca="false">IFERROR(IF(C48="","",WORKDAY(C48,IF(D48="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <f aca="false">IFERROR(IF(C48="","",WORKDAY(C48,IF(D48="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
       <c r="F48" s="14"/>
@@ -7084,13 +7084,13 @@
       </c>
       <c r="R48" s="11"/>
     </row>
-    <row r="49" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="10"/>
       <c r="B49" s="11"/>
       <c r="C49" s="12"/>
       <c r="D49" s="11"/>
       <c r="E49" s="13" t="str">
-        <f aca="false">IFERROR(IF(C49="","",WORKDAY(C49,IF(D49="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <f aca="false">IFERROR(IF(C49="","",WORKDAY(C49,IF(D49="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
       <c r="F49" s="14"/>
@@ -7110,13 +7110,13 @@
       </c>
       <c r="R49" s="11"/>
     </row>
-    <row r="50" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="10"/>
       <c r="B50" s="11"/>
       <c r="C50" s="12"/>
       <c r="D50" s="11"/>
       <c r="E50" s="13" t="str">
-        <f aca="false">IFERROR(IF(C50="","",WORKDAY(C50,IF(D50="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <f aca="false">IFERROR(IF(C50="","",WORKDAY(C50,IF(D50="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
       <c r="F50" s="14"/>
@@ -7136,13 +7136,13 @@
       </c>
       <c r="R50" s="11"/>
     </row>
-    <row r="51" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="10"/>
       <c r="B51" s="11"/>
       <c r="C51" s="12"/>
       <c r="D51" s="11"/>
       <c r="E51" s="13" t="str">
-        <f aca="false">IFERROR(IF(C51="","",WORKDAY(C51,IF(D51="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <f aca="false">IFERROR(IF(C51="","",WORKDAY(C51,IF(D51="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
       <c r="F51" s="14"/>
@@ -7162,13 +7162,13 @@
       </c>
       <c r="R51" s="11"/>
     </row>
-    <row r="52" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="10"/>
       <c r="B52" s="11"/>
       <c r="C52" s="12"/>
       <c r="D52" s="11"/>
       <c r="E52" s="13" t="str">
-        <f aca="false">IFERROR(IF(C52="","",WORKDAY(C52,IF(D52="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <f aca="false">IFERROR(IF(C52="","",WORKDAY(C52,IF(D52="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
       <c r="F52" s="14"/>
@@ -7188,13 +7188,13 @@
       </c>
       <c r="R52" s="11"/>
     </row>
-    <row r="53" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="10"/>
       <c r="B53" s="11"/>
       <c r="C53" s="12"/>
       <c r="D53" s="11"/>
       <c r="E53" s="13" t="str">
-        <f aca="false">IFERROR(IF(C53="","",WORKDAY(C53,IF(D53="Sim — elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
+        <f aca="false">IFERROR(IF(C53="","",WORKDAY(C53,IF(D53="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
       <c r="F53" s="14"/>
@@ -7229,7 +7229,7 @@
   </conditionalFormatting>
   <dataValidations count="151">
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D4" type="list">
-      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula1>"Não avaliado,Sim: elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K4" type="list">
@@ -7241,7 +7241,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D5" type="list">
-      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula1>"Não avaliado,Sim: elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K5" type="list">
@@ -7253,7 +7253,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D6" type="list">
-      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula1>"Não avaliado,Sim: elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K6" type="list">
@@ -7265,7 +7265,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D7" type="list">
-      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula1>"Não avaliado,Sim: elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K7" type="list">
@@ -7277,7 +7277,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D8" type="list">
-      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula1>"Não avaliado,Sim: elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K8" type="list">
@@ -7289,7 +7289,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D9" type="list">
-      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula1>"Não avaliado,Sim: elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K9" type="list">
@@ -7301,7 +7301,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D10" type="list">
-      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula1>"Não avaliado,Sim: elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K10" type="list">
@@ -7313,7 +7313,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D11" type="list">
-      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula1>"Não avaliado,Sim: elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K11" type="list">
@@ -7325,7 +7325,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D12" type="list">
-      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula1>"Não avaliado,Sim: elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K12" type="list">
@@ -7337,7 +7337,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D13" type="list">
-      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula1>"Não avaliado,Sim: elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K13" type="list">
@@ -7349,7 +7349,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D14" type="list">
-      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula1>"Não avaliado,Sim: elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K14" type="list">
@@ -7361,7 +7361,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D15" type="list">
-      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula1>"Não avaliado,Sim: elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K15" type="list">
@@ -7373,7 +7373,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D16" type="list">
-      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula1>"Não avaliado,Sim: elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K16" type="list">
@@ -7385,7 +7385,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D17" type="list">
-      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula1>"Não avaliado,Sim: elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K17" type="list">
@@ -7397,7 +7397,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D18" type="list">
-      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula1>"Não avaliado,Sim: elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K18" type="list">
@@ -7409,7 +7409,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D19" type="list">
-      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula1>"Não avaliado,Sim: elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K19" type="list">
@@ -7421,7 +7421,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D20" type="list">
-      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula1>"Não avaliado,Sim: elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K20" type="list">
@@ -7433,7 +7433,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D21" type="list">
-      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula1>"Não avaliado,Sim: elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K21" type="list">
@@ -7445,7 +7445,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D22" type="list">
-      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula1>"Não avaliado,Sim: elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K22" type="list">
@@ -7457,7 +7457,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D23" type="list">
-      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula1>"Não avaliado,Sim: elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K23" type="list">
@@ -7469,7 +7469,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D24" type="list">
-      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula1>"Não avaliado,Sim: elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K24" type="list">
@@ -7481,7 +7481,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D25" type="list">
-      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula1>"Não avaliado,Sim: elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K25" type="list">
@@ -7493,7 +7493,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D26" type="list">
-      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula1>"Não avaliado,Sim: elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K26" type="list">
@@ -7505,7 +7505,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D27" type="list">
-      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula1>"Não avaliado,Sim: elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K27" type="list">
@@ -7517,7 +7517,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D28" type="list">
-      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula1>"Não avaliado,Sim: elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K28" type="list">
@@ -7529,7 +7529,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D29" type="list">
-      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula1>"Não avaliado,Sim: elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K29" type="list">
@@ -7541,7 +7541,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D30" type="list">
-      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula1>"Não avaliado,Sim: elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K30" type="list">
@@ -7553,7 +7553,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D31" type="list">
-      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula1>"Não avaliado,Sim: elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K31" type="list">
@@ -7565,7 +7565,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D32" type="list">
-      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula1>"Não avaliado,Sim: elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K32" type="list">
@@ -7577,7 +7577,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D33" type="list">
-      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula1>"Não avaliado,Sim: elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K33" type="list">
@@ -7589,7 +7589,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D34" type="list">
-      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula1>"Não avaliado,Sim: elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K34" type="list">
@@ -7601,7 +7601,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D35" type="list">
-      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula1>"Não avaliado,Sim: elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K35" type="list">
@@ -7613,7 +7613,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D36" type="list">
-      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula1>"Não avaliado,Sim: elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K36" type="list">
@@ -7625,7 +7625,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D37" type="list">
-      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula1>"Não avaliado,Sim: elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K37" type="list">
@@ -7637,7 +7637,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D38" type="list">
-      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula1>"Não avaliado,Sim: elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K38" type="list">
@@ -7649,7 +7649,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D39" type="list">
-      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula1>"Não avaliado,Sim: elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K39" type="list">
@@ -7661,7 +7661,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D40" type="list">
-      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula1>"Não avaliado,Sim: elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K40" type="list">
@@ -7673,7 +7673,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D41" type="list">
-      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula1>"Não avaliado,Sim: elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K41" type="list">
@@ -7685,7 +7685,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D42" type="list">
-      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula1>"Não avaliado,Sim: elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K42" type="list">
@@ -7697,7 +7697,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D43" type="list">
-      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula1>"Não avaliado,Sim: elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K43" type="list">
@@ -7709,7 +7709,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D44" type="list">
-      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula1>"Não avaliado,Sim: elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K44" type="list">
@@ -7721,7 +7721,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D45" type="list">
-      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula1>"Não avaliado,Sim: elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K45" type="list">
@@ -7733,7 +7733,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D46" type="list">
-      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula1>"Não avaliado,Sim: elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K46" type="list">
@@ -7745,7 +7745,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D47" type="list">
-      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula1>"Não avaliado,Sim: elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K47" type="list">
@@ -7757,7 +7757,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D48" type="list">
-      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula1>"Não avaliado,Sim: elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K48" type="list">
@@ -7769,7 +7769,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D49" type="list">
-      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula1>"Não avaliado,Sim: elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K49" type="list">
@@ -7781,7 +7781,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D50" type="list">
-      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula1>"Não avaliado,Sim: elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K50" type="list">
@@ -7793,7 +7793,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D51" type="list">
-      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula1>"Não avaliado,Sim: elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K51" type="list">
@@ -7805,7 +7805,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D52" type="list">
-      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula1>"Não avaliado,Sim: elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K52" type="list">
@@ -7817,7 +7817,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D53" type="list">
-      <formula1>"Não avaliado,Sim — elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
+      <formula1>"Não avaliado,Sim: elegível (Resolução CD/ANPD nº 2/2022),Não elegível"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K53" type="list">
@@ -7828,7 +7828,7 @@
       <formula1>"Não avaliado,Pendente de decisão,Decidido: comunicar,Decidido: não comunicar"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Este identificador já existe nesta coluna. Cada ID deve ser único e estável (não reutilize nem renumere IDs já atribuídos). Padrão esperado: AVR-01." errorStyle="stop" errorTitle="ID duplicado" operator="between" prompt="Digite um identificador único e estável, padrão AVR-01. Não é gerado automaticamente — preserve o mesmo ID após inserir, excluir ou reordenar linhas." promptTitle="Identificador manual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A4:A53" type="custom">
+    <dataValidation allowBlank="true" error="Este identificador já existe nesta coluna. Cada ID deve ser único e estável (não reutilize nem renumere IDs já atribuídos). Padrão esperado: AVR-01." errorStyle="stop" errorTitle="ID duplicado" operator="between" prompt="Digite um identificador único e estável, padrão AVR-01. Não é gerado automaticamente; preserve o mesmo ID após inserir, excluir ou reordenar linhas." promptTitle="Identificador manual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A4:A53" type="custom">
       <formula1>OR(A4="",COUNTIF($A$4:$A$53,A4)&lt;=1)</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -7917,7 +7917,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
         <v>53</v>
       </c>
@@ -7946,7 +7946,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10"/>
       <c r="B5" s="11"/>
       <c r="C5" s="12"/>
@@ -7957,7 +7957,7 @@
       <c r="H5" s="11"/>
       <c r="I5" s="11"/>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10"/>
       <c r="B6" s="11"/>
       <c r="C6" s="12"/>
@@ -7968,7 +7968,7 @@
       <c r="H6" s="11"/>
       <c r="I6" s="11"/>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10"/>
       <c r="B7" s="11"/>
       <c r="C7" s="12"/>
@@ -7979,7 +7979,7 @@
       <c r="H7" s="11"/>
       <c r="I7" s="11"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10"/>
       <c r="B8" s="11"/>
       <c r="C8" s="12"/>
@@ -7990,7 +7990,7 @@
       <c r="H8" s="11"/>
       <c r="I8" s="11"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10"/>
       <c r="B9" s="11"/>
       <c r="C9" s="12"/>
@@ -8001,7 +8001,7 @@
       <c r="H9" s="11"/>
       <c r="I9" s="11"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10"/>
       <c r="B10" s="11"/>
       <c r="C10" s="12"/>
@@ -8012,7 +8012,7 @@
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10"/>
       <c r="B11" s="11"/>
       <c r="C11" s="12"/>
@@ -8023,7 +8023,7 @@
       <c r="H11" s="11"/>
       <c r="I11" s="11"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10"/>
       <c r="B12" s="11"/>
       <c r="C12" s="12"/>
@@ -8034,7 +8034,7 @@
       <c r="H12" s="11"/>
       <c r="I12" s="11"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10"/>
       <c r="B13" s="11"/>
       <c r="C13" s="12"/>
@@ -8045,7 +8045,7 @@
       <c r="H13" s="11"/>
       <c r="I13" s="11"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10"/>
       <c r="B14" s="11"/>
       <c r="C14" s="12"/>
@@ -8056,7 +8056,7 @@
       <c r="H14" s="11"/>
       <c r="I14" s="11"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10"/>
       <c r="B15" s="11"/>
       <c r="C15" s="12"/>
@@ -8067,7 +8067,7 @@
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10"/>
       <c r="B16" s="11"/>
       <c r="C16" s="12"/>
@@ -8078,7 +8078,7 @@
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10"/>
       <c r="B17" s="11"/>
       <c r="C17" s="12"/>
@@ -8089,7 +8089,7 @@
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10"/>
       <c r="B18" s="11"/>
       <c r="C18" s="12"/>
@@ -8100,7 +8100,7 @@
       <c r="H18" s="11"/>
       <c r="I18" s="11"/>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="10"/>
       <c r="B19" s="11"/>
       <c r="C19" s="12"/>
@@ -8111,7 +8111,7 @@
       <c r="H19" s="11"/>
       <c r="I19" s="11"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10"/>
       <c r="B20" s="11"/>
       <c r="C20" s="12"/>
@@ -8122,7 +8122,7 @@
       <c r="H20" s="11"/>
       <c r="I20" s="11"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="10"/>
       <c r="B21" s="11"/>
       <c r="C21" s="12"/>
@@ -8133,7 +8133,7 @@
       <c r="H21" s="11"/>
       <c r="I21" s="11"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="10"/>
       <c r="B22" s="11"/>
       <c r="C22" s="12"/>
@@ -8144,7 +8144,7 @@
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="10"/>
       <c r="B23" s="11"/>
       <c r="C23" s="12"/>
@@ -8155,7 +8155,7 @@
       <c r="H23" s="11"/>
       <c r="I23" s="11"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="10"/>
       <c r="B24" s="11"/>
       <c r="C24" s="12"/>
@@ -8166,7 +8166,7 @@
       <c r="H24" s="11"/>
       <c r="I24" s="11"/>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="10"/>
       <c r="B25" s="11"/>
       <c r="C25" s="12"/>
@@ -8177,7 +8177,7 @@
       <c r="H25" s="11"/>
       <c r="I25" s="11"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="10"/>
       <c r="B26" s="11"/>
       <c r="C26" s="12"/>
@@ -8188,7 +8188,7 @@
       <c r="H26" s="11"/>
       <c r="I26" s="11"/>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="10"/>
       <c r="B27" s="11"/>
       <c r="C27" s="12"/>
@@ -8199,7 +8199,7 @@
       <c r="H27" s="11"/>
       <c r="I27" s="11"/>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="10"/>
       <c r="B28" s="11"/>
       <c r="C28" s="12"/>
@@ -8210,7 +8210,7 @@
       <c r="H28" s="11"/>
       <c r="I28" s="11"/>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="10"/>
       <c r="B29" s="11"/>
       <c r="C29" s="12"/>
@@ -8221,7 +8221,7 @@
       <c r="H29" s="11"/>
       <c r="I29" s="11"/>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="10"/>
       <c r="B30" s="11"/>
       <c r="C30" s="12"/>
@@ -8232,7 +8232,7 @@
       <c r="H30" s="11"/>
       <c r="I30" s="11"/>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
       <c r="C31" s="12"/>
@@ -8243,7 +8243,7 @@
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="10"/>
       <c r="B32" s="11"/>
       <c r="C32" s="12"/>
@@ -8254,7 +8254,7 @@
       <c r="H32" s="11"/>
       <c r="I32" s="11"/>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10"/>
       <c r="B33" s="11"/>
       <c r="C33" s="12"/>
@@ -8265,7 +8265,7 @@
       <c r="H33" s="11"/>
       <c r="I33" s="11"/>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="10"/>
       <c r="B34" s="11"/>
       <c r="C34" s="12"/>
@@ -8276,7 +8276,7 @@
       <c r="H34" s="11"/>
       <c r="I34" s="11"/>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="10"/>
       <c r="B35" s="11"/>
       <c r="C35" s="12"/>
@@ -8287,7 +8287,7 @@
       <c r="H35" s="11"/>
       <c r="I35" s="11"/>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="10"/>
       <c r="B36" s="11"/>
       <c r="C36" s="12"/>
@@ -8298,7 +8298,7 @@
       <c r="H36" s="11"/>
       <c r="I36" s="11"/>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="10"/>
       <c r="B37" s="11"/>
       <c r="C37" s="12"/>
@@ -8309,7 +8309,7 @@
       <c r="H37" s="11"/>
       <c r="I37" s="11"/>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="10"/>
       <c r="B38" s="11"/>
       <c r="C38" s="12"/>
@@ -8320,7 +8320,7 @@
       <c r="H38" s="11"/>
       <c r="I38" s="11"/>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="10"/>
       <c r="B39" s="11"/>
       <c r="C39" s="12"/>
@@ -8331,7 +8331,7 @@
       <c r="H39" s="11"/>
       <c r="I39" s="11"/>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="10"/>
       <c r="B40" s="11"/>
       <c r="C40" s="12"/>
@@ -8342,7 +8342,7 @@
       <c r="H40" s="11"/>
       <c r="I40" s="11"/>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="10"/>
       <c r="B41" s="11"/>
       <c r="C41" s="12"/>
@@ -8353,7 +8353,7 @@
       <c r="H41" s="11"/>
       <c r="I41" s="11"/>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="10"/>
       <c r="B42" s="11"/>
       <c r="C42" s="12"/>
@@ -8364,7 +8364,7 @@
       <c r="H42" s="11"/>
       <c r="I42" s="11"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="10"/>
       <c r="B43" s="11"/>
       <c r="C43" s="12"/>
@@ -8375,7 +8375,7 @@
       <c r="H43" s="11"/>
       <c r="I43" s="11"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="10"/>
       <c r="B44" s="11"/>
       <c r="C44" s="12"/>
@@ -8386,7 +8386,7 @@
       <c r="H44" s="11"/>
       <c r="I44" s="11"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="10"/>
       <c r="B45" s="11"/>
       <c r="C45" s="12"/>
@@ -8397,7 +8397,7 @@
       <c r="H45" s="11"/>
       <c r="I45" s="11"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="10"/>
       <c r="B46" s="11"/>
       <c r="C46" s="12"/>
@@ -8408,7 +8408,7 @@
       <c r="H46" s="11"/>
       <c r="I46" s="11"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="10"/>
       <c r="B47" s="11"/>
       <c r="C47" s="12"/>
@@ -8419,7 +8419,7 @@
       <c r="H47" s="11"/>
       <c r="I47" s="11"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="10"/>
       <c r="B48" s="11"/>
       <c r="C48" s="12"/>
@@ -8430,7 +8430,7 @@
       <c r="H48" s="11"/>
       <c r="I48" s="11"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="10"/>
       <c r="B49" s="11"/>
       <c r="C49" s="12"/>
@@ -8441,7 +8441,7 @@
       <c r="H49" s="11"/>
       <c r="I49" s="11"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="10"/>
       <c r="B50" s="11"/>
       <c r="C50" s="12"/>
@@ -8452,7 +8452,7 @@
       <c r="H50" s="11"/>
       <c r="I50" s="11"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="10"/>
       <c r="B51" s="11"/>
       <c r="C51" s="12"/>
@@ -8463,7 +8463,7 @@
       <c r="H51" s="11"/>
       <c r="I51" s="11"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="10"/>
       <c r="B52" s="11"/>
       <c r="C52" s="12"/>
@@ -8474,7 +8474,7 @@
       <c r="H52" s="11"/>
       <c r="I52" s="11"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="10"/>
       <c r="B53" s="11"/>
       <c r="C53" s="12"/>
@@ -8499,7 +8499,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" error="Este identificador já existe nesta coluna. Cada ID deve ser único e estável (não reutilize nem renumere IDs já atribuídos). Padrão esperado: AVR-02." errorStyle="stop" errorTitle="ID duplicado" operator="between" prompt="Digite um identificador único e estável, padrão AVR-02. Não é gerado automaticamente — preserve o mesmo ID após inserir, excluir ou reordenar linhas." promptTitle="Identificador manual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A4:A53" type="custom">
+    <dataValidation allowBlank="true" error="Este identificador já existe nesta coluna. Cada ID deve ser único e estável (não reutilize nem renumere IDs já atribuídos). Padrão esperado: AVR-02." errorStyle="stop" errorTitle="ID duplicado" operator="between" prompt="Digite um identificador único e estável, padrão AVR-02. Não é gerado automaticamente; preserve o mesmo ID após inserir, excluir ou reordenar linhas." promptTitle="Identificador manual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A4:A53" type="custom">
       <formula1>OR(A4="",COUNTIF($A$4:$A$53,A4)&lt;=1)</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -8537,7 +8537,7 @@
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>146</v>
       </c>
@@ -8557,7 +8557,7 @@
       <c r="E3" s="16"/>
       <c r="F3" s="16"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="17" t="s">
         <v>148</v>
       </c>
@@ -8574,7 +8574,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="19" t="s">
         <v>153</v>
       </c>
@@ -8591,7 +8591,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="19" t="s">
         <v>157</v>
       </c>
@@ -8608,7 +8608,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="19" t="s">
         <v>159</v>
       </c>
@@ -8625,7 +8625,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="23" t="s">
         <v>160</v>
       </c>

--- a/instrumentos/exemplos/DAIR_Avaliacao_Riscos_Titulares_ANPD_v0.3_EXEMPLO-INC-2026-001.xlsx
+++ b/instrumentos/exemplos/DAIR_Avaliacao_Riscos_Titulares_ANPD_v0.3_EXEMPLO-INC-2026-001.xlsx
@@ -170,6 +170,18 @@
         </r>
       </text>
     </comment>
+    <comment ref="S3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">A ausência de comunicação também é uma decisão sujeita a registro obrigatório (Política, seções 11 e 13): quando a Decisão à ANPD (K) ou aos Titulares (L) for 'Decidido: não comunicar', este campo é obrigatório e deve registrar o fundamento, não apenas a conclusão. Formatação condicional sinaliza em vermelho quando vazio nessa condição.</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -197,7 +209,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="162">
   <si>
     <t xml:space="preserve">DAIR: Avaliação de Riscos aos Titulares e Decisão de Comunicação</t>
   </si>
@@ -545,6 +557,9 @@
   </si>
   <si>
     <t xml:space="preserve">Reavaliações Posteriores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motivo da Ausência de Comunicação (obrigatório quando a Decisão, à ANPD ou aos Titulares, for 'Decidido: não comunicar')</t>
   </si>
   <si>
     <t xml:space="preserve">Não avaliado</t>
@@ -882,100 +897,96 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1243,115 +1254,115 @@
   <dimension ref="A1:B14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="100"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="100"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
+      <c r="B1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3"/>
+      <c r="B2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="6" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="6" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="6" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="6" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1378,895 +1389,895 @@
   <dimension ref="A1:M53"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="1" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="K3" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="L3" s="9" t="s">
+      <c r="L3" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="M3" s="9" t="s">
+      <c r="M3" s="8" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="12" t="n">
+      <c r="D4" s="11" t="n">
         <v>46314.3923611111</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="L4" s="11" t="s">
+      <c r="L4" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="M4" s="11" t="s">
+      <c r="M4" s="10" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D5" s="12" t="n">
+      <c r="D5" s="11" t="n">
         <v>46314.5069444445</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="H5" s="11" t="s">
+      <c r="H5" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="I5" s="11" t="s">
+      <c r="I5" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="J5" s="11" t="s">
+      <c r="J5" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="K5" s="11" t="s">
+      <c r="K5" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="L5" s="11" t="s">
+      <c r="L5" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="M5" s="11" t="s">
+      <c r="M5" s="10" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
+      <c r="A6" s="9"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="11"/>
+      <c r="A7" s="9"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="11"/>
+      <c r="A8" s="9"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="11"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="11"/>
+      <c r="A9" s="9"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11"/>
+      <c r="A10" s="9"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
+      <c r="A11" s="9"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11"/>
+      <c r="A12" s="9"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="10"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="11"/>
+      <c r="A13" s="9"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="11"/>
+      <c r="A14" s="9"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
+      <c r="A15" s="9"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="11"/>
+      <c r="A16" s="9"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="11"/>
+      <c r="A17" s="9"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="10"/>
+      <c r="M17" s="10"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="11"/>
+      <c r="A18" s="9"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="10"/>
+      <c r="M18" s="10"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
-      <c r="J19" s="11"/>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="11"/>
+      <c r="A19" s="9"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="10"/>
+      <c r="J19" s="10"/>
+      <c r="K19" s="10"/>
+      <c r="L19" s="10"/>
+      <c r="M19" s="10"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="10"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11"/>
-      <c r="J20" s="11"/>
-      <c r="K20" s="11"/>
-      <c r="L20" s="11"/>
-      <c r="M20" s="11"/>
+      <c r="A20" s="9"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="10"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="10"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="11"/>
-      <c r="J21" s="11"/>
-      <c r="K21" s="11"/>
-      <c r="L21" s="11"/>
-      <c r="M21" s="11"/>
+      <c r="A21" s="9"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="10"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="10"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="11"/>
-      <c r="J22" s="11"/>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="11"/>
+      <c r="A22" s="9"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="10"/>
+      <c r="J22" s="10"/>
+      <c r="K22" s="10"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="10"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="10"/>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="11"/>
-      <c r="J23" s="11"/>
-      <c r="K23" s="11"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="11"/>
+      <c r="A23" s="9"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="10"/>
+      <c r="J23" s="10"/>
+      <c r="K23" s="10"/>
+      <c r="L23" s="10"/>
+      <c r="M23" s="10"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="10"/>
-      <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="11"/>
-      <c r="J24" s="11"/>
-      <c r="K24" s="11"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="11"/>
+      <c r="A24" s="9"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="10"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="10"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="11"/>
-      <c r="J25" s="11"/>
-      <c r="K25" s="11"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="11"/>
+      <c r="A25" s="9"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="10"/>
+      <c r="J25" s="10"/>
+      <c r="K25" s="10"/>
+      <c r="L25" s="10"/>
+      <c r="M25" s="10"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="10"/>
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11"/>
-      <c r="I26" s="11"/>
-      <c r="J26" s="11"/>
-      <c r="K26" s="11"/>
-      <c r="L26" s="11"/>
-      <c r="M26" s="11"/>
+      <c r="A26" s="9"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="10"/>
+      <c r="I26" s="10"/>
+      <c r="J26" s="10"/>
+      <c r="K26" s="10"/>
+      <c r="L26" s="10"/>
+      <c r="M26" s="10"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="10"/>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11"/>
-      <c r="I27" s="11"/>
-      <c r="J27" s="11"/>
-      <c r="K27" s="11"/>
-      <c r="L27" s="11"/>
-      <c r="M27" s="11"/>
+      <c r="A27" s="9"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="10"/>
+      <c r="I27" s="10"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="10"/>
+      <c r="L27" s="10"/>
+      <c r="M27" s="10"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="10"/>
-      <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="11"/>
-      <c r="H28" s="11"/>
-      <c r="I28" s="11"/>
-      <c r="J28" s="11"/>
-      <c r="K28" s="11"/>
-      <c r="L28" s="11"/>
-      <c r="M28" s="11"/>
+      <c r="A28" s="9"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="10"/>
+      <c r="I28" s="10"/>
+      <c r="J28" s="10"/>
+      <c r="K28" s="10"/>
+      <c r="L28" s="10"/>
+      <c r="M28" s="10"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="10"/>
-      <c r="B29" s="11"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="11"/>
-      <c r="H29" s="11"/>
-      <c r="I29" s="11"/>
-      <c r="J29" s="11"/>
-      <c r="K29" s="11"/>
-      <c r="L29" s="11"/>
-      <c r="M29" s="11"/>
+      <c r="A29" s="9"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="10"/>
+      <c r="H29" s="10"/>
+      <c r="I29" s="10"/>
+      <c r="J29" s="10"/>
+      <c r="K29" s="10"/>
+      <c r="L29" s="10"/>
+      <c r="M29" s="10"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="10"/>
-      <c r="B30" s="11"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="11"/>
-      <c r="H30" s="11"/>
-      <c r="I30" s="11"/>
-      <c r="J30" s="11"/>
-      <c r="K30" s="11"/>
-      <c r="L30" s="11"/>
-      <c r="M30" s="11"/>
+      <c r="A30" s="9"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="10"/>
+      <c r="H30" s="10"/>
+      <c r="I30" s="10"/>
+      <c r="J30" s="10"/>
+      <c r="K30" s="10"/>
+      <c r="L30" s="10"/>
+      <c r="M30" s="10"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="10"/>
-      <c r="B31" s="11"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="11"/>
-      <c r="H31" s="11"/>
-      <c r="I31" s="11"/>
-      <c r="J31" s="11"/>
-      <c r="K31" s="11"/>
-      <c r="L31" s="11"/>
-      <c r="M31" s="11"/>
+      <c r="A31" s="9"/>
+      <c r="B31" s="10"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="10"/>
+      <c r="I31" s="10"/>
+      <c r="J31" s="10"/>
+      <c r="K31" s="10"/>
+      <c r="L31" s="10"/>
+      <c r="M31" s="10"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="10"/>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="11"/>
-      <c r="J32" s="11"/>
-      <c r="K32" s="11"/>
-      <c r="L32" s="11"/>
-      <c r="M32" s="11"/>
+      <c r="A32" s="9"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="10"/>
+      <c r="G32" s="10"/>
+      <c r="H32" s="10"/>
+      <c r="I32" s="10"/>
+      <c r="J32" s="10"/>
+      <c r="K32" s="10"/>
+      <c r="L32" s="10"/>
+      <c r="M32" s="10"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="10"/>
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="11"/>
-      <c r="I33" s="11"/>
-      <c r="J33" s="11"/>
-      <c r="K33" s="11"/>
-      <c r="L33" s="11"/>
-      <c r="M33" s="11"/>
+      <c r="A33" s="9"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="10"/>
+      <c r="I33" s="10"/>
+      <c r="J33" s="10"/>
+      <c r="K33" s="10"/>
+      <c r="L33" s="10"/>
+      <c r="M33" s="10"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="10"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="11"/>
-      <c r="I34" s="11"/>
-      <c r="J34" s="11"/>
-      <c r="K34" s="11"/>
-      <c r="L34" s="11"/>
-      <c r="M34" s="11"/>
+      <c r="A34" s="9"/>
+      <c r="B34" s="10"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="10"/>
+      <c r="G34" s="10"/>
+      <c r="H34" s="10"/>
+      <c r="I34" s="10"/>
+      <c r="J34" s="10"/>
+      <c r="K34" s="10"/>
+      <c r="L34" s="10"/>
+      <c r="M34" s="10"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="10"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="12"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="11"/>
-      <c r="I35" s="11"/>
-      <c r="J35" s="11"/>
-      <c r="K35" s="11"/>
-      <c r="L35" s="11"/>
-      <c r="M35" s="11"/>
+      <c r="A35" s="9"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="10"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="10"/>
+      <c r="I35" s="10"/>
+      <c r="J35" s="10"/>
+      <c r="K35" s="10"/>
+      <c r="L35" s="10"/>
+      <c r="M35" s="10"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="10"/>
-      <c r="B36" s="11"/>
-      <c r="C36" s="11"/>
-      <c r="D36" s="12"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="11"/>
-      <c r="H36" s="11"/>
-      <c r="I36" s="11"/>
-      <c r="J36" s="11"/>
-      <c r="K36" s="11"/>
-      <c r="L36" s="11"/>
-      <c r="M36" s="11"/>
+      <c r="A36" s="9"/>
+      <c r="B36" s="10"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="10"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="10"/>
+      <c r="H36" s="10"/>
+      <c r="I36" s="10"/>
+      <c r="J36" s="10"/>
+      <c r="K36" s="10"/>
+      <c r="L36" s="10"/>
+      <c r="M36" s="10"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="10"/>
-      <c r="B37" s="11"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="12"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="11"/>
-      <c r="I37" s="11"/>
-      <c r="J37" s="11"/>
-      <c r="K37" s="11"/>
-      <c r="L37" s="11"/>
-      <c r="M37" s="11"/>
+      <c r="A37" s="9"/>
+      <c r="B37" s="10"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="10"/>
+      <c r="I37" s="10"/>
+      <c r="J37" s="10"/>
+      <c r="K37" s="10"/>
+      <c r="L37" s="10"/>
+      <c r="M37" s="10"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="10"/>
-      <c r="B38" s="11"/>
-      <c r="C38" s="11"/>
-      <c r="D38" s="12"/>
-      <c r="E38" s="11"/>
-      <c r="F38" s="11"/>
-      <c r="G38" s="11"/>
-      <c r="H38" s="11"/>
-      <c r="I38" s="11"/>
-      <c r="J38" s="11"/>
-      <c r="K38" s="11"/>
-      <c r="L38" s="11"/>
-      <c r="M38" s="11"/>
+      <c r="A38" s="9"/>
+      <c r="B38" s="10"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="10"/>
+      <c r="F38" s="10"/>
+      <c r="G38" s="10"/>
+      <c r="H38" s="10"/>
+      <c r="I38" s="10"/>
+      <c r="J38" s="10"/>
+      <c r="K38" s="10"/>
+      <c r="L38" s="10"/>
+      <c r="M38" s="10"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="10"/>
-      <c r="B39" s="11"/>
-      <c r="C39" s="11"/>
-      <c r="D39" s="12"/>
-      <c r="E39" s="11"/>
-      <c r="F39" s="11"/>
-      <c r="G39" s="11"/>
-      <c r="H39" s="11"/>
-      <c r="I39" s="11"/>
-      <c r="J39" s="11"/>
-      <c r="K39" s="11"/>
-      <c r="L39" s="11"/>
-      <c r="M39" s="11"/>
+      <c r="A39" s="9"/>
+      <c r="B39" s="10"/>
+      <c r="C39" s="10"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="10"/>
+      <c r="F39" s="10"/>
+      <c r="G39" s="10"/>
+      <c r="H39" s="10"/>
+      <c r="I39" s="10"/>
+      <c r="J39" s="10"/>
+      <c r="K39" s="10"/>
+      <c r="L39" s="10"/>
+      <c r="M39" s="10"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="10"/>
-      <c r="B40" s="11"/>
-      <c r="C40" s="11"/>
-      <c r="D40" s="12"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="11"/>
-      <c r="G40" s="11"/>
-      <c r="H40" s="11"/>
-      <c r="I40" s="11"/>
-      <c r="J40" s="11"/>
-      <c r="K40" s="11"/>
-      <c r="L40" s="11"/>
-      <c r="M40" s="11"/>
+      <c r="A40" s="9"/>
+      <c r="B40" s="10"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="10"/>
+      <c r="F40" s="10"/>
+      <c r="G40" s="10"/>
+      <c r="H40" s="10"/>
+      <c r="I40" s="10"/>
+      <c r="J40" s="10"/>
+      <c r="K40" s="10"/>
+      <c r="L40" s="10"/>
+      <c r="M40" s="10"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="10"/>
-      <c r="B41" s="11"/>
-      <c r="C41" s="11"/>
-      <c r="D41" s="12"/>
-      <c r="E41" s="11"/>
-      <c r="F41" s="11"/>
-      <c r="G41" s="11"/>
-      <c r="H41" s="11"/>
-      <c r="I41" s="11"/>
-      <c r="J41" s="11"/>
-      <c r="K41" s="11"/>
-      <c r="L41" s="11"/>
-      <c r="M41" s="11"/>
+      <c r="A41" s="9"/>
+      <c r="B41" s="10"/>
+      <c r="C41" s="10"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="10"/>
+      <c r="F41" s="10"/>
+      <c r="G41" s="10"/>
+      <c r="H41" s="10"/>
+      <c r="I41" s="10"/>
+      <c r="J41" s="10"/>
+      <c r="K41" s="10"/>
+      <c r="L41" s="10"/>
+      <c r="M41" s="10"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="10"/>
-      <c r="B42" s="11"/>
-      <c r="C42" s="11"/>
-      <c r="D42" s="12"/>
-      <c r="E42" s="11"/>
-      <c r="F42" s="11"/>
-      <c r="G42" s="11"/>
-      <c r="H42" s="11"/>
-      <c r="I42" s="11"/>
-      <c r="J42" s="11"/>
-      <c r="K42" s="11"/>
-      <c r="L42" s="11"/>
-      <c r="M42" s="11"/>
+      <c r="A42" s="9"/>
+      <c r="B42" s="10"/>
+      <c r="C42" s="10"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="10"/>
+      <c r="F42" s="10"/>
+      <c r="G42" s="10"/>
+      <c r="H42" s="10"/>
+      <c r="I42" s="10"/>
+      <c r="J42" s="10"/>
+      <c r="K42" s="10"/>
+      <c r="L42" s="10"/>
+      <c r="M42" s="10"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="10"/>
-      <c r="B43" s="11"/>
-      <c r="C43" s="11"/>
-      <c r="D43" s="12"/>
-      <c r="E43" s="11"/>
-      <c r="F43" s="11"/>
-      <c r="G43" s="11"/>
-      <c r="H43" s="11"/>
-      <c r="I43" s="11"/>
-      <c r="J43" s="11"/>
-      <c r="K43" s="11"/>
-      <c r="L43" s="11"/>
-      <c r="M43" s="11"/>
+      <c r="A43" s="9"/>
+      <c r="B43" s="10"/>
+      <c r="C43" s="10"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="10"/>
+      <c r="F43" s="10"/>
+      <c r="G43" s="10"/>
+      <c r="H43" s="10"/>
+      <c r="I43" s="10"/>
+      <c r="J43" s="10"/>
+      <c r="K43" s="10"/>
+      <c r="L43" s="10"/>
+      <c r="M43" s="10"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="10"/>
-      <c r="B44" s="11"/>
-      <c r="C44" s="11"/>
-      <c r="D44" s="12"/>
-      <c r="E44" s="11"/>
-      <c r="F44" s="11"/>
-      <c r="G44" s="11"/>
-      <c r="H44" s="11"/>
-      <c r="I44" s="11"/>
-      <c r="J44" s="11"/>
-      <c r="K44" s="11"/>
-      <c r="L44" s="11"/>
-      <c r="M44" s="11"/>
+      <c r="A44" s="9"/>
+      <c r="B44" s="10"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="10"/>
+      <c r="F44" s="10"/>
+      <c r="G44" s="10"/>
+      <c r="H44" s="10"/>
+      <c r="I44" s="10"/>
+      <c r="J44" s="10"/>
+      <c r="K44" s="10"/>
+      <c r="L44" s="10"/>
+      <c r="M44" s="10"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="10"/>
-      <c r="B45" s="11"/>
-      <c r="C45" s="11"/>
-      <c r="D45" s="12"/>
-      <c r="E45" s="11"/>
-      <c r="F45" s="11"/>
-      <c r="G45" s="11"/>
-      <c r="H45" s="11"/>
-      <c r="I45" s="11"/>
-      <c r="J45" s="11"/>
-      <c r="K45" s="11"/>
-      <c r="L45" s="11"/>
-      <c r="M45" s="11"/>
+      <c r="A45" s="9"/>
+      <c r="B45" s="10"/>
+      <c r="C45" s="10"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="10"/>
+      <c r="F45" s="10"/>
+      <c r="G45" s="10"/>
+      <c r="H45" s="10"/>
+      <c r="I45" s="10"/>
+      <c r="J45" s="10"/>
+      <c r="K45" s="10"/>
+      <c r="L45" s="10"/>
+      <c r="M45" s="10"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="10"/>
-      <c r="B46" s="11"/>
-      <c r="C46" s="11"/>
-      <c r="D46" s="12"/>
-      <c r="E46" s="11"/>
-      <c r="F46" s="11"/>
-      <c r="G46" s="11"/>
-      <c r="H46" s="11"/>
-      <c r="I46" s="11"/>
-      <c r="J46" s="11"/>
-      <c r="K46" s="11"/>
-      <c r="L46" s="11"/>
-      <c r="M46" s="11"/>
+      <c r="A46" s="9"/>
+      <c r="B46" s="10"/>
+      <c r="C46" s="10"/>
+      <c r="D46" s="11"/>
+      <c r="E46" s="10"/>
+      <c r="F46" s="10"/>
+      <c r="G46" s="10"/>
+      <c r="H46" s="10"/>
+      <c r="I46" s="10"/>
+      <c r="J46" s="10"/>
+      <c r="K46" s="10"/>
+      <c r="L46" s="10"/>
+      <c r="M46" s="10"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="10"/>
-      <c r="B47" s="11"/>
-      <c r="C47" s="11"/>
-      <c r="D47" s="12"/>
-      <c r="E47" s="11"/>
-      <c r="F47" s="11"/>
-      <c r="G47" s="11"/>
-      <c r="H47" s="11"/>
-      <c r="I47" s="11"/>
-      <c r="J47" s="11"/>
-      <c r="K47" s="11"/>
-      <c r="L47" s="11"/>
-      <c r="M47" s="11"/>
+      <c r="A47" s="9"/>
+      <c r="B47" s="10"/>
+      <c r="C47" s="10"/>
+      <c r="D47" s="11"/>
+      <c r="E47" s="10"/>
+      <c r="F47" s="10"/>
+      <c r="G47" s="10"/>
+      <c r="H47" s="10"/>
+      <c r="I47" s="10"/>
+      <c r="J47" s="10"/>
+      <c r="K47" s="10"/>
+      <c r="L47" s="10"/>
+      <c r="M47" s="10"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="10"/>
-      <c r="B48" s="11"/>
-      <c r="C48" s="11"/>
-      <c r="D48" s="12"/>
-      <c r="E48" s="11"/>
-      <c r="F48" s="11"/>
-      <c r="G48" s="11"/>
-      <c r="H48" s="11"/>
-      <c r="I48" s="11"/>
-      <c r="J48" s="11"/>
-      <c r="K48" s="11"/>
-      <c r="L48" s="11"/>
-      <c r="M48" s="11"/>
+      <c r="A48" s="9"/>
+      <c r="B48" s="10"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="10"/>
+      <c r="F48" s="10"/>
+      <c r="G48" s="10"/>
+      <c r="H48" s="10"/>
+      <c r="I48" s="10"/>
+      <c r="J48" s="10"/>
+      <c r="K48" s="10"/>
+      <c r="L48" s="10"/>
+      <c r="M48" s="10"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="10"/>
-      <c r="B49" s="11"/>
-      <c r="C49" s="11"/>
-      <c r="D49" s="12"/>
-      <c r="E49" s="11"/>
-      <c r="F49" s="11"/>
-      <c r="G49" s="11"/>
-      <c r="H49" s="11"/>
-      <c r="I49" s="11"/>
-      <c r="J49" s="11"/>
-      <c r="K49" s="11"/>
-      <c r="L49" s="11"/>
-      <c r="M49" s="11"/>
+      <c r="A49" s="9"/>
+      <c r="B49" s="10"/>
+      <c r="C49" s="10"/>
+      <c r="D49" s="11"/>
+      <c r="E49" s="10"/>
+      <c r="F49" s="10"/>
+      <c r="G49" s="10"/>
+      <c r="H49" s="10"/>
+      <c r="I49" s="10"/>
+      <c r="J49" s="10"/>
+      <c r="K49" s="10"/>
+      <c r="L49" s="10"/>
+      <c r="M49" s="10"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="10"/>
-      <c r="B50" s="11"/>
-      <c r="C50" s="11"/>
-      <c r="D50" s="12"/>
-      <c r="E50" s="11"/>
-      <c r="F50" s="11"/>
-      <c r="G50" s="11"/>
-      <c r="H50" s="11"/>
-      <c r="I50" s="11"/>
-      <c r="J50" s="11"/>
-      <c r="K50" s="11"/>
-      <c r="L50" s="11"/>
-      <c r="M50" s="11"/>
+      <c r="A50" s="9"/>
+      <c r="B50" s="10"/>
+      <c r="C50" s="10"/>
+      <c r="D50" s="11"/>
+      <c r="E50" s="10"/>
+      <c r="F50" s="10"/>
+      <c r="G50" s="10"/>
+      <c r="H50" s="10"/>
+      <c r="I50" s="10"/>
+      <c r="J50" s="10"/>
+      <c r="K50" s="10"/>
+      <c r="L50" s="10"/>
+      <c r="M50" s="10"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="10"/>
-      <c r="B51" s="11"/>
-      <c r="C51" s="11"/>
-      <c r="D51" s="12"/>
-      <c r="E51" s="11"/>
-      <c r="F51" s="11"/>
-      <c r="G51" s="11"/>
-      <c r="H51" s="11"/>
-      <c r="I51" s="11"/>
-      <c r="J51" s="11"/>
-      <c r="K51" s="11"/>
-      <c r="L51" s="11"/>
-      <c r="M51" s="11"/>
+      <c r="A51" s="9"/>
+      <c r="B51" s="10"/>
+      <c r="C51" s="10"/>
+      <c r="D51" s="11"/>
+      <c r="E51" s="10"/>
+      <c r="F51" s="10"/>
+      <c r="G51" s="10"/>
+      <c r="H51" s="10"/>
+      <c r="I51" s="10"/>
+      <c r="J51" s="10"/>
+      <c r="K51" s="10"/>
+      <c r="L51" s="10"/>
+      <c r="M51" s="10"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="10"/>
-      <c r="B52" s="11"/>
-      <c r="C52" s="11"/>
-      <c r="D52" s="12"/>
-      <c r="E52" s="11"/>
-      <c r="F52" s="11"/>
-      <c r="G52" s="11"/>
-      <c r="H52" s="11"/>
-      <c r="I52" s="11"/>
-      <c r="J52" s="11"/>
-      <c r="K52" s="11"/>
-      <c r="L52" s="11"/>
-      <c r="M52" s="11"/>
+      <c r="A52" s="9"/>
+      <c r="B52" s="10"/>
+      <c r="C52" s="10"/>
+      <c r="D52" s="11"/>
+      <c r="E52" s="10"/>
+      <c r="F52" s="10"/>
+      <c r="G52" s="10"/>
+      <c r="H52" s="10"/>
+      <c r="I52" s="10"/>
+      <c r="J52" s="10"/>
+      <c r="K52" s="10"/>
+      <c r="L52" s="10"/>
+      <c r="M52" s="10"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="10"/>
-      <c r="B53" s="11"/>
-      <c r="C53" s="11"/>
-      <c r="D53" s="12"/>
-      <c r="E53" s="11"/>
-      <c r="F53" s="11"/>
-      <c r="G53" s="11"/>
-      <c r="H53" s="11"/>
-      <c r="I53" s="11"/>
-      <c r="J53" s="11"/>
-      <c r="K53" s="11"/>
-      <c r="L53" s="11"/>
-      <c r="M53" s="11"/>
+      <c r="A53" s="9"/>
+      <c r="B53" s="10"/>
+      <c r="C53" s="10"/>
+      <c r="D53" s="11"/>
+      <c r="E53" s="10"/>
+      <c r="F53" s="10"/>
+      <c r="G53" s="10"/>
+      <c r="H53" s="10"/>
+      <c r="I53" s="10"/>
+      <c r="J53" s="10"/>
+      <c r="K53" s="10"/>
+      <c r="L53" s="10"/>
+      <c r="M53" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2506,1401 +2517,1401 @@
   <dimension ref="A1:S53"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="18" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="18" style="0" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
-      <c r="O2" s="8"/>
-      <c r="P2" s="8"/>
-      <c r="Q2" s="8"/>
-      <c r="R2" s="8"/>
-      <c r="S2" s="8"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="7"/>
+      <c r="Q2" s="7"/>
+      <c r="R2" s="7"/>
+      <c r="S2" s="7"/>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="K3" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="L3" s="9" t="s">
+      <c r="L3" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="M3" s="9" t="s">
+      <c r="M3" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="N3" s="9" t="s">
+      <c r="N3" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="O3" s="9" t="s">
+      <c r="O3" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="P3" s="9" t="s">
+      <c r="P3" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="Q3" s="9" t="s">
+      <c r="Q3" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="R3" s="9" t="s">
+      <c r="R3" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="S3" s="9" t="s">
+      <c r="S3" s="8" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="J4" s="11" t="str">
+      <c r="J4" s="10" t="str">
         <f aca="false">IF(COUNTIF(D4:I4,"Sim")&gt;0,"Sim",IF(COUNTIF(D4:I4,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Em apuração</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="L4" s="11" t="s">
+      <c r="L4" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="M4" s="11" t="s">
+      <c r="M4" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="N4" s="11" t="s">
+      <c r="N4" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="O4" s="11" t="s">
+      <c r="O4" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="P4" s="11" t="s">
+      <c r="P4" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="Q4" s="11" t="s">
+      <c r="Q4" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="R4" s="11" t="s">
+      <c r="R4" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="S4" s="11" t="s">
+      <c r="S4" s="10" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="H5" s="11" t="s">
+      <c r="H5" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="I5" s="11" t="s">
+      <c r="I5" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="J5" s="11" t="str">
+      <c r="J5" s="10" t="str">
         <f aca="false">IF(COUNTIF(D5:I5,"Sim")&gt;0,"Sim",IF(COUNTIF(D5:I5,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Sim</v>
       </c>
-      <c r="K5" s="11" t="s">
+      <c r="K5" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="L5" s="11" t="s">
+      <c r="L5" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="M5" s="11" t="s">
+      <c r="M5" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="N5" s="11" t="s">
+      <c r="N5" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="O5" s="11" t="s">
+      <c r="O5" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="P5" s="11" t="s">
+      <c r="P5" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="Q5" s="11" t="s">
+      <c r="Q5" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="R5" s="11" t="s">
+      <c r="R5" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="S5" s="11" t="s">
+      <c r="S5" s="10" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11" t="str">
+      <c r="A6" s="9"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10" t="str">
         <f aca="false">IF(COUNTIF(D6:I6,"Sim")&gt;0,"Sim",IF(COUNTIF(D6:I6,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
-      <c r="N6" s="11"/>
-      <c r="O6" s="11"/>
-      <c r="P6" s="11"/>
-      <c r="Q6" s="11"/>
-      <c r="R6" s="11"/>
-      <c r="S6" s="11"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="10"/>
+      <c r="P6" s="10"/>
+      <c r="Q6" s="10"/>
+      <c r="R6" s="10"/>
+      <c r="S6" s="10"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11" t="str">
+      <c r="A7" s="9"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10" t="str">
         <f aca="false">IF(COUNTIF(D7:I7,"Sim")&gt;0,"Sim",IF(COUNTIF(D7:I7,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="11"/>
-      <c r="N7" s="11"/>
-      <c r="O7" s="11"/>
-      <c r="P7" s="11"/>
-      <c r="Q7" s="11"/>
-      <c r="R7" s="11"/>
-      <c r="S7" s="11"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="10"/>
+      <c r="P7" s="10"/>
+      <c r="Q7" s="10"/>
+      <c r="R7" s="10"/>
+      <c r="S7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11" t="str">
+      <c r="A8" s="9"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10" t="str">
         <f aca="false">IF(COUNTIF(D8:I8,"Sim")&gt;0,"Sim",IF(COUNTIF(D8:I8,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="11"/>
-      <c r="N8" s="11"/>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="10"/>
+      <c r="P8" s="10"/>
+      <c r="Q8" s="10"/>
+      <c r="R8" s="10"/>
+      <c r="S8" s="10"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11" t="str">
+      <c r="A9" s="9"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10" t="str">
         <f aca="false">IF(COUNTIF(D9:I9,"Sim")&gt;0,"Sim",IF(COUNTIF(D9:I9,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K9" s="11"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="11"/>
-      <c r="N9" s="11"/>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="10"/>
+      <c r="P9" s="10"/>
+      <c r="Q9" s="10"/>
+      <c r="R9" s="10"/>
+      <c r="S9" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="11" t="str">
+      <c r="A10" s="9"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10" t="str">
         <f aca="false">IF(COUNTIF(D10:I10,"Sim")&gt;0,"Sim",IF(COUNTIF(D10:I10,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="11"/>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="10"/>
+      <c r="Q10" s="10"/>
+      <c r="R10" s="10"/>
+      <c r="S10" s="10"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11" t="str">
+      <c r="A11" s="9"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10" t="str">
         <f aca="false">IF(COUNTIF(D11:I11,"Sim")&gt;0,"Sim",IF(COUNTIF(D11:I11,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="11"/>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="10"/>
+      <c r="P11" s="10"/>
+      <c r="Q11" s="10"/>
+      <c r="R11" s="10"/>
+      <c r="S11" s="10"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11" t="str">
+      <c r="A12" s="9"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10" t="str">
         <f aca="false">IF(COUNTIF(D12:I12,"Sim")&gt;0,"Sim",IF(COUNTIF(D12:I12,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="11"/>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="10"/>
+      <c r="O12" s="10"/>
+      <c r="P12" s="10"/>
+      <c r="Q12" s="10"/>
+      <c r="R12" s="10"/>
+      <c r="S12" s="10"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="11" t="str">
+      <c r="A13" s="9"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10" t="str">
         <f aca="false">IF(COUNTIF(D13:I13,"Sim")&gt;0,"Sim",IF(COUNTIF(D13:I13,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
-      <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="10"/>
+      <c r="P13" s="10"/>
+      <c r="Q13" s="10"/>
+      <c r="R13" s="10"/>
+      <c r="S13" s="10"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11" t="str">
+      <c r="A14" s="9"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10" t="str">
         <f aca="false">IF(COUNTIF(D14:I14,"Sim")&gt;0,"Sim",IF(COUNTIF(D14:I14,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="11"/>
-      <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
-      <c r="R14" s="11"/>
-      <c r="S14" s="11"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="10"/>
+      <c r="P14" s="10"/>
+      <c r="Q14" s="10"/>
+      <c r="R14" s="10"/>
+      <c r="S14" s="10"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11" t="str">
+      <c r="A15" s="9"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10" t="str">
         <f aca="false">IF(COUNTIF(D15:I15,"Sim")&gt;0,"Sim",IF(COUNTIF(D15:I15,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="11"/>
-      <c r="O15" s="11"/>
-      <c r="P15" s="11"/>
-      <c r="Q15" s="11"/>
-      <c r="R15" s="11"/>
-      <c r="S15" s="11"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="10"/>
+      <c r="O15" s="10"/>
+      <c r="P15" s="10"/>
+      <c r="Q15" s="10"/>
+      <c r="R15" s="10"/>
+      <c r="S15" s="10"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11" t="str">
+      <c r="A16" s="9"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="10" t="str">
         <f aca="false">IF(COUNTIF(D16:I16,"Sim")&gt;0,"Sim",IF(COUNTIF(D16:I16,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="11"/>
-      <c r="O16" s="11"/>
-      <c r="P16" s="11"/>
-      <c r="Q16" s="11"/>
-      <c r="R16" s="11"/>
-      <c r="S16" s="11"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="10"/>
+      <c r="O16" s="10"/>
+      <c r="P16" s="10"/>
+      <c r="Q16" s="10"/>
+      <c r="R16" s="10"/>
+      <c r="S16" s="10"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="11" t="str">
+      <c r="A17" s="9"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="10" t="str">
         <f aca="false">IF(COUNTIF(D17:I17,"Sim")&gt;0,"Sim",IF(COUNTIF(D17:I17,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="11"/>
-      <c r="N17" s="11"/>
-      <c r="O17" s="11"/>
-      <c r="P17" s="11"/>
-      <c r="Q17" s="11"/>
-      <c r="R17" s="11"/>
-      <c r="S17" s="11"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="10"/>
+      <c r="M17" s="10"/>
+      <c r="N17" s="10"/>
+      <c r="O17" s="10"/>
+      <c r="P17" s="10"/>
+      <c r="Q17" s="10"/>
+      <c r="R17" s="10"/>
+      <c r="S17" s="10"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11"/>
-      <c r="J18" s="11" t="str">
+      <c r="A18" s="9"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10"/>
+      <c r="J18" s="10" t="str">
         <f aca="false">IF(COUNTIF(D18:I18,"Sim")&gt;0,"Sim",IF(COUNTIF(D18:I18,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="11"/>
-      <c r="O18" s="11"/>
-      <c r="P18" s="11"/>
-      <c r="Q18" s="11"/>
-      <c r="R18" s="11"/>
-      <c r="S18" s="11"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="10"/>
+      <c r="M18" s="10"/>
+      <c r="N18" s="10"/>
+      <c r="O18" s="10"/>
+      <c r="P18" s="10"/>
+      <c r="Q18" s="10"/>
+      <c r="R18" s="10"/>
+      <c r="S18" s="10"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
-      <c r="J19" s="11" t="str">
+      <c r="A19" s="9"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="10"/>
+      <c r="J19" s="10" t="str">
         <f aca="false">IF(COUNTIF(D19:I19,"Sim")&gt;0,"Sim",IF(COUNTIF(D19:I19,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="11"/>
-      <c r="N19" s="11"/>
-      <c r="O19" s="11"/>
-      <c r="P19" s="11"/>
-      <c r="Q19" s="11"/>
-      <c r="R19" s="11"/>
-      <c r="S19" s="11"/>
+      <c r="K19" s="10"/>
+      <c r="L19" s="10"/>
+      <c r="M19" s="10"/>
+      <c r="N19" s="10"/>
+      <c r="O19" s="10"/>
+      <c r="P19" s="10"/>
+      <c r="Q19" s="10"/>
+      <c r="R19" s="10"/>
+      <c r="S19" s="10"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="10"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11"/>
-      <c r="J20" s="11" t="str">
+      <c r="A20" s="9"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10" t="str">
         <f aca="false">IF(COUNTIF(D20:I20,"Sim")&gt;0,"Sim",IF(COUNTIF(D20:I20,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K20" s="11"/>
-      <c r="L20" s="11"/>
-      <c r="M20" s="11"/>
-      <c r="N20" s="11"/>
-      <c r="O20" s="11"/>
-      <c r="P20" s="11"/>
-      <c r="Q20" s="11"/>
-      <c r="R20" s="11"/>
-      <c r="S20" s="11"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="10"/>
+      <c r="O20" s="10"/>
+      <c r="P20" s="10"/>
+      <c r="Q20" s="10"/>
+      <c r="R20" s="10"/>
+      <c r="S20" s="10"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="10"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="11"/>
-      <c r="J21" s="11" t="str">
+      <c r="A21" s="9"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="10" t="str">
         <f aca="false">IF(COUNTIF(D21:I21,"Sim")&gt;0,"Sim",IF(COUNTIF(D21:I21,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K21" s="11"/>
-      <c r="L21" s="11"/>
-      <c r="M21" s="11"/>
-      <c r="N21" s="11"/>
-      <c r="O21" s="11"/>
-      <c r="P21" s="11"/>
-      <c r="Q21" s="11"/>
-      <c r="R21" s="11"/>
-      <c r="S21" s="11"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="10"/>
+      <c r="O21" s="10"/>
+      <c r="P21" s="10"/>
+      <c r="Q21" s="10"/>
+      <c r="R21" s="10"/>
+      <c r="S21" s="10"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="10"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="11"/>
-      <c r="J22" s="11" t="str">
+      <c r="A22" s="9"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="10"/>
+      <c r="J22" s="10" t="str">
         <f aca="false">IF(COUNTIF(D22:I22,"Sim")&gt;0,"Sim",IF(COUNTIF(D22:I22,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="11"/>
-      <c r="N22" s="11"/>
-      <c r="O22" s="11"/>
-      <c r="P22" s="11"/>
-      <c r="Q22" s="11"/>
-      <c r="R22" s="11"/>
-      <c r="S22" s="11"/>
+      <c r="K22" s="10"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="10"/>
+      <c r="O22" s="10"/>
+      <c r="P22" s="10"/>
+      <c r="Q22" s="10"/>
+      <c r="R22" s="10"/>
+      <c r="S22" s="10"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="10"/>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="11"/>
-      <c r="J23" s="11" t="str">
+      <c r="A23" s="9"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="10"/>
+      <c r="J23" s="10" t="str">
         <f aca="false">IF(COUNTIF(D23:I23,"Sim")&gt;0,"Sim",IF(COUNTIF(D23:I23,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K23" s="11"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="11"/>
-      <c r="N23" s="11"/>
-      <c r="O23" s="11"/>
-      <c r="P23" s="11"/>
-      <c r="Q23" s="11"/>
-      <c r="R23" s="11"/>
-      <c r="S23" s="11"/>
+      <c r="K23" s="10"/>
+      <c r="L23" s="10"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="10"/>
+      <c r="O23" s="10"/>
+      <c r="P23" s="10"/>
+      <c r="Q23" s="10"/>
+      <c r="R23" s="10"/>
+      <c r="S23" s="10"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="10"/>
-      <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="11"/>
-      <c r="J24" s="11" t="str">
+      <c r="A24" s="9"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="10" t="str">
         <f aca="false">IF(COUNTIF(D24:I24,"Sim")&gt;0,"Sim",IF(COUNTIF(D24:I24,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K24" s="11"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="11"/>
-      <c r="N24" s="11"/>
-      <c r="O24" s="11"/>
-      <c r="P24" s="11"/>
-      <c r="Q24" s="11"/>
-      <c r="R24" s="11"/>
-      <c r="S24" s="11"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="10"/>
+      <c r="N24" s="10"/>
+      <c r="O24" s="10"/>
+      <c r="P24" s="10"/>
+      <c r="Q24" s="10"/>
+      <c r="R24" s="10"/>
+      <c r="S24" s="10"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="10"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="11"/>
-      <c r="J25" s="11" t="str">
+      <c r="A25" s="9"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="10"/>
+      <c r="J25" s="10" t="str">
         <f aca="false">IF(COUNTIF(D25:I25,"Sim")&gt;0,"Sim",IF(COUNTIF(D25:I25,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K25" s="11"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="11"/>
-      <c r="N25" s="11"/>
-      <c r="O25" s="11"/>
-      <c r="P25" s="11"/>
-      <c r="Q25" s="11"/>
-      <c r="R25" s="11"/>
-      <c r="S25" s="11"/>
+      <c r="K25" s="10"/>
+      <c r="L25" s="10"/>
+      <c r="M25" s="10"/>
+      <c r="N25" s="10"/>
+      <c r="O25" s="10"/>
+      <c r="P25" s="10"/>
+      <c r="Q25" s="10"/>
+      <c r="R25" s="10"/>
+      <c r="S25" s="10"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="10"/>
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11"/>
-      <c r="I26" s="11"/>
-      <c r="J26" s="11" t="str">
+      <c r="A26" s="9"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="10"/>
+      <c r="I26" s="10"/>
+      <c r="J26" s="10" t="str">
         <f aca="false">IF(COUNTIF(D26:I26,"Sim")&gt;0,"Sim",IF(COUNTIF(D26:I26,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K26" s="11"/>
-      <c r="L26" s="11"/>
-      <c r="M26" s="11"/>
-      <c r="N26" s="11"/>
-      <c r="O26" s="11"/>
-      <c r="P26" s="11"/>
-      <c r="Q26" s="11"/>
-      <c r="R26" s="11"/>
-      <c r="S26" s="11"/>
+      <c r="K26" s="10"/>
+      <c r="L26" s="10"/>
+      <c r="M26" s="10"/>
+      <c r="N26" s="10"/>
+      <c r="O26" s="10"/>
+      <c r="P26" s="10"/>
+      <c r="Q26" s="10"/>
+      <c r="R26" s="10"/>
+      <c r="S26" s="10"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="10"/>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11"/>
-      <c r="I27" s="11"/>
-      <c r="J27" s="11" t="str">
+      <c r="A27" s="9"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="10"/>
+      <c r="I27" s="10"/>
+      <c r="J27" s="10" t="str">
         <f aca="false">IF(COUNTIF(D27:I27,"Sim")&gt;0,"Sim",IF(COUNTIF(D27:I27,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K27" s="11"/>
-      <c r="L27" s="11"/>
-      <c r="M27" s="11"/>
-      <c r="N27" s="11"/>
-      <c r="O27" s="11"/>
-      <c r="P27" s="11"/>
-      <c r="Q27" s="11"/>
-      <c r="R27" s="11"/>
-      <c r="S27" s="11"/>
+      <c r="K27" s="10"/>
+      <c r="L27" s="10"/>
+      <c r="M27" s="10"/>
+      <c r="N27" s="10"/>
+      <c r="O27" s="10"/>
+      <c r="P27" s="10"/>
+      <c r="Q27" s="10"/>
+      <c r="R27" s="10"/>
+      <c r="S27" s="10"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="10"/>
-      <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="11"/>
-      <c r="H28" s="11"/>
-      <c r="I28" s="11"/>
-      <c r="J28" s="11" t="str">
+      <c r="A28" s="9"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="10"/>
+      <c r="I28" s="10"/>
+      <c r="J28" s="10" t="str">
         <f aca="false">IF(COUNTIF(D28:I28,"Sim")&gt;0,"Sim",IF(COUNTIF(D28:I28,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K28" s="11"/>
-      <c r="L28" s="11"/>
-      <c r="M28" s="11"/>
-      <c r="N28" s="11"/>
-      <c r="O28" s="11"/>
-      <c r="P28" s="11"/>
-      <c r="Q28" s="11"/>
-      <c r="R28" s="11"/>
-      <c r="S28" s="11"/>
+      <c r="K28" s="10"/>
+      <c r="L28" s="10"/>
+      <c r="M28" s="10"/>
+      <c r="N28" s="10"/>
+      <c r="O28" s="10"/>
+      <c r="P28" s="10"/>
+      <c r="Q28" s="10"/>
+      <c r="R28" s="10"/>
+      <c r="S28" s="10"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="10"/>
-      <c r="B29" s="11"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="11"/>
-      <c r="H29" s="11"/>
-      <c r="I29" s="11"/>
-      <c r="J29" s="11" t="str">
+      <c r="A29" s="9"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="10"/>
+      <c r="H29" s="10"/>
+      <c r="I29" s="10"/>
+      <c r="J29" s="10" t="str">
         <f aca="false">IF(COUNTIF(D29:I29,"Sim")&gt;0,"Sim",IF(COUNTIF(D29:I29,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K29" s="11"/>
-      <c r="L29" s="11"/>
-      <c r="M29" s="11"/>
-      <c r="N29" s="11"/>
-      <c r="O29" s="11"/>
-      <c r="P29" s="11"/>
-      <c r="Q29" s="11"/>
-      <c r="R29" s="11"/>
-      <c r="S29" s="11"/>
+      <c r="K29" s="10"/>
+      <c r="L29" s="10"/>
+      <c r="M29" s="10"/>
+      <c r="N29" s="10"/>
+      <c r="O29" s="10"/>
+      <c r="P29" s="10"/>
+      <c r="Q29" s="10"/>
+      <c r="R29" s="10"/>
+      <c r="S29" s="10"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="10"/>
-      <c r="B30" s="11"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="11"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="11"/>
-      <c r="H30" s="11"/>
-      <c r="I30" s="11"/>
-      <c r="J30" s="11" t="str">
+      <c r="A30" s="9"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="10"/>
+      <c r="H30" s="10"/>
+      <c r="I30" s="10"/>
+      <c r="J30" s="10" t="str">
         <f aca="false">IF(COUNTIF(D30:I30,"Sim")&gt;0,"Sim",IF(COUNTIF(D30:I30,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K30" s="11"/>
-      <c r="L30" s="11"/>
-      <c r="M30" s="11"/>
-      <c r="N30" s="11"/>
-      <c r="O30" s="11"/>
-      <c r="P30" s="11"/>
-      <c r="Q30" s="11"/>
-      <c r="R30" s="11"/>
-      <c r="S30" s="11"/>
+      <c r="K30" s="10"/>
+      <c r="L30" s="10"/>
+      <c r="M30" s="10"/>
+      <c r="N30" s="10"/>
+      <c r="O30" s="10"/>
+      <c r="P30" s="10"/>
+      <c r="Q30" s="10"/>
+      <c r="R30" s="10"/>
+      <c r="S30" s="10"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="10"/>
-      <c r="B31" s="11"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="11"/>
-      <c r="H31" s="11"/>
-      <c r="I31" s="11"/>
-      <c r="J31" s="11" t="str">
+      <c r="A31" s="9"/>
+      <c r="B31" s="10"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="10"/>
+      <c r="I31" s="10"/>
+      <c r="J31" s="10" t="str">
         <f aca="false">IF(COUNTIF(D31:I31,"Sim")&gt;0,"Sim",IF(COUNTIF(D31:I31,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K31" s="11"/>
-      <c r="L31" s="11"/>
-      <c r="M31" s="11"/>
-      <c r="N31" s="11"/>
-      <c r="O31" s="11"/>
-      <c r="P31" s="11"/>
-      <c r="Q31" s="11"/>
-      <c r="R31" s="11"/>
-      <c r="S31" s="11"/>
+      <c r="K31" s="10"/>
+      <c r="L31" s="10"/>
+      <c r="M31" s="10"/>
+      <c r="N31" s="10"/>
+      <c r="O31" s="10"/>
+      <c r="P31" s="10"/>
+      <c r="Q31" s="10"/>
+      <c r="R31" s="10"/>
+      <c r="S31" s="10"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="10"/>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="11"/>
-      <c r="J32" s="11" t="str">
+      <c r="A32" s="9"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="10"/>
+      <c r="G32" s="10"/>
+      <c r="H32" s="10"/>
+      <c r="I32" s="10"/>
+      <c r="J32" s="10" t="str">
         <f aca="false">IF(COUNTIF(D32:I32,"Sim")&gt;0,"Sim",IF(COUNTIF(D32:I32,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K32" s="11"/>
-      <c r="L32" s="11"/>
-      <c r="M32" s="11"/>
-      <c r="N32" s="11"/>
-      <c r="O32" s="11"/>
-      <c r="P32" s="11"/>
-      <c r="Q32" s="11"/>
-      <c r="R32" s="11"/>
-      <c r="S32" s="11"/>
+      <c r="K32" s="10"/>
+      <c r="L32" s="10"/>
+      <c r="M32" s="10"/>
+      <c r="N32" s="10"/>
+      <c r="O32" s="10"/>
+      <c r="P32" s="10"/>
+      <c r="Q32" s="10"/>
+      <c r="R32" s="10"/>
+      <c r="S32" s="10"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="10"/>
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="11"/>
-      <c r="I33" s="11"/>
-      <c r="J33" s="11" t="str">
+      <c r="A33" s="9"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="10"/>
+      <c r="I33" s="10"/>
+      <c r="J33" s="10" t="str">
         <f aca="false">IF(COUNTIF(D33:I33,"Sim")&gt;0,"Sim",IF(COUNTIF(D33:I33,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K33" s="11"/>
-      <c r="L33" s="11"/>
-      <c r="M33" s="11"/>
-      <c r="N33" s="11"/>
-      <c r="O33" s="11"/>
-      <c r="P33" s="11"/>
-      <c r="Q33" s="11"/>
-      <c r="R33" s="11"/>
-      <c r="S33" s="11"/>
+      <c r="K33" s="10"/>
+      <c r="L33" s="10"/>
+      <c r="M33" s="10"/>
+      <c r="N33" s="10"/>
+      <c r="O33" s="10"/>
+      <c r="P33" s="10"/>
+      <c r="Q33" s="10"/>
+      <c r="R33" s="10"/>
+      <c r="S33" s="10"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="10"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="11"/>
-      <c r="I34" s="11"/>
-      <c r="J34" s="11" t="str">
+      <c r="A34" s="9"/>
+      <c r="B34" s="10"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="10"/>
+      <c r="G34" s="10"/>
+      <c r="H34" s="10"/>
+      <c r="I34" s="10"/>
+      <c r="J34" s="10" t="str">
         <f aca="false">IF(COUNTIF(D34:I34,"Sim")&gt;0,"Sim",IF(COUNTIF(D34:I34,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K34" s="11"/>
-      <c r="L34" s="11"/>
-      <c r="M34" s="11"/>
-      <c r="N34" s="11"/>
-      <c r="O34" s="11"/>
-      <c r="P34" s="11"/>
-      <c r="Q34" s="11"/>
-      <c r="R34" s="11"/>
-      <c r="S34" s="11"/>
+      <c r="K34" s="10"/>
+      <c r="L34" s="10"/>
+      <c r="M34" s="10"/>
+      <c r="N34" s="10"/>
+      <c r="O34" s="10"/>
+      <c r="P34" s="10"/>
+      <c r="Q34" s="10"/>
+      <c r="R34" s="10"/>
+      <c r="S34" s="10"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="10"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="11"/>
-      <c r="I35" s="11"/>
-      <c r="J35" s="11" t="str">
+      <c r="A35" s="9"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="10"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="10"/>
+      <c r="I35" s="10"/>
+      <c r="J35" s="10" t="str">
         <f aca="false">IF(COUNTIF(D35:I35,"Sim")&gt;0,"Sim",IF(COUNTIF(D35:I35,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K35" s="11"/>
-      <c r="L35" s="11"/>
-      <c r="M35" s="11"/>
-      <c r="N35" s="11"/>
-      <c r="O35" s="11"/>
-      <c r="P35" s="11"/>
-      <c r="Q35" s="11"/>
-      <c r="R35" s="11"/>
-      <c r="S35" s="11"/>
+      <c r="K35" s="10"/>
+      <c r="L35" s="10"/>
+      <c r="M35" s="10"/>
+      <c r="N35" s="10"/>
+      <c r="O35" s="10"/>
+      <c r="P35" s="10"/>
+      <c r="Q35" s="10"/>
+      <c r="R35" s="10"/>
+      <c r="S35" s="10"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="10"/>
-      <c r="B36" s="11"/>
-      <c r="C36" s="11"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="11"/>
-      <c r="H36" s="11"/>
-      <c r="I36" s="11"/>
-      <c r="J36" s="11" t="str">
+      <c r="A36" s="9"/>
+      <c r="B36" s="10"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="10"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="10"/>
+      <c r="H36" s="10"/>
+      <c r="I36" s="10"/>
+      <c r="J36" s="10" t="str">
         <f aca="false">IF(COUNTIF(D36:I36,"Sim")&gt;0,"Sim",IF(COUNTIF(D36:I36,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K36" s="11"/>
-      <c r="L36" s="11"/>
-      <c r="M36" s="11"/>
-      <c r="N36" s="11"/>
-      <c r="O36" s="11"/>
-      <c r="P36" s="11"/>
-      <c r="Q36" s="11"/>
-      <c r="R36" s="11"/>
-      <c r="S36" s="11"/>
+      <c r="K36" s="10"/>
+      <c r="L36" s="10"/>
+      <c r="M36" s="10"/>
+      <c r="N36" s="10"/>
+      <c r="O36" s="10"/>
+      <c r="P36" s="10"/>
+      <c r="Q36" s="10"/>
+      <c r="R36" s="10"/>
+      <c r="S36" s="10"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="10"/>
-      <c r="B37" s="11"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="11"/>
-      <c r="I37" s="11"/>
-      <c r="J37" s="11" t="str">
+      <c r="A37" s="9"/>
+      <c r="B37" s="10"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="10"/>
+      <c r="I37" s="10"/>
+      <c r="J37" s="10" t="str">
         <f aca="false">IF(COUNTIF(D37:I37,"Sim")&gt;0,"Sim",IF(COUNTIF(D37:I37,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K37" s="11"/>
-      <c r="L37" s="11"/>
-      <c r="M37" s="11"/>
-      <c r="N37" s="11"/>
-      <c r="O37" s="11"/>
-      <c r="P37" s="11"/>
-      <c r="Q37" s="11"/>
-      <c r="R37" s="11"/>
-      <c r="S37" s="11"/>
+      <c r="K37" s="10"/>
+      <c r="L37" s="10"/>
+      <c r="M37" s="10"/>
+      <c r="N37" s="10"/>
+      <c r="O37" s="10"/>
+      <c r="P37" s="10"/>
+      <c r="Q37" s="10"/>
+      <c r="R37" s="10"/>
+      <c r="S37" s="10"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="10"/>
-      <c r="B38" s="11"/>
-      <c r="C38" s="11"/>
-      <c r="D38" s="11"/>
-      <c r="E38" s="11"/>
-      <c r="F38" s="11"/>
-      <c r="G38" s="11"/>
-      <c r="H38" s="11"/>
-      <c r="I38" s="11"/>
-      <c r="J38" s="11" t="str">
+      <c r="A38" s="9"/>
+      <c r="B38" s="10"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="10"/>
+      <c r="F38" s="10"/>
+      <c r="G38" s="10"/>
+      <c r="H38" s="10"/>
+      <c r="I38" s="10"/>
+      <c r="J38" s="10" t="str">
         <f aca="false">IF(COUNTIF(D38:I38,"Sim")&gt;0,"Sim",IF(COUNTIF(D38:I38,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K38" s="11"/>
-      <c r="L38" s="11"/>
-      <c r="M38" s="11"/>
-      <c r="N38" s="11"/>
-      <c r="O38" s="11"/>
-      <c r="P38" s="11"/>
-      <c r="Q38" s="11"/>
-      <c r="R38" s="11"/>
-      <c r="S38" s="11"/>
+      <c r="K38" s="10"/>
+      <c r="L38" s="10"/>
+      <c r="M38" s="10"/>
+      <c r="N38" s="10"/>
+      <c r="O38" s="10"/>
+      <c r="P38" s="10"/>
+      <c r="Q38" s="10"/>
+      <c r="R38" s="10"/>
+      <c r="S38" s="10"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="10"/>
-      <c r="B39" s="11"/>
-      <c r="C39" s="11"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="11"/>
-      <c r="F39" s="11"/>
-      <c r="G39" s="11"/>
-      <c r="H39" s="11"/>
-      <c r="I39" s="11"/>
-      <c r="J39" s="11" t="str">
+      <c r="A39" s="9"/>
+      <c r="B39" s="10"/>
+      <c r="C39" s="10"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="10"/>
+      <c r="F39" s="10"/>
+      <c r="G39" s="10"/>
+      <c r="H39" s="10"/>
+      <c r="I39" s="10"/>
+      <c r="J39" s="10" t="str">
         <f aca="false">IF(COUNTIF(D39:I39,"Sim")&gt;0,"Sim",IF(COUNTIF(D39:I39,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K39" s="11"/>
-      <c r="L39" s="11"/>
-      <c r="M39" s="11"/>
-      <c r="N39" s="11"/>
-      <c r="O39" s="11"/>
-      <c r="P39" s="11"/>
-      <c r="Q39" s="11"/>
-      <c r="R39" s="11"/>
-      <c r="S39" s="11"/>
+      <c r="K39" s="10"/>
+      <c r="L39" s="10"/>
+      <c r="M39" s="10"/>
+      <c r="N39" s="10"/>
+      <c r="O39" s="10"/>
+      <c r="P39" s="10"/>
+      <c r="Q39" s="10"/>
+      <c r="R39" s="10"/>
+      <c r="S39" s="10"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="10"/>
-      <c r="B40" s="11"/>
-      <c r="C40" s="11"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="11"/>
-      <c r="G40" s="11"/>
-      <c r="H40" s="11"/>
-      <c r="I40" s="11"/>
-      <c r="J40" s="11" t="str">
+      <c r="A40" s="9"/>
+      <c r="B40" s="10"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="10"/>
+      <c r="E40" s="10"/>
+      <c r="F40" s="10"/>
+      <c r="G40" s="10"/>
+      <c r="H40" s="10"/>
+      <c r="I40" s="10"/>
+      <c r="J40" s="10" t="str">
         <f aca="false">IF(COUNTIF(D40:I40,"Sim")&gt;0,"Sim",IF(COUNTIF(D40:I40,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K40" s="11"/>
-      <c r="L40" s="11"/>
-      <c r="M40" s="11"/>
-      <c r="N40" s="11"/>
-      <c r="O40" s="11"/>
-      <c r="P40" s="11"/>
-      <c r="Q40" s="11"/>
-      <c r="R40" s="11"/>
-      <c r="S40" s="11"/>
+      <c r="K40" s="10"/>
+      <c r="L40" s="10"/>
+      <c r="M40" s="10"/>
+      <c r="N40" s="10"/>
+      <c r="O40" s="10"/>
+      <c r="P40" s="10"/>
+      <c r="Q40" s="10"/>
+      <c r="R40" s="10"/>
+      <c r="S40" s="10"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="10"/>
-      <c r="B41" s="11"/>
-      <c r="C41" s="11"/>
-      <c r="D41" s="11"/>
-      <c r="E41" s="11"/>
-      <c r="F41" s="11"/>
-      <c r="G41" s="11"/>
-      <c r="H41" s="11"/>
-      <c r="I41" s="11"/>
-      <c r="J41" s="11" t="str">
+      <c r="A41" s="9"/>
+      <c r="B41" s="10"/>
+      <c r="C41" s="10"/>
+      <c r="D41" s="10"/>
+      <c r="E41" s="10"/>
+      <c r="F41" s="10"/>
+      <c r="G41" s="10"/>
+      <c r="H41" s="10"/>
+      <c r="I41" s="10"/>
+      <c r="J41" s="10" t="str">
         <f aca="false">IF(COUNTIF(D41:I41,"Sim")&gt;0,"Sim",IF(COUNTIF(D41:I41,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K41" s="11"/>
-      <c r="L41" s="11"/>
-      <c r="M41" s="11"/>
-      <c r="N41" s="11"/>
-      <c r="O41" s="11"/>
-      <c r="P41" s="11"/>
-      <c r="Q41" s="11"/>
-      <c r="R41" s="11"/>
-      <c r="S41" s="11"/>
+      <c r="K41" s="10"/>
+      <c r="L41" s="10"/>
+      <c r="M41" s="10"/>
+      <c r="N41" s="10"/>
+      <c r="O41" s="10"/>
+      <c r="P41" s="10"/>
+      <c r="Q41" s="10"/>
+      <c r="R41" s="10"/>
+      <c r="S41" s="10"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="10"/>
-      <c r="B42" s="11"/>
-      <c r="C42" s="11"/>
-      <c r="D42" s="11"/>
-      <c r="E42" s="11"/>
-      <c r="F42" s="11"/>
-      <c r="G42" s="11"/>
-      <c r="H42" s="11"/>
-      <c r="I42" s="11"/>
-      <c r="J42" s="11" t="str">
+      <c r="A42" s="9"/>
+      <c r="B42" s="10"/>
+      <c r="C42" s="10"/>
+      <c r="D42" s="10"/>
+      <c r="E42" s="10"/>
+      <c r="F42" s="10"/>
+      <c r="G42" s="10"/>
+      <c r="H42" s="10"/>
+      <c r="I42" s="10"/>
+      <c r="J42" s="10" t="str">
         <f aca="false">IF(COUNTIF(D42:I42,"Sim")&gt;0,"Sim",IF(COUNTIF(D42:I42,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K42" s="11"/>
-      <c r="L42" s="11"/>
-      <c r="M42" s="11"/>
-      <c r="N42" s="11"/>
-      <c r="O42" s="11"/>
-      <c r="P42" s="11"/>
-      <c r="Q42" s="11"/>
-      <c r="R42" s="11"/>
-      <c r="S42" s="11"/>
+      <c r="K42" s="10"/>
+      <c r="L42" s="10"/>
+      <c r="M42" s="10"/>
+      <c r="N42" s="10"/>
+      <c r="O42" s="10"/>
+      <c r="P42" s="10"/>
+      <c r="Q42" s="10"/>
+      <c r="R42" s="10"/>
+      <c r="S42" s="10"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="10"/>
-      <c r="B43" s="11"/>
-      <c r="C43" s="11"/>
-      <c r="D43" s="11"/>
-      <c r="E43" s="11"/>
-      <c r="F43" s="11"/>
-      <c r="G43" s="11"/>
-      <c r="H43" s="11"/>
-      <c r="I43" s="11"/>
-      <c r="J43" s="11" t="str">
+      <c r="A43" s="9"/>
+      <c r="B43" s="10"/>
+      <c r="C43" s="10"/>
+      <c r="D43" s="10"/>
+      <c r="E43" s="10"/>
+      <c r="F43" s="10"/>
+      <c r="G43" s="10"/>
+      <c r="H43" s="10"/>
+      <c r="I43" s="10"/>
+      <c r="J43" s="10" t="str">
         <f aca="false">IF(COUNTIF(D43:I43,"Sim")&gt;0,"Sim",IF(COUNTIF(D43:I43,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K43" s="11"/>
-      <c r="L43" s="11"/>
-      <c r="M43" s="11"/>
-      <c r="N43" s="11"/>
-      <c r="O43" s="11"/>
-      <c r="P43" s="11"/>
-      <c r="Q43" s="11"/>
-      <c r="R43" s="11"/>
-      <c r="S43" s="11"/>
+      <c r="K43" s="10"/>
+      <c r="L43" s="10"/>
+      <c r="M43" s="10"/>
+      <c r="N43" s="10"/>
+      <c r="O43" s="10"/>
+      <c r="P43" s="10"/>
+      <c r="Q43" s="10"/>
+      <c r="R43" s="10"/>
+      <c r="S43" s="10"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="10"/>
-      <c r="B44" s="11"/>
-      <c r="C44" s="11"/>
-      <c r="D44" s="11"/>
-      <c r="E44" s="11"/>
-      <c r="F44" s="11"/>
-      <c r="G44" s="11"/>
-      <c r="H44" s="11"/>
-      <c r="I44" s="11"/>
-      <c r="J44" s="11" t="str">
+      <c r="A44" s="9"/>
+      <c r="B44" s="10"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="10"/>
+      <c r="E44" s="10"/>
+      <c r="F44" s="10"/>
+      <c r="G44" s="10"/>
+      <c r="H44" s="10"/>
+      <c r="I44" s="10"/>
+      <c r="J44" s="10" t="str">
         <f aca="false">IF(COUNTIF(D44:I44,"Sim")&gt;0,"Sim",IF(COUNTIF(D44:I44,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K44" s="11"/>
-      <c r="L44" s="11"/>
-      <c r="M44" s="11"/>
-      <c r="N44" s="11"/>
-      <c r="O44" s="11"/>
-      <c r="P44" s="11"/>
-      <c r="Q44" s="11"/>
-      <c r="R44" s="11"/>
-      <c r="S44" s="11"/>
+      <c r="K44" s="10"/>
+      <c r="L44" s="10"/>
+      <c r="M44" s="10"/>
+      <c r="N44" s="10"/>
+      <c r="O44" s="10"/>
+      <c r="P44" s="10"/>
+      <c r="Q44" s="10"/>
+      <c r="R44" s="10"/>
+      <c r="S44" s="10"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="10"/>
-      <c r="B45" s="11"/>
-      <c r="C45" s="11"/>
-      <c r="D45" s="11"/>
-      <c r="E45" s="11"/>
-      <c r="F45" s="11"/>
-      <c r="G45" s="11"/>
-      <c r="H45" s="11"/>
-      <c r="I45" s="11"/>
-      <c r="J45" s="11" t="str">
+      <c r="A45" s="9"/>
+      <c r="B45" s="10"/>
+      <c r="C45" s="10"/>
+      <c r="D45" s="10"/>
+      <c r="E45" s="10"/>
+      <c r="F45" s="10"/>
+      <c r="G45" s="10"/>
+      <c r="H45" s="10"/>
+      <c r="I45" s="10"/>
+      <c r="J45" s="10" t="str">
         <f aca="false">IF(COUNTIF(D45:I45,"Sim")&gt;0,"Sim",IF(COUNTIF(D45:I45,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K45" s="11"/>
-      <c r="L45" s="11"/>
-      <c r="M45" s="11"/>
-      <c r="N45" s="11"/>
-      <c r="O45" s="11"/>
-      <c r="P45" s="11"/>
-      <c r="Q45" s="11"/>
-      <c r="R45" s="11"/>
-      <c r="S45" s="11"/>
+      <c r="K45" s="10"/>
+      <c r="L45" s="10"/>
+      <c r="M45" s="10"/>
+      <c r="N45" s="10"/>
+      <c r="O45" s="10"/>
+      <c r="P45" s="10"/>
+      <c r="Q45" s="10"/>
+      <c r="R45" s="10"/>
+      <c r="S45" s="10"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="10"/>
-      <c r="B46" s="11"/>
-      <c r="C46" s="11"/>
-      <c r="D46" s="11"/>
-      <c r="E46" s="11"/>
-      <c r="F46" s="11"/>
-      <c r="G46" s="11"/>
-      <c r="H46" s="11"/>
-      <c r="I46" s="11"/>
-      <c r="J46" s="11" t="str">
+      <c r="A46" s="9"/>
+      <c r="B46" s="10"/>
+      <c r="C46" s="10"/>
+      <c r="D46" s="10"/>
+      <c r="E46" s="10"/>
+      <c r="F46" s="10"/>
+      <c r="G46" s="10"/>
+      <c r="H46" s="10"/>
+      <c r="I46" s="10"/>
+      <c r="J46" s="10" t="str">
         <f aca="false">IF(COUNTIF(D46:I46,"Sim")&gt;0,"Sim",IF(COUNTIF(D46:I46,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K46" s="11"/>
-      <c r="L46" s="11"/>
-      <c r="M46" s="11"/>
-      <c r="N46" s="11"/>
-      <c r="O46" s="11"/>
-      <c r="P46" s="11"/>
-      <c r="Q46" s="11"/>
-      <c r="R46" s="11"/>
-      <c r="S46" s="11"/>
+      <c r="K46" s="10"/>
+      <c r="L46" s="10"/>
+      <c r="M46" s="10"/>
+      <c r="N46" s="10"/>
+      <c r="O46" s="10"/>
+      <c r="P46" s="10"/>
+      <c r="Q46" s="10"/>
+      <c r="R46" s="10"/>
+      <c r="S46" s="10"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="10"/>
-      <c r="B47" s="11"/>
-      <c r="C47" s="11"/>
-      <c r="D47" s="11"/>
-      <c r="E47" s="11"/>
-      <c r="F47" s="11"/>
-      <c r="G47" s="11"/>
-      <c r="H47" s="11"/>
-      <c r="I47" s="11"/>
-      <c r="J47" s="11" t="str">
+      <c r="A47" s="9"/>
+      <c r="B47" s="10"/>
+      <c r="C47" s="10"/>
+      <c r="D47" s="10"/>
+      <c r="E47" s="10"/>
+      <c r="F47" s="10"/>
+      <c r="G47" s="10"/>
+      <c r="H47" s="10"/>
+      <c r="I47" s="10"/>
+      <c r="J47" s="10" t="str">
         <f aca="false">IF(COUNTIF(D47:I47,"Sim")&gt;0,"Sim",IF(COUNTIF(D47:I47,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K47" s="11"/>
-      <c r="L47" s="11"/>
-      <c r="M47" s="11"/>
-      <c r="N47" s="11"/>
-      <c r="O47" s="11"/>
-      <c r="P47" s="11"/>
-      <c r="Q47" s="11"/>
-      <c r="R47" s="11"/>
-      <c r="S47" s="11"/>
+      <c r="K47" s="10"/>
+      <c r="L47" s="10"/>
+      <c r="M47" s="10"/>
+      <c r="N47" s="10"/>
+      <c r="O47" s="10"/>
+      <c r="P47" s="10"/>
+      <c r="Q47" s="10"/>
+      <c r="R47" s="10"/>
+      <c r="S47" s="10"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="10"/>
-      <c r="B48" s="11"/>
-      <c r="C48" s="11"/>
-      <c r="D48" s="11"/>
-      <c r="E48" s="11"/>
-      <c r="F48" s="11"/>
-      <c r="G48" s="11"/>
-      <c r="H48" s="11"/>
-      <c r="I48" s="11"/>
-      <c r="J48" s="11" t="str">
+      <c r="A48" s="9"/>
+      <c r="B48" s="10"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="10"/>
+      <c r="E48" s="10"/>
+      <c r="F48" s="10"/>
+      <c r="G48" s="10"/>
+      <c r="H48" s="10"/>
+      <c r="I48" s="10"/>
+      <c r="J48" s="10" t="str">
         <f aca="false">IF(COUNTIF(D48:I48,"Sim")&gt;0,"Sim",IF(COUNTIF(D48:I48,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K48" s="11"/>
-      <c r="L48" s="11"/>
-      <c r="M48" s="11"/>
-      <c r="N48" s="11"/>
-      <c r="O48" s="11"/>
-      <c r="P48" s="11"/>
-      <c r="Q48" s="11"/>
-      <c r="R48" s="11"/>
-      <c r="S48" s="11"/>
+      <c r="K48" s="10"/>
+      <c r="L48" s="10"/>
+      <c r="M48" s="10"/>
+      <c r="N48" s="10"/>
+      <c r="O48" s="10"/>
+      <c r="P48" s="10"/>
+      <c r="Q48" s="10"/>
+      <c r="R48" s="10"/>
+      <c r="S48" s="10"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="10"/>
-      <c r="B49" s="11"/>
-      <c r="C49" s="11"/>
-      <c r="D49" s="11"/>
-      <c r="E49" s="11"/>
-      <c r="F49" s="11"/>
-      <c r="G49" s="11"/>
-      <c r="H49" s="11"/>
-      <c r="I49" s="11"/>
-      <c r="J49" s="11" t="str">
+      <c r="A49" s="9"/>
+      <c r="B49" s="10"/>
+      <c r="C49" s="10"/>
+      <c r="D49" s="10"/>
+      <c r="E49" s="10"/>
+      <c r="F49" s="10"/>
+      <c r="G49" s="10"/>
+      <c r="H49" s="10"/>
+      <c r="I49" s="10"/>
+      <c r="J49" s="10" t="str">
         <f aca="false">IF(COUNTIF(D49:I49,"Sim")&gt;0,"Sim",IF(COUNTIF(D49:I49,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K49" s="11"/>
-      <c r="L49" s="11"/>
-      <c r="M49" s="11"/>
-      <c r="N49" s="11"/>
-      <c r="O49" s="11"/>
-      <c r="P49" s="11"/>
-      <c r="Q49" s="11"/>
-      <c r="R49" s="11"/>
-      <c r="S49" s="11"/>
+      <c r="K49" s="10"/>
+      <c r="L49" s="10"/>
+      <c r="M49" s="10"/>
+      <c r="N49" s="10"/>
+      <c r="O49" s="10"/>
+      <c r="P49" s="10"/>
+      <c r="Q49" s="10"/>
+      <c r="R49" s="10"/>
+      <c r="S49" s="10"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="10"/>
-      <c r="B50" s="11"/>
-      <c r="C50" s="11"/>
-      <c r="D50" s="11"/>
-      <c r="E50" s="11"/>
-      <c r="F50" s="11"/>
-      <c r="G50" s="11"/>
-      <c r="H50" s="11"/>
-      <c r="I50" s="11"/>
-      <c r="J50" s="11" t="str">
+      <c r="A50" s="9"/>
+      <c r="B50" s="10"/>
+      <c r="C50" s="10"/>
+      <c r="D50" s="10"/>
+      <c r="E50" s="10"/>
+      <c r="F50" s="10"/>
+      <c r="G50" s="10"/>
+      <c r="H50" s="10"/>
+      <c r="I50" s="10"/>
+      <c r="J50" s="10" t="str">
         <f aca="false">IF(COUNTIF(D50:I50,"Sim")&gt;0,"Sim",IF(COUNTIF(D50:I50,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K50" s="11"/>
-      <c r="L50" s="11"/>
-      <c r="M50" s="11"/>
-      <c r="N50" s="11"/>
-      <c r="O50" s="11"/>
-      <c r="P50" s="11"/>
-      <c r="Q50" s="11"/>
-      <c r="R50" s="11"/>
-      <c r="S50" s="11"/>
+      <c r="K50" s="10"/>
+      <c r="L50" s="10"/>
+      <c r="M50" s="10"/>
+      <c r="N50" s="10"/>
+      <c r="O50" s="10"/>
+      <c r="P50" s="10"/>
+      <c r="Q50" s="10"/>
+      <c r="R50" s="10"/>
+      <c r="S50" s="10"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="10"/>
-      <c r="B51" s="11"/>
-      <c r="C51" s="11"/>
-      <c r="D51" s="11"/>
-      <c r="E51" s="11"/>
-      <c r="F51" s="11"/>
-      <c r="G51" s="11"/>
-      <c r="H51" s="11"/>
-      <c r="I51" s="11"/>
-      <c r="J51" s="11" t="str">
+      <c r="A51" s="9"/>
+      <c r="B51" s="10"/>
+      <c r="C51" s="10"/>
+      <c r="D51" s="10"/>
+      <c r="E51" s="10"/>
+      <c r="F51" s="10"/>
+      <c r="G51" s="10"/>
+      <c r="H51" s="10"/>
+      <c r="I51" s="10"/>
+      <c r="J51" s="10" t="str">
         <f aca="false">IF(COUNTIF(D51:I51,"Sim")&gt;0,"Sim",IF(COUNTIF(D51:I51,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K51" s="11"/>
-      <c r="L51" s="11"/>
-      <c r="M51" s="11"/>
-      <c r="N51" s="11"/>
-      <c r="O51" s="11"/>
-      <c r="P51" s="11"/>
-      <c r="Q51" s="11"/>
-      <c r="R51" s="11"/>
-      <c r="S51" s="11"/>
+      <c r="K51" s="10"/>
+      <c r="L51" s="10"/>
+      <c r="M51" s="10"/>
+      <c r="N51" s="10"/>
+      <c r="O51" s="10"/>
+      <c r="P51" s="10"/>
+      <c r="Q51" s="10"/>
+      <c r="R51" s="10"/>
+      <c r="S51" s="10"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="10"/>
-      <c r="B52" s="11"/>
-      <c r="C52" s="11"/>
-      <c r="D52" s="11"/>
-      <c r="E52" s="11"/>
-      <c r="F52" s="11"/>
-      <c r="G52" s="11"/>
-      <c r="H52" s="11"/>
-      <c r="I52" s="11"/>
-      <c r="J52" s="11" t="str">
+      <c r="A52" s="9"/>
+      <c r="B52" s="10"/>
+      <c r="C52" s="10"/>
+      <c r="D52" s="10"/>
+      <c r="E52" s="10"/>
+      <c r="F52" s="10"/>
+      <c r="G52" s="10"/>
+      <c r="H52" s="10"/>
+      <c r="I52" s="10"/>
+      <c r="J52" s="10" t="str">
         <f aca="false">IF(COUNTIF(D52:I52,"Sim")&gt;0,"Sim",IF(COUNTIF(D52:I52,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K52" s="11"/>
-      <c r="L52" s="11"/>
-      <c r="M52" s="11"/>
-      <c r="N52" s="11"/>
-      <c r="O52" s="11"/>
-      <c r="P52" s="11"/>
-      <c r="Q52" s="11"/>
-      <c r="R52" s="11"/>
-      <c r="S52" s="11"/>
+      <c r="K52" s="10"/>
+      <c r="L52" s="10"/>
+      <c r="M52" s="10"/>
+      <c r="N52" s="10"/>
+      <c r="O52" s="10"/>
+      <c r="P52" s="10"/>
+      <c r="Q52" s="10"/>
+      <c r="R52" s="10"/>
+      <c r="S52" s="10"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="10"/>
-      <c r="B53" s="11"/>
-      <c r="C53" s="11"/>
-      <c r="D53" s="11"/>
-      <c r="E53" s="11"/>
-      <c r="F53" s="11"/>
-      <c r="G53" s="11"/>
-      <c r="H53" s="11"/>
-      <c r="I53" s="11"/>
-      <c r="J53" s="11" t="str">
+      <c r="A53" s="9"/>
+      <c r="B53" s="10"/>
+      <c r="C53" s="10"/>
+      <c r="D53" s="10"/>
+      <c r="E53" s="10"/>
+      <c r="F53" s="10"/>
+      <c r="G53" s="10"/>
+      <c r="H53" s="10"/>
+      <c r="I53" s="10"/>
+      <c r="J53" s="10" t="str">
         <f aca="false">IF(COUNTIF(D53:I53,"Sim")&gt;0,"Sim",IF(COUNTIF(D53:I53,"Em apuração")&gt;0,"Em apuração","Não"))</f>
         <v>Não</v>
       </c>
-      <c r="K53" s="11"/>
-      <c r="L53" s="11"/>
-      <c r="M53" s="11"/>
-      <c r="N53" s="11"/>
-      <c r="O53" s="11"/>
-      <c r="P53" s="11"/>
-      <c r="Q53" s="11"/>
-      <c r="R53" s="11"/>
-      <c r="S53" s="11"/>
+      <c r="K53" s="10"/>
+      <c r="L53" s="10"/>
+      <c r="M53" s="10"/>
+      <c r="N53" s="10"/>
+      <c r="O53" s="10"/>
+      <c r="P53" s="10"/>
+      <c r="Q53" s="10"/>
+      <c r="R53" s="10"/>
+      <c r="S53" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5737,1487 +5748,1543 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R53"/>
+  <dimension ref="A1:S53"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="1" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="30"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
-      <c r="O2" s="8"/>
-      <c r="P2" s="8"/>
-      <c r="Q2" s="8"/>
-      <c r="R2" s="8"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="7"/>
+      <c r="Q2" s="7"/>
+      <c r="R2" s="7"/>
+      <c r="S2" s="7"/>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="K3" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="L3" s="9" t="s">
+      <c r="L3" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="M3" s="9" t="s">
+      <c r="M3" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="N3" s="9" t="s">
+      <c r="N3" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="O3" s="9" t="s">
+      <c r="O3" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="P3" s="9" t="s">
+      <c r="P3" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="Q3" s="9" t="s">
+      <c r="Q3" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="R3" s="9" t="s">
+      <c r="R3" s="8" t="s">
         <v>115</v>
       </c>
+      <c r="S3" s="8" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="C4" s="12" t="n">
+      <c r="C4" s="11" t="n">
         <v>46314.3923611111</v>
       </c>
-      <c r="D4" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="E4" s="13" t="n">
+      <c r="D4" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="E4" s="12" t="n">
         <f aca="false">IFERROR(IF(C4="","",WORKDAY(C4,IF(D4="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v>46317</v>
       </c>
-      <c r="F4" s="14"/>
-      <c r="G4" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="H4" s="11" t="s">
+      <c r="F4" s="13"/>
+      <c r="G4" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="H4" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="I4" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="J4" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="K4" s="11" t="s">
+      <c r="J4" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="L4" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="M4" s="11" t="s">
+      <c r="K4" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="N4" s="12"/>
-      <c r="O4" s="11" t="s">
+      <c r="L4" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="M4" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="N4" s="11"/>
+      <c r="O4" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="P4" s="12"/>
-      <c r="Q4" s="15" t="str">
+      <c r="P4" s="11"/>
+      <c r="Q4" s="14" t="str">
         <f aca="false">IFERROR(IF(P4="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P4,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R4" s="11" t="s">
-        <v>122</v>
-      </c>
+      <c r="R4" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="S4" s="10"/>
     </row>
     <row r="5" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="C5" s="12" t="n">
+      <c r="C5" s="11" t="n">
         <v>46314.3923611111</v>
       </c>
-      <c r="D5" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="E5" s="13" t="n">
+      <c r="D5" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="E5" s="12" t="n">
         <f aca="false">IFERROR(IF(C5="","",WORKDAY(C5,IF(D5="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v>46317</v>
       </c>
-      <c r="F5" s="14" t="n">
+      <c r="F5" s="13" t="n">
         <v>46317</v>
       </c>
-      <c r="G5" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="H5" s="11" t="s">
+      <c r="G5" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="I5" s="11" t="s">
+      <c r="H5" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="J5" s="11" t="s">
+      <c r="I5" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="K5" s="11" t="s">
+      <c r="J5" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="L5" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="M5" s="11" t="s">
+      <c r="K5" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="N5" s="12" t="n">
+      <c r="L5" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="M5" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="N5" s="11" t="n">
         <v>46314.5069444445</v>
       </c>
-      <c r="O5" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="P5" s="12"/>
-      <c r="Q5" s="15" t="str">
+      <c r="O5" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="14" t="str">
         <f aca="false">IFERROR(IF(P5="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P5,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R5" s="11" t="s">
-        <v>131</v>
-      </c>
+      <c r="R5" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="S5" s="10"/>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="13" t="str">
+      <c r="A6" s="9"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="12" t="str">
         <f aca="false">IFERROR(IF(C6="","",WORKDAY(C6,IF(D6="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F6" s="14"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
-      <c r="N6" s="12"/>
-      <c r="O6" s="11"/>
-      <c r="P6" s="12"/>
-      <c r="Q6" s="15" t="str">
+      <c r="F6" s="13"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="11"/>
+      <c r="O6" s="10"/>
+      <c r="P6" s="11"/>
+      <c r="Q6" s="14" t="str">
         <f aca="false">IFERROR(IF(P6="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P6,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R6" s="11"/>
+      <c r="R6" s="10"/>
+      <c r="S6" s="10"/>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="13" t="str">
+      <c r="A7" s="9"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="12" t="str">
         <f aca="false">IFERROR(IF(C7="","",WORKDAY(C7,IF(D7="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F7" s="14"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="11"/>
-      <c r="N7" s="12"/>
-      <c r="O7" s="11"/>
-      <c r="P7" s="12"/>
-      <c r="Q7" s="15" t="str">
+      <c r="F7" s="13"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="10"/>
+      <c r="P7" s="11"/>
+      <c r="Q7" s="14" t="str">
         <f aca="false">IFERROR(IF(P7="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P7,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R7" s="11"/>
+      <c r="R7" s="10"/>
+      <c r="S7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="13" t="str">
+      <c r="A8" s="9"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="12" t="str">
         <f aca="false">IFERROR(IF(C8="","",WORKDAY(C8,IF(D8="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F8" s="14"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="11"/>
-      <c r="N8" s="12"/>
-      <c r="O8" s="11"/>
-      <c r="P8" s="12"/>
-      <c r="Q8" s="15" t="str">
+      <c r="F8" s="13"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="11"/>
+      <c r="O8" s="10"/>
+      <c r="P8" s="11"/>
+      <c r="Q8" s="14" t="str">
         <f aca="false">IFERROR(IF(P8="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P8,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R8" s="11"/>
+      <c r="R8" s="10"/>
+      <c r="S8" s="10"/>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="13" t="str">
+      <c r="A9" s="9"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="12" t="str">
         <f aca="false">IFERROR(IF(C9="","",WORKDAY(C9,IF(D9="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F9" s="14"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="11"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="11"/>
-      <c r="N9" s="12"/>
-      <c r="O9" s="11"/>
-      <c r="P9" s="12"/>
-      <c r="Q9" s="15" t="str">
+      <c r="F9" s="13"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="11"/>
+      <c r="O9" s="10"/>
+      <c r="P9" s="11"/>
+      <c r="Q9" s="14" t="str">
         <f aca="false">IFERROR(IF(P9="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P9,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R9" s="11"/>
+      <c r="R9" s="10"/>
+      <c r="S9" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="13" t="str">
+      <c r="A10" s="9"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="12" t="str">
         <f aca="false">IFERROR(IF(C10="","",WORKDAY(C10,IF(D10="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F10" s="14"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="12"/>
-      <c r="O10" s="11"/>
-      <c r="P10" s="12"/>
-      <c r="Q10" s="15" t="str">
+      <c r="F10" s="13"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="11"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="11"/>
+      <c r="Q10" s="14" t="str">
         <f aca="false">IFERROR(IF(P10="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P10,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R10" s="11"/>
+      <c r="R10" s="10"/>
+      <c r="S10" s="10"/>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="13" t="str">
+      <c r="A11" s="9"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="12" t="str">
         <f aca="false">IFERROR(IF(C11="","",WORKDAY(C11,IF(D11="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F11" s="14"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="12"/>
-      <c r="O11" s="11"/>
-      <c r="P11" s="12"/>
-      <c r="Q11" s="15" t="str">
+      <c r="F11" s="13"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="10"/>
+      <c r="P11" s="11"/>
+      <c r="Q11" s="14" t="str">
         <f aca="false">IFERROR(IF(P11="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P11,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R11" s="11"/>
+      <c r="R11" s="10"/>
+      <c r="S11" s="10"/>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="13" t="str">
+      <c r="A12" s="9"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="12" t="str">
         <f aca="false">IFERROR(IF(C12="","",WORKDAY(C12,IF(D12="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F12" s="14"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="12"/>
-      <c r="O12" s="11"/>
-      <c r="P12" s="12"/>
-      <c r="Q12" s="15" t="str">
+      <c r="F12" s="13"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="11"/>
+      <c r="O12" s="10"/>
+      <c r="P12" s="11"/>
+      <c r="Q12" s="14" t="str">
         <f aca="false">IFERROR(IF(P12="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P12,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R12" s="11"/>
+      <c r="R12" s="10"/>
+      <c r="S12" s="10"/>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="13" t="str">
+      <c r="A13" s="9"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="12" t="str">
         <f aca="false">IFERROR(IF(C13="","",WORKDAY(C13,IF(D13="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F13" s="14"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="11"/>
-      <c r="N13" s="12"/>
-      <c r="O13" s="11"/>
-      <c r="P13" s="12"/>
-      <c r="Q13" s="15" t="str">
+      <c r="F13" s="13"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="11"/>
+      <c r="O13" s="10"/>
+      <c r="P13" s="11"/>
+      <c r="Q13" s="14" t="str">
         <f aca="false">IFERROR(IF(P13="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P13,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R13" s="11"/>
+      <c r="R13" s="10"/>
+      <c r="S13" s="10"/>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="13" t="str">
+      <c r="A14" s="9"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="12" t="str">
         <f aca="false">IFERROR(IF(C14="","",WORKDAY(C14,IF(D14="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F14" s="14"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="12"/>
-      <c r="O14" s="11"/>
-      <c r="P14" s="12"/>
-      <c r="Q14" s="15" t="str">
+      <c r="F14" s="13"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="11"/>
+      <c r="O14" s="10"/>
+      <c r="P14" s="11"/>
+      <c r="Q14" s="14" t="str">
         <f aca="false">IFERROR(IF(P14="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P14,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R14" s="11"/>
+      <c r="R14" s="10"/>
+      <c r="S14" s="10"/>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="13" t="str">
+      <c r="A15" s="9"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="12" t="str">
         <f aca="false">IFERROR(IF(C15="","",WORKDAY(C15,IF(D15="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F15" s="14"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="12"/>
-      <c r="O15" s="11"/>
-      <c r="P15" s="12"/>
-      <c r="Q15" s="15" t="str">
+      <c r="F15" s="13"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="10"/>
+      <c r="P15" s="11"/>
+      <c r="Q15" s="14" t="str">
         <f aca="false">IFERROR(IF(P15="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P15,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R15" s="11"/>
+      <c r="R15" s="10"/>
+      <c r="S15" s="10"/>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="13" t="str">
+      <c r="A16" s="9"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="12" t="str">
         <f aca="false">IFERROR(IF(C16="","",WORKDAY(C16,IF(D16="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F16" s="14"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="12"/>
-      <c r="O16" s="11"/>
-      <c r="P16" s="12"/>
-      <c r="Q16" s="15" t="str">
+      <c r="F16" s="13"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="11"/>
+      <c r="O16" s="10"/>
+      <c r="P16" s="11"/>
+      <c r="Q16" s="14" t="str">
         <f aca="false">IFERROR(IF(P16="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P16,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R16" s="11"/>
+      <c r="R16" s="10"/>
+      <c r="S16" s="10"/>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="13" t="str">
+      <c r="A17" s="9"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="12" t="str">
         <f aca="false">IFERROR(IF(C17="","",WORKDAY(C17,IF(D17="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F17" s="14"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="11"/>
-      <c r="N17" s="12"/>
-      <c r="O17" s="11"/>
-      <c r="P17" s="12"/>
-      <c r="Q17" s="15" t="str">
+      <c r="F17" s="13"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="10"/>
+      <c r="M17" s="10"/>
+      <c r="N17" s="11"/>
+      <c r="O17" s="10"/>
+      <c r="P17" s="11"/>
+      <c r="Q17" s="14" t="str">
         <f aca="false">IFERROR(IF(P17="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P17,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R17" s="11"/>
+      <c r="R17" s="10"/>
+      <c r="S17" s="10"/>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="13" t="str">
+      <c r="A18" s="9"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="12" t="str">
         <f aca="false">IFERROR(IF(C18="","",WORKDAY(C18,IF(D18="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F18" s="14"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="12"/>
-      <c r="O18" s="11"/>
-      <c r="P18" s="12"/>
-      <c r="Q18" s="15" t="str">
+      <c r="F18" s="13"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="10"/>
+      <c r="M18" s="10"/>
+      <c r="N18" s="11"/>
+      <c r="O18" s="10"/>
+      <c r="P18" s="11"/>
+      <c r="Q18" s="14" t="str">
         <f aca="false">IFERROR(IF(P18="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P18,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R18" s="11"/>
+      <c r="R18" s="10"/>
+      <c r="S18" s="10"/>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="13" t="str">
+      <c r="A19" s="9"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="12" t="str">
         <f aca="false">IFERROR(IF(C19="","",WORKDAY(C19,IF(D19="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F19" s="14"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
-      <c r="J19" s="11"/>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="11"/>
-      <c r="N19" s="12"/>
-      <c r="O19" s="11"/>
-      <c r="P19" s="12"/>
-      <c r="Q19" s="15" t="str">
+      <c r="F19" s="13"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="10"/>
+      <c r="J19" s="10"/>
+      <c r="K19" s="10"/>
+      <c r="L19" s="10"/>
+      <c r="M19" s="10"/>
+      <c r="N19" s="11"/>
+      <c r="O19" s="10"/>
+      <c r="P19" s="11"/>
+      <c r="Q19" s="14" t="str">
         <f aca="false">IFERROR(IF(P19="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P19,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R19" s="11"/>
+      <c r="R19" s="10"/>
+      <c r="S19" s="10"/>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="10"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="13" t="str">
+      <c r="A20" s="9"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="12" t="str">
         <f aca="false">IFERROR(IF(C20="","",WORKDAY(C20,IF(D20="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F20" s="14"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11"/>
-      <c r="J20" s="11"/>
-      <c r="K20" s="11"/>
-      <c r="L20" s="11"/>
-      <c r="M20" s="11"/>
-      <c r="N20" s="12"/>
-      <c r="O20" s="11"/>
-      <c r="P20" s="12"/>
-      <c r="Q20" s="15" t="str">
+      <c r="F20" s="13"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="11"/>
+      <c r="O20" s="10"/>
+      <c r="P20" s="11"/>
+      <c r="Q20" s="14" t="str">
         <f aca="false">IFERROR(IF(P20="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P20,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R20" s="11"/>
+      <c r="R20" s="10"/>
+      <c r="S20" s="10"/>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="10"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="13" t="str">
+      <c r="A21" s="9"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="12" t="str">
         <f aca="false">IFERROR(IF(C21="","",WORKDAY(C21,IF(D21="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F21" s="14"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="11"/>
-      <c r="J21" s="11"/>
-      <c r="K21" s="11"/>
-      <c r="L21" s="11"/>
-      <c r="M21" s="11"/>
-      <c r="N21" s="12"/>
-      <c r="O21" s="11"/>
-      <c r="P21" s="12"/>
-      <c r="Q21" s="15" t="str">
+      <c r="F21" s="13"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="11"/>
+      <c r="O21" s="10"/>
+      <c r="P21" s="11"/>
+      <c r="Q21" s="14" t="str">
         <f aca="false">IFERROR(IF(P21="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P21,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R21" s="11"/>
+      <c r="R21" s="10"/>
+      <c r="S21" s="10"/>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="10"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="13" t="str">
+      <c r="A22" s="9"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="12" t="str">
         <f aca="false">IFERROR(IF(C22="","",WORKDAY(C22,IF(D22="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F22" s="14"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="11"/>
-      <c r="J22" s="11"/>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="11"/>
-      <c r="N22" s="12"/>
-      <c r="O22" s="11"/>
-      <c r="P22" s="12"/>
-      <c r="Q22" s="15" t="str">
+      <c r="F22" s="13"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="10"/>
+      <c r="J22" s="10"/>
+      <c r="K22" s="10"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="11"/>
+      <c r="O22" s="10"/>
+      <c r="P22" s="11"/>
+      <c r="Q22" s="14" t="str">
         <f aca="false">IFERROR(IF(P22="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P22,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R22" s="11"/>
+      <c r="R22" s="10"/>
+      <c r="S22" s="10"/>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="10"/>
-      <c r="B23" s="11"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="13" t="str">
+      <c r="A23" s="9"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="12" t="str">
         <f aca="false">IFERROR(IF(C23="","",WORKDAY(C23,IF(D23="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F23" s="14"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="11"/>
-      <c r="J23" s="11"/>
-      <c r="K23" s="11"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="11"/>
-      <c r="N23" s="12"/>
-      <c r="O23" s="11"/>
-      <c r="P23" s="12"/>
-      <c r="Q23" s="15" t="str">
+      <c r="F23" s="13"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="10"/>
+      <c r="J23" s="10"/>
+      <c r="K23" s="10"/>
+      <c r="L23" s="10"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="11"/>
+      <c r="O23" s="10"/>
+      <c r="P23" s="11"/>
+      <c r="Q23" s="14" t="str">
         <f aca="false">IFERROR(IF(P23="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P23,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R23" s="11"/>
+      <c r="R23" s="10"/>
+      <c r="S23" s="10"/>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="10"/>
-      <c r="B24" s="11"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="13" t="str">
+      <c r="A24" s="9"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="12" t="str">
         <f aca="false">IFERROR(IF(C24="","",WORKDAY(C24,IF(D24="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F24" s="14"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="11"/>
-      <c r="J24" s="11"/>
-      <c r="K24" s="11"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="11"/>
-      <c r="N24" s="12"/>
-      <c r="O24" s="11"/>
-      <c r="P24" s="12"/>
-      <c r="Q24" s="15" t="str">
+      <c r="F24" s="13"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="10"/>
+      <c r="N24" s="11"/>
+      <c r="O24" s="10"/>
+      <c r="P24" s="11"/>
+      <c r="Q24" s="14" t="str">
         <f aca="false">IFERROR(IF(P24="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P24,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R24" s="11"/>
+      <c r="R24" s="10"/>
+      <c r="S24" s="10"/>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="10"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="13" t="str">
+      <c r="A25" s="9"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="12" t="str">
         <f aca="false">IFERROR(IF(C25="","",WORKDAY(C25,IF(D25="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F25" s="14"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="11"/>
-      <c r="J25" s="11"/>
-      <c r="K25" s="11"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="11"/>
-      <c r="N25" s="12"/>
-      <c r="O25" s="11"/>
-      <c r="P25" s="12"/>
-      <c r="Q25" s="15" t="str">
+      <c r="F25" s="13"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="10"/>
+      <c r="J25" s="10"/>
+      <c r="K25" s="10"/>
+      <c r="L25" s="10"/>
+      <c r="M25" s="10"/>
+      <c r="N25" s="11"/>
+      <c r="O25" s="10"/>
+      <c r="P25" s="11"/>
+      <c r="Q25" s="14" t="str">
         <f aca="false">IFERROR(IF(P25="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P25,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R25" s="11"/>
+      <c r="R25" s="10"/>
+      <c r="S25" s="10"/>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="10"/>
-      <c r="B26" s="11"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="13" t="str">
+      <c r="A26" s="9"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="12" t="str">
         <f aca="false">IFERROR(IF(C26="","",WORKDAY(C26,IF(D26="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F26" s="14"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11"/>
-      <c r="I26" s="11"/>
-      <c r="J26" s="11"/>
-      <c r="K26" s="11"/>
-      <c r="L26" s="11"/>
-      <c r="M26" s="11"/>
-      <c r="N26" s="12"/>
-      <c r="O26" s="11"/>
-      <c r="P26" s="12"/>
-      <c r="Q26" s="15" t="str">
+      <c r="F26" s="13"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="10"/>
+      <c r="I26" s="10"/>
+      <c r="J26" s="10"/>
+      <c r="K26" s="10"/>
+      <c r="L26" s="10"/>
+      <c r="M26" s="10"/>
+      <c r="N26" s="11"/>
+      <c r="O26" s="10"/>
+      <c r="P26" s="11"/>
+      <c r="Q26" s="14" t="str">
         <f aca="false">IFERROR(IF(P26="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P26,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R26" s="11"/>
+      <c r="R26" s="10"/>
+      <c r="S26" s="10"/>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="10"/>
-      <c r="B27" s="11"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="13" t="str">
+      <c r="A27" s="9"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="12" t="str">
         <f aca="false">IFERROR(IF(C27="","",WORKDAY(C27,IF(D27="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F27" s="14"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11"/>
-      <c r="I27" s="11"/>
-      <c r="J27" s="11"/>
-      <c r="K27" s="11"/>
-      <c r="L27" s="11"/>
-      <c r="M27" s="11"/>
-      <c r="N27" s="12"/>
-      <c r="O27" s="11"/>
-      <c r="P27" s="12"/>
-      <c r="Q27" s="15" t="str">
+      <c r="F27" s="13"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="10"/>
+      <c r="I27" s="10"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="10"/>
+      <c r="L27" s="10"/>
+      <c r="M27" s="10"/>
+      <c r="N27" s="11"/>
+      <c r="O27" s="10"/>
+      <c r="P27" s="11"/>
+      <c r="Q27" s="14" t="str">
         <f aca="false">IFERROR(IF(P27="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P27,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R27" s="11"/>
+      <c r="R27" s="10"/>
+      <c r="S27" s="10"/>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="10"/>
-      <c r="B28" s="11"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="13" t="str">
+      <c r="A28" s="9"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="12" t="str">
         <f aca="false">IFERROR(IF(C28="","",WORKDAY(C28,IF(D28="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F28" s="14"/>
-      <c r="G28" s="11"/>
-      <c r="H28" s="11"/>
-      <c r="I28" s="11"/>
-      <c r="J28" s="11"/>
-      <c r="K28" s="11"/>
-      <c r="L28" s="11"/>
-      <c r="M28" s="11"/>
-      <c r="N28" s="12"/>
-      <c r="O28" s="11"/>
-      <c r="P28" s="12"/>
-      <c r="Q28" s="15" t="str">
+      <c r="F28" s="13"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="10"/>
+      <c r="I28" s="10"/>
+      <c r="J28" s="10"/>
+      <c r="K28" s="10"/>
+      <c r="L28" s="10"/>
+      <c r="M28" s="10"/>
+      <c r="N28" s="11"/>
+      <c r="O28" s="10"/>
+      <c r="P28" s="11"/>
+      <c r="Q28" s="14" t="str">
         <f aca="false">IFERROR(IF(P28="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P28,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R28" s="11"/>
+      <c r="R28" s="10"/>
+      <c r="S28" s="10"/>
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="10"/>
-      <c r="B29" s="11"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="13" t="str">
+      <c r="A29" s="9"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="12" t="str">
         <f aca="false">IFERROR(IF(C29="","",WORKDAY(C29,IF(D29="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F29" s="14"/>
-      <c r="G29" s="11"/>
-      <c r="H29" s="11"/>
-      <c r="I29" s="11"/>
-      <c r="J29" s="11"/>
-      <c r="K29" s="11"/>
-      <c r="L29" s="11"/>
-      <c r="M29" s="11"/>
-      <c r="N29" s="12"/>
-      <c r="O29" s="11"/>
-      <c r="P29" s="12"/>
-      <c r="Q29" s="15" t="str">
+      <c r="F29" s="13"/>
+      <c r="G29" s="10"/>
+      <c r="H29" s="10"/>
+      <c r="I29" s="10"/>
+      <c r="J29" s="10"/>
+      <c r="K29" s="10"/>
+      <c r="L29" s="10"/>
+      <c r="M29" s="10"/>
+      <c r="N29" s="11"/>
+      <c r="O29" s="10"/>
+      <c r="P29" s="11"/>
+      <c r="Q29" s="14" t="str">
         <f aca="false">IFERROR(IF(P29="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P29,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R29" s="11"/>
+      <c r="R29" s="10"/>
+      <c r="S29" s="10"/>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="10"/>
-      <c r="B30" s="11"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="11"/>
-      <c r="E30" s="13" t="str">
+      <c r="A30" s="9"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="12" t="str">
         <f aca="false">IFERROR(IF(C30="","",WORKDAY(C30,IF(D30="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F30" s="14"/>
-      <c r="G30" s="11"/>
-      <c r="H30" s="11"/>
-      <c r="I30" s="11"/>
-      <c r="J30" s="11"/>
-      <c r="K30" s="11"/>
-      <c r="L30" s="11"/>
-      <c r="M30" s="11"/>
-      <c r="N30" s="12"/>
-      <c r="O30" s="11"/>
-      <c r="P30" s="12"/>
-      <c r="Q30" s="15" t="str">
+      <c r="F30" s="13"/>
+      <c r="G30" s="10"/>
+      <c r="H30" s="10"/>
+      <c r="I30" s="10"/>
+      <c r="J30" s="10"/>
+      <c r="K30" s="10"/>
+      <c r="L30" s="10"/>
+      <c r="M30" s="10"/>
+      <c r="N30" s="11"/>
+      <c r="O30" s="10"/>
+      <c r="P30" s="11"/>
+      <c r="Q30" s="14" t="str">
         <f aca="false">IFERROR(IF(P30="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P30,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R30" s="11"/>
+      <c r="R30" s="10"/>
+      <c r="S30" s="10"/>
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="10"/>
-      <c r="B31" s="11"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="13" t="str">
+      <c r="A31" s="9"/>
+      <c r="B31" s="10"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="12" t="str">
         <f aca="false">IFERROR(IF(C31="","",WORKDAY(C31,IF(D31="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F31" s="14"/>
-      <c r="G31" s="11"/>
-      <c r="H31" s="11"/>
-      <c r="I31" s="11"/>
-      <c r="J31" s="11"/>
-      <c r="K31" s="11"/>
-      <c r="L31" s="11"/>
-      <c r="M31" s="11"/>
-      <c r="N31" s="12"/>
-      <c r="O31" s="11"/>
-      <c r="P31" s="12"/>
-      <c r="Q31" s="15" t="str">
+      <c r="F31" s="13"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="10"/>
+      <c r="I31" s="10"/>
+      <c r="J31" s="10"/>
+      <c r="K31" s="10"/>
+      <c r="L31" s="10"/>
+      <c r="M31" s="10"/>
+      <c r="N31" s="11"/>
+      <c r="O31" s="10"/>
+      <c r="P31" s="11"/>
+      <c r="Q31" s="14" t="str">
         <f aca="false">IFERROR(IF(P31="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P31,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R31" s="11"/>
+      <c r="R31" s="10"/>
+      <c r="S31" s="10"/>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="10"/>
-      <c r="B32" s="11"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="13" t="str">
+      <c r="A32" s="9"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="12" t="str">
         <f aca="false">IFERROR(IF(C32="","",WORKDAY(C32,IF(D32="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F32" s="14"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="11"/>
-      <c r="J32" s="11"/>
-      <c r="K32" s="11"/>
-      <c r="L32" s="11"/>
-      <c r="M32" s="11"/>
-      <c r="N32" s="12"/>
-      <c r="O32" s="11"/>
-      <c r="P32" s="12"/>
-      <c r="Q32" s="15" t="str">
+      <c r="F32" s="13"/>
+      <c r="G32" s="10"/>
+      <c r="H32" s="10"/>
+      <c r="I32" s="10"/>
+      <c r="J32" s="10"/>
+      <c r="K32" s="10"/>
+      <c r="L32" s="10"/>
+      <c r="M32" s="10"/>
+      <c r="N32" s="11"/>
+      <c r="O32" s="10"/>
+      <c r="P32" s="11"/>
+      <c r="Q32" s="14" t="str">
         <f aca="false">IFERROR(IF(P32="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P32,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R32" s="11"/>
+      <c r="R32" s="10"/>
+      <c r="S32" s="10"/>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="10"/>
-      <c r="B33" s="11"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="13" t="str">
+      <c r="A33" s="9"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="12" t="str">
         <f aca="false">IFERROR(IF(C33="","",WORKDAY(C33,IF(D33="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F33" s="14"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="11"/>
-      <c r="I33" s="11"/>
-      <c r="J33" s="11"/>
-      <c r="K33" s="11"/>
-      <c r="L33" s="11"/>
-      <c r="M33" s="11"/>
-      <c r="N33" s="12"/>
-      <c r="O33" s="11"/>
-      <c r="P33" s="12"/>
-      <c r="Q33" s="15" t="str">
+      <c r="F33" s="13"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="10"/>
+      <c r="I33" s="10"/>
+      <c r="J33" s="10"/>
+      <c r="K33" s="10"/>
+      <c r="L33" s="10"/>
+      <c r="M33" s="10"/>
+      <c r="N33" s="11"/>
+      <c r="O33" s="10"/>
+      <c r="P33" s="11"/>
+      <c r="Q33" s="14" t="str">
         <f aca="false">IFERROR(IF(P33="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P33,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R33" s="11"/>
+      <c r="R33" s="10"/>
+      <c r="S33" s="10"/>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="10"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="13" t="str">
+      <c r="A34" s="9"/>
+      <c r="B34" s="10"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="12" t="str">
         <f aca="false">IFERROR(IF(C34="","",WORKDAY(C34,IF(D34="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F34" s="14"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="11"/>
-      <c r="I34" s="11"/>
-      <c r="J34" s="11"/>
-      <c r="K34" s="11"/>
-      <c r="L34" s="11"/>
-      <c r="M34" s="11"/>
-      <c r="N34" s="12"/>
-      <c r="O34" s="11"/>
-      <c r="P34" s="12"/>
-      <c r="Q34" s="15" t="str">
+      <c r="F34" s="13"/>
+      <c r="G34" s="10"/>
+      <c r="H34" s="10"/>
+      <c r="I34" s="10"/>
+      <c r="J34" s="10"/>
+      <c r="K34" s="10"/>
+      <c r="L34" s="10"/>
+      <c r="M34" s="10"/>
+      <c r="N34" s="11"/>
+      <c r="O34" s="10"/>
+      <c r="P34" s="11"/>
+      <c r="Q34" s="14" t="str">
         <f aca="false">IFERROR(IF(P34="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P34,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R34" s="11"/>
+      <c r="R34" s="10"/>
+      <c r="S34" s="10"/>
     </row>
     <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="10"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="12"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="13" t="str">
+      <c r="A35" s="9"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="12" t="str">
         <f aca="false">IFERROR(IF(C35="","",WORKDAY(C35,IF(D35="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F35" s="14"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="11"/>
-      <c r="I35" s="11"/>
-      <c r="J35" s="11"/>
-      <c r="K35" s="11"/>
-      <c r="L35" s="11"/>
-      <c r="M35" s="11"/>
-      <c r="N35" s="12"/>
-      <c r="O35" s="11"/>
-      <c r="P35" s="12"/>
-      <c r="Q35" s="15" t="str">
+      <c r="F35" s="13"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="10"/>
+      <c r="I35" s="10"/>
+      <c r="J35" s="10"/>
+      <c r="K35" s="10"/>
+      <c r="L35" s="10"/>
+      <c r="M35" s="10"/>
+      <c r="N35" s="11"/>
+      <c r="O35" s="10"/>
+      <c r="P35" s="11"/>
+      <c r="Q35" s="14" t="str">
         <f aca="false">IFERROR(IF(P35="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P35,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R35" s="11"/>
+      <c r="R35" s="10"/>
+      <c r="S35" s="10"/>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="10"/>
-      <c r="B36" s="11"/>
-      <c r="C36" s="12"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="13" t="str">
+      <c r="A36" s="9"/>
+      <c r="B36" s="10"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="12" t="str">
         <f aca="false">IFERROR(IF(C36="","",WORKDAY(C36,IF(D36="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F36" s="14"/>
-      <c r="G36" s="11"/>
-      <c r="H36" s="11"/>
-      <c r="I36" s="11"/>
-      <c r="J36" s="11"/>
-      <c r="K36" s="11"/>
-      <c r="L36" s="11"/>
-      <c r="M36" s="11"/>
-      <c r="N36" s="12"/>
-      <c r="O36" s="11"/>
-      <c r="P36" s="12"/>
-      <c r="Q36" s="15" t="str">
+      <c r="F36" s="13"/>
+      <c r="G36" s="10"/>
+      <c r="H36" s="10"/>
+      <c r="I36" s="10"/>
+      <c r="J36" s="10"/>
+      <c r="K36" s="10"/>
+      <c r="L36" s="10"/>
+      <c r="M36" s="10"/>
+      <c r="N36" s="11"/>
+      <c r="O36" s="10"/>
+      <c r="P36" s="11"/>
+      <c r="Q36" s="14" t="str">
         <f aca="false">IFERROR(IF(P36="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P36,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R36" s="11"/>
+      <c r="R36" s="10"/>
+      <c r="S36" s="10"/>
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="10"/>
-      <c r="B37" s="11"/>
-      <c r="C37" s="12"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="13" t="str">
+      <c r="A37" s="9"/>
+      <c r="B37" s="10"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="12" t="str">
         <f aca="false">IFERROR(IF(C37="","",WORKDAY(C37,IF(D37="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F37" s="14"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="11"/>
-      <c r="I37" s="11"/>
-      <c r="J37" s="11"/>
-      <c r="K37" s="11"/>
-      <c r="L37" s="11"/>
-      <c r="M37" s="11"/>
-      <c r="N37" s="12"/>
-      <c r="O37" s="11"/>
-      <c r="P37" s="12"/>
-      <c r="Q37" s="15" t="str">
+      <c r="F37" s="13"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="10"/>
+      <c r="I37" s="10"/>
+      <c r="J37" s="10"/>
+      <c r="K37" s="10"/>
+      <c r="L37" s="10"/>
+      <c r="M37" s="10"/>
+      <c r="N37" s="11"/>
+      <c r="O37" s="10"/>
+      <c r="P37" s="11"/>
+      <c r="Q37" s="14" t="str">
         <f aca="false">IFERROR(IF(P37="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P37,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R37" s="11"/>
+      <c r="R37" s="10"/>
+      <c r="S37" s="10"/>
     </row>
     <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="10"/>
-      <c r="B38" s="11"/>
-      <c r="C38" s="12"/>
-      <c r="D38" s="11"/>
-      <c r="E38" s="13" t="str">
+      <c r="A38" s="9"/>
+      <c r="B38" s="10"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="12" t="str">
         <f aca="false">IFERROR(IF(C38="","",WORKDAY(C38,IF(D38="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F38" s="14"/>
-      <c r="G38" s="11"/>
-      <c r="H38" s="11"/>
-      <c r="I38" s="11"/>
-      <c r="J38" s="11"/>
-      <c r="K38" s="11"/>
-      <c r="L38" s="11"/>
-      <c r="M38" s="11"/>
-      <c r="N38" s="12"/>
-      <c r="O38" s="11"/>
-      <c r="P38" s="12"/>
-      <c r="Q38" s="15" t="str">
+      <c r="F38" s="13"/>
+      <c r="G38" s="10"/>
+      <c r="H38" s="10"/>
+      <c r="I38" s="10"/>
+      <c r="J38" s="10"/>
+      <c r="K38" s="10"/>
+      <c r="L38" s="10"/>
+      <c r="M38" s="10"/>
+      <c r="N38" s="11"/>
+      <c r="O38" s="10"/>
+      <c r="P38" s="11"/>
+      <c r="Q38" s="14" t="str">
         <f aca="false">IFERROR(IF(P38="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P38,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R38" s="11"/>
+      <c r="R38" s="10"/>
+      <c r="S38" s="10"/>
     </row>
     <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="10"/>
-      <c r="B39" s="11"/>
-      <c r="C39" s="12"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="13" t="str">
+      <c r="A39" s="9"/>
+      <c r="B39" s="10"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="12" t="str">
         <f aca="false">IFERROR(IF(C39="","",WORKDAY(C39,IF(D39="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F39" s="14"/>
-      <c r="G39" s="11"/>
-      <c r="H39" s="11"/>
-      <c r="I39" s="11"/>
-      <c r="J39" s="11"/>
-      <c r="K39" s="11"/>
-      <c r="L39" s="11"/>
-      <c r="M39" s="11"/>
-      <c r="N39" s="12"/>
-      <c r="O39" s="11"/>
-      <c r="P39" s="12"/>
-      <c r="Q39" s="15" t="str">
+      <c r="F39" s="13"/>
+      <c r="G39" s="10"/>
+      <c r="H39" s="10"/>
+      <c r="I39" s="10"/>
+      <c r="J39" s="10"/>
+      <c r="K39" s="10"/>
+      <c r="L39" s="10"/>
+      <c r="M39" s="10"/>
+      <c r="N39" s="11"/>
+      <c r="O39" s="10"/>
+      <c r="P39" s="11"/>
+      <c r="Q39" s="14" t="str">
         <f aca="false">IFERROR(IF(P39="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P39,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R39" s="11"/>
+      <c r="R39" s="10"/>
+      <c r="S39" s="10"/>
     </row>
     <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="10"/>
-      <c r="B40" s="11"/>
-      <c r="C40" s="12"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="13" t="str">
+      <c r="A40" s="9"/>
+      <c r="B40" s="10"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="10"/>
+      <c r="E40" s="12" t="str">
         <f aca="false">IFERROR(IF(C40="","",WORKDAY(C40,IF(D40="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F40" s="14"/>
-      <c r="G40" s="11"/>
-      <c r="H40" s="11"/>
-      <c r="I40" s="11"/>
-      <c r="J40" s="11"/>
-      <c r="K40" s="11"/>
-      <c r="L40" s="11"/>
-      <c r="M40" s="11"/>
-      <c r="N40" s="12"/>
-      <c r="O40" s="11"/>
-      <c r="P40" s="12"/>
-      <c r="Q40" s="15" t="str">
+      <c r="F40" s="13"/>
+      <c r="G40" s="10"/>
+      <c r="H40" s="10"/>
+      <c r="I40" s="10"/>
+      <c r="J40" s="10"/>
+      <c r="K40" s="10"/>
+      <c r="L40" s="10"/>
+      <c r="M40" s="10"/>
+      <c r="N40" s="11"/>
+      <c r="O40" s="10"/>
+      <c r="P40" s="11"/>
+      <c r="Q40" s="14" t="str">
         <f aca="false">IFERROR(IF(P40="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P40,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R40" s="11"/>
+      <c r="R40" s="10"/>
+      <c r="S40" s="10"/>
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="10"/>
-      <c r="B41" s="11"/>
-      <c r="C41" s="12"/>
-      <c r="D41" s="11"/>
-      <c r="E41" s="13" t="str">
+      <c r="A41" s="9"/>
+      <c r="B41" s="10"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="10"/>
+      <c r="E41" s="12" t="str">
         <f aca="false">IFERROR(IF(C41="","",WORKDAY(C41,IF(D41="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F41" s="14"/>
-      <c r="G41" s="11"/>
-      <c r="H41" s="11"/>
-      <c r="I41" s="11"/>
-      <c r="J41" s="11"/>
-      <c r="K41" s="11"/>
-      <c r="L41" s="11"/>
-      <c r="M41" s="11"/>
-      <c r="N41" s="12"/>
-      <c r="O41" s="11"/>
-      <c r="P41" s="12"/>
-      <c r="Q41" s="15" t="str">
+      <c r="F41" s="13"/>
+      <c r="G41" s="10"/>
+      <c r="H41" s="10"/>
+      <c r="I41" s="10"/>
+      <c r="J41" s="10"/>
+      <c r="K41" s="10"/>
+      <c r="L41" s="10"/>
+      <c r="M41" s="10"/>
+      <c r="N41" s="11"/>
+      <c r="O41" s="10"/>
+      <c r="P41" s="11"/>
+      <c r="Q41" s="14" t="str">
         <f aca="false">IFERROR(IF(P41="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P41,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R41" s="11"/>
+      <c r="R41" s="10"/>
+      <c r="S41" s="10"/>
     </row>
     <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="10"/>
-      <c r="B42" s="11"/>
-      <c r="C42" s="12"/>
-      <c r="D42" s="11"/>
-      <c r="E42" s="13" t="str">
+      <c r="A42" s="9"/>
+      <c r="B42" s="10"/>
+      <c r="C42" s="11"/>
+      <c r="D42" s="10"/>
+      <c r="E42" s="12" t="str">
         <f aca="false">IFERROR(IF(C42="","",WORKDAY(C42,IF(D42="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F42" s="14"/>
-      <c r="G42" s="11"/>
-      <c r="H42" s="11"/>
-      <c r="I42" s="11"/>
-      <c r="J42" s="11"/>
-      <c r="K42" s="11"/>
-      <c r="L42" s="11"/>
-      <c r="M42" s="11"/>
-      <c r="N42" s="12"/>
-      <c r="O42" s="11"/>
-      <c r="P42" s="12"/>
-      <c r="Q42" s="15" t="str">
+      <c r="F42" s="13"/>
+      <c r="G42" s="10"/>
+      <c r="H42" s="10"/>
+      <c r="I42" s="10"/>
+      <c r="J42" s="10"/>
+      <c r="K42" s="10"/>
+      <c r="L42" s="10"/>
+      <c r="M42" s="10"/>
+      <c r="N42" s="11"/>
+      <c r="O42" s="10"/>
+      <c r="P42" s="11"/>
+      <c r="Q42" s="14" t="str">
         <f aca="false">IFERROR(IF(P42="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P42,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R42" s="11"/>
+      <c r="R42" s="10"/>
+      <c r="S42" s="10"/>
     </row>
     <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="10"/>
-      <c r="B43" s="11"/>
-      <c r="C43" s="12"/>
-      <c r="D43" s="11"/>
-      <c r="E43" s="13" t="str">
+      <c r="A43" s="9"/>
+      <c r="B43" s="10"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="10"/>
+      <c r="E43" s="12" t="str">
         <f aca="false">IFERROR(IF(C43="","",WORKDAY(C43,IF(D43="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F43" s="14"/>
-      <c r="G43" s="11"/>
-      <c r="H43" s="11"/>
-      <c r="I43" s="11"/>
-      <c r="J43" s="11"/>
-      <c r="K43" s="11"/>
-      <c r="L43" s="11"/>
-      <c r="M43" s="11"/>
-      <c r="N43" s="12"/>
-      <c r="O43" s="11"/>
-      <c r="P43" s="12"/>
-      <c r="Q43" s="15" t="str">
+      <c r="F43" s="13"/>
+      <c r="G43" s="10"/>
+      <c r="H43" s="10"/>
+      <c r="I43" s="10"/>
+      <c r="J43" s="10"/>
+      <c r="K43" s="10"/>
+      <c r="L43" s="10"/>
+      <c r="M43" s="10"/>
+      <c r="N43" s="11"/>
+      <c r="O43" s="10"/>
+      <c r="P43" s="11"/>
+      <c r="Q43" s="14" t="str">
         <f aca="false">IFERROR(IF(P43="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P43,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R43" s="11"/>
+      <c r="R43" s="10"/>
+      <c r="S43" s="10"/>
     </row>
     <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="10"/>
-      <c r="B44" s="11"/>
-      <c r="C44" s="12"/>
-      <c r="D44" s="11"/>
-      <c r="E44" s="13" t="str">
+      <c r="A44" s="9"/>
+      <c r="B44" s="10"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="10"/>
+      <c r="E44" s="12" t="str">
         <f aca="false">IFERROR(IF(C44="","",WORKDAY(C44,IF(D44="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F44" s="14"/>
-      <c r="G44" s="11"/>
-      <c r="H44" s="11"/>
-      <c r="I44" s="11"/>
-      <c r="J44" s="11"/>
-      <c r="K44" s="11"/>
-      <c r="L44" s="11"/>
-      <c r="M44" s="11"/>
-      <c r="N44" s="12"/>
-      <c r="O44" s="11"/>
-      <c r="P44" s="12"/>
-      <c r="Q44" s="15" t="str">
+      <c r="F44" s="13"/>
+      <c r="G44" s="10"/>
+      <c r="H44" s="10"/>
+      <c r="I44" s="10"/>
+      <c r="J44" s="10"/>
+      <c r="K44" s="10"/>
+      <c r="L44" s="10"/>
+      <c r="M44" s="10"/>
+      <c r="N44" s="11"/>
+      <c r="O44" s="10"/>
+      <c r="P44" s="11"/>
+      <c r="Q44" s="14" t="str">
         <f aca="false">IFERROR(IF(P44="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P44,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R44" s="11"/>
+      <c r="R44" s="10"/>
+      <c r="S44" s="10"/>
     </row>
     <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="10"/>
-      <c r="B45" s="11"/>
-      <c r="C45" s="12"/>
-      <c r="D45" s="11"/>
-      <c r="E45" s="13" t="str">
+      <c r="A45" s="9"/>
+      <c r="B45" s="10"/>
+      <c r="C45" s="11"/>
+      <c r="D45" s="10"/>
+      <c r="E45" s="12" t="str">
         <f aca="false">IFERROR(IF(C45="","",WORKDAY(C45,IF(D45="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F45" s="14"/>
-      <c r="G45" s="11"/>
-      <c r="H45" s="11"/>
-      <c r="I45" s="11"/>
-      <c r="J45" s="11"/>
-      <c r="K45" s="11"/>
-      <c r="L45" s="11"/>
-      <c r="M45" s="11"/>
-      <c r="N45" s="12"/>
-      <c r="O45" s="11"/>
-      <c r="P45" s="12"/>
-      <c r="Q45" s="15" t="str">
+      <c r="F45" s="13"/>
+      <c r="G45" s="10"/>
+      <c r="H45" s="10"/>
+      <c r="I45" s="10"/>
+      <c r="J45" s="10"/>
+      <c r="K45" s="10"/>
+      <c r="L45" s="10"/>
+      <c r="M45" s="10"/>
+      <c r="N45" s="11"/>
+      <c r="O45" s="10"/>
+      <c r="P45" s="11"/>
+      <c r="Q45" s="14" t="str">
         <f aca="false">IFERROR(IF(P45="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P45,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R45" s="11"/>
+      <c r="R45" s="10"/>
+      <c r="S45" s="10"/>
     </row>
     <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="10"/>
-      <c r="B46" s="11"/>
-      <c r="C46" s="12"/>
-      <c r="D46" s="11"/>
-      <c r="E46" s="13" t="str">
+      <c r="A46" s="9"/>
+      <c r="B46" s="10"/>
+      <c r="C46" s="11"/>
+      <c r="D46" s="10"/>
+      <c r="E46" s="12" t="str">
         <f aca="false">IFERROR(IF(C46="","",WORKDAY(C46,IF(D46="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F46" s="14"/>
-      <c r="G46" s="11"/>
-      <c r="H46" s="11"/>
-      <c r="I46" s="11"/>
-      <c r="J46" s="11"/>
-      <c r="K46" s="11"/>
-      <c r="L46" s="11"/>
-      <c r="M46" s="11"/>
-      <c r="N46" s="12"/>
-      <c r="O46" s="11"/>
-      <c r="P46" s="12"/>
-      <c r="Q46" s="15" t="str">
+      <c r="F46" s="13"/>
+      <c r="G46" s="10"/>
+      <c r="H46" s="10"/>
+      <c r="I46" s="10"/>
+      <c r="J46" s="10"/>
+      <c r="K46" s="10"/>
+      <c r="L46" s="10"/>
+      <c r="M46" s="10"/>
+      <c r="N46" s="11"/>
+      <c r="O46" s="10"/>
+      <c r="P46" s="11"/>
+      <c r="Q46" s="14" t="str">
         <f aca="false">IFERROR(IF(P46="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P46,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R46" s="11"/>
+      <c r="R46" s="10"/>
+      <c r="S46" s="10"/>
     </row>
     <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="10"/>
-      <c r="B47" s="11"/>
-      <c r="C47" s="12"/>
-      <c r="D47" s="11"/>
-      <c r="E47" s="13" t="str">
+      <c r="A47" s="9"/>
+      <c r="B47" s="10"/>
+      <c r="C47" s="11"/>
+      <c r="D47" s="10"/>
+      <c r="E47" s="12" t="str">
         <f aca="false">IFERROR(IF(C47="","",WORKDAY(C47,IF(D47="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F47" s="14"/>
-      <c r="G47" s="11"/>
-      <c r="H47" s="11"/>
-      <c r="I47" s="11"/>
-      <c r="J47" s="11"/>
-      <c r="K47" s="11"/>
-      <c r="L47" s="11"/>
-      <c r="M47" s="11"/>
-      <c r="N47" s="12"/>
-      <c r="O47" s="11"/>
-      <c r="P47" s="12"/>
-      <c r="Q47" s="15" t="str">
+      <c r="F47" s="13"/>
+      <c r="G47" s="10"/>
+      <c r="H47" s="10"/>
+      <c r="I47" s="10"/>
+      <c r="J47" s="10"/>
+      <c r="K47" s="10"/>
+      <c r="L47" s="10"/>
+      <c r="M47" s="10"/>
+      <c r="N47" s="11"/>
+      <c r="O47" s="10"/>
+      <c r="P47" s="11"/>
+      <c r="Q47" s="14" t="str">
         <f aca="false">IFERROR(IF(P47="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P47,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R47" s="11"/>
+      <c r="R47" s="10"/>
+      <c r="S47" s="10"/>
     </row>
     <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="10"/>
-      <c r="B48" s="11"/>
-      <c r="C48" s="12"/>
-      <c r="D48" s="11"/>
-      <c r="E48" s="13" t="str">
+      <c r="A48" s="9"/>
+      <c r="B48" s="10"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="10"/>
+      <c r="E48" s="12" t="str">
         <f aca="false">IFERROR(IF(C48="","",WORKDAY(C48,IF(D48="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F48" s="14"/>
-      <c r="G48" s="11"/>
-      <c r="H48" s="11"/>
-      <c r="I48" s="11"/>
-      <c r="J48" s="11"/>
-      <c r="K48" s="11"/>
-      <c r="L48" s="11"/>
-      <c r="M48" s="11"/>
-      <c r="N48" s="12"/>
-      <c r="O48" s="11"/>
-      <c r="P48" s="12"/>
-      <c r="Q48" s="15" t="str">
+      <c r="F48" s="13"/>
+      <c r="G48" s="10"/>
+      <c r="H48" s="10"/>
+      <c r="I48" s="10"/>
+      <c r="J48" s="10"/>
+      <c r="K48" s="10"/>
+      <c r="L48" s="10"/>
+      <c r="M48" s="10"/>
+      <c r="N48" s="11"/>
+      <c r="O48" s="10"/>
+      <c r="P48" s="11"/>
+      <c r="Q48" s="14" t="str">
         <f aca="false">IFERROR(IF(P48="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P48,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R48" s="11"/>
+      <c r="R48" s="10"/>
+      <c r="S48" s="10"/>
     </row>
     <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="10"/>
-      <c r="B49" s="11"/>
-      <c r="C49" s="12"/>
-      <c r="D49" s="11"/>
-      <c r="E49" s="13" t="str">
+      <c r="A49" s="9"/>
+      <c r="B49" s="10"/>
+      <c r="C49" s="11"/>
+      <c r="D49" s="10"/>
+      <c r="E49" s="12" t="str">
         <f aca="false">IFERROR(IF(C49="","",WORKDAY(C49,IF(D49="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F49" s="14"/>
-      <c r="G49" s="11"/>
-      <c r="H49" s="11"/>
-      <c r="I49" s="11"/>
-      <c r="J49" s="11"/>
-      <c r="K49" s="11"/>
-      <c r="L49" s="11"/>
-      <c r="M49" s="11"/>
-      <c r="N49" s="12"/>
-      <c r="O49" s="11"/>
-      <c r="P49" s="12"/>
-      <c r="Q49" s="15" t="str">
+      <c r="F49" s="13"/>
+      <c r="G49" s="10"/>
+      <c r="H49" s="10"/>
+      <c r="I49" s="10"/>
+      <c r="J49" s="10"/>
+      <c r="K49" s="10"/>
+      <c r="L49" s="10"/>
+      <c r="M49" s="10"/>
+      <c r="N49" s="11"/>
+      <c r="O49" s="10"/>
+      <c r="P49" s="11"/>
+      <c r="Q49" s="14" t="str">
         <f aca="false">IFERROR(IF(P49="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P49,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R49" s="11"/>
+      <c r="R49" s="10"/>
+      <c r="S49" s="10"/>
     </row>
     <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="10"/>
-      <c r="B50" s="11"/>
-      <c r="C50" s="12"/>
-      <c r="D50" s="11"/>
-      <c r="E50" s="13" t="str">
+      <c r="A50" s="9"/>
+      <c r="B50" s="10"/>
+      <c r="C50" s="11"/>
+      <c r="D50" s="10"/>
+      <c r="E50" s="12" t="str">
         <f aca="false">IFERROR(IF(C50="","",WORKDAY(C50,IF(D50="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F50" s="14"/>
-      <c r="G50" s="11"/>
-      <c r="H50" s="11"/>
-      <c r="I50" s="11"/>
-      <c r="J50" s="11"/>
-      <c r="K50" s="11"/>
-      <c r="L50" s="11"/>
-      <c r="M50" s="11"/>
-      <c r="N50" s="12"/>
-      <c r="O50" s="11"/>
-      <c r="P50" s="12"/>
-      <c r="Q50" s="15" t="str">
+      <c r="F50" s="13"/>
+      <c r="G50" s="10"/>
+      <c r="H50" s="10"/>
+      <c r="I50" s="10"/>
+      <c r="J50" s="10"/>
+      <c r="K50" s="10"/>
+      <c r="L50" s="10"/>
+      <c r="M50" s="10"/>
+      <c r="N50" s="11"/>
+      <c r="O50" s="10"/>
+      <c r="P50" s="11"/>
+      <c r="Q50" s="14" t="str">
         <f aca="false">IFERROR(IF(P50="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P50,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R50" s="11"/>
+      <c r="R50" s="10"/>
+      <c r="S50" s="10"/>
     </row>
     <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="10"/>
-      <c r="B51" s="11"/>
-      <c r="C51" s="12"/>
-      <c r="D51" s="11"/>
-      <c r="E51" s="13" t="str">
+      <c r="A51" s="9"/>
+      <c r="B51" s="10"/>
+      <c r="C51" s="11"/>
+      <c r="D51" s="10"/>
+      <c r="E51" s="12" t="str">
         <f aca="false">IFERROR(IF(C51="","",WORKDAY(C51,IF(D51="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F51" s="14"/>
-      <c r="G51" s="11"/>
-      <c r="H51" s="11"/>
-      <c r="I51" s="11"/>
-      <c r="J51" s="11"/>
-      <c r="K51" s="11"/>
-      <c r="L51" s="11"/>
-      <c r="M51" s="11"/>
-      <c r="N51" s="12"/>
-      <c r="O51" s="11"/>
-      <c r="P51" s="12"/>
-      <c r="Q51" s="15" t="str">
+      <c r="F51" s="13"/>
+      <c r="G51" s="10"/>
+      <c r="H51" s="10"/>
+      <c r="I51" s="10"/>
+      <c r="J51" s="10"/>
+      <c r="K51" s="10"/>
+      <c r="L51" s="10"/>
+      <c r="M51" s="10"/>
+      <c r="N51" s="11"/>
+      <c r="O51" s="10"/>
+      <c r="P51" s="11"/>
+      <c r="Q51" s="14" t="str">
         <f aca="false">IFERROR(IF(P51="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P51,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R51" s="11"/>
+      <c r="R51" s="10"/>
+      <c r="S51" s="10"/>
     </row>
     <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="10"/>
-      <c r="B52" s="11"/>
-      <c r="C52" s="12"/>
-      <c r="D52" s="11"/>
-      <c r="E52" s="13" t="str">
+      <c r="A52" s="9"/>
+      <c r="B52" s="10"/>
+      <c r="C52" s="11"/>
+      <c r="D52" s="10"/>
+      <c r="E52" s="12" t="str">
         <f aca="false">IFERROR(IF(C52="","",WORKDAY(C52,IF(D52="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F52" s="14"/>
-      <c r="G52" s="11"/>
-      <c r="H52" s="11"/>
-      <c r="I52" s="11"/>
-      <c r="J52" s="11"/>
-      <c r="K52" s="11"/>
-      <c r="L52" s="11"/>
-      <c r="M52" s="11"/>
-      <c r="N52" s="12"/>
-      <c r="O52" s="11"/>
-      <c r="P52" s="12"/>
-      <c r="Q52" s="15" t="str">
+      <c r="F52" s="13"/>
+      <c r="G52" s="10"/>
+      <c r="H52" s="10"/>
+      <c r="I52" s="10"/>
+      <c r="J52" s="10"/>
+      <c r="K52" s="10"/>
+      <c r="L52" s="10"/>
+      <c r="M52" s="10"/>
+      <c r="N52" s="11"/>
+      <c r="O52" s="10"/>
+      <c r="P52" s="11"/>
+      <c r="Q52" s="14" t="str">
         <f aca="false">IFERROR(IF(P52="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P52,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R52" s="11"/>
+      <c r="R52" s="10"/>
+      <c r="S52" s="10"/>
     </row>
     <row r="53" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="10"/>
-      <c r="B53" s="11"/>
-      <c r="C53" s="12"/>
-      <c r="D53" s="11"/>
-      <c r="E53" s="13" t="str">
+      <c r="A53" s="9"/>
+      <c r="B53" s="10"/>
+      <c r="C53" s="11"/>
+      <c r="D53" s="10"/>
+      <c r="E53" s="12" t="str">
         <f aca="false">IFERROR(IF(C53="","",WORKDAY(C53,IF(D53="Sim: elegível (Resolução CD/ANPD nº 2/2022)",6,3))),"Verificar formato de data em C"&amp;ROW())</f>
         <v/>
       </c>
-      <c r="F53" s="14"/>
-      <c r="G53" s="11"/>
-      <c r="H53" s="11"/>
-      <c r="I53" s="11"/>
-      <c r="J53" s="11"/>
-      <c r="K53" s="11"/>
-      <c r="L53" s="11"/>
-      <c r="M53" s="11"/>
-      <c r="N53" s="12"/>
-      <c r="O53" s="11"/>
-      <c r="P53" s="12"/>
-      <c r="Q53" s="15" t="str">
+      <c r="F53" s="13"/>
+      <c r="G53" s="10"/>
+      <c r="H53" s="10"/>
+      <c r="I53" s="10"/>
+      <c r="J53" s="10"/>
+      <c r="K53" s="10"/>
+      <c r="L53" s="10"/>
+      <c r="M53" s="10"/>
+      <c r="N53" s="11"/>
+      <c r="O53" s="10"/>
+      <c r="P53" s="11"/>
+      <c r="Q53" s="14" t="str">
         <f aca="false">IFERROR(IF(P53="","Sem data de comunicação efetiva registrada","Até "&amp;TEXT(WORKDAY(P53,20),"dd/mm/yyyy")),"Verificar formato de data em P"&amp;ROW())</f>
         <v>Sem data de comunicação efetiva registrada</v>
       </c>
-      <c r="R53" s="11"/>
+      <c r="R53" s="10"/>
+      <c r="S53" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:R1"/>
-    <mergeCell ref="A2:R2"/>
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A2:S2"/>
   </mergeCells>
   <conditionalFormatting sqref="A4:A53">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -7225,6 +7292,11 @@
     </cfRule>
     <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND($A4&lt;&gt;"",OR(COUNTIFS(Caracterizacao!$A$4:$A$53,$A4,Caracterizacao!$B$4:$B$53,$B4)=0,COUNTIFS(Avaliacao_Regulatoria!$A$4:$A$53,$A4,Avaliacao_Regulatoria!$B$4:$B$53,$B4)=0))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S4:S53">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>AND(OR($K4="Decidido: não comunicar",$L4="Decidido: não comunicar"),$S4="")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="151">
@@ -7852,638 +7924,638 @@
   <dimension ref="A1:I53"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="30"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
+      <c r="A1" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="E3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="E3" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="F3" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="G3" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="H3" s="8" t="s">
         <v>138</v>
       </c>
+      <c r="I3" s="8" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="C4" s="12" t="n">
+      <c r="C4" s="11" t="n">
         <v>46314.5069444445</v>
       </c>
-      <c r="D4" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="E4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="G4" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="H4" s="10" t="s">
         <v>144</v>
       </c>
+      <c r="I4" s="10" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
+      <c r="A5" s="9"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
+      <c r="A6" s="9"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
+      <c r="A7" s="9"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="A8" s="9"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+      <c r="A9" s="9"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
+      <c r="A10" s="9"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
+      <c r="A11" s="9"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+      <c r="A12" s="9"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
+      <c r="A13" s="9"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
+      <c r="A14" s="9"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
+      <c r="A15" s="9"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
+      <c r="A16" s="9"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
+      <c r="A17" s="9"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11"/>
+      <c r="A18" s="9"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
+      <c r="A19" s="9"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="10"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="10"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11"/>
+      <c r="A20" s="9"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="10"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="11"/>
+      <c r="A21" s="9"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="10"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="10"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="11"/>
+      <c r="A22" s="9"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="10"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="10"/>
-      <c r="B23" s="11"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="11"/>
+      <c r="A23" s="9"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="10"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="10"/>
-      <c r="B24" s="11"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="11"/>
+      <c r="A24" s="9"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="10"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="10"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="11"/>
+      <c r="A25" s="9"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="10"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="10"/>
-      <c r="B26" s="11"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11"/>
-      <c r="I26" s="11"/>
+      <c r="A26" s="9"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="10"/>
+      <c r="I26" s="10"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="10"/>
-      <c r="B27" s="11"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11"/>
-      <c r="I27" s="11"/>
+      <c r="A27" s="9"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="10"/>
+      <c r="I27" s="10"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="10"/>
-      <c r="B28" s="11"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="11"/>
-      <c r="H28" s="11"/>
-      <c r="I28" s="11"/>
+      <c r="A28" s="9"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="10"/>
+      <c r="I28" s="10"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="10"/>
-      <c r="B29" s="11"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="11"/>
-      <c r="H29" s="11"/>
-      <c r="I29" s="11"/>
+      <c r="A29" s="9"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="10"/>
+      <c r="H29" s="10"/>
+      <c r="I29" s="10"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="10"/>
-      <c r="B30" s="11"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="11"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="11"/>
-      <c r="H30" s="11"/>
-      <c r="I30" s="11"/>
+      <c r="A30" s="9"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="10"/>
+      <c r="H30" s="10"/>
+      <c r="I30" s="10"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="10"/>
-      <c r="B31" s="11"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="11"/>
-      <c r="H31" s="11"/>
-      <c r="I31" s="11"/>
+      <c r="A31" s="9"/>
+      <c r="B31" s="10"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="10"/>
+      <c r="I31" s="10"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="10"/>
-      <c r="B32" s="11"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="11"/>
+      <c r="A32" s="9"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="10"/>
+      <c r="G32" s="10"/>
+      <c r="H32" s="10"/>
+      <c r="I32" s="10"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="10"/>
-      <c r="B33" s="11"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="11"/>
-      <c r="I33" s="11"/>
+      <c r="A33" s="9"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="10"/>
+      <c r="I33" s="10"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="10"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="11"/>
-      <c r="I34" s="11"/>
+      <c r="A34" s="9"/>
+      <c r="B34" s="10"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="10"/>
+      <c r="G34" s="10"/>
+      <c r="H34" s="10"/>
+      <c r="I34" s="10"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="10"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="12"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="11"/>
-      <c r="I35" s="11"/>
+      <c r="A35" s="9"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="10"/>
+      <c r="I35" s="10"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="10"/>
-      <c r="B36" s="11"/>
-      <c r="C36" s="12"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="11"/>
-      <c r="H36" s="11"/>
-      <c r="I36" s="11"/>
+      <c r="A36" s="9"/>
+      <c r="B36" s="10"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="10"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="10"/>
+      <c r="H36" s="10"/>
+      <c r="I36" s="10"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="10"/>
-      <c r="B37" s="11"/>
-      <c r="C37" s="12"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="11"/>
-      <c r="I37" s="11"/>
+      <c r="A37" s="9"/>
+      <c r="B37" s="10"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="10"/>
+      <c r="I37" s="10"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="10"/>
-      <c r="B38" s="11"/>
-      <c r="C38" s="12"/>
-      <c r="D38" s="11"/>
-      <c r="E38" s="11"/>
-      <c r="F38" s="11"/>
-      <c r="G38" s="11"/>
-      <c r="H38" s="11"/>
-      <c r="I38" s="11"/>
+      <c r="A38" s="9"/>
+      <c r="B38" s="10"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="10"/>
+      <c r="F38" s="10"/>
+      <c r="G38" s="10"/>
+      <c r="H38" s="10"/>
+      <c r="I38" s="10"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="10"/>
-      <c r="B39" s="11"/>
-      <c r="C39" s="12"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="11"/>
-      <c r="F39" s="11"/>
-      <c r="G39" s="11"/>
-      <c r="H39" s="11"/>
-      <c r="I39" s="11"/>
+      <c r="A39" s="9"/>
+      <c r="B39" s="10"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="10"/>
+      <c r="F39" s="10"/>
+      <c r="G39" s="10"/>
+      <c r="H39" s="10"/>
+      <c r="I39" s="10"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="10"/>
-      <c r="B40" s="11"/>
-      <c r="C40" s="12"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="11"/>
-      <c r="G40" s="11"/>
-      <c r="H40" s="11"/>
-      <c r="I40" s="11"/>
+      <c r="A40" s="9"/>
+      <c r="B40" s="10"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="10"/>
+      <c r="E40" s="10"/>
+      <c r="F40" s="10"/>
+      <c r="G40" s="10"/>
+      <c r="H40" s="10"/>
+      <c r="I40" s="10"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="10"/>
-      <c r="B41" s="11"/>
-      <c r="C41" s="12"/>
-      <c r="D41" s="11"/>
-      <c r="E41" s="11"/>
-      <c r="F41" s="11"/>
-      <c r="G41" s="11"/>
-      <c r="H41" s="11"/>
-      <c r="I41" s="11"/>
+      <c r="A41" s="9"/>
+      <c r="B41" s="10"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="10"/>
+      <c r="E41" s="10"/>
+      <c r="F41" s="10"/>
+      <c r="G41" s="10"/>
+      <c r="H41" s="10"/>
+      <c r="I41" s="10"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="10"/>
-      <c r="B42" s="11"/>
-      <c r="C42" s="12"/>
-      <c r="D42" s="11"/>
-      <c r="E42" s="11"/>
-      <c r="F42" s="11"/>
-      <c r="G42" s="11"/>
-      <c r="H42" s="11"/>
-      <c r="I42" s="11"/>
+      <c r="A42" s="9"/>
+      <c r="B42" s="10"/>
+      <c r="C42" s="11"/>
+      <c r="D42" s="10"/>
+      <c r="E42" s="10"/>
+      <c r="F42" s="10"/>
+      <c r="G42" s="10"/>
+      <c r="H42" s="10"/>
+      <c r="I42" s="10"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="10"/>
-      <c r="B43" s="11"/>
-      <c r="C43" s="12"/>
-      <c r="D43" s="11"/>
-      <c r="E43" s="11"/>
-      <c r="F43" s="11"/>
-      <c r="G43" s="11"/>
-      <c r="H43" s="11"/>
-      <c r="I43" s="11"/>
+      <c r="A43" s="9"/>
+      <c r="B43" s="10"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="10"/>
+      <c r="E43" s="10"/>
+      <c r="F43" s="10"/>
+      <c r="G43" s="10"/>
+      <c r="H43" s="10"/>
+      <c r="I43" s="10"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="10"/>
-      <c r="B44" s="11"/>
-      <c r="C44" s="12"/>
-      <c r="D44" s="11"/>
-      <c r="E44" s="11"/>
-      <c r="F44" s="11"/>
-      <c r="G44" s="11"/>
-      <c r="H44" s="11"/>
-      <c r="I44" s="11"/>
+      <c r="A44" s="9"/>
+      <c r="B44" s="10"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="10"/>
+      <c r="E44" s="10"/>
+      <c r="F44" s="10"/>
+      <c r="G44" s="10"/>
+      <c r="H44" s="10"/>
+      <c r="I44" s="10"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="10"/>
-      <c r="B45" s="11"/>
-      <c r="C45" s="12"/>
-      <c r="D45" s="11"/>
-      <c r="E45" s="11"/>
-      <c r="F45" s="11"/>
-      <c r="G45" s="11"/>
-      <c r="H45" s="11"/>
-      <c r="I45" s="11"/>
+      <c r="A45" s="9"/>
+      <c r="B45" s="10"/>
+      <c r="C45" s="11"/>
+      <c r="D45" s="10"/>
+      <c r="E45" s="10"/>
+      <c r="F45" s="10"/>
+      <c r="G45" s="10"/>
+      <c r="H45" s="10"/>
+      <c r="I45" s="10"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="10"/>
-      <c r="B46" s="11"/>
-      <c r="C46" s="12"/>
-      <c r="D46" s="11"/>
-      <c r="E46" s="11"/>
-      <c r="F46" s="11"/>
-      <c r="G46" s="11"/>
-      <c r="H46" s="11"/>
-      <c r="I46" s="11"/>
+      <c r="A46" s="9"/>
+      <c r="B46" s="10"/>
+      <c r="C46" s="11"/>
+      <c r="D46" s="10"/>
+      <c r="E46" s="10"/>
+      <c r="F46" s="10"/>
+      <c r="G46" s="10"/>
+      <c r="H46" s="10"/>
+      <c r="I46" s="10"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="10"/>
-      <c r="B47" s="11"/>
-      <c r="C47" s="12"/>
-      <c r="D47" s="11"/>
-      <c r="E47" s="11"/>
-      <c r="F47" s="11"/>
-      <c r="G47" s="11"/>
-      <c r="H47" s="11"/>
-      <c r="I47" s="11"/>
+      <c r="A47" s="9"/>
+      <c r="B47" s="10"/>
+      <c r="C47" s="11"/>
+      <c r="D47" s="10"/>
+      <c r="E47" s="10"/>
+      <c r="F47" s="10"/>
+      <c r="G47" s="10"/>
+      <c r="H47" s="10"/>
+      <c r="I47" s="10"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="10"/>
-      <c r="B48" s="11"/>
-      <c r="C48" s="12"/>
-      <c r="D48" s="11"/>
-      <c r="E48" s="11"/>
-      <c r="F48" s="11"/>
-      <c r="G48" s="11"/>
-      <c r="H48" s="11"/>
-      <c r="I48" s="11"/>
+      <c r="A48" s="9"/>
+      <c r="B48" s="10"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="10"/>
+      <c r="E48" s="10"/>
+      <c r="F48" s="10"/>
+      <c r="G48" s="10"/>
+      <c r="H48" s="10"/>
+      <c r="I48" s="10"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="10"/>
-      <c r="B49" s="11"/>
-      <c r="C49" s="12"/>
-      <c r="D49" s="11"/>
-      <c r="E49" s="11"/>
-      <c r="F49" s="11"/>
-      <c r="G49" s="11"/>
-      <c r="H49" s="11"/>
-      <c r="I49" s="11"/>
+      <c r="A49" s="9"/>
+      <c r="B49" s="10"/>
+      <c r="C49" s="11"/>
+      <c r="D49" s="10"/>
+      <c r="E49" s="10"/>
+      <c r="F49" s="10"/>
+      <c r="G49" s="10"/>
+      <c r="H49" s="10"/>
+      <c r="I49" s="10"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="10"/>
-      <c r="B50" s="11"/>
-      <c r="C50" s="12"/>
-      <c r="D50" s="11"/>
-      <c r="E50" s="11"/>
-      <c r="F50" s="11"/>
-      <c r="G50" s="11"/>
-      <c r="H50" s="11"/>
-      <c r="I50" s="11"/>
+      <c r="A50" s="9"/>
+      <c r="B50" s="10"/>
+      <c r="C50" s="11"/>
+      <c r="D50" s="10"/>
+      <c r="E50" s="10"/>
+      <c r="F50" s="10"/>
+      <c r="G50" s="10"/>
+      <c r="H50" s="10"/>
+      <c r="I50" s="10"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="10"/>
-      <c r="B51" s="11"/>
-      <c r="C51" s="12"/>
-      <c r="D51" s="11"/>
-      <c r="E51" s="11"/>
-      <c r="F51" s="11"/>
-      <c r="G51" s="11"/>
-      <c r="H51" s="11"/>
-      <c r="I51" s="11"/>
+      <c r="A51" s="9"/>
+      <c r="B51" s="10"/>
+      <c r="C51" s="11"/>
+      <c r="D51" s="10"/>
+      <c r="E51" s="10"/>
+      <c r="F51" s="10"/>
+      <c r="G51" s="10"/>
+      <c r="H51" s="10"/>
+      <c r="I51" s="10"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="10"/>
-      <c r="B52" s="11"/>
-      <c r="C52" s="12"/>
-      <c r="D52" s="11"/>
-      <c r="E52" s="11"/>
-      <c r="F52" s="11"/>
-      <c r="G52" s="11"/>
-      <c r="H52" s="11"/>
-      <c r="I52" s="11"/>
+      <c r="A52" s="9"/>
+      <c r="B52" s="10"/>
+      <c r="C52" s="11"/>
+      <c r="D52" s="10"/>
+      <c r="E52" s="10"/>
+      <c r="F52" s="10"/>
+      <c r="G52" s="10"/>
+      <c r="H52" s="10"/>
+      <c r="I52" s="10"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="10"/>
-      <c r="B53" s="11"/>
-      <c r="C53" s="12"/>
-      <c r="D53" s="11"/>
-      <c r="E53" s="11"/>
-      <c r="F53" s="11"/>
-      <c r="G53" s="11"/>
-      <c r="H53" s="11"/>
-      <c r="I53" s="11"/>
+      <c r="A53" s="9"/>
+      <c r="B53" s="10"/>
+      <c r="C53" s="11"/>
+      <c r="D53" s="10"/>
+      <c r="E53" s="10"/>
+      <c r="F53" s="10"/>
+      <c r="G53" s="10"/>
+      <c r="H53" s="10"/>
+      <c r="I53" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -8523,117 +8595,117 @@
   <dimension ref="A1:F10"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+      <c r="A1" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="A2" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="16" t="s">
-        <v>147</v>
-      </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
+      <c r="A3" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="17" t="s">
-        <v>148</v>
-      </c>
-      <c r="B5" s="18" t="s">
+      <c r="A5" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="B5" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="C5" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="D5" s="17" t="s">
         <v>152</v>
       </c>
+      <c r="E5" s="17" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
-        <v>153</v>
-      </c>
-      <c r="B6" s="20" t="s">
+      <c r="A6" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="C6" s="20" t="s">
-        <v>154</v>
-      </c>
-      <c r="D6" s="21" t="s">
+      <c r="B6" s="19" t="s">
         <v>155</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="C6" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="D6" s="20" t="s">
         <v>156</v>
       </c>
+      <c r="E6" s="20" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="D7" s="20" t="s">
         <v>157</v>
       </c>
-      <c r="B7" s="20" t="s">
-        <v>154</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="D7" s="21" t="s">
+      <c r="E7" s="21" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="B8" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="E7" s="22" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+      <c r="C8" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="D8" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="B8" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>156</v>
-      </c>
-      <c r="D8" s="22" t="s">
-        <v>158</v>
-      </c>
-      <c r="E8" s="22" t="s">
-        <v>158</v>
+      <c r="E8" s="21" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="23" t="s">
-        <v>160</v>
-      </c>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="23"/>
+      <c r="A10" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="4">
